--- a/Assets/ConfigTables/Data/Shared/Text.xlsx
+++ b/Assets/ConfigTables/Data/Shared/Text.xlsx
@@ -902,7 +902,7 @@
   </si>
   <si>
     <t>亲爱的孩子：
-当你读到这封信时，我大概已经不能再亲手给你煮一杯咖啡了。请不要为此责怪自己。你走过的路、做过的决定，都值得被好好珍惜。
+当你读到这封信时，我大概已经不能再亲手给你煮1111111111111111111杯咖啡了。请不要为此责怪自己。你走过的路、做过的决定，都值得被好好珍惜。
 我把圣诺特的沸点咖啡馆留给你。钥匙和交接的手续已经安排妥当，那里会是你新的起点。它不算大，却收留过许多疲惫的人，也藏着我们还没来得及一起度过的日子。
 我一直盼着与你重逢，听你说说这些年去了哪里，又变成了什么样的人。没能等到这一天，是我最放不下的遗憾。
 愿你在忙碌时也记得吃饭，在难过时也有人陪伴。经营一家咖啡馆之前，先照顾好自己。不必成为我，只要成为你自己。

--- a/Assets/ConfigTables/Data/Shared/Text.xlsx
+++ b/Assets/ConfigTables/Data/Shared/Text.xlsx
@@ -1272,7 +1272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D150"/>
+  <dimension ref="A1:D214"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3683,6 +3683,1094 @@
         </is>
       </c>
     </row>
+    <row r="151">
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>character.laurent.name</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>洛朗·迪蒙</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>character.laurent.desc</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>王室审计院高官，主张税收改革与削减王室开支的正直官僚。</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>character.clovis.name</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>克洛维·康多尔</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>character.clovis.desc</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>奥尔狄亚王国康多尔王朝第十二任君主，也是阿莉耶诺尔的父亲。</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>character.renaud.name</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>雷诺·康多尔</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>character.renaud.desc</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>国王的弟弟，王室近卫骑兵统帅，奥格隆公爵。</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>character.elion.name</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>埃利昂·康多尔</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>character.elion.desc</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>国王的堂弟，亲民且支持改革的埃利昂公爵，咖啡馆常客。</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>character.alienor.name</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>阿莉耶诺尔·康多尔</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>character.alienor.desc</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>国王的女儿与继承人，知识丰富，喜爱异国植物，渴望了解宫廷外的世界。</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>character.queen.name</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>王后</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>character.queen.desc</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>深居简出的奥尔狄亚王后。</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>character.bertrand.name</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>贝特朗·康多尔</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>character.bertrand.desc</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>国王的叔祖父，反对以外貌和血统评判身份。</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>character.sade.name</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>萨德</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>character.sade.desc</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>南岸教堂神父、监查司司长，为人温和，体恤民众。</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>character.mamion.name</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>马米翁</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>character.mamion.desc</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>圣谐教会大主教，关心教民、心怀怜悯，坚定维护传统。</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>character.lucien.name</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>吕西安</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>character.lucien.desc</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>甘泉教堂神父、教务司司长，温和而有自己的见解。</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>character.lesou.name</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>勒苏</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>character.lesou.desc</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>流民领袖，务实仗义，关怀底层民众，在贫民聚集区颇有号召力。</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>character.sylvain.name</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>西尔万·瓦隆</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>character.sylvain.desc</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>灰墙学院资深历史学教授，也是皇女的宫廷历史老师，幽默而博学。</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>character.antoine.name</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>安托万·马尚</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>character.antoine.desc</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>精于算计的富商，重视商业自由与金钱利益。</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>character.lefebvre.name</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>勒费弗尔</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>character.lefebvre.desc</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>秩序部审查官，出身寒门，喜爱剑术与酒。</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>character.duval.name</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>杜瓦尔·米尼耶</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>character.duval.desc</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>主角的叔叔，温和有礼、严于律己，留下了沸点咖啡馆。</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>character.adele.name</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>阿黛尔·米尼耶</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>character.adele.desc</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>咖啡馆店员、杜瓦尔的养女。善良活泼，精力充沛，喜欢探索新事物。</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>character.emmanuel.name</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>埃马纽埃尔·索雷尔</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>character.emmanuel.desc</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>技艺娴熟的外科医生，成熟健谈，工作之余喜欢在咖啡馆闲聊。</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>character.sparrow.name</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>麻雀</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>character.sparrow.desc</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>阿黛尔的朋友，和奶奶相依为命的街头少年，讲义气而好面子。</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>character.thibaut.name</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>蒂博·卡隆</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>character.thibaut.desc</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>残疾退伍老兵与情报商，沉默寡言，善于观察，欧仁的老友。</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>character.octave.name</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>奥克塔夫·韦尔内</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>character.octave.desc</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>国家军队将军，热情正直，忠于国家。</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>character.eugene.name</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>欧仁·迪布瓦</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>character.eugene.desc</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>可雇佣的退伍老兵与保镖，可靠而压抑，战后睡眠不佳，与蒂博相识多年。</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>character.colette.name</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>柯莱特·布吕内</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>character.colette.desc</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>可雇佣店员，曾任贵族府侍女，伶俐健谈，富有同情心。</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>character.pascal.name</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>帕斯卡尔·勒鲁</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>character.pascal.desc</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>结实能干的青年印刷工，也为咖啡馆跑腿。</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>character.marie.name</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>雅克·马尚</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>character.marie.desc</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>咖啡馆前代理店长，举止利落，谨慎而善于周旋。</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>character.guest_a.name</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>客人A</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>character.guest_a.desc</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>街区中可遇见的普通客人A。</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>character.guest_b.name</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>客人B</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>character.guest_b.desc</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>街区中可遇见的普通客人B。</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>character.guest_c.name</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>客人C</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>character.guest_c.desc</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>街区中可遇见的普通客人C。</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>character.guest_d.name</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>客人D</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>character.guest_d.desc</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>街区中可遇见的普通客人D。</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>character.soldier_a.name</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>军人A</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>character.soldier_a.desc</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>街区中可遇见的普通军人A。</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>character.soldier_b.name</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>军人B</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>character.soldier_b.desc</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>街区中可遇见的普通军人B。</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>character.soldier_c.name</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>军人C</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>character.soldier_c.desc</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>街区中可遇见的普通军人C。</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>character.soldier_d.name</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>军人D</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>character.soldier_d.desc</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>街区中可遇见的普通军人D。</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assets/ConfigTables/Data/Shared/Text.xlsx
+++ b/Assets/ConfigTables/Data/Shared/Text.xlsx
@@ -1272,7 +1272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D214"/>
+  <dimension ref="A1:D219"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4771,6 +4771,91 @@
         </is>
       </c>
     </row>
+    <row r="215">
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>map.position.saint_sylvain.name</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>圣西尔万郊区</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>地图重要地点名称</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>map.position.saint_street.name</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>圣徒街</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>地图重要地点名称</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>map.position.capital_court.name</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>首都法院</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>地图重要地点名称</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>map.position.city_hall.name</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>市政厅</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>地图重要地点名称</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>map.position.garden_district.name</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>花园区</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>地图重要地点名称</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assets/ConfigTables/Data/Shared/Text.xlsx
+++ b/Assets/ConfigTables/Data/Shared/Text.xlsx
@@ -1272,7 +1272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D219"/>
+  <dimension ref="A1:D308"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4856,6 +4856,1531 @@
         </is>
       </c>
     </row>
+    <row r="220">
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>condition.a_educated</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>a_educated</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>条件系统配置迁移 / 测试样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>condition.ab_swear</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>ab_swear</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>条件系统配置迁移 / 测试样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>condition.accepted_tea</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>accepted_tea</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>条件系统配置迁移 / 测试样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>condition.b_arrested</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>b_arrested</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>条件系统配置迁移 / 测试样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>condition.bc_swear</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>bc_swear</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>条件系统配置迁移 / 测试样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>condition.comrade</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>comrade</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>条件系统配置迁移 / 测试样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>condition.eloped</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>eloped</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>条件系统配置迁移 / 测试样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>condition.fled</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>fled</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>条件系统配置迁移 / 测试样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>condition.met_in_secret</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>met_in_secret</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>条件系统配置迁移 / 测试样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>condition.musician_end</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>musician_end</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>条件系统配置迁移 / 测试样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>condition.npc.npc_b.dead</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>npc.npc_b.dead</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>条件系统配置迁移 / 测试样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>condition.player_influence</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>player_influence</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>条件系统配置迁移 / 测试样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>condition.revolution</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>revolution</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>条件系统配置迁移 / 测试样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>condition.specialization.player.letter.literature</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>文学知识专精</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>条件系统配置迁移 / 测试样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>condition.specialization.player.letter.politics</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>政治知识专精</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>条件系统配置迁移 / 测试样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>condition.specialization.player.letter.religion</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>宗教知识专精</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>条件系统配置迁移 / 测试样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>condition.specialization.player.letter.science</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>科学知识专精</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>条件系统配置迁移 / 测试样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>condition.standoff_done</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>standoff_done</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>条件系统配置迁移 / 测试样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>condition.test.delivery.enabled</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>test.delivery.enabled</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>条件系统配置迁移 / 测试样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>act_test_delivery_cumulative.name</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>累计交付测试</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>条件系统配置迁移 / 测试样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>act_test_delivery_cumulative.desc</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>每天交药品2份、食物1份，消耗1行动点；成功5次完成。</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>条件系统配置迁移 / 测试样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>EV_TEST_DELIVERY_CUMULATIVE.title</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>累计交付完成</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>条件系统配置迁移 / 测试样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>EV_TEST_DELIVERY_CUMULATIVE.body</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>已完成五天交付，获得收据。</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>条件系统配置迁移 / 测试样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>EV_TEST_DELIVERY_CUMULATIVE_MILESTONE.title</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>累计交付进展</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>条件系统配置迁移 / 测试样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>EV_TEST_DELIVERY_CUMULATIVE_MILESTONE.body</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>已成功交付两次；此提示不会因连续中断而重复。</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>条件系统配置迁移 / 测试样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>ending_test_cumulative.title</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>累计交付测试结局</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>条件系统配置迁移 / 测试样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>ending_test_cumulative.message</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>测试交付已经完成。</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>条件系统配置迁移 / 测试样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>act_test_delivery_consecutive.name</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>连续交付测试</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>条件系统配置迁移 / 测试样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>act_test_delivery_consecutive.desc</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>每天交药品2份、食物1份，消耗1行动点；成功5次完成。</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>条件系统配置迁移 / 测试样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>EV_TEST_DELIVERY_CONSECUTIVE.title</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>连续交付完成</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>条件系统配置迁移 / 测试样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>EV_TEST_DELIVERY_CONSECUTIVE.body</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>已完成五天交付，获得收据。</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>条件系统配置迁移 / 测试样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>EV_TEST_DELIVERY_CONSECUTIVE_MILESTONE.title</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>连续交付进展</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>条件系统配置迁移 / 测试样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>EV_TEST_DELIVERY_CONSECUTIVE_MILESTONE.body</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>已成功交付两次；此提示不会因连续中断而重复。</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>条件系统配置迁移 / 测试样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>ending_test_consecutive.title</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>连续交付测试结局</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>条件系统配置迁移 / 测试样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>ending_test_consecutive.message</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>测试交付已经完成。</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>条件系统配置迁移 / 测试样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>player.attribute.language</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>语言</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>player.attribute.language.desc</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>影响表达、说服与沟通。</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>player.attribute.courage</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>勇气</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>player.attribute.courage.desc</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>影响面对风险与压力时的行动。</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>player.attribute.wisdom</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>智慧</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>player.attribute.wisdom.desc</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>影响分析、推理与解决问题。</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>player.attribute.perception</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>知觉</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>player.attribute.perception.desc</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>影响观察环境、察觉细节与情绪。</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>creation.origin.waif.label</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>贫寒</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>creation.origin.waif.desc</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>贫寒</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>creation.origin.commoner.label</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>平民</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>creation.origin.commoner.desc</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>平民</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>creation.origin.noble.label</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>富贵</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>creation.origin.noble.desc</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>富贵</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>creation.temperament.kind.label</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>善良</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>creation.temperament.kind.desc</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>善良</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>creation.temperament.sincere.label</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>赤诚</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>creation.temperament.sincere.desc</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>赤诚</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>creation.memory.brave.label</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>勇敢</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>creation.memory.brave.desc</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>勇敢</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>creation.memory.insightful.label</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>明睿</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>creation.memory.insightful.desc</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>明睿</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>creation.education.religion.label</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>神学</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>creation.education.religion.desc</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>神学</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>creation.education.literature.label</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>文学</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>creation.education.literature.desc</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>文学</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>creation.education.science.label</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>数学与物理科学</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>creation.education.science.desc</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>数学与物理科学</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>creation.education.politics.label</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>历史与官房学</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>creation.education.politics.desc</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>历史与官房学</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>creation.trait.language.label</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>能言善辩</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>creation.trait.language.desc</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>能言善辩</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>creation.trait.courage.label</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>坚定无畏</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>creation.trait.courage.desc</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>坚定无畏</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>creation.trait.wisdom.label</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>聪颖睿智</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>creation.trait.wisdom.desc</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>聪颖睿智</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>creation.trait.perception.label</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>敏锐细腻</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>creation.trait.perception.desc</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>敏锐细腻</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>player.background.template</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>出身{0}，曾修习{3}；{1}、{2}，如今已是{4}的人。</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>player.origin.waif</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>流浪儿</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>player.origin.commoner</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>平民</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>player.origin.noble</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>贵族</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>player.external.money</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>共用资金</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>player.external.action_points</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>行动点</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>player.external.action_points_max</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>行动点上限</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Player runtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>demo.cafe.before</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>【特殊来访示例】我想先点一杯咖啡，等餐的时候聊聊吧。</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>特殊来访示例</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>demo.cafe.served</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>【特殊来访示例】谢谢，咖啡收到了。我会继续留在座位上。</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>特殊来访示例</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>demo.cafe.chat</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>【特殊来访示例】喝完咖啡后，我们还能继续聊天。</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>特殊来访示例</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>demo.cafe.leaving</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>示例来访进入离店阶段</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>特殊来访反馈示例</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>demo.cafe.ended</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>示例来访已结束</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>特殊来访反馈示例</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr"/>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>first.day.perception.success.title</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>察觉旧友</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>首日咖啡馆知觉检定分支</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr"/>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>first.day.perception.success</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>老太太说这家店“乱套”，而不是“落魄”。我想，她或许是叔叔为数不多的老客人，或者说是他的朋友。
+我听过许多他朋友的故事，结果无一例外。没想到还有活着的人。
+可能是看出老太太想点餐，阿黛尔递来一张自己无聊时手绘的餐单。
+顾客B：“小杯黑咖啡，无糖，就这样。”
+B太太是新沸点咖啡的第一位客人。就让我们以此为契机，开始享受手冲咖啡带来的乐趣吧！</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>首日咖啡馆知觉检定分支</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr"/>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>first.day.perception.failure.title</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>古怪的来客</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>首日咖啡馆知觉检定分支</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr"/>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>first.day.perception.failure</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>不知怎么，总觉得她身上的气息突然变了。
+我没心思琢磨这位古怪老太太爱琢磨些什么，还好她把视线收了回去。
+可能是看出老太太想点餐，阿黛尔递来一张自己无聊时手绘的餐单。
+顾客B：“小杯黑咖啡，无糖，就这样。”
+B太太是新沸点咖啡的第一位客人。就让我们以此为契机，开始享受手冲咖啡带来的乐趣吧！</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>首日咖啡馆知觉检定分支</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assets/ConfigTables/Data/Shared/Text.xlsx
+++ b/Assets/ConfigTables/Data/Shared/Text.xlsx
@@ -1272,7 +1272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D308"/>
+  <dimension ref="A1:D446"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3055,12 +3055,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>初来乍到 · 沸点咖啡馆</t>
+          <t>重新启航</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>第一天咖啡馆引入演出</t>
+          <t>文案-新手教程.docx；原文保留</t>
         </is>
       </c>
     </row>
@@ -3099,233 +3099,12 @@
       </c>
     </row>
     <row r="115">
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>opening.line.01</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>你AAAAAAAAAAA测试推开沸点咖啡馆的门。吧台后的年轻女子放下抹布，先看了看你的行李，又看向你手里的信。</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>第一天咖啡馆引入演出</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>opening.line.02</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>你就是他一直惦记的那个孩子吧？我是阿黛尔，这里的店员。欢迎来到圣诺特。</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>第一天咖啡馆引入演出</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>opening.line.03</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>我是来接手咖啡馆的。他在信里说，这里会是我的新起点。</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>第一天咖啡馆引入演出</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>opening.line.04</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>嗯，沸点咖啡馆。名字听起来很厉害，实际上连热水壶都比我们脾气大。别怕，我会陪你把它打理好。</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>第一天咖啡馆引入演出</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>opening.line.05</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>你叔叔总说，一杯咖啡不只用来提神。有些人进门，是想找个能喘口气的地方。</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>第一天咖啡馆引入演出</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>opening.line.06</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>他还说过什么？</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>第一天咖啡馆引入演出</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>opening.line.07</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>他说，等你来了，就把靠窗的位置留给你……他一直盼着亲口听你讲这些年的事。</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>第一天咖啡馆引入演出</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>opening.line.08</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>阿黛尔低头理了理围裙，停了一会儿，再抬起头时已经重新露出笑容。</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>第一天咖啡馆引入演出</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>opening.line.09</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>好啦，伤心的事我们慢慢说。今天先从第一杯咖啡开始，我可不会让新店主第一天就手忙脚乱。</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>第一天咖啡馆引入演出</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>opening.line.10</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>客人来了，先看清他们的订单，再按配方准备原料、使用设备。做好的饮品记得交给对应的客人。</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>第一天咖啡馆引入演出</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>opening.line.11</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>不确定的时候就查看订单和配方，别急着乱试。先把一位客人照顾好，再接下一位。</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>第一天咖啡馆引入演出</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>opening.line.12</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>那就拜托你了，阿黛尔。</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>第一天咖啡馆引入演出</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>opening.line.13</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>当然。不过店主也要记得照顾好自己——这是你叔叔留给我们的规矩。准备好了？我们开门吧。</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>第一天咖啡馆引入演出</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="340" customHeight="1">
-      <c r="B128" s="6" t="inlineStr">
+      <c r="B115" s="6" t="inlineStr">
         <is>
           <t>opening.letter.body</t>
         </is>
       </c>
-      <c r="C128" s="6" t="inlineStr">
+      <c r="C115" s="6" t="inlineStr">
         <is>
           <t>亲爱的孩子：
 当你读到这封信时，我大概已经不能再亲手给你煮1111111111111111111杯咖啡了。请不要为此责怪自己。你走过的路、做过的决定，都值得被好好珍惜。
@@ -3336,362 +3115,583 @@
 而这一次，是我想对你说——欢迎回家。</t>
         </is>
       </c>
-      <c r="D128" s="6" t="inlineStr">
+      <c r="D115" s="6" t="inlineStr">
         <is>
           <t>第一天开场信件正文</t>
         </is>
       </c>
     </row>
+    <row r="116">
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>opening.letter.signature</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>—— 永远惦念你的叔叔</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>第一天开场信件署名</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>narrative.test.conversation.title</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>对话演出测试</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>narrative.test.conversation.01</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>你好，今天的店里很安静。</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>narrative.test.conversation.02</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>是啊，我正好有件事想和你聊聊。</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>narrative.test.conversation.03</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>对话事件已通过 Narrative 配置进入正式对话演出。</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>narrative.test.notice.title</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>街区消息</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>narrative.test.notice.body</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>通知事件已通过 presentationKey 加载策划表内容，并进入正式通知界面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>narrative.test.reading.title</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>测试记录</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>narrative.test.reading.01</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>阅读页与文本行来自独立 Luban 表。</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>narrative.test.reading.02</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>第二页展示 dialogue 行的说话人数据。</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="n"/>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>action.meet_b.name</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>与B见面</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>行动名称</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="n"/>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>action.meet_b.desc</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>前往约定地点与B见面。</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>行动描述</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="340" customHeight="1">
+      <c r="A128" s="3" t="n"/>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>action.c_with_b.name</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>安排C与B会面</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>行动名称</t>
+        </is>
+      </c>
+    </row>
     <row r="129" ht="35" customHeight="1">
-      <c r="B129" s="6" t="inlineStr">
-        <is>
-          <t>opening.letter.signature</t>
-        </is>
-      </c>
-      <c r="C129" s="6" t="inlineStr">
-        <is>
-          <t>—— 永远惦念你的叔叔</t>
-        </is>
-      </c>
-      <c r="D129" s="6" t="inlineStr">
-        <is>
-          <t>第一天开场信件署名</t>
+      <c r="A129" s="3" t="n"/>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>action.c_with_b.desc</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>促成C与B进行一次会面。</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>行动描述</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>narrative.test.conversation.title</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>对话演出测试</t>
+      <c r="A130" s="3" t="n"/>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>action.salon.name</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>前往沙龙</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>行动名称</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>narrative.test.conversation.01</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>你好，今天的店里很安静。</t>
+      <c r="A131" s="3" t="n"/>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>action.salon.desc</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>参加沙龙，接触新的思想。</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>行动描述</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>narrative.test.conversation.02</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>是啊，我正好有件事想和你聊聊。</t>
+      <c r="A132" s="3" t="n"/>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>action.peer.name</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>观察C的动向</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>行动名称</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>narrative.test.conversation.03</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>对话事件已通过 Narrative 配置进入正式对话演出。</t>
+      <c r="A133" s="3" t="n"/>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>action.peer.desc</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>前往相关地点，收集C的消息。</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>行动描述</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>narrative.test.notice.title</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>街区消息</t>
+      <c r="A134" s="3" t="n"/>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>map.position.cafe.name</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>咖啡馆</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>地图地点名称</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>narrative.test.notice.body</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>通知事件已通过 presentationKey 加载策划表内容，并进入正式通知界面。</t>
+      <c r="A135" s="3" t="n"/>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>map.position.market.name</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>集市</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>地图地点名称</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>narrative.test.reading.title</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>测试记录</t>
+      <c r="A136" s="3" t="n"/>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>map.position.library.name</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>图书馆</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>地图地点名称</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>narrative.test.reading.01</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>阅读页与文本行来自独立 Luban 表。</t>
+      <c r="A137" s="3" t="n"/>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>map.position.temporary.name</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>临时事件</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>地图地点名称</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="B138" t="inlineStr">
         <is>
-          <t>narrative.test.reading.02</t>
+          <t>character.laurent.name</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>第二页展示 dialogue 行的说话人数据。</t>
+          <t>洛朗·迪蒙</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="3" t="n"/>
-      <c r="B139" s="3" t="inlineStr">
-        <is>
-          <t>action.meet_b.name</t>
-        </is>
-      </c>
-      <c r="C139" s="3" t="inlineStr">
-        <is>
-          <t>与B见面</t>
-        </is>
-      </c>
-      <c r="D139" s="3" t="inlineStr">
-        <is>
-          <t>行动名称</t>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>character.laurent.desc</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>王室审计院高官，主张税收改革与削减王室开支的正直官僚。</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="3" t="n"/>
-      <c r="B140" s="3" t="inlineStr">
-        <is>
-          <t>action.meet_b.desc</t>
-        </is>
-      </c>
-      <c r="C140" s="3" t="inlineStr">
-        <is>
-          <t>前往约定地点与B见面。</t>
-        </is>
-      </c>
-      <c r="D140" s="3" t="inlineStr">
-        <is>
-          <t>行动描述</t>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>character.clovis.name</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>克洛维·康多尔</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="3" t="n"/>
-      <c r="B141" s="3" t="inlineStr">
-        <is>
-          <t>action.c_with_b.name</t>
-        </is>
-      </c>
-      <c r="C141" s="3" t="inlineStr">
-        <is>
-          <t>安排C与B会面</t>
-        </is>
-      </c>
-      <c r="D141" s="3" t="inlineStr">
-        <is>
-          <t>行动名称</t>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>character.clovis.desc</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>奥尔狄亚王国康多尔王朝第十二任君主，也是阿莉耶诺尔的父亲。</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="3" t="n"/>
-      <c r="B142" s="3" t="inlineStr">
-        <is>
-          <t>action.c_with_b.desc</t>
-        </is>
-      </c>
-      <c r="C142" s="3" t="inlineStr">
-        <is>
-          <t>促成C与B进行一次会面。</t>
-        </is>
-      </c>
-      <c r="D142" s="3" t="inlineStr">
-        <is>
-          <t>行动描述</t>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>character.renaud.name</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>雷诺·康多尔</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="3" t="n"/>
-      <c r="B143" s="3" t="inlineStr">
-        <is>
-          <t>action.salon.name</t>
-        </is>
-      </c>
-      <c r="C143" s="3" t="inlineStr">
-        <is>
-          <t>前往沙龙</t>
-        </is>
-      </c>
-      <c r="D143" s="3" t="inlineStr">
-        <is>
-          <t>行动名称</t>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>character.renaud.desc</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>国王的弟弟，王室近卫骑兵统帅，奥格隆公爵。</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="3" t="n"/>
-      <c r="B144" s="3" t="inlineStr">
-        <is>
-          <t>action.salon.desc</t>
-        </is>
-      </c>
-      <c r="C144" s="3" t="inlineStr">
-        <is>
-          <t>参加沙龙，接触新的思想。</t>
-        </is>
-      </c>
-      <c r="D144" s="3" t="inlineStr">
-        <is>
-          <t>行动描述</t>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>character.elion.name</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>埃利昂·康多尔</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="3" t="n"/>
-      <c r="B145" s="3" t="inlineStr">
-        <is>
-          <t>action.peer.name</t>
-        </is>
-      </c>
-      <c r="C145" s="3" t="inlineStr">
-        <is>
-          <t>观察C的动向</t>
-        </is>
-      </c>
-      <c r="D145" s="3" t="inlineStr">
-        <is>
-          <t>行动名称</t>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>character.elion.desc</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>国王的堂弟，亲民且支持改革的埃利昂公爵，咖啡馆常客。</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="3" t="n"/>
-      <c r="B146" s="3" t="inlineStr">
-        <is>
-          <t>action.peer.desc</t>
-        </is>
-      </c>
-      <c r="C146" s="3" t="inlineStr">
-        <is>
-          <t>前往相关地点，收集C的消息。</t>
-        </is>
-      </c>
-      <c r="D146" s="3" t="inlineStr">
-        <is>
-          <t>行动描述</t>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>character.alienor.name</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>阿莉耶诺尔·康多尔</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="3" t="n"/>
-      <c r="B147" s="3" t="inlineStr">
-        <is>
-          <t>map.position.cafe.name</t>
-        </is>
-      </c>
-      <c r="C147" s="3" t="inlineStr">
-        <is>
-          <t>咖啡馆</t>
-        </is>
-      </c>
-      <c r="D147" s="3" t="inlineStr">
-        <is>
-          <t>地图地点名称</t>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>character.alienor.desc</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>国王的女儿与继承人，知识丰富，喜爱异国植物，渴望了解宫廷外的世界。</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="3" t="n"/>
-      <c r="B148" s="3" t="inlineStr">
-        <is>
-          <t>map.position.market.name</t>
-        </is>
-      </c>
-      <c r="C148" s="3" t="inlineStr">
-        <is>
-          <t>集市</t>
-        </is>
-      </c>
-      <c r="D148" s="3" t="inlineStr">
-        <is>
-          <t>地图地点名称</t>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>character.queen.name</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>王后</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="3" t="n"/>
-      <c r="B149" s="3" t="inlineStr">
-        <is>
-          <t>map.position.library.name</t>
-        </is>
-      </c>
-      <c r="C149" s="3" t="inlineStr">
-        <is>
-          <t>图书馆</t>
-        </is>
-      </c>
-      <c r="D149" s="3" t="inlineStr">
-        <is>
-          <t>地图地点名称</t>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>character.queen.desc</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>深居简出的奥尔狄亚王后。</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="3" t="n"/>
-      <c r="B150" s="3" t="inlineStr">
-        <is>
-          <t>map.position.temporary.name</t>
-        </is>
-      </c>
-      <c r="C150" s="3" t="inlineStr">
-        <is>
-          <t>临时事件</t>
-        </is>
-      </c>
-      <c r="D150" s="3" t="inlineStr">
-        <is>
-          <t>地图地点名称</t>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>character.bertrand.name</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>贝特朗·康多尔</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>人物.xlsx公开设定；秘密不公开</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="B151" t="inlineStr">
         <is>
-          <t>character.laurent.name</t>
+          <t>character.bertrand.desc</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>洛朗·迪蒙</t>
+          <t>国王的叔祖父，反对以外貌和血统评判身份。</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -3703,12 +3703,12 @@
     <row r="152">
       <c r="B152" t="inlineStr">
         <is>
-          <t>character.laurent.desc</t>
+          <t>character.sade.name</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>王室审计院高官，主张税收改革与削减王室开支的正直官僚。</t>
+          <t>萨德</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -3720,12 +3720,12 @@
     <row r="153">
       <c r="B153" t="inlineStr">
         <is>
-          <t>character.clovis.name</t>
+          <t>character.sade.desc</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>克洛维·康多尔</t>
+          <t>南岸教堂神父、监查司司长，为人温和，体恤民众。</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -3737,12 +3737,12 @@
     <row r="154">
       <c r="B154" t="inlineStr">
         <is>
-          <t>character.clovis.desc</t>
+          <t>character.mamion.name</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>奥尔狄亚王国康多尔王朝第十二任君主，也是阿莉耶诺尔的父亲。</t>
+          <t>马米翁</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -3754,12 +3754,12 @@
     <row r="155">
       <c r="B155" t="inlineStr">
         <is>
-          <t>character.renaud.name</t>
+          <t>character.mamion.desc</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>雷诺·康多尔</t>
+          <t>圣谐教会大主教，关心教民、心怀怜悯，坚定维护传统。</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -3771,12 +3771,12 @@
     <row r="156">
       <c r="B156" t="inlineStr">
         <is>
-          <t>character.renaud.desc</t>
+          <t>character.lucien.name</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>国王的弟弟，王室近卫骑兵统帅，奥格隆公爵。</t>
+          <t>吕西安</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -3788,12 +3788,12 @@
     <row r="157">
       <c r="B157" t="inlineStr">
         <is>
-          <t>character.elion.name</t>
+          <t>character.lucien.desc</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>埃利昂·康多尔</t>
+          <t>甘泉教堂神父、教务司司长，温和而有自己的见解。</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -3805,12 +3805,12 @@
     <row r="158">
       <c r="B158" t="inlineStr">
         <is>
-          <t>character.elion.desc</t>
+          <t>character.lesou.name</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>国王的堂弟，亲民且支持改革的埃利昂公爵，咖啡馆常客。</t>
+          <t>勒苏</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -3822,12 +3822,12 @@
     <row r="159">
       <c r="B159" t="inlineStr">
         <is>
-          <t>character.alienor.name</t>
+          <t>character.lesou.desc</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>阿莉耶诺尔·康多尔</t>
+          <t>流民领袖，务实仗义，关怀底层民众，在贫民聚集区颇有号召力。</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -3839,12 +3839,12 @@
     <row r="160">
       <c r="B160" t="inlineStr">
         <is>
-          <t>character.alienor.desc</t>
+          <t>character.sylvain.name</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>国王的女儿与继承人，知识丰富，喜爱异国植物，渴望了解宫廷外的世界。</t>
+          <t>西尔万·瓦隆</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -3856,12 +3856,12 @@
     <row r="161">
       <c r="B161" t="inlineStr">
         <is>
-          <t>character.queen.name</t>
+          <t>character.sylvain.desc</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>王后</t>
+          <t>灰墙学院资深历史学教授，也是皇女的宫廷历史老师，幽默而博学。</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -3873,12 +3873,12 @@
     <row r="162">
       <c r="B162" t="inlineStr">
         <is>
-          <t>character.queen.desc</t>
+          <t>character.antoine.name</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>深居简出的奥尔狄亚王后。</t>
+          <t>安托万·马尚</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -3890,12 +3890,12 @@
     <row r="163">
       <c r="B163" t="inlineStr">
         <is>
-          <t>character.bertrand.name</t>
+          <t>character.antoine.desc</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>贝特朗·康多尔</t>
+          <t>精于算计的富商，重视商业自由与金钱利益。</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -3907,12 +3907,12 @@
     <row r="164">
       <c r="B164" t="inlineStr">
         <is>
-          <t>character.bertrand.desc</t>
+          <t>character.lefebvre.name</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>国王的叔祖父，反对以外貌和血统评判身份。</t>
+          <t>勒费弗尔</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -3924,12 +3924,12 @@
     <row r="165">
       <c r="B165" t="inlineStr">
         <is>
-          <t>character.sade.name</t>
+          <t>character.lefebvre.desc</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>萨德</t>
+          <t>秩序部审查官，出身寒门，喜爱剑术与酒。</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -3941,12 +3941,12 @@
     <row r="166">
       <c r="B166" t="inlineStr">
         <is>
-          <t>character.sade.desc</t>
+          <t>character.duval.name</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>南岸教堂神父、监查司司长，为人温和，体恤民众。</t>
+          <t>杜瓦尔·米尼耶</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -3958,12 +3958,12 @@
     <row r="167">
       <c r="B167" t="inlineStr">
         <is>
-          <t>character.mamion.name</t>
+          <t>character.duval.desc</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>马米翁</t>
+          <t>主角的叔叔，温和有礼、严于律己，留下了沸点咖啡馆。</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -3975,12 +3975,12 @@
     <row r="168">
       <c r="B168" t="inlineStr">
         <is>
-          <t>character.mamion.desc</t>
+          <t>character.adele.name</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>圣谐教会大主教，关心教民、心怀怜悯，坚定维护传统。</t>
+          <t>阿黛尔·米尼耶</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -3992,12 +3992,12 @@
     <row r="169">
       <c r="B169" t="inlineStr">
         <is>
-          <t>character.lucien.name</t>
+          <t>character.adele.desc</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>吕西安</t>
+          <t>咖啡馆店员、杜瓦尔的养女。善良活泼，精力充沛，喜欢探索新事物。</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -4009,12 +4009,12 @@
     <row r="170">
       <c r="B170" t="inlineStr">
         <is>
-          <t>character.lucien.desc</t>
+          <t>character.emmanuel.name</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>甘泉教堂神父、教务司司长，温和而有自己的见解。</t>
+          <t>埃马纽埃尔·索雷尔</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -4026,12 +4026,12 @@
     <row r="171">
       <c r="B171" t="inlineStr">
         <is>
-          <t>character.lesou.name</t>
+          <t>character.emmanuel.desc</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>勒苏</t>
+          <t>技艺娴熟的外科医生，成熟健谈，工作之余喜欢在咖啡馆闲聊。</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -4043,12 +4043,12 @@
     <row r="172">
       <c r="B172" t="inlineStr">
         <is>
-          <t>character.lesou.desc</t>
+          <t>character.sparrow.name</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>流民领袖，务实仗义，关怀底层民众，在贫民聚集区颇有号召力。</t>
+          <t>麻雀</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -4060,12 +4060,12 @@
     <row r="173">
       <c r="B173" t="inlineStr">
         <is>
-          <t>character.sylvain.name</t>
+          <t>character.sparrow.desc</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>西尔万·瓦隆</t>
+          <t>阿黛尔的朋友，和奶奶相依为命的街头少年，讲义气而好面子。</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -4077,12 +4077,12 @@
     <row r="174">
       <c r="B174" t="inlineStr">
         <is>
-          <t>character.sylvain.desc</t>
+          <t>character.thibaut.name</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>灰墙学院资深历史学教授，也是皇女的宫廷历史老师，幽默而博学。</t>
+          <t>蒂博·卡隆</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -4094,12 +4094,12 @@
     <row r="175">
       <c r="B175" t="inlineStr">
         <is>
-          <t>character.antoine.name</t>
+          <t>character.thibaut.desc</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>安托万·马尚</t>
+          <t>残疾退伍老兵与情报商，沉默寡言，善于观察，欧仁的老友。</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -4111,12 +4111,12 @@
     <row r="176">
       <c r="B176" t="inlineStr">
         <is>
-          <t>character.antoine.desc</t>
+          <t>character.octave.name</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>精于算计的富商，重视商业自由与金钱利益。</t>
+          <t>奥克塔夫·韦尔内</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -4128,12 +4128,12 @@
     <row r="177">
       <c r="B177" t="inlineStr">
         <is>
-          <t>character.lefebvre.name</t>
+          <t>character.octave.desc</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>勒费弗尔</t>
+          <t>国家军队将军，热情正直，忠于国家。</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -4145,12 +4145,12 @@
     <row r="178">
       <c r="B178" t="inlineStr">
         <is>
-          <t>character.lefebvre.desc</t>
+          <t>character.eugene.name</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>秩序部审查官，出身寒门，喜爱剑术与酒。</t>
+          <t>欧仁·迪布瓦</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -4162,12 +4162,12 @@
     <row r="179">
       <c r="B179" t="inlineStr">
         <is>
-          <t>character.duval.name</t>
+          <t>character.eugene.desc</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>杜瓦尔·米尼耶</t>
+          <t>可雇佣的退伍老兵与保镖，可靠而压抑，战后睡眠不佳，与蒂博相识多年。</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -4179,12 +4179,12 @@
     <row r="180">
       <c r="B180" t="inlineStr">
         <is>
-          <t>character.duval.desc</t>
+          <t>character.colette.name</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>主角的叔叔，温和有礼、严于律己，留下了沸点咖啡馆。</t>
+          <t>柯莱特·布吕内</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -4196,12 +4196,12 @@
     <row r="181">
       <c r="B181" t="inlineStr">
         <is>
-          <t>character.adele.name</t>
+          <t>character.colette.desc</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>阿黛尔·米尼耶</t>
+          <t>可雇佣店员，曾任贵族府侍女，伶俐健谈，富有同情心。</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -4213,12 +4213,12 @@
     <row r="182">
       <c r="B182" t="inlineStr">
         <is>
-          <t>character.adele.desc</t>
+          <t>character.pascal.name</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>咖啡馆店员、杜瓦尔的养女。善良活泼，精力充沛，喜欢探索新事物。</t>
+          <t>帕斯卡尔·勒鲁</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -4230,12 +4230,12 @@
     <row r="183">
       <c r="B183" t="inlineStr">
         <is>
-          <t>character.emmanuel.name</t>
+          <t>character.pascal.desc</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>埃马纽埃尔·索雷尔</t>
+          <t>结实能干的青年印刷工，也为咖啡馆跑腿。</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -4247,12 +4247,12 @@
     <row r="184">
       <c r="B184" t="inlineStr">
         <is>
-          <t>character.emmanuel.desc</t>
+          <t>character.marie.name</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>技艺娴熟的外科医生，成熟健谈，工作之余喜欢在咖啡馆闲聊。</t>
+          <t>雅克·马尚</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -4264,12 +4264,12 @@
     <row r="185">
       <c r="B185" t="inlineStr">
         <is>
-          <t>character.sparrow.name</t>
+          <t>character.marie.desc</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>麻雀</t>
+          <t>咖啡馆前代理店长，举止利落，谨慎而善于周旋。</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -4281,12 +4281,12 @@
     <row r="186">
       <c r="B186" t="inlineStr">
         <is>
-          <t>character.sparrow.desc</t>
+          <t>character.guest_a.name</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>阿黛尔的朋友，和奶奶相依为命的街头少年，讲义气而好面子。</t>
+          <t>客人A</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -4298,12 +4298,12 @@
     <row r="187">
       <c r="B187" t="inlineStr">
         <is>
-          <t>character.thibaut.name</t>
+          <t>character.guest_a.desc</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>蒂博·卡隆</t>
+          <t>街区中可遇见的普通客人A。</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -4315,12 +4315,12 @@
     <row r="188">
       <c r="B188" t="inlineStr">
         <is>
-          <t>character.thibaut.desc</t>
+          <t>character.guest_b.name</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>残疾退伍老兵与情报商，沉默寡言，善于观察，欧仁的老友。</t>
+          <t>客人B</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -4332,12 +4332,12 @@
     <row r="189">
       <c r="B189" t="inlineStr">
         <is>
-          <t>character.octave.name</t>
+          <t>character.guest_b.desc</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>奥克塔夫·韦尔内</t>
+          <t>街区中可遇见的普通客人B。</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -4349,12 +4349,12 @@
     <row r="190">
       <c r="B190" t="inlineStr">
         <is>
-          <t>character.octave.desc</t>
+          <t>character.guest_c.name</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>国家军队将军，热情正直，忠于国家。</t>
+          <t>客人C</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -4366,12 +4366,12 @@
     <row r="191">
       <c r="B191" t="inlineStr">
         <is>
-          <t>character.eugene.name</t>
+          <t>character.guest_c.desc</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>欧仁·迪布瓦</t>
+          <t>街区中可遇见的普通客人C。</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -4383,12 +4383,12 @@
     <row r="192">
       <c r="B192" t="inlineStr">
         <is>
-          <t>character.eugene.desc</t>
+          <t>character.guest_d.name</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>可雇佣的退伍老兵与保镖，可靠而压抑，战后睡眠不佳，与蒂博相识多年。</t>
+          <t>客人D</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -4400,12 +4400,12 @@
     <row r="193">
       <c r="B193" t="inlineStr">
         <is>
-          <t>character.colette.name</t>
+          <t>character.guest_d.desc</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>柯莱特·布吕内</t>
+          <t>街区中可遇见的普通客人D。</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -4417,12 +4417,12 @@
     <row r="194">
       <c r="B194" t="inlineStr">
         <is>
-          <t>character.colette.desc</t>
+          <t>character.soldier_a.name</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>可雇佣店员，曾任贵族府侍女，伶俐健谈，富有同情心。</t>
+          <t>军人A</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -4434,12 +4434,12 @@
     <row r="195">
       <c r="B195" t="inlineStr">
         <is>
-          <t>character.pascal.name</t>
+          <t>character.soldier_a.desc</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>帕斯卡尔·勒鲁</t>
+          <t>街区中可遇见的普通军人A。</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -4451,12 +4451,12 @@
     <row r="196">
       <c r="B196" t="inlineStr">
         <is>
-          <t>character.pascal.desc</t>
+          <t>character.soldier_b.name</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>结实能干的青年印刷工，也为咖啡馆跑腿。</t>
+          <t>军人B</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -4468,12 +4468,12 @@
     <row r="197">
       <c r="B197" t="inlineStr">
         <is>
-          <t>character.marie.name</t>
+          <t>character.soldier_b.desc</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>雅克·马尚</t>
+          <t>街区中可遇见的普通军人B。</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -4485,12 +4485,12 @@
     <row r="198">
       <c r="B198" t="inlineStr">
         <is>
-          <t>character.marie.desc</t>
+          <t>character.soldier_c.name</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>咖啡馆前代理店长，举止利落，谨慎而善于周旋。</t>
+          <t>军人C</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -4502,12 +4502,12 @@
     <row r="199">
       <c r="B199" t="inlineStr">
         <is>
-          <t>character.guest_a.name</t>
+          <t>character.soldier_c.desc</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>客人A</t>
+          <t>街区中可遇见的普通军人C。</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -4519,12 +4519,12 @@
     <row r="200">
       <c r="B200" t="inlineStr">
         <is>
-          <t>character.guest_a.desc</t>
+          <t>character.soldier_d.name</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>街区中可遇见的普通客人A。</t>
+          <t>军人D</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -4536,12 +4536,12 @@
     <row r="201">
       <c r="B201" t="inlineStr">
         <is>
-          <t>character.guest_b.name</t>
+          <t>character.soldier_d.desc</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>客人B</t>
+          <t>街区中可遇见的普通军人D。</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -4553,318 +4553,318 @@
     <row r="202">
       <c r="B202" t="inlineStr">
         <is>
-          <t>character.guest_b.desc</t>
+          <t>map.position.saint_sylvain.name</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>街区中可遇见的普通客人B。</t>
+          <t>圣西尔万郊区</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>人物.xlsx公开设定；秘密不公开</t>
+          <t>地图重要地点名称</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="B203" t="inlineStr">
         <is>
-          <t>character.guest_c.name</t>
+          <t>map.position.saint_street.name</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>客人C</t>
+          <t>圣徒街</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>人物.xlsx公开设定；秘密不公开</t>
+          <t>地图重要地点名称</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="B204" t="inlineStr">
         <is>
-          <t>character.guest_c.desc</t>
+          <t>map.position.capital_court.name</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>街区中可遇见的普通客人C。</t>
+          <t>首都法院</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>人物.xlsx公开设定；秘密不公开</t>
+          <t>地图重要地点名称</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="B205" t="inlineStr">
         <is>
-          <t>character.guest_d.name</t>
+          <t>map.position.city_hall.name</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>客人D</t>
+          <t>市政厅</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>人物.xlsx公开设定；秘密不公开</t>
+          <t>地图重要地点名称</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="B206" t="inlineStr">
         <is>
-          <t>character.guest_d.desc</t>
+          <t>map.position.garden_district.name</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>街区中可遇见的普通客人D。</t>
+          <t>花园区</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>人物.xlsx公开设定；秘密不公开</t>
+          <t>地图重要地点名称</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="B207" t="inlineStr">
         <is>
-          <t>character.soldier_a.name</t>
+          <t>condition.a_educated</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>军人A</t>
+          <t>a_educated</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>人物.xlsx公开设定；秘密不公开</t>
+          <t>条件系统配置迁移 / 测试样例</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="B208" t="inlineStr">
         <is>
-          <t>character.soldier_a.desc</t>
+          <t>condition.ab_swear</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>街区中可遇见的普通军人A。</t>
+          <t>ab_swear</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>人物.xlsx公开设定；秘密不公开</t>
+          <t>条件系统配置迁移 / 测试样例</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="B209" t="inlineStr">
         <is>
-          <t>character.soldier_b.name</t>
+          <t>condition.accepted_tea</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>军人B</t>
+          <t>accepted_tea</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>人物.xlsx公开设定；秘密不公开</t>
+          <t>条件系统配置迁移 / 测试样例</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="B210" t="inlineStr">
         <is>
-          <t>character.soldier_b.desc</t>
+          <t>condition.b_arrested</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>街区中可遇见的普通军人B。</t>
+          <t>b_arrested</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>人物.xlsx公开设定；秘密不公开</t>
+          <t>条件系统配置迁移 / 测试样例</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="B211" t="inlineStr">
         <is>
-          <t>character.soldier_c.name</t>
+          <t>condition.bc_swear</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>军人C</t>
+          <t>bc_swear</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>人物.xlsx公开设定；秘密不公开</t>
+          <t>条件系统配置迁移 / 测试样例</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="B212" t="inlineStr">
         <is>
-          <t>character.soldier_c.desc</t>
+          <t>condition.comrade</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>街区中可遇见的普通军人C。</t>
+          <t>comrade</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>人物.xlsx公开设定；秘密不公开</t>
+          <t>条件系统配置迁移 / 测试样例</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="B213" t="inlineStr">
         <is>
-          <t>character.soldier_d.name</t>
+          <t>condition.eloped</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>军人D</t>
+          <t>eloped</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>人物.xlsx公开设定；秘密不公开</t>
+          <t>条件系统配置迁移 / 测试样例</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="B214" t="inlineStr">
         <is>
-          <t>character.soldier_d.desc</t>
+          <t>condition.fled</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>街区中可遇见的普通军人D。</t>
+          <t>fled</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>人物.xlsx公开设定；秘密不公开</t>
+          <t>条件系统配置迁移 / 测试样例</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="B215" t="inlineStr">
         <is>
-          <t>map.position.saint_sylvain.name</t>
+          <t>condition.met_in_secret</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>圣西尔万郊区</t>
+          <t>met_in_secret</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>地图重要地点名称</t>
+          <t>条件系统配置迁移 / 测试样例</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="B216" t="inlineStr">
         <is>
-          <t>map.position.saint_street.name</t>
+          <t>condition.musician_end</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>圣徒街</t>
+          <t>musician_end</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>地图重要地点名称</t>
+          <t>条件系统配置迁移 / 测试样例</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="B217" t="inlineStr">
         <is>
-          <t>map.position.capital_court.name</t>
+          <t>condition.npc.npc_b.dead</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>首都法院</t>
+          <t>npc.npc_b.dead</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>地图重要地点名称</t>
+          <t>条件系统配置迁移 / 测试样例</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="B218" t="inlineStr">
         <is>
-          <t>map.position.city_hall.name</t>
+          <t>condition.player_influence</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>市政厅</t>
+          <t>player_influence</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>地图重要地点名称</t>
+          <t>条件系统配置迁移 / 测试样例</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="B219" t="inlineStr">
         <is>
-          <t>map.position.garden_district.name</t>
+          <t>condition.revolution</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>花园区</t>
+          <t>revolution</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>地图重要地点名称</t>
+          <t>条件系统配置迁移 / 测试样例</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="B220" t="inlineStr">
         <is>
-          <t>condition.a_educated</t>
+          <t>condition.specialization.player.letter.literature</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>a_educated</t>
+          <t>文学知识专精</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -4876,12 +4876,12 @@
     <row r="221">
       <c r="B221" t="inlineStr">
         <is>
-          <t>condition.ab_swear</t>
+          <t>condition.specialization.player.letter.politics</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>ab_swear</t>
+          <t>政治知识专精</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -4893,12 +4893,12 @@
     <row r="222">
       <c r="B222" t="inlineStr">
         <is>
-          <t>condition.accepted_tea</t>
+          <t>condition.specialization.player.letter.religion</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>accepted_tea</t>
+          <t>宗教知识专精</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -4910,12 +4910,12 @@
     <row r="223">
       <c r="B223" t="inlineStr">
         <is>
-          <t>condition.b_arrested</t>
+          <t>condition.specialization.player.letter.science</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>b_arrested</t>
+          <t>科学知识专精</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -4927,12 +4927,12 @@
     <row r="224">
       <c r="B224" t="inlineStr">
         <is>
-          <t>condition.bc_swear</t>
+          <t>condition.standoff_done</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>bc_swear</t>
+          <t>standoff_done</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -4944,12 +4944,12 @@
     <row r="225">
       <c r="B225" t="inlineStr">
         <is>
-          <t>condition.comrade</t>
+          <t>condition.test.delivery.enabled</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>comrade</t>
+          <t>test.delivery.enabled</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -4961,12 +4961,12 @@
     <row r="226">
       <c r="B226" t="inlineStr">
         <is>
-          <t>condition.eloped</t>
+          <t>act_test_delivery_cumulative.name</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>eloped</t>
+          <t>累计交付测试</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -4978,12 +4978,12 @@
     <row r="227">
       <c r="B227" t="inlineStr">
         <is>
-          <t>condition.fled</t>
+          <t>act_test_delivery_cumulative.desc</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>fled</t>
+          <t>每天交药品2份、食物1份，消耗1行动点；成功5次完成。</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -4995,12 +4995,12 @@
     <row r="228">
       <c r="B228" t="inlineStr">
         <is>
-          <t>condition.met_in_secret</t>
+          <t>EV_TEST_DELIVERY_CUMULATIVE.title</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>met_in_secret</t>
+          <t>累计交付完成</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -5012,12 +5012,12 @@
     <row r="229">
       <c r="B229" t="inlineStr">
         <is>
-          <t>condition.musician_end</t>
+          <t>EV_TEST_DELIVERY_CUMULATIVE.body</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>musician_end</t>
+          <t>已完成五天交付，获得收据。</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -5029,12 +5029,12 @@
     <row r="230">
       <c r="B230" t="inlineStr">
         <is>
-          <t>condition.npc.npc_b.dead</t>
+          <t>EV_TEST_DELIVERY_CUMULATIVE_MILESTONE.title</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>npc.npc_b.dead</t>
+          <t>累计交付进展</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -5046,12 +5046,12 @@
     <row r="231">
       <c r="B231" t="inlineStr">
         <is>
-          <t>condition.player_influence</t>
+          <t>EV_TEST_DELIVERY_CUMULATIVE_MILESTONE.body</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>player_influence</t>
+          <t>已成功交付两次；此提示不会因连续中断而重复。</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -5063,12 +5063,12 @@
     <row r="232">
       <c r="B232" t="inlineStr">
         <is>
-          <t>condition.revolution</t>
+          <t>ending_test_cumulative.title</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>revolution</t>
+          <t>累计交付测试结局</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -5080,12 +5080,12 @@
     <row r="233">
       <c r="B233" t="inlineStr">
         <is>
-          <t>condition.specialization.player.letter.literature</t>
+          <t>ending_test_cumulative.message</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>文学知识专精</t>
+          <t>测试交付已经完成。</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -5097,12 +5097,12 @@
     <row r="234">
       <c r="B234" t="inlineStr">
         <is>
-          <t>condition.specialization.player.letter.politics</t>
+          <t>act_test_delivery_consecutive.name</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>政治知识专精</t>
+          <t>连续交付测试</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -5114,12 +5114,12 @@
     <row r="235">
       <c r="B235" t="inlineStr">
         <is>
-          <t>condition.specialization.player.letter.religion</t>
+          <t>act_test_delivery_consecutive.desc</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>宗教知识专精</t>
+          <t>每天交药品2份、食物1份，消耗1行动点；成功5次完成。</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -5131,12 +5131,12 @@
     <row r="236">
       <c r="B236" t="inlineStr">
         <is>
-          <t>condition.specialization.player.letter.science</t>
+          <t>EV_TEST_DELIVERY_CONSECUTIVE.title</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>科学知识专精</t>
+          <t>连续交付完成</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -5148,12 +5148,12 @@
     <row r="237">
       <c r="B237" t="inlineStr">
         <is>
-          <t>condition.standoff_done</t>
+          <t>EV_TEST_DELIVERY_CONSECUTIVE.body</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>standoff_done</t>
+          <t>已完成五天交付，获得收据。</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -5165,12 +5165,12 @@
     <row r="238">
       <c r="B238" t="inlineStr">
         <is>
-          <t>condition.test.delivery.enabled</t>
+          <t>EV_TEST_DELIVERY_CONSECUTIVE_MILESTONE.title</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>test.delivery.enabled</t>
+          <t>连续交付进展</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -5182,12 +5182,12 @@
     <row r="239">
       <c r="B239" t="inlineStr">
         <is>
-          <t>act_test_delivery_cumulative.name</t>
+          <t>EV_TEST_DELIVERY_CONSECUTIVE_MILESTONE.body</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>累计交付测试</t>
+          <t>已成功交付两次；此提示不会因连续中断而重复。</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -5199,12 +5199,12 @@
     <row r="240">
       <c r="B240" t="inlineStr">
         <is>
-          <t>act_test_delivery_cumulative.desc</t>
+          <t>ending_test_consecutive.title</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>每天交药品2份、食物1份，消耗1行动点；成功5次完成。</t>
+          <t>连续交付测试结局</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -5216,12 +5216,12 @@
     <row r="241">
       <c r="B241" t="inlineStr">
         <is>
-          <t>EV_TEST_DELIVERY_CUMULATIVE.title</t>
+          <t>ending_test_consecutive.message</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>累计交付完成</t>
+          <t>测试交付已经完成。</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -5233,233 +5233,233 @@
     <row r="242">
       <c r="B242" t="inlineStr">
         <is>
-          <t>EV_TEST_DELIVERY_CUMULATIVE.body</t>
+          <t>player.attribute.language</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>已完成五天交付，获得收据。</t>
+          <t>语言</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>条件系统配置迁移 / 测试样例</t>
+          <t>Player runtime</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="B243" t="inlineStr">
         <is>
-          <t>EV_TEST_DELIVERY_CUMULATIVE_MILESTONE.title</t>
+          <t>player.attribute.language.desc</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>累计交付进展</t>
+          <t>影响表达、说服与沟通。</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>条件系统配置迁移 / 测试样例</t>
+          <t>Player runtime</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="B244" t="inlineStr">
         <is>
-          <t>EV_TEST_DELIVERY_CUMULATIVE_MILESTONE.body</t>
+          <t>player.attribute.courage</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>已成功交付两次；此提示不会因连续中断而重复。</t>
+          <t>勇气</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>条件系统配置迁移 / 测试样例</t>
+          <t>Player runtime</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="B245" t="inlineStr">
         <is>
-          <t>ending_test_cumulative.title</t>
+          <t>player.attribute.courage.desc</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>累计交付测试结局</t>
+          <t>影响面对风险与压力时的行动。</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>条件系统配置迁移 / 测试样例</t>
+          <t>Player runtime</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="B246" t="inlineStr">
         <is>
-          <t>ending_test_cumulative.message</t>
+          <t>player.attribute.wisdom</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>测试交付已经完成。</t>
+          <t>智慧</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>条件系统配置迁移 / 测试样例</t>
+          <t>Player runtime</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="B247" t="inlineStr">
         <is>
-          <t>act_test_delivery_consecutive.name</t>
+          <t>player.attribute.wisdom.desc</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>连续交付测试</t>
+          <t>影响分析、推理与解决问题。</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>条件系统配置迁移 / 测试样例</t>
+          <t>Player runtime</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="B248" t="inlineStr">
         <is>
-          <t>act_test_delivery_consecutive.desc</t>
+          <t>player.attribute.perception</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>每天交药品2份、食物1份，消耗1行动点；成功5次完成。</t>
+          <t>知觉</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>条件系统配置迁移 / 测试样例</t>
+          <t>Player runtime</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="B249" t="inlineStr">
         <is>
-          <t>EV_TEST_DELIVERY_CONSECUTIVE.title</t>
+          <t>player.attribute.perception.desc</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>连续交付完成</t>
+          <t>影响观察环境、察觉细节与情绪。</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>条件系统配置迁移 / 测试样例</t>
+          <t>Player runtime</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="B250" t="inlineStr">
         <is>
-          <t>EV_TEST_DELIVERY_CONSECUTIVE.body</t>
+          <t>creation.origin.waif.label</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>已完成五天交付，获得收据。</t>
+          <t>贫寒</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>条件系统配置迁移 / 测试样例</t>
+          <t>Player runtime</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="B251" t="inlineStr">
         <is>
-          <t>EV_TEST_DELIVERY_CONSECUTIVE_MILESTONE.title</t>
+          <t>creation.origin.waif.desc</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>连续交付进展</t>
+          <t>贫寒</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>条件系统配置迁移 / 测试样例</t>
+          <t>Player runtime</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="B252" t="inlineStr">
         <is>
-          <t>EV_TEST_DELIVERY_CONSECUTIVE_MILESTONE.body</t>
+          <t>creation.origin.commoner.label</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>已成功交付两次；此提示不会因连续中断而重复。</t>
+          <t>平民</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>条件系统配置迁移 / 测试样例</t>
+          <t>Player runtime</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="B253" t="inlineStr">
         <is>
-          <t>ending_test_consecutive.title</t>
+          <t>creation.origin.commoner.desc</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>连续交付测试结局</t>
+          <t>平民</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>条件系统配置迁移 / 测试样例</t>
+          <t>Player runtime</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="B254" t="inlineStr">
         <is>
-          <t>ending_test_consecutive.message</t>
+          <t>creation.origin.noble.label</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>测试交付已经完成。</t>
+          <t>富贵</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>条件系统配置迁移 / 测试样例</t>
+          <t>Player runtime</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="B255" t="inlineStr">
         <is>
-          <t>player.attribute.language</t>
+          <t>creation.origin.noble.desc</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>语言</t>
+          <t>富贵</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -5471,12 +5471,12 @@
     <row r="256">
       <c r="B256" t="inlineStr">
         <is>
-          <t>player.attribute.language.desc</t>
+          <t>creation.temperament.kind.label</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>影响表达、说服与沟通。</t>
+          <t>善良</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -5488,12 +5488,12 @@
     <row r="257">
       <c r="B257" t="inlineStr">
         <is>
-          <t>player.attribute.courage</t>
+          <t>creation.temperament.kind.desc</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>勇气</t>
+          <t>善良</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -5505,12 +5505,12 @@
     <row r="258">
       <c r="B258" t="inlineStr">
         <is>
-          <t>player.attribute.courage.desc</t>
+          <t>creation.temperament.sincere.label</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>影响面对风险与压力时的行动。</t>
+          <t>赤诚</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -5522,12 +5522,12 @@
     <row r="259">
       <c r="B259" t="inlineStr">
         <is>
-          <t>player.attribute.wisdom</t>
+          <t>creation.temperament.sincere.desc</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>智慧</t>
+          <t>赤诚</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -5539,12 +5539,12 @@
     <row r="260">
       <c r="B260" t="inlineStr">
         <is>
-          <t>player.attribute.wisdom.desc</t>
+          <t>creation.memory.brave.label</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>影响分析、推理与解决问题。</t>
+          <t>勇敢</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -5556,12 +5556,12 @@
     <row r="261">
       <c r="B261" t="inlineStr">
         <is>
-          <t>player.attribute.perception</t>
+          <t>creation.memory.brave.desc</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>知觉</t>
+          <t>勇敢</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -5573,12 +5573,12 @@
     <row r="262">
       <c r="B262" t="inlineStr">
         <is>
-          <t>player.attribute.perception.desc</t>
+          <t>creation.memory.insightful.label</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>影响观察环境、察觉细节与情绪。</t>
+          <t>明睿</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -5590,12 +5590,12 @@
     <row r="263">
       <c r="B263" t="inlineStr">
         <is>
-          <t>creation.origin.waif.label</t>
+          <t>creation.memory.insightful.desc</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>贫寒</t>
+          <t>明睿</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -5607,12 +5607,12 @@
     <row r="264">
       <c r="B264" t="inlineStr">
         <is>
-          <t>creation.origin.waif.desc</t>
+          <t>creation.education.religion.label</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>贫寒</t>
+          <t>神学</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -5624,12 +5624,12 @@
     <row r="265">
       <c r="B265" t="inlineStr">
         <is>
-          <t>creation.origin.commoner.label</t>
+          <t>creation.education.religion.desc</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>平民</t>
+          <t>神学</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -5641,12 +5641,12 @@
     <row r="266">
       <c r="B266" t="inlineStr">
         <is>
-          <t>creation.origin.commoner.desc</t>
+          <t>creation.education.literature.label</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>平民</t>
+          <t>文学</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -5658,12 +5658,12 @@
     <row r="267">
       <c r="B267" t="inlineStr">
         <is>
-          <t>creation.origin.noble.label</t>
+          <t>creation.education.literature.desc</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>富贵</t>
+          <t>文学</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -5675,12 +5675,12 @@
     <row r="268">
       <c r="B268" t="inlineStr">
         <is>
-          <t>creation.origin.noble.desc</t>
+          <t>creation.education.science.label</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>富贵</t>
+          <t>数学与物理科学</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -5692,12 +5692,12 @@
     <row r="269">
       <c r="B269" t="inlineStr">
         <is>
-          <t>creation.temperament.kind.label</t>
+          <t>creation.education.science.desc</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>善良</t>
+          <t>数学与物理科学</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -5709,12 +5709,12 @@
     <row r="270">
       <c r="B270" t="inlineStr">
         <is>
-          <t>creation.temperament.kind.desc</t>
+          <t>creation.education.politics.label</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>善良</t>
+          <t>历史与官房学</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -5726,12 +5726,12 @@
     <row r="271">
       <c r="B271" t="inlineStr">
         <is>
-          <t>creation.temperament.sincere.label</t>
+          <t>creation.education.politics.desc</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>赤诚</t>
+          <t>历史与官房学</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -5743,12 +5743,12 @@
     <row r="272">
       <c r="B272" t="inlineStr">
         <is>
-          <t>creation.temperament.sincere.desc</t>
+          <t>creation.trait.language.label</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>赤诚</t>
+          <t>能言善辩</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -5760,12 +5760,12 @@
     <row r="273">
       <c r="B273" t="inlineStr">
         <is>
-          <t>creation.memory.brave.label</t>
+          <t>creation.trait.language.desc</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>勇敢</t>
+          <t>能言善辩</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -5777,12 +5777,12 @@
     <row r="274">
       <c r="B274" t="inlineStr">
         <is>
-          <t>creation.memory.brave.desc</t>
+          <t>creation.trait.courage.label</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>勇敢</t>
+          <t>坚定无畏</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -5794,12 +5794,12 @@
     <row r="275">
       <c r="B275" t="inlineStr">
         <is>
-          <t>creation.memory.insightful.label</t>
+          <t>creation.trait.courage.desc</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>明睿</t>
+          <t>坚定无畏</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -5811,12 +5811,12 @@
     <row r="276">
       <c r="B276" t="inlineStr">
         <is>
-          <t>creation.memory.insightful.desc</t>
+          <t>creation.trait.wisdom.label</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>明睿</t>
+          <t>聪颖睿智</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -5828,12 +5828,12 @@
     <row r="277">
       <c r="B277" t="inlineStr">
         <is>
-          <t>creation.education.religion.label</t>
+          <t>creation.trait.wisdom.desc</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>神学</t>
+          <t>聪颖睿智</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -5845,12 +5845,12 @@
     <row r="278">
       <c r="B278" t="inlineStr">
         <is>
-          <t>creation.education.religion.desc</t>
+          <t>creation.trait.perception.label</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>神学</t>
+          <t>敏锐细腻</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -5862,12 +5862,12 @@
     <row r="279">
       <c r="B279" t="inlineStr">
         <is>
-          <t>creation.education.literature.label</t>
+          <t>creation.trait.perception.desc</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>文学</t>
+          <t>敏锐细腻</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -5879,12 +5879,12 @@
     <row r="280">
       <c r="B280" t="inlineStr">
         <is>
-          <t>creation.education.literature.desc</t>
+          <t>player.background.template</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>文学</t>
+          <t>出身{0}，曾修习{3}；{1}、{2}，如今已是{4}的人。</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -5896,12 +5896,12 @@
     <row r="281">
       <c r="B281" t="inlineStr">
         <is>
-          <t>creation.education.science.label</t>
+          <t>player.origin.waif</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>数学与物理科学</t>
+          <t>流浪儿</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -5913,12 +5913,12 @@
     <row r="282">
       <c r="B282" t="inlineStr">
         <is>
-          <t>creation.education.science.desc</t>
+          <t>player.origin.commoner</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>数学与物理科学</t>
+          <t>平民</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -5930,12 +5930,12 @@
     <row r="283">
       <c r="B283" t="inlineStr">
         <is>
-          <t>creation.education.politics.label</t>
+          <t>player.origin.noble</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>历史与官房学</t>
+          <t>贵族</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -5947,12 +5947,12 @@
     <row r="284">
       <c r="B284" t="inlineStr">
         <is>
-          <t>creation.education.politics.desc</t>
+          <t>player.external.money</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>历史与官房学</t>
+          <t>共用资金</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -5964,12 +5964,12 @@
     <row r="285">
       <c r="B285" t="inlineStr">
         <is>
-          <t>creation.trait.language.label</t>
+          <t>player.external.action_points</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>能言善辩</t>
+          <t>行动点</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -5981,12 +5981,12 @@
     <row r="286">
       <c r="B286" t="inlineStr">
         <is>
-          <t>creation.trait.language.desc</t>
+          <t>player.external.action_points_max</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>能言善辩</t>
+          <t>行动点上限</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -5998,335 +5998,112 @@
     <row r="287">
       <c r="B287" t="inlineStr">
         <is>
-          <t>creation.trait.courage.label</t>
+          <t>demo.cafe.before</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>坚定无畏</t>
+          <t>【特殊来访示例】我想先点一杯咖啡，等餐的时候聊聊吧。</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Player runtime</t>
+          <t>特殊来访示例</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="B288" t="inlineStr">
         <is>
-          <t>creation.trait.courage.desc</t>
+          <t>demo.cafe.served</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>坚定无畏</t>
+          <t>【特殊来访示例】谢谢，咖啡收到了。我会继续留在座位上。</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Player runtime</t>
+          <t>特殊来访示例</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="B289" t="inlineStr">
         <is>
-          <t>creation.trait.wisdom.label</t>
+          <t>demo.cafe.chat</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>聪颖睿智</t>
+          <t>【特殊来访示例】喝完咖啡后，我们还能继续聊天。</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Player runtime</t>
+          <t>特殊来访示例</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="B290" t="inlineStr">
         <is>
-          <t>creation.trait.wisdom.desc</t>
+          <t>demo.cafe.leaving</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>聪颖睿智</t>
+          <t>示例来访进入离店阶段</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Player runtime</t>
+          <t>特殊来访反馈示例</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="B291" t="inlineStr">
         <is>
-          <t>creation.trait.perception.label</t>
+          <t>demo.cafe.ended</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>敏锐细腻</t>
+          <t>示例来访已结束</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Player runtime</t>
+          <t>特殊来访反馈示例</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="B292" t="inlineStr">
         <is>
-          <t>creation.trait.perception.desc</t>
+          <t>first.day.perception.success.title</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>敏锐细腻</t>
+          <t>察觉旧友</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Player runtime</t>
+          <t>首日咖啡馆知觉检定分支</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="B293" t="inlineStr">
         <is>
-          <t>player.background.template</t>
+          <t>first.day.perception.success</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
-        <is>
-          <t>出身{0}，曾修习{3}；{1}、{2}，如今已是{4}的人。</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>Player runtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>player.origin.waif</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>流浪儿</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>Player runtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>player.origin.commoner</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>平民</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr">
-        <is>
-          <t>Player runtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>player.origin.noble</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>贵族</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>Player runtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>player.external.money</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>共用资金</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>Player runtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>player.external.action_points</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>行动点</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>Player runtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>player.external.action_points_max</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>行动点上限</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>Player runtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>demo.cafe.before</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>【特殊来访示例】我想先点一杯咖啡，等餐的时候聊聊吧。</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>特殊来访示例</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>demo.cafe.served</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>【特殊来访示例】谢谢，咖啡收到了。我会继续留在座位上。</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>特殊来访示例</t>
-        </is>
-      </c>
-    </row>
-    <row r="302">
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>demo.cafe.chat</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>【特殊来访示例】喝完咖啡后，我们还能继续聊天。</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>特殊来访示例</t>
-        </is>
-      </c>
-    </row>
-    <row r="303">
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>demo.cafe.leaving</t>
-        </is>
-      </c>
-      <c r="C303" t="inlineStr">
-        <is>
-          <t>示例来访进入离店阶段</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>特殊来访反馈示例</t>
-        </is>
-      </c>
-    </row>
-    <row r="304">
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>demo.cafe.ended</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>示例来访已结束</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>特殊来访反馈示例</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="inlineStr"/>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>first.day.perception.success.title</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>察觉旧友</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>首日咖啡馆知觉检定分支</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="inlineStr"/>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>first.day.perception.success</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr">
         <is>
           <t>老太太说这家店“乱套”，而不是“落魄”。我想，她或许是叔叔为数不多的老客人，或者说是他的朋友。
 我听过许多他朋友的故事，结果无一例外。没想到还有活着的人。
@@ -6335,38 +6112,36 @@
 B太太是新沸点咖啡的第一位客人。就让我们以此为契机，开始享受手冲咖啡带来的乐趣吧！</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr">
+      <c r="D293" t="inlineStr">
         <is>
           <t>首日咖啡馆知觉检定分支</t>
         </is>
       </c>
     </row>
-    <row r="307">
-      <c r="A307" t="inlineStr"/>
-      <c r="B307" t="inlineStr">
+    <row r="294">
+      <c r="B294" t="inlineStr">
         <is>
           <t>first.day.perception.failure.title</t>
         </is>
       </c>
-      <c r="C307" t="inlineStr">
+      <c r="C294" t="inlineStr">
         <is>
           <t>古怪的来客</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr">
+      <c r="D294" t="inlineStr">
         <is>
           <t>首日咖啡馆知觉检定分支</t>
         </is>
       </c>
     </row>
-    <row r="308">
-      <c r="A308" t="inlineStr"/>
-      <c r="B308" t="inlineStr">
+    <row r="295">
+      <c r="B295" t="inlineStr">
         <is>
           <t>first.day.perception.failure</t>
         </is>
       </c>
-      <c r="C308" t="inlineStr">
+      <c r="C295" t="inlineStr">
         <is>
           <t>不知怎么，总觉得她身上的气息突然变了。
 我没心思琢磨这位古怪老太太爱琢磨些什么，还好她把视线收了回去。
@@ -6375,9 +6150,2568 @@
 B太太是新沸点咖啡的第一位客人。就让我们以此为契机，开始享受手冲咖啡带来的乐趣吧！</t>
         </is>
       </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>首日咖啡馆知觉检定分支</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.customer.name</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>顾客B</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>文案-新手教程.docx；原文保留</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>opening.line.01</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>哼哼，现在就由我来给店长介绍一下咖啡馆吧！</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>原稿段落 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>opening.line.02</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>这是大堂，顾客会在吧台下单取餐。</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>原稿段落 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>opening.line.03</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>操作间就在吧台旁边！不过要等一会才可以进去。</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>原稿段落 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>opening.line.04</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>这个楼梯通往二层，但我还没整理，等我们赚够钱，就可以进行扩充升级……</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>原稿段落 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>opening.line.05</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>我们在一楼经过的地方都一尘不染，宽敞明亮，萦绕着淡淡咖啡香</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>原稿段落 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>opening.line.06</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>和杂乱无章的二楼对比，一下能就看出阿黛尔花了多少心思</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>原稿段落 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>opening.line.07</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>你也是够不容易的</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>原稿段落 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>opening.line.08</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>你是指清理吗……确实挺累的，但看着一家乱糟糟的店因为变成这样，就觉得，觉得——</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>原稿段落 13</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.customer_arrives.title</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>customer_arrives</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>文案-新手教程.docx；原文保留</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.customer_arrives.01</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>进来的是一个衣着普通的老太太，记不住脸</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>原稿段落 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.customer_arrives.02</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>你们是新店家？我路过了，就进来看看……怎么还叫沸点咖啡？不换个名字？</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>原稿段落 16</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.customer_arrives.03</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>嗯？为什么要换名字？</t>
+        </is>
+      </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>首日咖啡馆知觉检定分支</t>
+          <t>原稿段落 17</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.customer_arrives.04</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>哎呀，自从最开始那个店主说不回王都了，这家店就乱套咯……</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>原稿段落 18</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.customer_arrives.05</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>您说的是我叔叔杜尔瓦吧。</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>原稿段落 19</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.customer_arrives.06</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>她看了我一眼，我回以微笑。</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>原稿段落 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.perception_success.title</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>perception_success</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>文案-新手教程.docx；原文保留</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.perception_success.01</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>落魄</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>原稿段落 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.perception_success.02</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>老客人</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>原稿段落 23</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.perception_success.03</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>我听过许多他朋友的故事，结果无一例外。没想到还有活着的人</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>原稿段落 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.perception_success.04</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>这位小姑娘是叔叔的女儿阿黛尔。</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>原稿段落 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.perception_success.05</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>这家店现在是我们主管，和过去同根同源，所以平时会更长修剪下树的枝蔓，提升美观。</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>原稿段落 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.perception_success.06</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>阿黛尔，你和这位太太说说这两天你做了什么</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>原稿段落 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.perception_success.07</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>换了好喝的新豆子，在采购新的基底，还买了新杯子……还来了个新咖啡师！</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>原稿段落 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.perception_success.08</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>咖啡师也换了？</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>原稿段落 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.perception_success.09</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>就是我们{playername}店长可会做咖啡啦，您要不尝尝啊，不可能比以前差！</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>原稿段落 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.perception_failure.title</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>perception_failure</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>文案-新手教程.docx；原文保留</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.perception_failure.01</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>不知怎么，总感觉她身上的气息突然变了</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>原稿段落 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.perception_failure.02</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>我没心思琢磨古怪的老太太爱琢磨些什么</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>原稿段落 32</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.perception_failure.03</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>还好她把视线收了回去</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>原稿段落 33</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.order_confirmed.title</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>order_confirmed</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>文案-新手教程.docx；原文保留</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.order_confirmed.01</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>可能是看出老太太想点餐，阿黛尔塞去一张自己无聊手绘的餐单</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>原稿段落 35</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.order_confirmed.02</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>小杯装黑咖啡 ，无糖，就这样</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>原稿段落 36</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.order_confirmed.03</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>B太太——新沸点咖啡的第一位客人</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>原稿段落 37</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.order_confirmed.04</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>就让我们以此为契机，开始享受手冲咖啡带来的乐趣吧！</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>原稿段落 38</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.workstation_open.title</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>workstation_open</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>文案-新手教程.docx；原文保留</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.workstation_open.01</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>[演出说明：背景：大堂-吧台；UI正式开放，点击吧台的桌面可立刻转换至操作台视角，]</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>原稿段落 40</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.make_coffee_base.title</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>make_coffee_base</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>文案-新手教程.docx；原文保留</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.make_coffee_base.01</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>哎呀呀，还没正式营业，就有了一笔生意进账。但是店长，你都不说话。看着有点紧张？哦，因为是第一次！我会全程提醒你的！首先，要确认客户订单上的需求！</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>原稿段落 45</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.make_coffee_base.02</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>顾客姓名：B顾客要求：无糖黑咖，其他随便配料表:咖啡原液（咖啡粉+开水）根据浓度/甜度要求，加入适量清水/方糖顾客姓名：B顾客要求：无糖黑咖，其他随便配料表:咖啡原液（咖啡粉+开水）根据浓度/甜度要求，加入适量清水/方糖</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>原稿段落 46</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.make_coffee_base.03</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>按照要求，首先我们要配置咖啡原液；然后将其注杯——</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>原稿段落 51</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.pour_into_cup.title</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>pour_into_cup</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>文案-新手教程.docx；原文保留</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.pour_into_cup.01</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>按照要求，首先我们要配置咖啡原液；然后将其注杯——</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>原稿段落 51</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.adjust_strength.title</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>adjust_strength</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>文案-新手教程.docx；原文保留</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.adjust_strength.01</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>其后，查看浓度与甜度要求，判断是否添入清水与方糖；今天顾客似乎只要求了无糖；</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>原稿段落 52</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.adjust_sweetness.title</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>adjust_sweetness</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>文案-新手教程.docx；原文保留</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.adjust_sweetness.01</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>其后，查看浓度与甜度要求，判断是否添入清水与方糖；今天顾客似乎只要求了无糖；</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>原稿段落 52</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.adjust_sweetness.02</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>制作配方不止一种，探索是无止境的，欢迎你放飞天马般的想象力，解锁多元趣味组合！</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>原稿段落 53</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.demo_grind.title</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>研磨</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>文案-新手教程.docx；原文保留</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.demo_grind.01</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>研磨</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>原稿枚举展开；未添加玩法</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.demo_boil.title</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>烧水</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>文案-新手教程.docx；原文保留</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.demo_boil.01</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>烧水</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>原稿枚举展开；未添加玩法</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.demo_brew.title</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>冲泡</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>文案-新手教程.docx；原文保留</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.demo_brew.01</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>冲泡</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>原稿枚举展开；未添加玩法</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.demo_cup.title</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>装杯</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>文案-新手教程.docx；原文保留</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.demo_cup.01</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>装杯</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>原稿枚举展开；未添加玩法</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.demo_base.title</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>基底</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>文案-新手教程.docx；原文保留</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.demo_base.01</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>基底</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>原稿枚举展开；未添加玩法</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.demo_strength.title</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>调浓度</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>文案-新手教程.docx；原文保留</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.demo_strength.01</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>调浓度</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>原稿枚举展开；未添加玩法</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.demo_sweetness.title</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>甜度</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>文案-新手教程.docx；原文保留</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.demo_sweetness.01</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>甜度</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>原稿枚举展开；未添加玩法</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.demo_serve.title</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>出餐</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>文案-新手教程.docx；原文保留</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.demo_serve.01</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>出餐</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>原稿枚举展开；未添加玩法</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.serve_customer.title</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>serve_customer</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>文案-新手教程.docx；原文保留</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.serve_customer.01</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>怎么样？！好紧张啊！</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>原稿段落 67</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.result_excellent.title</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>独一无二</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>文案-新手教程.docx；原文保留</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.result_excellent.01</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>这个咖啡嘛……简直就是独一无二！</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>原稿枚举展开；未添加玩法</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.result_excellent.02</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>金钱+200</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>原稿枚举展开；未添加玩法</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.result_good.title</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>滴滴香浓</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>文案-新手教程.docx；原文保留</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.result_good.01</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>这个咖啡嘛……简直就是滴滴香浓！</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>原稿枚举展开；未添加玩法</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.result_good.02</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>金钱+150</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>原稿枚举展开；未添加玩法</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.result_average.title</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>中庸之道</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>文案-新手教程.docx；原文保留</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.result_average.01</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>这个咖啡嘛……简直就是中庸之道！</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>原稿枚举展开；未添加玩法</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.result_average.02</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>金钱+50</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>原稿枚举展开；未添加玩法</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.result_bad.title</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>食不知味</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>文案-新手教程.docx；原文保留</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.result_bad.01</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>这个咖啡嘛……简直就是食不知味！</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>原稿枚举展开；未添加玩法</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.result_bad.02</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>金钱+10</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>原稿枚举展开；未添加玩法</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.result_refund.title</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>好想退钱</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>文案-新手教程.docx；原文保留</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.result_refund.01</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>这个咖啡嘛……简直就是好想退钱！</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>原稿枚举展开；未添加玩法</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.result_refund.02</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>金钱-200，打回重做</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>原稿枚举展开；未添加玩法</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.ending.title</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>ending</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>文案-新手教程.docx；原文保留</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.ending.01</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr"/>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>原稿段落 70</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.ending.02</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>还真是不知道怎么说的一天呢，不过也算真的开始重回正轨了。</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>原稿段落 71</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.ending.03</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>阿黛尔去休息了。我望着空旷的大厅，许久都没有动身</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>原稿段落 73</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.ending.04</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>今天实在太辗转奔波，希望明天生活能开始进入正轨</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>原稿段落 74</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.ending.05</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>愿神保佑沸点咖啡店</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>原稿段落 75</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.ending.06</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr"/>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>原稿段落 76</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p000</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>文案 - 教程关：第一杯咖啡</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p002</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>（接开幕文案）</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p003</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>（切大地图，聚焦咖啡馆，其余地点锁定）</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p004</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>（click 跳转一楼大堂）</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p006</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>重新启航（已对齐，可执行）</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p007</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>[背景图：一楼大堂，开门风铃/铃铛声响]</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p008</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>[演出说明：对应背景图：切大堂、操作间、二楼（杂乱）、三楼]</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p009</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>阿黛尔·米尼耶：「哼哼，现在就由我来给店长介绍一下咖啡馆吧！」「这是大堂，顾客会在吧台下单取餐。」「操作间就在吧台旁边！不过要等一会才可以进去。」「这个楼梯通往二层，但我还没整理，等我们赚够钱，就可以进行扩充升级……」</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p010</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>我们在一楼经过的地方都一尘不染，宽敞明亮，萦绕着淡淡咖啡香</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p011</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>和杂乱无章的二楼对比，一下能就看出阿黛尔花了多少心思</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p012</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>{playername}：你也是够不容易的</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p013</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>阿黛尔·米尼耶：（#思索）「你是指清理吗……确实挺累的，但看着一家乱糟糟的店因为变成这样，就觉得，觉得——」</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p014</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[开门风铃/铃铛声（同前），黑色剪影立绘出] </t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p015</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>进来的是一个衣着普通的老太太，记不住脸</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p016</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>顾客B：「你们是新店家？我路过了，就进来看看……怎么还叫沸点咖啡？不换个名字？」</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p017</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>阿黛尔·米尼耶：（#迷惑）「嗯？为什么要换名字？」</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p018</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>顾客B：「哎呀，自从最开始那个店主说不回王都了，这家店就乱套咯……」</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p019</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>{playername}：「您说的是我叔叔杜尔瓦吧。」</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p020</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>她看了我一眼，我回以微笑。</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p021</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t xml:space="preserve">开启知觉鉴定，知觉≥3触发 </t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p022</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>老太太说这家店是乱套，而不用「落魄」做形容</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p023</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>我想她可能是叔叔的「老客人」，或者说他为数不多的朋友</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p024</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>（程序附文本插入：知觉判定成功，触发隐藏剧情）</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p025</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>我听过许多他朋友的故事，结果无一例外。没想到还有活着的人</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p026</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>{playername}：「这位小姑娘是叔叔的女儿阿黛尔。」「这家店现在是我们主管，和过去同根同源，所以平时会更长修剪下树的枝蔓，提升美观。」「阿黛尔，你和这位太太说说这两天你做了什么」</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p027</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>阿黛尔·米尼耶：「换了好喝的新豆子，在采购新的基底，还买了新杯子……还来了个新咖啡师！」</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p028</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>顾客B：「咖啡师也换了？」</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p029</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>阿黛尔·米尼耶：（#开心）「就是我们{playername}店长可会做咖啡啦，您要不尝尝啊，不可能比以前差！」</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p030</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>(知觉鉴定失败，知觉＜3，触发以下剧情)</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p031</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>不知怎么，总感觉她身上的气息突然变了</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p032</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>我没心思琢磨古怪的老太太爱琢磨些什么</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p033</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>还好她把视线收了回去</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p034</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>(无论知觉检定是否达标，都强制进入）</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p035</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>可能是看出老太太想点餐，阿黛尔塞去一张自己无聊手绘的餐单</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p036</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>顾客B：（思索）「小杯装黑咖啡 ，无糖，就这样」</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p037</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>B太太——新沸点咖啡的第一位客人</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p038</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>就让我们以此为契机，开始享受手冲咖啡带来的乐趣吧！</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p040</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>[演出说明：背景：大堂-吧台；UI正式开放，点击吧台的桌面可立刻转换至操作台视角，]</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p042</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>咖啡怎么出餐</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p043</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>[演出说明：UI正式开放，点击吧台的桌面可立刻转换至操作台视角，弹窗显示具体说明，譬如如何操作等界面，具体逻辑参见玩法。当阿黛尔讲解功能时对应区域播放操作动画。]</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p044</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>[操作台]</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p045</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>阿黛尔·米尼耶：（#开心）哎呀呀，还没正式营业，就有了一笔生意进账。但是店长，你都不说话。看着有点紧张？哦，因为是第一次！我会全程提醒你的！首先，要确认客户订单上的需求！</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p046</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>顾客姓名：B顾客要求：无糖黑咖，其他随便配料表:咖啡原液（咖啡粉+开水）根据浓度/甜度要求，加入适量清水/方糖顾客姓名：B顾客要求：无糖黑咖，其他随便配料表:咖啡原液（咖啡粉+开水）根据浓度/甜度要求，加入适量清水/方糖</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p050</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>（操作步骤动画说明，需要Highlight强调）</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p051</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>阿黛尔·米尼耶：按照要求，首先我们要配置咖啡原液；然后将其注杯——</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p052</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>其后，查看浓度与甜度要求，判断是否添入清水与方糖；今天顾客似乎只要求了无糖；</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p053</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>制作配方不止一种，探索是无止境的，欢迎你放飞天马般的想象力，解锁多元趣味组合！</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p054</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>[演出说明：弹出说明对话框，玩家可以选择性查看操作动画演示，研磨、烧水、冲泡、装杯、基底、调浓度、甜度，出餐多流程；之后玩家自由发挥。]（参考牧场物语）</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p055</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>（玩家自由调配过程）</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p057</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>（出餐按钮 Buttuon 按钮，切吧台）</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p065</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>我的第一次如何？</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p066</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>[演出说明-背景：大堂-吧台，顾客立绘，送餐动画，（通用NPC：可以不用喝咖啡动作，有交互角色需要]</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p067</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>阿黛尔·米尼耶：（#焦虑）「怎么样？！好紧张啊！」</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p068</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>顾客B：「这个咖啡嘛……简直就是    （按数值判定显示：独一无二[金钱+200]；滴滴香浓[金钱+150] 中庸之道[金钱+50];食不知味[金钱+10]；好想退钱[金钱-200，打回重做]）！」</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p069</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[演出说明，背景-同上，金钱效果UI，结算动画：独一无二+滴滴香浓：烟花效果+喝彩声，中庸之道：无动画，食不知味、好想退钱丑化emoji铺满屏幕，维持五秒。] </t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p070</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>（顾客离开）</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p071</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>阿黛尔·米尼耶：（#平静）「还真是不知道怎么说的一天呢，不过也算真的开始重回正轨了。」</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p072</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>（过场动画：阿黛尔立绘闪出）</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p073</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>阿黛尔去休息了。我望着空旷的大厅，许久都没有动身</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p074</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>今天实在太辗转奔波，希望明天生活能开始进入正轨</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p075</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>愿神保佑沸点咖啡店</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p076</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>（切黑场）</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>cafe.tutorial.source.p077</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>（过场动画）</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>原稿完整归档（含舞台说明）；不自动播放</t>
         </is>
       </c>
     </row>

--- a/Assets/ConfigTables/Data/Shared/Text.xlsx
+++ b/Assets/ConfigTables/Data/Shared/Text.xlsx
@@ -1272,7 +1272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D446"/>
+  <dimension ref="A1:D499"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7556,7 +7556,6 @@
           <t>cafe.tutorial.ending.01</t>
         </is>
       </c>
-      <c r="C378" t="inlineStr"/>
       <c r="D378" t="inlineStr">
         <is>
           <t>原稿段落 70</t>
@@ -7637,7 +7636,6 @@
           <t>cafe.tutorial.ending.06</t>
         </is>
       </c>
-      <c r="C383" t="inlineStr"/>
       <c r="D383" t="inlineStr">
         <is>
           <t>原稿段落 76</t>
@@ -8712,6 +8710,642 @@
       <c r="D446" t="inlineStr">
         <is>
           <t>原稿完整归档（含舞台说明）；不自动播放</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>arrival.title</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>初来乍到</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>arrival.start.01</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>我放下了手中的信件，望向车棚外熙熙攘攘的人群</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>arrival.start.02</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>这是圣诺特最繁华的街道——圣徒街</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>arrival.start.03</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>客商的叫卖声与来往车马的嘶鸣声不绝于耳，而那些为达官显贵所推崇的店面被围堵得水泄不通</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>arrival.start.04</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>马车慢了下来，停在圣徒街217号店面之前</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>arrival.start.05</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>这是一间咖啡店，名叫“沸点咖啡馆”，坐落于圣徒街靠近旧城区的十字路口</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>arrival.start.06</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>与圣徒街上其他那些生意兴隆的店铺不同，沸点咖啡馆内门可罗雀，来往的人群也不为这家店驻足</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>arrival.start.07</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>我站在咖啡馆前，不由得咋舌</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>arrival.start.08</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>这可是王都最繁华的商业街，虽然只是一角，但租金昂贵</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>arrival.start.09</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>照这个状况，这家咖啡店恐怕已经处于半倒闭状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>arrival.start.10</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>这就是...叔叔说的咖啡店？真的假的......</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>arrival.start.11</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>请问你是{playername}吧？</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>arrival.start.12</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>是的，你应该就是米尼耶叔叔信里提到的阿黛尔·米尼耶？</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>arrival.start.13</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>没错，我就是阿黛尔，欢迎来到沸点咖啡馆！想必你就是爸爸之前提到的那位{playername}吧，爸爸可没少夸赞你呢。</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>arrival.reply.1.01</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>你们这咖啡馆真是......颇具特色......</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>arrival.reply.2.01</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>额......这咖啡馆真在营业吗？</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-1.1</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>你们这咖啡馆真是......颇具特色......</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-1.2</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>额......这咖啡馆真在营业吗？</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>arrival.agent.01</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>这个，那个，这家咖啡馆现在的确遇到了些经营上的问题，欸嘿嘿。</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>arrival.agent.02</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>我也是昨天才到王都，当时也是被咖啡馆的状况吓了一跳。爸爸说让我和你一起经营咖啡馆，但是我一时也还没头绪如何处理这烂摊子。</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>arrival.agent.03</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>杜瓦尔叔叔就这么让小工自己管理这咖啡馆？</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>arrival.agent.04</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>爸爸他找了个朋友当代理店长，帮忙管理，但是——阿黛尔左顾右盼，审视了下四周，凑近了小声说道最近风头紧，那位代理店长不小心犯了点事，这家咖啡馆就被人三番五次骚扰。代理店长也在两个月前不知所踪，只是留了封信给小工，嘱咐小工按时上班并且按时派人送工资过来。</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>arrival.insight.01</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>风头紧，还犯事，不会和坊间流传的作乱分子有关吧？这烂摊子真要接吗？</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>arrival.request.01</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>抱歉，我能力有限，可能不太能担得起把这个咖啡店经营好的重任。</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>arrival.request.02</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>我......我相信你，爸爸和我说了，你有能力和品格能够拯救这家店。阿黛尔不由得露出急切的神情，抓住我的衣袖想要挽留。这家店是爸爸最喜欢的店。他现在身体不好，不得不在南边养病，但医生说，医生说他可能——</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>arrival.request.03</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>一抹悲伤随着阿黛尔眼角的泪显现出来。我连忙安慰她，希望她能平复下来。</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>arrival.request.04</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>抱歉，有些失态了。阿黛尔抹去眼角的泪，冷静了下来。爸爸重病，妈妈得留在他身边照顾，这家店的代理店长也不知所踪，爸爸只好让我来帮忙。但我又没有经营谋生的经验，年龄也太小，只靠我的话真地可能没法拯救这家咖啡店——所以，拜托你。</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>arrival.decision.01</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>要接手沸点咖啡馆吗？</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-2.1</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>强硬拒绝</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-2.2</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>接受委托</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>arrival.refuse.01</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>我拒绝了阿黛尔的请求</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>arrival.refuse.02</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>面对这困难的挑战，我不认为自己可以重新让沸点咖啡馆焕发风采</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>arrival.refuse.03</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>阿黛尔也没有进一步挽留我，选择自己一个人继续维系这家咖啡馆</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>arrival.refuse.04</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>我用剩下的盘缠离开了王都，重新回到了家乡，回归过去的生活</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>arrival.refuse.05</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>一切都没有改变，一切都如此安宁</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>arrival.refuse.06</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>王都后来发生的那些离奇的故事，也与我再没有关系</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>arrival.refuse.07</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>就这样度过了一生</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>arrival.refuse.08</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>达成End if0 “未开始就已结束”</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>arrival.refuse.09</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>要重新做出抉择吗？</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-3.1</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>重新抉择</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>MA70.10.06-S1-3.2</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>就此别离</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>arrival.accept.01</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>好吧，我愿意尝试一下。</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>arrival.accept.02</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>真......真的吗？</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>arrival.accept.03</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>当然是真的。你不相信的话，那不如我就直接跑路？</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>arrival.accept.04</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>不不不，我当然相信你。只是有点激动，谢谢，谢谢你！阿黛尔眼角的泪还未干，脸上却已洋溢着笑容欢迎来到沸点咖啡店！新任店长！</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>arrival.accept.05</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>跟我走吧，我带你了解下我们咖啡店现在的状况。</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>arrival.accept.06</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>阿黛尔领着我向柜台走去</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>arrival.accept.07</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>正当我踏出脚步时，一道寒意从背后传来，似有目光在那阴影中盯着我</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>arrival.accept.08</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>我猛然回头，却只看到那些陌生的脸，他们在街道上来去，不曾对我有所停留</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>arrival.accept.09</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>那股骇人的恶意，似是发现了什么，收敛了身形，隐匿在涌动的人潮中</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>arrival.accept.10</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>店长？没事吧？</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>arrival.accept.11</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>没事，刚来王都对很多事情不习惯而已，我们进去吧。</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>arrival.accept.12</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>我跟着阿黛尔向店深处走去，消失在阴影之中</t>
         </is>
       </c>
     </row>

--- a/Assets/ConfigTables/Data/Shared/Text.xlsx
+++ b/Assets/ConfigTables/Data/Shared/Text.xlsx
@@ -1272,7 +1272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D499"/>
+  <dimension ref="A1:D510"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8724,628 +8724,1080 @@
           <t>初来乍到</t>
         </is>
       </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="B448" t="inlineStr">
         <is>
-          <t>arrival.start.01</t>
+          <t>arrival.start.01.01</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
           <t>我放下了手中的信件，望向车棚外熙熙攘攘的人群</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="B449" t="inlineStr">
         <is>
-          <t>arrival.start.02</t>
+          <t>arrival.start.01.02</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
           <t>这是圣诺特最繁华的街道——圣徒街</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="B450" t="inlineStr">
         <is>
-          <t>arrival.start.03</t>
+          <t>arrival.start.01.03</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
           <t>客商的叫卖声与来往车马的嘶鸣声不绝于耳，而那些为达官显贵所推崇的店面被围堵得水泄不通</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="B451" t="inlineStr">
         <is>
-          <t>arrival.start.04</t>
+          <t>arrival.start.01.04</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
           <t>马车慢了下来，停在圣徒街217号店面之前</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="B452" t="inlineStr">
         <is>
-          <t>arrival.start.05</t>
+          <t>arrival.start.02.01</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
           <t>这是一间咖啡店，名叫“沸点咖啡馆”，坐落于圣徒街靠近旧城区的十字路口</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="B453" t="inlineStr">
         <is>
-          <t>arrival.start.06</t>
+          <t>arrival.start.02.02</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
           <t>与圣徒街上其他那些生意兴隆的店铺不同，沸点咖啡馆内门可罗雀，来往的人群也不为这家店驻足</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="B454" t="inlineStr">
         <is>
-          <t>arrival.start.07</t>
+          <t>arrival.start.02.03</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
           <t>我站在咖啡馆前，不由得咋舌</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="B455" t="inlineStr">
         <is>
-          <t>arrival.start.08</t>
+          <t>arrival.start.02.04</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
           <t>这可是王都最繁华的商业街，虽然只是一角，但租金昂贵</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="B456" t="inlineStr">
         <is>
-          <t>arrival.start.09</t>
+          <t>arrival.start.02.05</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
           <t>照这个状况，这家咖啡店恐怕已经处于半倒闭状态</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="B457" t="inlineStr">
         <is>
-          <t>arrival.start.10</t>
+          <t>arrival.start.02.06</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>这就是...叔叔说的咖啡店？真的假的......</t>
+          <t>这就是...叔叔说的咖啡店？</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="B458" t="inlineStr">
         <is>
-          <t>arrival.start.11</t>
+          <t>arrival.start.02.07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>请问你是{playername}吧？</t>
+          <t>真的假的......</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="B459" t="inlineStr">
         <is>
-          <t>arrival.start.12</t>
+          <t>arrival.start.02.08</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>是的，你应该就是米尼耶叔叔信里提到的阿黛尔·米尼耶？</t>
+          <t>请问你是{playername}吧？</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="B460" t="inlineStr">
         <is>
-          <t>arrival.start.13</t>
+          <t>arrival.start.02.09</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>没错，我就是阿黛尔，欢迎来到沸点咖啡馆！想必你就是爸爸之前提到的那位{playername}吧，爸爸可没少夸赞你呢。</t>
+          <t>是的，你应该就是米尼耶叔叔信里提到的阿黛尔·米尼耶？</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="B461" t="inlineStr">
         <is>
-          <t>arrival.reply.1.01</t>
+          <t>arrival.start.02.10</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>你们这咖啡馆真是......颇具特色......</t>
+          <t>没错，我就是阿黛尔，欢迎来到沸点咖啡馆！想必你就是爸爸之前提到的那位{playername}吧，爸爸可没少夸赞你呢。</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="B462" t="inlineStr">
         <is>
-          <t>arrival.reply.2.01</t>
+          <t>arrival.reply.1.01.01</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>额......这咖啡馆真在营业吗？</t>
+          <t>你们这咖啡馆真是......颇具特色......</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="B463" t="inlineStr">
         <is>
-          <t>MA70.10.06-S1-1.1</t>
+          <t>arrival.reply.2.01.01</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>你们这咖啡馆真是......颇具特色......</t>
+          <t>额......这咖啡馆真在营业吗？</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="B464" t="inlineStr">
         <is>
-          <t>MA70.10.06-S1-1.2</t>
+          <t>MA70.10.06-S1-1.1</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>额......这咖啡馆真在营业吗？</t>
+          <t>你们这咖啡馆真是......颇具特色......</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="B465" t="inlineStr">
         <is>
-          <t>arrival.agent.01</t>
+          <t>MA70.10.06-S1-1.2</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>这个，那个，这家咖啡馆现在的确遇到了些经营上的问题，欸嘿嘿。</t>
+          <t>额......这咖啡馆真在营业吗？</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="B466" t="inlineStr">
         <is>
-          <t>arrival.agent.02</t>
+          <t>arrival.agent.01.01</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>我也是昨天才到王都，当时也是被咖啡馆的状况吓了一跳。爸爸说让我和你一起经营咖啡馆，但是我一时也还没头绪如何处理这烂摊子。</t>
+          <t>这个，那个，这家咖啡馆现在的确遇到了些经营上的问题，欸嘿嘿。</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="B467" t="inlineStr">
         <is>
-          <t>arrival.agent.03</t>
+          <t>arrival.agent.01.02</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>杜瓦尔叔叔就这么让小工自己管理这咖啡馆？</t>
+          <t>我也是昨天才到王都，当时也是被咖啡馆的状况吓了一跳。爸爸说让我和你一起经营咖啡馆，但是我一时也还没头绪如何处理这烂摊子。</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="B468" t="inlineStr">
         <is>
-          <t>arrival.agent.04</t>
+          <t>arrival.agent.01.03</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>爸爸他找了个朋友当代理店长，帮忙管理，但是——阿黛尔左顾右盼，审视了下四周，凑近了小声说道最近风头紧，那位代理店长不小心犯了点事，这家咖啡馆就被人三番五次骚扰。代理店长也在两个月前不知所踪，只是留了封信给小工，嘱咐小工按时上班并且按时派人送工资过来。</t>
+          <t>杜瓦尔叔叔就这么让小工自己管理这咖啡馆？</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="B469" t="inlineStr">
         <is>
-          <t>arrival.insight.01</t>
+          <t>arrival.agent.01.04</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>风头紧，还犯事，不会和坊间流传的作乱分子有关吧？这烂摊子真要接吗？</t>
+          <t>爸爸他找了个朋友当代理店长，帮忙管理，但是——</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="B470" t="inlineStr">
         <is>
-          <t>arrival.request.01</t>
+          <t>arrival.agent.01.05</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>抱歉，我能力有限，可能不太能担得起把这个咖啡店经营好的重任。</t>
+          <t>阿黛尔左顾右盼，审视了下四周，凑近了小声说道</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="B471" t="inlineStr">
         <is>
-          <t>arrival.request.02</t>
+          <t>arrival.agent.01.06</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>我......我相信你，爸爸和我说了，你有能力和品格能够拯救这家店。阿黛尔不由得露出急切的神情，抓住我的衣袖想要挽留。这家店是爸爸最喜欢的店。他现在身体不好，不得不在南边养病，但医生说，医生说他可能——</t>
+          <t>最近风头紧，那位代理店长不小心犯了点事，这家咖啡馆就被人三番五次骚扰。</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="B472" t="inlineStr">
         <is>
-          <t>arrival.request.03</t>
+          <t>arrival.agent.01.07</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>一抹悲伤随着阿黛尔眼角的泪显现出来。我连忙安慰她，希望她能平复下来。</t>
+          <t>代理店长也在两个月前不知所踪，只是留了封信给小工，嘱咐小工按时上班并且按时派人送工资过来。</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="B473" t="inlineStr">
         <is>
-          <t>arrival.request.04</t>
+          <t>arrival.insight.01.01</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>抱歉，有些失态了。阿黛尔抹去眼角的泪，冷静了下来。爸爸重病，妈妈得留在他身边照顾，这家店的代理店长也不知所踪，爸爸只好让我来帮忙。但我又没有经营谋生的经验，年龄也太小，只靠我的话真地可能没法拯救这家咖啡店——所以，拜托你。</t>
+          <t>风头紧，还犯事，不会和坊间流传的作乱分子有关吧？这烂摊子真要接吗？</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="B474" t="inlineStr">
         <is>
-          <t>arrival.decision.01</t>
+          <t>arrival.request.01.01</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>要接手沸点咖啡馆吗？</t>
+          <t>抱歉，我能力有限，可能不太能担得起把这个咖啡店经营好的重任。</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="B475" t="inlineStr">
         <is>
-          <t>MA70.10.06-S1-2.1</t>
+          <t>arrival.request.01.02</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>强硬拒绝</t>
+          <t>我......我相信你，爸爸和我说了，你有能力和品格能够拯救这家店。</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="B476" t="inlineStr">
         <is>
-          <t>MA70.10.06-S1-2.2</t>
+          <t>arrival.request.01.03</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>接受委托</t>
+          <t>阿黛尔不由得露出急切的神情，抓住我的衣袖想要挽留。</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="B477" t="inlineStr">
         <is>
-          <t>arrival.refuse.01</t>
+          <t>arrival.request.01.04</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>我拒绝了阿黛尔的请求</t>
+          <t>这家店是爸爸最喜欢的店。他现在身体不好，不得不在南边养病，但医生说，医生说他可能——</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="B478" t="inlineStr">
         <is>
-          <t>arrival.refuse.02</t>
+          <t>arrival.request.01.05</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>面对这困难的挑战，我不认为自己可以重新让沸点咖啡馆焕发风采</t>
+          <t>一抹悲伤随着阿黛尔眼角的泪显现出来。我连忙安慰她，希望她能平复下来。</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="B479" t="inlineStr">
         <is>
-          <t>arrival.refuse.03</t>
+          <t>arrival.request.01.06</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>阿黛尔也没有进一步挽留我，选择自己一个人继续维系这家咖啡馆</t>
+          <t>抱歉，有些失态了。</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="B480" t="inlineStr">
         <is>
-          <t>arrival.refuse.04</t>
+          <t>arrival.request.01.07</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>我用剩下的盘缠离开了王都，重新回到了家乡，回归过去的生活</t>
+          <t>阿黛尔抹去眼角的泪，冷静了下来。</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="B481" t="inlineStr">
         <is>
-          <t>arrival.refuse.05</t>
+          <t>arrival.request.01.08</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>一切都没有改变，一切都如此安宁</t>
+          <t>爸爸重病，妈妈得留在他身边照顾，这家店的代理店长也不知所踪，爸爸只好让我来帮忙。</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="B482" t="inlineStr">
         <is>
-          <t>arrival.refuse.06</t>
+          <t>arrival.request.01.09</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>王都后来发生的那些离奇的故事，也与我再没有关系</t>
+          <t>但我又没有经营谋生的经验，年龄也太小，只靠我的话真地可能没法拯救这家咖啡店——所以，拜托你。</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="B483" t="inlineStr">
         <is>
-          <t>arrival.refuse.07</t>
+          <t>arrival.decision.01.01</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>就这样度过了一生</t>
+          <t>要接手沸点咖啡馆吗？</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="B484" t="inlineStr">
         <is>
-          <t>arrival.refuse.08</t>
+          <t>MA70.10.06-S1-2.1</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>达成End if0 “未开始就已结束”</t>
+          <t>强硬拒绝</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="B485" t="inlineStr">
         <is>
-          <t>arrival.refuse.09</t>
+          <t>MA70.10.06-S1-2.2</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>要重新做出抉择吗？</t>
+          <t>接受委托</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="B486" t="inlineStr">
         <is>
-          <t>MA70.10.06-S1-3.1</t>
+          <t>arrival.refuse.01.01</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>重新抉择</t>
+          <t>我拒绝了阿黛尔的请求</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="B487" t="inlineStr">
         <is>
-          <t>MA70.10.06-S1-3.2</t>
+          <t>arrival.refuse.01.02</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>就此别离</t>
+          <t>面对这困难的挑战，我不认为自己可以重新让沸点咖啡馆焕发风采</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="B488" t="inlineStr">
         <is>
-          <t>arrival.accept.01</t>
+          <t>arrival.refuse.01.03</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>好吧，我愿意尝试一下。</t>
+          <t>阿黛尔也没有进一步挽留我，选择自己一个人继续维系这家咖啡馆</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="B489" t="inlineStr">
         <is>
-          <t>arrival.accept.02</t>
+          <t>arrival.refuse.01.04</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>真......真的吗？</t>
+          <t>我用剩下的盘缠离开了王都，重新回到了家乡，回归过去的生活</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="B490" t="inlineStr">
         <is>
-          <t>arrival.accept.03</t>
+          <t>arrival.refuse.01.05</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>当然是真的。你不相信的话，那不如我就直接跑路？</t>
+          <t>一切都没有改变，一切都如此安宁</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="B491" t="inlineStr">
         <is>
-          <t>arrival.accept.04</t>
+          <t>arrival.refuse.01.06</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>不不不，我当然相信你。只是有点激动，谢谢，谢谢你！阿黛尔眼角的泪还未干，脸上却已洋溢着笑容欢迎来到沸点咖啡店！新任店长！</t>
+          <t>王都后来发生的那些离奇的故事，也与我再没有关系</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="B492" t="inlineStr">
         <is>
-          <t>arrival.accept.05</t>
+          <t>arrival.refuse.01.07</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>跟我走吧，我带你了解下我们咖啡店现在的状况。</t>
+          <t>就这样度过了一生</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="B493" t="inlineStr">
         <is>
-          <t>arrival.accept.06</t>
+          <t>arrival.refuse.01.08</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>阿黛尔领着我向柜台走去</t>
+          <t>未开始就已结束</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="B494" t="inlineStr">
         <is>
-          <t>arrival.accept.07</t>
+          <t>arrival.refuse.01.09</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>正当我踏出脚步时，一道寒意从背后传来，似有目光在那阴影中盯着我</t>
+          <t>要重新做出抉择吗？</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="B495" t="inlineStr">
         <is>
-          <t>arrival.accept.08</t>
+          <t>MA70.10.06-S1-3.1</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>我猛然回头，却只看到那些陌生的脸，他们在街道上来去，不曾对我有所停留</t>
+          <t>重新抉择</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="B496" t="inlineStr">
         <is>
-          <t>arrival.accept.09</t>
+          <t>MA70.10.06-S1-3.2</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>那股骇人的恶意，似是发现了什么，收敛了身形，隐匿在涌动的人潮中</t>
+          <t>就此别离</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="B497" t="inlineStr">
         <is>
-          <t>arrival.accept.10</t>
+          <t>arrival.accept.01.01</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>店长？没事吧？</t>
+          <t>好吧，我愿意尝试一下。</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="B498" t="inlineStr">
         <is>
-          <t>arrival.accept.11</t>
+          <t>arrival.accept.01.02</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>没事，刚来王都对很多事情不习惯而已，我们进去吧。</t>
+          <t>真......真的吗？</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="B499" t="inlineStr">
         <is>
-          <t>arrival.accept.12</t>
+          <t>arrival.accept.01.03</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
+          <t>当然是真的。你不相信的话，那不如我就直接跑路？</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>arrival.accept.01.04</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>不不不，我当然相信你。只是有点激动，谢谢，谢谢你！</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>arrival.accept.01.05</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>阿黛尔眼角的泪还未干，脸上却已洋溢着笑容</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>arrival.accept.01.06</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>欢迎来到沸点咖啡店！新任店长！</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>arrival.accept.01.07</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>跟我走吧，我带你了解下我们咖啡店现在的状况。</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>arrival.accept.01.08</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>阿黛尔领着我向柜台走去</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>arrival.accept.02.01</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>正当我踏出脚步时，一道寒意从背后传来，似有目光在那阴影中盯着我</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>arrival.accept.02.02</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>我猛然回头，却只看到那些陌生的脸，他们在街道上来去，不曾对我有所停留</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>arrival.accept.02.03</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>那股骇人的恶意，似是发现了什么，收敛了身形，隐匿在涌动的人潮中</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>arrival.accept.02.04</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>店长？没事吧？</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>arrival.accept.02.05</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>没事，刚来王都对很多事情不习惯而已，我们进去吧。</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>arrival.accept.02.06</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
           <t>我跟着阿黛尔向店深处走去，消失在阴影之中</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>FirstArrivalAndPassiveChecksSpec.md</t>
         </is>
       </c>
     </row>

--- a/Assets/ConfigTables/Data/Shared/Text.xlsx
+++ b/Assets/ConfigTables/Data/Shared/Text.xlsx
@@ -1004,6 +1004,12 @@
     <author>D-church source</author>
     <author>C source map</author>
     <author>A-neutral source</author>
+    <author>E-church source routing</author>
+    <author>A-neutral preview</author>
+    <author>B-rose</author>
+    <author>D-church</author>
+    <author>A-neutral-formal</author>
+    <author>A05-neutral-reporter</author>
   </authors>
   <commentList>
     <comment ref="C511" authorId="0" shapeId="0">
@@ -11247,6 +11253,2462 @@
         <t>D:\桌面\文案\中立\MA70.10.18-S1.docx
 A-1018.s1-P097
 我望了一眼记者方才坐过的位置。桌上除了几枚铜币，就只剩下一圈浅淡的杯痕。</t>
+      </text>
+    </comment>
+    <comment ref="C2101" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P004
+由于咖啡馆昨天举办了活动，客流量渐渐变大，我和阿黛尔的工作甚至可以用繁忙来形容。这样的热闹延续到了今天，直到中午时分人流量才减少，我们终于可以获得片刻的歇息了。</t>
+      </text>
+    </comment>
+    <comment ref="C2102" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P006
+一名中年男人出现，在离我最近的吧台座位坐下</t>
+      </text>
+    </comment>
+    <comment ref="C2103" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P008
+{playername}：「您好，欢迎光临沸点咖啡馆！」</t>
+      </text>
+    </comment>
+    <comment ref="C2104" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P009
+客人：（#平静）「你好。」</t>
+      </text>
+    </comment>
+    <comment ref="C2105" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P010
+{playername}：「先生，请问您想喝点什么呢？店内的咖啡目前广受好评呢。」</t>
+      </text>
+    </comment>
+    <comment ref="C2106" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P011
+客人：（#平静）「是吗，那来一杯经典的无糖黑咖啡。」</t>
+      </text>
+    </comment>
+    <comment ref="C2107" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P012
+{playername}：「好的，请稍等片刻。」</t>
+      </text>
+    </comment>
+    <comment ref="C2108" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P014
+客人：（#平静）「还不错。」</t>
+      </text>
+    </comment>
+    <comment ref="C2109" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P015
+{playname}：「谢谢您的肯定！请慢慢品尝。」</t>
+      </text>
+    </comment>
+    <comment ref="C2110" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P017
+暂时没有更多客人了，正好趁闲暇时放松一下吧</t>
+      </text>
+    </comment>
+    <comment ref="C2111" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P018
+不知道下午客流量怎么样，一旦忙起来就觉得时间过得飞快，不过这也意味着叔叔交给我的咖啡馆逐渐走上正途了。</t>
+      </text>
+    </comment>
+    <comment ref="C2112" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P019
+说起咖啡馆，没想到背后竟然和一些神秘组织有关系，感觉被牵扯进了很不得了的事件中。</t>
+      </text>
+    </comment>
+    <comment ref="C2113" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P020
+不知道是不是我的错觉，总觉得这位客人一直在看着我。是对咖啡不满意吗，或者是我今天穿的不对劲？</t>
+      </text>
+    </comment>
+    <comment ref="C2114" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P021
+他看起来也像是一个工人，今天来的工人怎么这么多，但他应该不会是神秘人那边派来的人吧？好在意，要不问一下吧。</t>
+      </text>
+    </comment>
+    <comment ref="C2115" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P023
+暂时没有更多客人了，正好趁闲暇时放松一下吧。</t>
+      </text>
+    </comment>
+    <comment ref="C2116" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P024
+不知道下午客流量怎么样，一旦忙起来就觉得时间过得飞快，不过这也意味着叔叔交给我的咖啡馆逐渐走上正途了。</t>
+      </text>
+    </comment>
+    <comment ref="C2117" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P025
+说起咖啡馆，没想到其居然和一些说不清的组织有所牵扯，感觉被牵扯进了很不得了的事件中。</t>
+      </text>
+    </comment>
+    <comment ref="C2118" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P026
+这位客人看起来也像是一个工人，今天的来的工人怎么这么多，但他应该不会是神秘人那边派来的人吧？好在意，要不问一下吧。</t>
+      </text>
+    </comment>
+    <comment ref="C2119" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P027
+{playername}：「先生，请问您对咖啡有什么建议吗？咖啡馆重新开业，我们希望能在客人们的建议下进一步提高！如果有想法但是不好意思直接说，也可以通过写信的方式告诉我们，您瞧，我们上午刚收到一封顾客送来的建议信呢。」</t>
+      </text>
+    </comment>
+    <comment ref="C2120" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P029
+我一边出示装着信的信封，一边假装不经意地盯着他</t>
+      </text>
+    </comment>
+    <comment ref="C2121" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P030
+他没有多看信一眼，只是看着我</t>
+      </text>
+    </comment>
+    <comment ref="C2122" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P031
+客人：（#平静）「不，不，没有任何意见。」放下咖啡「店长，我有一个问题想问你。」</t>
+      </text>
+    </comment>
+    <comment ref="C2123" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P031
+客人：（#平静）「不，不，没有任何意见。」放下咖啡「店长，我有一个问题想问你。」</t>
+      </text>
+    </comment>
+    <comment ref="C2124" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P032
+{playername}：「啊，好的，先生，您请问。」</t>
+      </text>
+    </comment>
+    <comment ref="C2125" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P033
+他对信没有任何反应，看来并不是神秘人那边派来的人</t>
+      </text>
+    </comment>
+    <comment ref="C2126" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P034
+或许只是个普通工人吧</t>
+      </text>
+    </comment>
+    <comment ref="C2127" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P035
+客人：（#疑惑）「王城中，甚至圣徒街上都并不只有一家咖啡馆，但是它们有些并不向普通平民开放，而我看见各阶层的人民都可以自由进入你们的店中。您是出于怎样的考虑呢？」</t>
+      </text>
+    </comment>
+    <comment ref="C2128" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P037
+①「只要能够赚钱就好，我们并不在乎客人的身份。我的叔叔杜瓦尔和前几任店长也是这样做的。将人划分三六九等是政治家的思想，却是和商人无关的。」[王庭-教会倾向+0]</t>
+      </text>
+    </comment>
+    <comment ref="C2129" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P038
+②「我只是想看见客人喝到我做的咖啡之后露出满意的笑容，这样就已经足够了，别的因素不是我要考虑的。」[王庭-教会倾向+0]</t>
+      </text>
+    </comment>
+    <comment ref="C2130" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P039
+③「我认为咖啡馆只面向部分人群开放本身就是错误的，其应当是面向普罗大众而存在的，不应以政治地位、经济实力等原因而将部分人拒之门外。我的叔叔杜瓦尔和前几任店长也是这样做的，我延续着他们的精神。」[王庭-教会倾向-1]</t>
+      </text>
+    </comment>
+    <comment ref="C2131" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P041
+客人：（#痛苦）「好的，我明白了。我之前是一名工人，生活在圣西尔万郊区，但是前段时间不幸在工作中受伤，成为了跛脚。唉，许多工厂都因为这点而排斥我。我近日一直为此感到烦忧，昨日听说圣徒街的沸点咖啡馆重新开业了，味道不错且面向大众开放，我实在感到好奇，所以今日特地前来。」</t>
+      </text>
+    </comment>
+    <comment ref="C2132" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P042
+顺着他的话我不由得认真打量起面前这个男子</t>
+      </text>
+    </comment>
+    <comment ref="C2133" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P043
+眼角周围有淡淡的皱纹，年纪并不小了，身上隐隐传来一阵烟味。或许是最近郁闷时常抽。</t>
+      </text>
+    </comment>
+    <comment ref="C2134" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P044
+但是整体打理得很整齐，眼神也透露出坚毅，看起来是一个对自身和生活有一定追求的人。</t>
+      </text>
+    </comment>
+    <comment ref="C2135" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P045
+{playername}：「这实在是我们的荣幸，先生。希望这杯咖啡能让您感到些许慰藉。」</t>
+      </text>
+    </comment>
+    <comment ref="C2136" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P046
+客人：（#疑惑）「好的。店长，您听闻前几日埃利昂公爵和教会的人在旧城区和圣西尔万郊区救济贫民的事情了吗？」</t>
+      </text>
+    </comment>
+    <comment ref="C2137" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P047
+{playername}：「有所耳闻。」</t>
+      </text>
+    </comment>
+    <comment ref="C2138" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P048
+客人：（#兴奋）「很高兴您有所了解。我那天就在被救济的队伍中，这是我最近感受过的最大的善意了，那粥虽然并不算得上十分美味，但足以饱腹了。虽然当下百姓的生活困难，没想到王庭和教会还是有一些有理想和良心的人为我们这些人而奔走着。」</t>
+      </text>
+    </comment>
+    <comment ref="C2139" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P050
+①「很高兴得知这件事，我刚来到此地，没想到上层还有埃利昂公爵这样的人物。」</t>
+      </text>
+    </comment>
+    <comment ref="C2140" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P051
+②「很高兴得知这件事，但是我相当怀疑王庭和教会中真的存在这样的人吗？」</t>
+      </text>
+    </comment>
+    <comment ref="C2141" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P052
+③「很高兴得知这件事，希望百姓的生活能过得越来越好。」</t>
+      </text>
+    </comment>
+    <comment ref="C2142" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P054
+客人：（#兴奋）「正是如此，店长。您不知道昨天的盛况……」</t>
+      </text>
+    </comment>
+    <comment ref="C2143" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P057
+他突然眯着眼睛打量了我一下</t>
+      </text>
+    </comment>
+    <comment ref="C2144" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P058
+客人：（#思索）「店长，您不相信吗？埃利昂公爵他们施粥是实实在在发生的事。」</t>
+      </text>
+    </comment>
+    <comment ref="C2145" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P059
+我感到他的态度冷却了一些</t>
+      </text>
+    </comment>
+    <comment ref="C2146" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P060
+{playername}：「不，先生，我相信这一点。我只是……算了，你当我未曾说过吧。」</t>
+      </text>
+    </comment>
+    <comment ref="C2147" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P061
+客人：（#平静）「好的，您不要紧张，我只是看见您觉得亲切，忍不住多聊了两句。我觉得王庭和教会并非全然糟糕透顶的……」</t>
+      </text>
+    </comment>
+    <comment ref="C2148" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P064
+他好像对我的回答并不满意，皱了皱眉</t>
+      </text>
+    </comment>
+    <comment ref="C2149" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P065
+客人：（#平静）「好吧……」</t>
+      </text>
+    </comment>
+    <comment ref="C2150" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P067
+他似乎还想说话，但此时新的客人走近了吧台</t>
+      </text>
+    </comment>
+    <comment ref="C2151" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P068
+客人：（#平静）「一不注意，竟然已经这个点了，我还需要去找找有没有我能盛任的工作。感谢您的咖啡，有机会我会再来拜访的。」</t>
+      </text>
+    </comment>
+    <comment ref="C2152" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P069
+{playername}：「再见，先生！祝您能早日找到一个满意的工作。」</t>
+      </text>
+    </comment>
+    <comment ref="C2153" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P070
+他放下咖啡，站起来离开，这时我才发现他的左脚确实行走起来不太便利</t>
+      </text>
+    </comment>
+    <comment ref="C2154" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P071
+他的身影越来越远，随着咖啡馆的门一开一闭，我便再也看不见他的身影了</t>
+      </text>
+    </comment>
+    <comment ref="C2155" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P073
+真是不容易</t>
+      </text>
+    </comment>
+    <comment ref="C2156" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P074
+我在心中叹口气</t>
+      </text>
+    </comment>
+    <comment ref="C2157" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
+church.1014.s2.P075
+然后快速转换思绪，面对客人新的要求，开启了新的工作。</t>
+      </text>
+    </comment>
+    <comment ref="C2158" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P003
+今天咖啡店的生意也相当不错</t>
+      </text>
+    </comment>
+    <comment ref="C2159" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P004
+我正在为客人制作咖啡时，突然听见一阵嘈杂的脚步声</t>
+      </text>
+    </comment>
+    <comment ref="C2160" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P006
+然后是阿黛尔同步响起的惊呼声</t>
+      </text>
+    </comment>
+    <comment ref="C2161" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P007
+阿黛尔·米尼耶：（#迷惑）「天呐，教会监察司的人？{playername}店长！{playername}店长！」</t>
+      </text>
+    </comment>
+    <comment ref="C2162" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P008
+我回过头，看见一群穿着统一制式服装的人</t>
+      </text>
+    </comment>
+    <comment ref="C2163" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P009
+「教会监察司」，刚才阿黛尔好像这样称呼着他们</t>
+      </text>
+    </comment>
+    <comment ref="C2164" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P010
+他们站定在咖啡馆中，其中一个看起来像领头的人则缓步站定在我面前</t>
+      </text>
+    </comment>
+    <comment ref="C2165" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P012
+我面前的客人惊慌失措地在我们之间来回转着，但是不敢有所动静</t>
+      </text>
+    </comment>
+    <comment ref="C2166" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P013
+疑似领头的人：（#迷惑）「你就是{playername}，沸点咖啡馆的现任店长？」</t>
+      </text>
+    </comment>
+    <comment ref="C2167" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P014
+{playername}：「是的。」</t>
+      </text>
+    </comment>
+    <comment ref="C2168" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P015
+疑似领头的人：（#平静）「我们是教会监察司，今日奉命前来圣徒街搜查。我是今日负责带队的监察官，希望你能认真配合调查，不然的话——」</t>
+      </text>
+    </comment>
+    <comment ref="C2169" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P016
+他未说完，但配合着他凶狠的目光，在场的人都对这未尽的话心知肚明</t>
+      </text>
+    </comment>
+    <comment ref="C2170" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P017
+我的大脑急速运转着</t>
+      </text>
+    </comment>
+    <comment ref="C2171" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P018
+教会监察司为什么会来圣徒街搜查？商铺经营不归监察司管吧？哦对了，好像听谁提过前几日街头有人散布修改「王选者」法律的消息……只有这个可能了。不过这和我也没什么大关系，随机应对即可吧。</t>
+      </text>
+    </comment>
+    <comment ref="C2172" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P020
+①「好吧，但是能否请小心对待店中的客人和设备，我们还要继续营业的。」</t>
+      </text>
+    </comment>
+    <comment ref="C2173" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P021
+②「我们咖啡馆正大光明，你们可以随意搜查。但是能否请小心对待店中的客人和设备，我们还要继续营业的。」</t>
+      </text>
+    </comment>
+    <comment ref="C2174" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P022
+③「如果我不同意会怎么样呢？」</t>
+      </text>
+    </comment>
+    <comment ref="C2175" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P024
+监察官：（#不屑）「哼，用不着你来指导工作。」「各人员注意，仔细搜查，不要放过任何一个角落。」</t>
+      </text>
+    </comment>
+    <comment ref="C2176" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P027
+我们隔着吧台看着对方的眼睛对峙，谁也不肯服输，许久他先移开目光并缓慢开口</t>
+      </text>
+    </comment>
+    <comment ref="C2177" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P028
+监察官：（#平静）「哼，年轻人，我很欣赏你的勇气，但建议你要记得区分勇敢和鲁莽。」「今日是必定要开展检查的。各人员注意，仔细搜查，不要放过任何一个角落。」</t>
+      </text>
+    </comment>
+    <comment ref="C2178" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P030
+我们隔着吧台看着对方的眼睛对峙，谁也不肯服输，最终我感到他身上的威严压过了我，我率先移开目光</t>
+      </text>
+    </comment>
+    <comment ref="C2179" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P031
+监察官：（#不屑）「年轻人，我想你是刚来到圣诺特，还不太了解情况，我们的搜查不需要你的同意。」「现在碍于你的态度，我可能要采取一些特别措施了，来人。」</t>
+      </text>
+    </comment>
+    <comment ref="C2180" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P032
+两个穿着制式服装的人从两边走上前来，将我从吧台中推出来，一左一右地扣押着我</t>
+      </text>
+    </comment>
+    <comment ref="C2181" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P033
+监察官：（#平静）「现在可以配合检查了吧，店长。」「各人员注意，仔细搜查，不要放过任何一个角落。」</t>
+      </text>
+    </comment>
+    <comment ref="C2182" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P035
+众监察员：「是。」</t>
+      </text>
+    </comment>
+    <comment ref="C2183" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P036
+他们四下分散开来，我看见他们的身影在大堂中忙碌着，甚至对顾客开展了简短的问询，部分顾客不堪其扰趁乱离开了。</t>
+      </text>
+    </comment>
+    <comment ref="C2184" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P037
+唉，不知道会不会影响以后的生意。</t>
+      </text>
+    </comment>
+    <comment ref="C2185" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P038
+突然想起神秘人给我留下的那封信好像被我顺手放在了吧台的抽屉中，密信他们看不懂应该不要紧……但是我该如何解释呢……</t>
+      </text>
+    </comment>
+    <comment ref="C2186" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P039
+然而怕什么来什么。很快他们便搜查到了吧台区域，在我如鼓擂的心跳声中他们在抽屉中找到了那封信，并递交给了监察官。</t>
+      </text>
+    </comment>
+    <comment ref="C2187" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P040
+监察官打开那封信看了看，然后走到我面前</t>
+      </text>
+    </comment>
+    <comment ref="C2188" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P041
+监察官：（#思索）「解释一下吗，{playername}店长？这封信上写的是什么，告诉我。」</t>
+      </text>
+    </comment>
+    <comment ref="C2189" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P044
+①「这是我们内部每日记录进货、出账的账单，为了节省时间而简写为这种形式。」（语言检定）</t>
+      </text>
+    </comment>
+    <comment ref="C2190" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P045
+②「这不过我的一封私人信件，监察司奉命搜查商铺，可没有资格逼问一封私人信件写了什么。」（勇气检定）</t>
+      </text>
+    </comment>
+    <comment ref="C2191" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P046
+③「我想长官你们是来搜查与「王选者」法律相关的吧，这不过一封我的私人信件能有什么关系呢？」（智慧检定）</t>
+      </text>
+    </comment>
+    <comment ref="C2192" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P047
+④「这不过是一封普通的私人信件，我看不出有什么被怀疑的必要。长官，您不会是早就对我有所怀疑吧？」（知觉检定）</t>
+      </text>
+    </comment>
+    <comment ref="C2193" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P049
+监察官：（#思索）「账单？那你详细给我讲讲这个账单的构成。」</t>
+      </text>
+    </comment>
+    <comment ref="C2194" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P051
+我快速回忆了一下信上的数字，然后不疾不徐地开口</t>
+      </text>
+    </comment>
+    <comment ref="C2195" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P052
+{playername}：「这些数字代表着店里咖啡豆、设备、餐具等物品的购买量、支出金额、每日消耗量、待购买量等数据，我叔叔当店长时就立下了这样的规矩，后面代代传承。」「这本来是我们的商业机密，但是长官你都发问了，我只能悉数奉告了。」</t>
+      </text>
+    </comment>
+    <comment ref="C2196" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P053
+监察官边听着我的讲述边试图理解信上的数字</t>
+      </text>
+    </comment>
+    <comment ref="C2197" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P054
+监察官：（#思索）「哼，听起来倒是有鼻子有眼。」</t>
+      </text>
+    </comment>
+    <comment ref="C2198" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P055
+他低头又看了一遍信纸，眉头紧皱，却没有从中找到能够反驳我的证据，他又盯着我看了片刻，最终将信纸递还给我。</t>
+      </text>
+    </comment>
+    <comment ref="C2199" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P056
+监察官：（#平静）「暂时没有证据证明这封信与我们搜查的东西有关。收好你的东西。」</t>
+      </text>
+    </comment>
+    <comment ref="C2200" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P057
+我接过信纸，尽量平静地点了点头。</t>
+      </text>
+    </comment>
+    <comment ref="C2201" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P059
+我努力组织着语言，试图把信上的内容解释清楚，却发现自己越说越混乱。</t>
+      </text>
+    </comment>
+    <comment ref="C2202" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P060
+{playername}：「这……这是以前店里留下的账单记录方式，应该是采购……或者别的什么记录，具体内容我也不太清楚。」</t>
+      </text>
+    </comment>
+    <comment ref="C2203" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P061
+监察官的表情逐渐变得严厉</t>
+      </text>
+    </comment>
+    <comment ref="C2204" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P062
+监察官：（#思索）「你自己的店里发现的信，你却连内容都说不清楚？」</t>
+      </text>
+    </comment>
+    <comment ref="C2205" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P063
+我张了张嘴，一时找不到更合适的说辞。</t>
+      </text>
+    </comment>
+    <comment ref="C2206" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P064
+监察官将信纸收了起来，冷冷地看着我。</t>
+      </text>
+    </comment>
+    <comment ref="C2207" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P065
+监察官：）#平静「你的解释前后矛盾。带走，等候进一步调查。」</t>
+      </text>
+    </comment>
+    <comment ref="C2208" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P067
+监察官：（#思索）「私人信件？我看见的可是写着一串数字的不明信件。」</t>
+      </text>
+    </comment>
+    <comment ref="C2209" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P068
+我再次对上他探究的眼睛</t>
+      </text>
+    </comment>
+    <comment ref="C2210" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P070
+我毫不畏惧地直视着他，没有试图争抢那封信，也没有慌张，一字一句地说道</t>
+      </text>
+    </comment>
+    <comment ref="C2211" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P071
+{playername}；「您可以搜查，也可以暂时扣下这封信。但在没有证据之前，请不要把无法解读的信件直接说成不法密信。这不过是前任店长给我留下的关于咖啡馆内部账单。」</t>
+      </text>
+    </comment>
+    <comment ref="C2212" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P072
+咖啡馆内安静了下来，所有人都在看着我们</t>
+      </text>
+    </comment>
+    <comment ref="C2213" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P073
+我继续说道</t>
+      </text>
+    </comment>
+    <comment ref="C2214" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P074
+{playername}：「如果您认为我有问题，可以按照教会的程序调查。我会配合，但不会承认自己没有做过的事。」</t>
+      </text>
+    </comment>
+    <comment ref="C2215" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P075
+监察官的目光在我脸上停留了许久，像是在判断我究竟是虚张声势，还是确实问心无愧。</t>
+      </text>
+    </comment>
+    <comment ref="C2216" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P076
+最终他冷哼一声，将信纸拍在桌上。</t>
+      </text>
+    </comment>
+    <comment ref="C2217" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P077
+监察官：（#平静）「哼，没有证据，我们也不会仅凭一封无从解读的信抓人。收好你的信，但是如果之后我们发现有什么问题，你等着被传唤吧。」</t>
+      </text>
+    </comment>
+    <comment ref="C2218" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P078
+{playername}：「我明白。」</t>
+      </text>
+    </comment>
+    <comment ref="C2219" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P080
+我想要反驳，却被监察官凌厉的目光压得说不出话来。</t>
+      </text>
+    </comment>
+    <comment ref="C2220" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P081
+{playername}：「这……这是前任店长给我留下的关于咖啡馆内部账单的信件……但是……我也不知道上面具体是什么意思……」</t>
+      </text>
+    </comment>
+    <comment ref="C2221" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P082
+监察官：（#思索）「不知道具体意思？那么你怎么知道这是咖啡馆内部账单？」</t>
+      </text>
+    </comment>
+    <comment ref="C2222" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P083
+我张张嘴又闭上，他充满威严与怀疑的目光刺痛了我，不敢再继续辩解</t>
+      </text>
+    </comment>
+    <comment ref="C2223" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P084
+监察官看着我的沉默，像是已经得出了自己的判断。</t>
+      </text>
+    </comment>
+    <comment ref="C2224" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P085
+监察官：（#平静）「那正好，信带走，回去让我们监察司的人好好领会一下你所谓的「私人信件」。至于你，随我们走一趟。」</t>
+      </text>
+    </comment>
+    <comment ref="C2225" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P088
+监察官：（#思索）「你倒是很清楚我们为何而来。」</t>
+      </text>
+    </comment>
+    <comment ref="C2226" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P089
+我指了指他手中的信纸</t>
+      </text>
+    </comment>
+    <comment ref="C2227" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P090
+{playername}：「但这只是一封私人信件，是前任店长给我留下的之前店铺的账单，没有提到「王选者」，也没有任何与法律修改相关的内容，只不过是一串普通数字罢了。而且我听闻前几天是在民间宣扬「王选者」，如果对方采取这样隐晦的方式，并不能达到宣传的目的吧。」</t>
+      </text>
+    </comment>
+    <comment ref="C2228" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P091
+监察官听闻多看了我两眼</t>
+      </text>
+    </comment>
+    <comment ref="C2229" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P092
+监察官：（#思索）「你倒是想得挺清楚。不过你说得没错，目前确实没有证据证明这封信与那件事有关。」</t>
+      </text>
+    </comment>
+    <comment ref="C2230" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P093
+他又沉默了片刻，最终选择将信纸递给身旁的监察员，几名监察员低声讨论后也无法确认其中有什么异常。</t>
+      </text>
+    </comment>
+    <comment ref="C2231" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P094
+监察官：（#平静）「信你收好。至于你，继续留在店里接受调查，不得擅自离开圣徒街。」</t>
+      </text>
+    </comment>
+    <comment ref="C2232" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P096
+监察官：（#思索）「你倒是很清楚我们为何而来。」</t>
+      </text>
+    </comment>
+    <comment ref="C2233" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P097
+我试图继续说出一些合理而又道理的理由来摆脱嫌疑，但脑中一片混乱，只能勉强找出几个听起来合理的词。</t>
+      </text>
+    </comment>
+    <comment ref="C2234" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P098
+{playername}：「这封信……是我与前任店长沟通的私人信件……上面写的东西应该是店铺内部经营状况，可能就是之前他们订购咖啡豆和机器设备的开销……没什么重要的。怎么看都与你们要查的东西无关吧……」</t>
+      </text>
+    </comment>
+    <comment ref="C2235" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P099
+话一出口，我便意识到自己的解释漏洞百出。</t>
+      </text>
+    </comment>
+    <comment ref="C2236" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P100
+监察官：（#思索）「可能？应该？{playername}店长，你连自己要解释什么都不知道。」</t>
+      </text>
+    </comment>
+    <comment ref="C2237" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P101
+我试图继续补充，却只能让事情变得更加糟糕。</t>
+      </text>
+    </comment>
+    <comment ref="C2238" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P102
+监察官：（#平静）「你的说辞无法令人信服。」「先把人带走，信件作为证物收存。」</t>
+      </text>
+    </comment>
+    <comment ref="C2239" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P104
+我注意到监察官虽然拿着信纸，却没有认真揣摩上面的数字含义，反而仔细观察着我的反应</t>
+      </text>
+    </comment>
+    <comment ref="C2240" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P106
+我看出来了，他并没有读懂信上的内容，他在意的是我是否会因此露出破绽</t>
+      </text>
+    </comment>
+    <comment ref="C2241" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P107
+我让自己的语气尽量平稳，目光坦荡地对上监察官探究的眼神</t>
+      </text>
+    </comment>
+    <comment ref="C2242" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P108
+{playernanem}：「这不过是前任店长给我留下的店铺内部的账单罢了，这样的单子我这还有很多。不知道长官您要搜查的是什么，但想必是与国家大事相关，我想不会是这种写了一串普通数字的私人信件吧。」</t>
+      </text>
+    </comment>
+    <comment ref="C2243" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P109
+监察官听了我话又探究地看了信纸两眼</t>
+      </text>
+    </comment>
+    <comment ref="C2244" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P110
+我趁势说道</t>
+      </text>
+    </comment>
+    <comment ref="C2245" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P111
+{playername}：「您可以把它带回去找人辨认。但我相信，无论如何解读，它都只是一张记录店铺经营状况的账单。」</t>
+      </text>
+    </comment>
+    <comment ref="C2246" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P112
+监察官看向身后的监察员。对方检查了信纸和抽屉，低声说了几句，似乎没有发现新的线索。</t>
+      </text>
+    </comment>
+    <comment ref="C2247" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P113
+监察官：（#平静）「……暂时按普通信件处理。你继续营业，但近期不要离开圣徒街。」</t>
+      </text>
+    </comment>
+    <comment ref="C2248" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P114
+{playernmae}：「我知道了。」</t>
+      </text>
+    </comment>
+    <comment ref="C2249" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P116
+我试图观察监察官的脸色以获取更多信息，却没能从他的神情中看出任何端倪。</t>
+      </text>
+    </comment>
+    <comment ref="C2250" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P117
+{playername}：「我不知道它是什么……或许是前任店长给我留下的信息吧……前任店长在店里留下了不少东西，我还没有一一检查。」</t>
+      </text>
+    </comment>
+    <comment ref="C2251" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P118
+监察官：（#平静）「你说自己没有检查过，却在我没有给你出示这封信具体内容的情况下说这是前任店长留下的。显然，你的解释站不住脚。」</t>
+      </text>
+    </comment>
+    <comment ref="C2252" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P119
+他似笑非笑地看着我</t>
+      </text>
+    </comment>
+    <comment ref="C2253" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P120
+我这才意识到，自己的话已经被对方抓住了漏洞。</t>
+      </text>
+    </comment>
+    <comment ref="C2254" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P121
+监察官示意监察员上前，将信纸递交给他，随后监察员将信纸收进一个文件袋中。</t>
+      </text>
+    </comment>
+    <comment ref="C2255" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P122
+监察官：（#平静）「带走。等你想清楚之后，再向我们解释。」</t>
+      </text>
+    </comment>
+    <comment ref="C2256" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P124
+很快，教会监察司的人离开了咖啡馆，前往圣徒街其他店铺里搜寻</t>
+      </text>
+    </comment>
+    <comment ref="C2257" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P125
+他们离开后，阿黛尔赶紧跑过来关切地询问我</t>
+      </text>
+    </comment>
+    <comment ref="C2258" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P126
+阿黛尔·米尼耶：（#激动）「{playername}店长，你刚才真实太厉害了！面对教会监察司的人还能如此镇定地面对！」</t>
+      </text>
+    </comment>
+    <comment ref="C2259" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P127
+听完阿黛尔的话我感到一丝无奈，原来刚才的我在她眼里是这样的吗</t>
+      </text>
+    </comment>
+    <comment ref="C2260" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P128
+我现在感到一丝后怕，如果刚才没有应对得当，现在的我是会被他们带走审问吗？</t>
+      </text>
+    </comment>
+    <comment ref="C2261" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P129
+幸好我事先有想好万一被发现应当如何应对，才逃过这一劫</t>
+      </text>
+    </comment>
+    <comment ref="C2262" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P130
+看来以后需要把这些东西隐藏得更加隐蔽才好。不，还是赶紧找个机会把信都给烧掉吧</t>
+      </text>
+    </comment>
+    <comment ref="C2263" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P131
+阿黛尔不休的话打断了我的思绪</t>
+      </text>
+    </comment>
+    <comment ref="C2264" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P132
+阿黛尔·米尼耶：（#悲伤）「不过刚才由于监察司的到来，好多顾客都离开了呢……不知道接下来生意会不会受到影响……」</t>
+      </text>
+    </comment>
+    <comment ref="C2265" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P133
+这时我才想起刚才被迫停留在我和监察司中间的倒霉顾客</t>
+      </text>
+    </comment>
+    <comment ref="C2266" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P134
+目前店里没有发现那位顾客的身影，或许是什么时候趁乱离开了吧</t>
+      </text>
+    </comment>
+    <comment ref="C2267" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P135
+店里的设备没有遭到损坏，看来监察司搜查的时候还是有分寸的</t>
+      </text>
+    </comment>
+    <comment ref="C2268" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P136
+今天发生了这样的事，未来几天还是低调点吧</t>
+      </text>
+    </comment>
+    <comment ref="C2269" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P137
+{playername}：「希望不会吧。阿黛尔，未来两天我们还是正常营业，但是低调一些。我担心再次引来什么大麻烦。」</t>
+      </text>
+    </comment>
+    <comment ref="C2270" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P138
+阿黛尔·米尼耶：（#开心）「我也正有此意呢，店长！」</t>
+      </text>
+    </comment>
+    <comment ref="C2271" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P139
+{playername}：「阿黛尔，振作精神，我们还要准备迎接接下来的客人呢！」</t>
+      </text>
+    </comment>
+    <comment ref="C2272" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P140
+阿黛尔·米尼耶：（#开心）「店长，你说得对！那我去门口继续招揽一下客人~」</t>
+      </text>
+    </comment>
+    <comment ref="C2273" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P141
+阿黛尔蹦蹦跳跳地离开了</t>
+      </text>
+    </comment>
+    <comment ref="C2274" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P142
+我趁机将几封信烧毁，然后若无其事地回到吧台</t>
+      </text>
+    </comment>
+    <comment ref="C2275" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P144
+不知道接下来会迎接怎样的挑战和危机呢……</t>
+      </text>
+    </comment>
+    <comment ref="C2276" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P147
+我在所有人的注视下被监察司的人带走了，离开咖啡馆前我最后看见的是阿黛尔满是担忧的脸</t>
+      </text>
+    </comment>
+    <comment ref="C2277" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P148
+他们会如何审问我呢？我要说什么呢？这封信涉及的密文是否会被他们觉察呢？</t>
+      </text>
+    </comment>
+    <comment ref="C2278" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P149
+带着万千思绪，我被带到了教会看守所中</t>
+      </text>
+    </comment>
+    <comment ref="C2279" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P150
+啊，从刚毕业的大学生到咖啡馆店长再到在押犯原来只需要一个月吗……</t>
+      </text>
+    </comment>
+    <comment ref="C2280" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P151
+我被分配进了一个单独的房间，等待监察司的检查结果</t>
+      </text>
+    </comment>
+    <comment ref="C2281" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
+church.1020.s1.P152
+我就此陷入了无尽的等待</t>
+      </text>
+    </comment>
+    <comment ref="C2282" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P006
+我被带到看守所后，已经见证了第三次日出。</t>
+      </text>
+    </comment>
+    <comment ref="C2283" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P007
+在这间狭小的拘押室里，我甚至开始怀念咖啡馆那张吱呀作响的旧椅子。</t>
+      </text>
+    </comment>
+    <comment ref="C2284" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P008
+不知道阿黛尔现在怎么样了，咖啡馆有没有正常营业……</t>
+      </text>
+    </comment>
+    <comment ref="C2285" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P010
+看守：⌈出来，有人要见你。⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2286" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P013
+监察官：⌈经过调查，我们没有发现你直接参与非法结社活动的证据。⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2287" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P014
+{playername}：⌈所以我可以离开了？⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2288" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P015
+监察官：⌈别急。那些密文的来源仍然不明，我们还需要你作出一些保证。⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2289" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P016
+监察官：⌈如果今后发现任何与乱党有关的情报，你必须向教会报告。⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2290" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P017
+{playername}：⌈……⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2291" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P018
+监察官：⌈你也可以拒绝。但调查结束前，我们恐怕不能放你走。⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2292" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P019
+他看了看桌上的文件，似乎在等待我的回答。</t>
+      </text>
+    </comment>
+    <comment ref="C2293" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P021
+①⌈既然没有犯罪证据，你们就没有理由继续拘押我。⌋（语言检定）</t>
+      </text>
+    </comment>
+    <comment ref="C2294" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P022
+②⌈或许我们可以商量一个更方便的解决办法。⌋（资金条件）</t>
+      </text>
+    </comment>
+    <comment ref="C2295" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P023
+③⌈既然如此，你们就继续调查吧。⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2296" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P025
+{playername}：⌈没有证据就继续拘押一位合法经营的店主，这恐怕也不符合教会的规定吧？⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2297" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P026
+监察官：⌈你是在质疑监察司的决定？⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2298" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P027
+{playername}：⌈我当然尊重教会的职责，但你刚刚也说了，调查没有发现我参与乱党的证据。⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2299" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P028
+{playername}：⌈况且，沸点咖啡馆在圣徒街经营了那么多年，应该不算一家完全没有人认识的店铺。⌋⌈你们可以向街坊邻居调查，也可以在之后继续观察咖啡馆的经营。但至少现在，没有必要让我继续待在这里。⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2300" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P029
+监察官：⌈嗯……⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2301" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P032
+监察官：⌈倒也有些道理。⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2302" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P033
+他沉思片刻，在文件上签了字。</t>
+      </text>
+    </comment>
+    <comment ref="C2303" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P034
+监察官：⌈好吧，你可以走了。但调查还没结束，今后记得配合监察司。⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2304" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P037
+监察官：⌈是否符合规定，恐怕还轮不到你来判断。带他回去。⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2305" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P040
+{playername}：⌈继续调查既耽误你们的时间，也耽误我的生意。或许有个对双方都方便的办法？⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2306" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P041
+我暗示了一下能够支付的金额。</t>
+      </text>
+    </comment>
+    <comment ref="C2307" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P042
+监察官抬起头，意味深长地看了我一眼。</t>
+      </text>
+    </comment>
+    <comment ref="C2308" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P043
+监察官：⌈你是沸点咖啡馆的店长是吧？一会儿我派人跟着你去，把钱打点清楚再说。⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2309" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P044
+{playername}：⌈好的，好的，当然可以。⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2310" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P045
+监察官：⌈不过我要这个数。⌋（数值待定）</t>
+      </text>
+    </comment>
+    <comment ref="C2311" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P046
+{playername}：⌈抢劫啊？⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2312" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P047
+监察官：⌈哎，看来你不乐意，那就只好多关几天咯！⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2313" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P048
+监察官：⌈嘶......看来你是个聪明人。既然没有发现犯罪证据，我们当然没有必要继续浪费时间。⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2314" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P054
+看来今天又得在这里过夜了。</t>
+      </text>
+    </comment>
+    <comment ref="C2315" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P055
+我靠在墙边，正想着阿黛尔会不会已经把我当成失踪人口，铁门却再次打开了。</t>
+      </text>
+    </comment>
+    <comment ref="C2316" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P057
+看守：⌈出来，你可以走了。⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2317" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P058
+{playername}：⌈啊？可是刚刚不是还说……⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2318" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P059
+看守：⌈上面送来了新的释放手续。你还想留下来不成？⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2319" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P060
+他将一份盖好印章的文件塞进我手中。</t>
+      </text>
+    </comment>
+    <comment ref="C2320" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P061
+上面清清楚楚地写着：「证据不足，准予释放。」</t>
+      </text>
+    </comment>
+    <comment ref="C2321" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P062
+怎么突然就证据不足了？</t>
+      </text>
+    </comment>
+    <comment ref="C2322" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P063
+不过，我当然没有理由拒绝。</t>
+      </text>
+    </comment>
+    <comment ref="C2323" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P065
+我看了看那张文件。</t>
+      </text>
+    </comment>
+    <comment ref="C2324" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P066
+上面的印章和其他文书没有什么区别。</t>
+      </text>
+    </comment>
+    <comment ref="C2325" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P067
+不过，在旁边的登记簿上，我的名字似乎被人重新填写过一次。</t>
+      </text>
+    </comment>
+    <comment ref="C2326" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P068
+原本的字迹已经被墨水覆盖，又用另一种笔迹写上了新的处理结果。</t>
+      </text>
+    </comment>
+    <comment ref="C2327" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P069
+而且，记录上标注的释放时间，似乎比我刚刚被带回牢房的时间还要早。</t>
+      </text>
+    </comment>
+    <comment ref="C2328" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P070
+……</t>
+      </text>
+    </comment>
+    <comment ref="C2329" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P071
+有人修改了我的拘押记录？</t>
+      </text>
+    </comment>
+    <comment ref="C2330" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P073
+{playername}：⌈请问，是谁批准释放我的？⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2331" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P074
+看守：⌈登记上写得很清楚，按照规定处理的。⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2332" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P075
+{playername}：⌈我是说，刚刚是谁来办理手续的？⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2333" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P076
+看守：⌈我哪知道？今天送过来的文件这么多。⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2334" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P077
+看守：⌈话怎么这么多？再问我就和上面说你不服命令，重新把你关进去。⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2335" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P078
+{playername}：⌈……⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2336" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P079
+算了。</t>
+      </text>
+    </comment>
+    <comment ref="C2337" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P080
+不管究竟是谁帮了我，现在最重要的事情，还是赶紧离开这个地方。</t>
+      </text>
+    </comment>
+    <comment ref="C2338" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P088
+{playername}：⌈我回来了！⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2339" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P089
+阿黛尔：（#迷惑）⌈……{playername}？⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2340" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P090
+她愣了一下，随即快步走来。</t>
+      </text>
+    </comment>
+    <comment ref="C2341" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P091
+阿黛尔：（#兴奋）⌈你终于回来了！⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2342" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P092
+阿黛尔：（#焦虑）⌈他们没有对你怎么样吧？⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2343" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P093
+{playername}：⌈没有没有，只是被关了几天。⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2344" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P094
+阿黛尔：（#焦虑）⌈这还叫没什么！我去问了好几次，他们都不肯告诉我什么时候放你回来。⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2345" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P095
+{playername}：⌈抱歉，让你担心了。⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2346" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P096
+阿黛尔：（#平静）⌈……回来就好。⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2347" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P097
+她替我拉开椅子。</t>
+      </text>
+    </comment>
+    <comment ref="C2348" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P098
+阿黛尔：（#思索）⌈不过，他们怎么突然愿意放人了？⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2349" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P101
+{playername}：⌈他们本来也没找到犯罪证据，我和监察官讲了讲道理，就把我放了。⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2350" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P102
+阿黛尔：（#开心）⌈那真是太好了，至少教会的人还愿意讲道理。⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2351" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P103
+阿黛尔：（#思索）⌈不过，既然他们已经盯上了咖啡馆，以后还是得小心。⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2352" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P105
+{playername}：⌈花了点钱，总算让他们同意放人了。⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2353" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P106
+阿黛尔：（#迷惑）⌈花钱？你是说……⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2354" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P107
+{playername}：⌈嘘！别说出来。⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2355" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P108
+阿黛尔：（#焦虑）⌈这些人真是……⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2356" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P109
+她叹了口气。</t>
+      </text>
+    </comment>
+    <comment ref="C2357" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P110
+{playername}：⌈你一会让把钱筹一下送过去。⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2358" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P111
+阿黛尔：（#生气）⌈我才不做这种事情呢！⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2359" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P112
+{playername}：⌈那行，一会儿我去干这脏活累活吧......⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2360" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P114
+{playername}：⌈说实话，我也不知道。他们本来还要继续调查，结果突然有人送来文件，说我可以走了。⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2361" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P115
+阿黛尔：（#迷惑）⌈突然有人送来文件？⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2362" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P116
+{playername}：⌈是啊，连看守都不知道怎么回事。真奇怪。⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2363" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P117
+阿黛尔似乎想到了什么，沉默了一会儿。</t>
+      </text>
+    </comment>
+    <comment ref="C2364" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P118
+阿黛尔：（#思索）⌈原来如此......⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2365" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P119
+{playername}：⌈你知道些什么？⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2366" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P120
+阿黛尔：（#焦虑）⌈啊？没有，我也只是猜测……⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2367" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P121
+{playername}：⌈猜测什么？⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2368" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P122
+阿黛尔：（#思索）⌈以前杜瓦尔先生经营咖啡馆的时候，认识不少人。有些人虽然不方便公开露面，但很重视这家店。⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2369" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P123
+阿黛尔：（#思索）⌈如果他们知道你被教会带走了，或许不会坐视不管。⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2370" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P124
+{playername}：⌈你是说，有人暗中帮了我？⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2371" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P125
+阿黛尔：（#平静）⌈只是猜测而已，我也不确定。⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2372" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P126
+她低头整理起桌上的餐具，似乎不打算继续这个话题。</t>
+      </text>
+    </comment>
+    <comment ref="C2373" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P127
+阿黛尔：（#思索）⌈不过，如果真是他们……看来那些人还没有忘记这里。⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2374" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P128
+{playername}：⌈那些人？⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2375" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P129
+阿黛尔：（#尴尬）⌈没什么。你才刚回来，先休息吧。⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2376" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P131
+阿黛尔：（#开心）⌈总之，欢迎回来，店长先生。⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2377" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P132
+{playername}：⌈嗯，我回来了。⌋</t>
+      </text>
+    </comment>
+    <comment ref="C2378" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P133
+我靠在椅背上，终于松了口气。</t>
+      </text>
+    </comment>
+    <comment ref="C2379" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P134
+咖啡馆似乎什么都没有改变。</t>
+      </text>
+    </comment>
+    <comment ref="C2380" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P135
+不过我的心态已经完全不同，</t>
+      </text>
+    </comment>
+    <comment ref="C2381" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P136
+在监牢里度过的三天却让我后背发凉。</t>
+      </text>
+    </comment>
+    <comment ref="C2382" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P137
+我这次能因信的的事情被抓进去，下一次又会因为什么遭遇不测。</t>
+      </text>
+    </comment>
+    <comment ref="C2383" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P138
+三天前，教会监察司的人突然闯进咖啡馆，将我带走。</t>
+      </text>
+    </comment>
+    <comment ref="C2384" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P139
+三天后，我终于回到了这里。</t>
+      </text>
+    </comment>
+    <comment ref="C2385" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P140
+但那几封密文仍然被扣押在教会手中。</t>
+      </text>
+    </comment>
+    <comment ref="C2386" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P141
+而且，在离开看守所之前，他们还专门提醒我：</t>
+      </text>
+    </comment>
+    <comment ref="C2387" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P142
+如果发现有关乱党的情报，必须向教会报告。</t>
+      </text>
+    </comment>
+    <comment ref="C2388" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P143
+……</t>
+      </text>
+    </comment>
+    <comment ref="C2389" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P144
+这算什么意思？</t>
+      </text>
+    </comment>
+    <comment ref="C2390" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P145
+今后要是那个神秘人再给我送来几封信，难道我还得主动跑去监察司告诉他们？</t>
+      </text>
+    </comment>
+    <comment ref="C2391" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P146
+开什么玩笑。</t>
+      </text>
+    </comment>
+    <comment ref="C2392" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P147
+可是，如果不这么做……</t>
+      </text>
+    </comment>
+    <comment ref="C2393" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P148
+我抬起头，看向正在厨房里忙碌的阿黛尔。</t>
+      </text>
+    </comment>
+    <comment ref="C2394" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P149
+自从来到这家店，怪事就一个接着一个。</t>
+      </text>
+    </comment>
+    <comment ref="C2395" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P150
+王都圣诺特的漩涡下面究竟有多少骇人的存在？它们在谋划些什么？为什么我会被卷到这些事情里？我还能保护我和身边的人吗？</t>
+      </text>
+    </comment>
+    <comment ref="C2396" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P151
+三日关押积累下来的疲惫与巨大的思考量冲撞着我的思绪，</t>
+      </text>
+    </comment>
+    <comment ref="C2397" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
+church.1023.s1.P152
+我再也无力去支撑精神，倒在座椅上睡去......</t>
+      </text>
+    </comment>
+    <comment ref="C2398" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
+church.1023.s2.P005
+距离上次与监察官会面又过了不知多少天</t>
+      </text>
+    </comment>
+    <comment ref="C2399" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
+church.1023.s2.P006
+这段日子里我尝试与外界联系，却都失败了</t>
+      </text>
+    </comment>
+    <comment ref="C2400" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
+church.1023.s2.P007
+我所能接触到的只有这四方墙壁</t>
+      </text>
+    </comment>
+    <comment ref="C2401" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
+church.1023.s2.P008
+不知道今日是何日，不知道咖啡馆怎么样了，不知道阿黛尔怎么样了，不知道我离开之后神秘人是否还在接触咖啡馆……</t>
+      </text>
+    </comment>
+    <comment ref="C2402" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
+church.1023.s2.P009
+不知道……不知道……什么都不知道……</t>
+      </text>
+    </comment>
+    <comment ref="C2403" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
+church.1023.s2.P010
+我的意识在这种日子中渐渐模糊……</t>
+      </text>
+    </comment>
+    <comment ref="C2404" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
+church.1023.s2.P013
+沉寂和单调，是我牢狱生活的全部</t>
+      </text>
+    </comment>
+    <comment ref="C2405" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
+church.1023.s2.P014
+直到某一天我的世界出现了新的声音</t>
+      </text>
+    </comment>
+    <comment ref="C2406" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
+church.1023.s2.P016
+那是几个穿着制服的人，走进了关押我的房间内</t>
+      </text>
+    </comment>
+    <comment ref="C2407" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
+church.1023.s2.P017
+他们对着我说了一串话</t>
+      </text>
+    </comment>
+    <comment ref="C2408" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
+church.1023.s2.P018
+但由于脱离外界太久，意识模糊，我只能隐隐约约辨认出几个词，什么「革命」 「镇压」 「清算」……</t>
+      </text>
+    </comment>
+    <comment ref="C2409" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
+church.1023.s2.P019
+在我还未能理解这些词句的意思时</t>
+      </text>
+    </comment>
+    <comment ref="C2410" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
+church.1023.s2.P020
+我感到我被他们强行从地上拉了起来，被推动着向外走</t>
+      </text>
+    </comment>
+    <comment ref="C2411" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
+church.1023.s2.P021
+方墙以外的世界</t>
+      </text>
+    </comment>
+    <comment ref="C2412" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
+church.1023.s2.P022
+新鲜的空气</t>
+      </text>
+    </comment>
+    <comment ref="C2413" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
+church.1023.s2.P023
+曾经我渴求无数次的东西就这样呈现在我面前</t>
+      </text>
+    </comment>
+    <comment ref="C2414" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
+church.1023.s2.P024
+现下我却无暇顾及</t>
+      </text>
+    </comment>
+    <comment ref="C2415" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
+church.1023.s2.P025
+我不知道我会被他们带往哪里</t>
+      </text>
+    </comment>
+    <comment ref="C2416" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
+church.1023.s2.P026
+就这样走着，走着……</t>
+      </text>
+    </comment>
+    <comment ref="C2417" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
+church.1023.s2.P027
+这里是哪里？</t>
+      </text>
+    </comment>
+    <comment ref="C2418" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
+church.1023.s2.P028
+刑场？</t>
+      </text>
+    </comment>
+    <comment ref="C2419" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
+church.1023.s2.P029
+我要死了吗？</t>
+      </text>
+    </comment>
+    <comment ref="C2420" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
+church.1023.s2.P030
+为什么？</t>
+      </text>
+    </comment>
+    <comment ref="C2421" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
+church.1023.s2.P031
+为什么？为什么？为什么？为什么？为什么？</t>
+      </text>
+    </comment>
+    <comment ref="C2422" authorId="3" shapeId="0">
+      <text>
+        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
+church.1023.s2.P032
+带着这样的想法，我迎来了人生的终点。</t>
+      </text>
+    </comment>
+    <comment ref="B2426" authorId="6" shapeId="0">
+      <text>
+        <t>{
+  "scope": "E blocked configuration preparation"
+}</t>
+      </text>
+    </comment>
+    <comment ref="B2427" authorId="6" shapeId="0">
+      <text>
+        <t>{
+  "scope": "E blocked configuration preparation"
+}</t>
+      </text>
+    </comment>
+    <comment ref="B2428" authorId="6" shapeId="0">
+      <text>
+        <t>{
+  "scope": "E blocked configuration preparation"
+}</t>
+      </text>
+    </comment>
+    <comment ref="B2429" authorId="6" shapeId="0">
+      <text>
+        <t>{
+  "scope": "E blocked configuration preparation"
+}</t>
+      </text>
+    </comment>
+    <comment ref="B2430" authorId="6" shapeId="0">
+      <text>
+        <t>{
+  "scope": "E blocked configuration preparation"
+}</t>
+      </text>
+    </comment>
+    <comment ref="B2431" authorId="6" shapeId="0">
+      <text>
+        <t>{
+  "scope": "E blocked configuration preparation"
+}</t>
+      </text>
+    </comment>
+    <comment ref="B2432" authorId="6" shapeId="0">
+      <text>
+        <t>{
+  "scope": "E blocked configuration preparation"
+}</t>
+      </text>
+    </comment>
+    <comment ref="B2433" authorId="6" shapeId="0">
+      <text>
+        <t>{
+  "scope": "E blocked configuration preparation"
+}</t>
+      </text>
+    </comment>
+    <comment ref="B2434" authorId="6" shapeId="0">
+      <text>
+        <t>{
+  "scope": "E blocked configuration preparation"
+}</t>
+      </text>
+    </comment>
+    <comment ref="B2435" authorId="6" shapeId="0">
+      <text>
+        <t>{
+  "scope": "E blocked configuration preparation"
+}</t>
+      </text>
+    </comment>
+    <comment ref="B2436" authorId="6" shapeId="0">
+      <text>
+        <t>{
+  "scope": "E blocked configuration preparation"
+}</t>
+      </text>
+    </comment>
+    <comment ref="B2437" authorId="7" shapeId="0">
+      <text>
+        <t>{"batch": "A05", "source_map_line": "1447b2784eca6638ccf67a572ba8863d0abd3b6db0e02bb6015bac2457ca108a"}</t>
+      </text>
+    </comment>
+    <comment ref="B2438" authorId="8" shapeId="0">
+      <text>
+        <t>B1016 source mapped; stops at P015; no completion or brewing</t>
+      </text>
+    </comment>
+    <comment ref="B2439" authorId="8" shapeId="0">
+      <text>
+        <t>B1016 source mapped; stops at P015; no completion or brewing</t>
+      </text>
+    </comment>
+    <comment ref="B2440" authorId="8" shapeId="0">
+      <text>
+        <t>B1012 source-map; result-free blocked construction</t>
+      </text>
+    </comment>
+    <comment ref="B2445" authorId="9" shapeId="0">
+      <text>
+        <t>D1023 blocked source preparation; source numbering preserved; no outcomes.</t>
+      </text>
+    </comment>
+    <comment ref="B2446" authorId="10" shapeId="0">
+      <text>
+        <t>{"batch": "A01-A04-formal", "authorization": "User A01-A04 formal source-table decision", "owner": null}</t>
+      </text>
+    </comment>
+    <comment ref="B2447" authorId="10" shapeId="0">
+      <text>
+        <t>{"batch": "A01-A04-formal", "authorization": "User A01-A04 formal source-table decision", "owner": null}</t>
+      </text>
+    </comment>
+    <comment ref="B2448" authorId="10" shapeId="0">
+      <text>
+        <t>{"batch": "A01-A04-formal", "authorization": "User A01-A04 formal source-table decision", "owner": null}</t>
+      </text>
+    </comment>
+    <comment ref="B2449" authorId="10" shapeId="0">
+      <text>
+        <t>{"batch": "A01-A04-formal", "authorization": "User A01-A04 formal source-table decision", "owner": null}</t>
+      </text>
+    </comment>
+    <comment ref="B2450" authorId="10" shapeId="0">
+      <text>
+        <t>{"batch": "A01-A04-formal", "authorization": "User A01-A04 formal source-table decision", "owner": null}</t>
+      </text>
+    </comment>
+    <comment ref="B2451" authorId="10" shapeId="0">
+      <text>
+        <t>{"batch": "A01-A04-formal", "authorization": "User A01-A04 formal source-table decision", "owner": null}</t>
+      </text>
+    </comment>
+    <comment ref="B2452" authorId="10" shapeId="0">
+      <text>
+        <t>{"batch": "A01-A04-formal", "authorization": "User A01-A04 formal source-table decision", "owner": null}</t>
+      </text>
+    </comment>
+    <comment ref="B2453" authorId="10" shapeId="0">
+      <text>
+        <t>{"batch": "A01-A04-formal", "authorization": "User A01-A04 formal source-table decision", "owner": null}</t>
+      </text>
+    </comment>
+    <comment ref="B2454" authorId="10" shapeId="0">
+      <text>
+        <t>{"batch": "A01-A04-formal", "authorization": "User A01-A04 formal source-table decision", "owner": null}</t>
+      </text>
+    </comment>
+    <comment ref="B2455" authorId="10" shapeId="0">
+      <text>
+        <t>{"batch": "A01-A04-formal", "authorization": "User A01-A04 formal source-table decision", "owner": null}</t>
+      </text>
+    </comment>
+    <comment ref="B2456" authorId="10" shapeId="0">
+      <text>
+        <t>{"batch": "A01-A04-formal", "authorization": "User A01-A04 formal source-table decision", "owner": null}</t>
+      </text>
+    </comment>
+    <comment ref="B2457" authorId="10" shapeId="0">
+      <text>
+        <t>{"batch": "A01-A04-formal", "authorization": "User A01-A04 formal source-table decision", "owner": null}</t>
+      </text>
+    </comment>
+    <comment ref="B2458" authorId="10" shapeId="0">
+      <text>
+        <t>{"batch": "A01-A04-formal", "authorization": "User A01-A04 formal source-table decision", "owner": null}</t>
+      </text>
+    </comment>
+    <comment ref="B2459" authorId="11" shapeId="0">
+      <text>
+        <t>{"batch": "A05-reporter", "authorization": "Parent-authorized A05 formal source tables"}</t>
+      </text>
+    </comment>
+    <comment ref="B2460" authorId="11" shapeId="0">
+      <text>
+        <t>{"batch": "A05-reporter", "authorization": "Parent-authorized A05 formal source tables"}</t>
+      </text>
+    </comment>
+    <comment ref="B2461" authorId="11" shapeId="0">
+      <text>
+        <t>{"batch": "A05-reporter", "authorization": "Parent-authorized A05 formal source tables"}</t>
+      </text>
+    </comment>
+    <comment ref="B2462" authorId="11" shapeId="0">
+      <text>
+        <t>{"batch": "A05-reporter", "authorization": "Parent-authorized A05 formal source tables"}</t>
+      </text>
+    </comment>
+    <comment ref="B2463" authorId="11" shapeId="0">
+      <text>
+        <t>{"batch": "A05-reporter", "authorization": "Parent-authorized A05 formal source tables"}</t>
+      </text>
+    </comment>
+    <comment ref="B2464" authorId="11" shapeId="0">
+      <text>
+        <t>{"batch": "A05-reporter", "authorization": "Parent-authorized A05 formal source tables"}</t>
+      </text>
+    </comment>
+    <comment ref="B2465" authorId="11" shapeId="0">
+      <text>
+        <t>{"batch": "A05-reporter", "authorization": "Parent-authorized A05 formal source tables"}</t>
       </text>
     </comment>
   </commentList>
@@ -11530,7 +13992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2100"/>
+  <dimension ref="A1:D2465"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -42495,7 +44957,7 @@
       </c>
       <c r="C1830" t="inlineStr">
         <is>
-          <t>那就定在两天后，怎么样？</t>
+          <t>那就定在三天后，怎么样？</t>
         </is>
       </c>
       <c r="D1830" t="inlineStr">
@@ -42512,7 +44974,7 @@
       </c>
       <c r="C1831" t="inlineStr">
         <is>
-          <t>两天后……好！时间应该足够了！</t>
+          <t>三天后……好！时间应该足够了！</t>
         </is>
       </c>
       <c r="D1831" t="inlineStr">
@@ -42529,7 +44991,7 @@
       </c>
       <c r="C1832" t="inlineStr">
         <is>
-          <t>那今天营业结束后，我们就一起商量一下具体的安排。</t>
+          <t>那就先按这个安排准备，今天营业结束后，我们再一起核对一下细节。</t>
         </is>
       </c>
       <c r="D1832" t="inlineStr">
@@ -42665,7 +45127,7 @@
       </c>
       <c r="C1840" t="inlineStr">
         <is>
-          <t>清晨的咖啡馆还没有正式营业。</t>
+          <t>早间的第一拨客人散去后，咖啡馆迎来了一段短暂的整理时间。</t>
         </is>
       </c>
       <c r="D1840" t="inlineStr">
@@ -42682,7 +45144,7 @@
       </c>
       <c r="C1841" t="inlineStr">
         <is>
-          <t>为了准备即将到来的促销活动，我比往常早起了一些。桌椅已经摆放妥当，柜台上堆着几张写了一半的告示，旁边则是昨晚整理好的账簿。</t>
+          <t>为了准备即将到来的促销活动，我趁客流稍缓整理了一下店里。桌椅已经摆放妥当，柜台上堆着几张写了一半的告示，旁边则是昨晚整理好的账簿。</t>
         </is>
       </c>
       <c r="D1841" t="inlineStr">
@@ -42716,7 +45178,7 @@
       </c>
       <c r="C1843" t="inlineStr">
         <is>
-          <t>早安。请问这里已经开始营业了吗？</t>
+          <t>早上好。请问现在方便接待吗？</t>
         </is>
       </c>
       <c r="D1843" t="inlineStr">
@@ -42767,7 +45229,7 @@
       </c>
       <c r="C1846" t="inlineStr">
         <is>
-          <t>看来我来得稍早了一些。不过，既然门没有锁上，想必也不至于打扰太久。</t>
+          <t>看来我来得不太凑巧。不过，既然门没有锁上，想必也不至于打扰太久。</t>
         </is>
       </c>
       <c r="D1846" t="inlineStr">
@@ -42784,7 +45246,7 @@
       </c>
       <c r="C1847" t="inlineStr">
         <is>
-          <t>您好，先生。我们确实还没正式营业。</t>
+          <t>您好，先生。我们正在整理店里。</t>
         </is>
       </c>
       <c r="D1847" t="inlineStr">
@@ -42920,7 +45382,7 @@
       </c>
       <c r="C1855" t="inlineStr">
         <is>
-          <t>您是第一次来这里吗？虽然还没正式营业，不过咖啡已经准备好了。若是不介意，不妨进来坐坐。</t>
+          <t>您是第一次来这里吗？我们正在整理，不过咖啡已经准备好了。若是不介意，不妨进来坐坐。</t>
         </is>
       </c>
       <c r="D1855" t="inlineStr">
@@ -42937,7 +45399,7 @@
       </c>
       <c r="C1856" t="inlineStr">
         <is>
-          <t>如此说来，我倒没有拒绝的理由了。能在清晨遇到一位热情的店主，总是件令人愉快的事。</t>
+          <t>如此说来，我倒没有拒绝的理由了。能在早间遇到一位热情的店主，总是件令人愉快的事。</t>
         </is>
       </c>
       <c r="D1856" t="inlineStr">
@@ -42954,7 +45416,7 @@
       </c>
       <c r="C1857" t="inlineStr">
         <is>
-          <t>您要是愿意的话，也可以先坐一会儿。我们很快就能营业了。</t>
+          <t>您要是愿意的话，也可以先坐一会儿。我们很快就能整理好。</t>
         </is>
       </c>
       <c r="D1857" t="inlineStr">
@@ -42988,7 +45450,7 @@
       </c>
       <c r="C1859" t="inlineStr">
         <is>
-          <t>抱歉，先生，我们还需要准备一会儿。如果您不介意，可以等正式营业之后再来。</t>
+          <t>抱歉，先生，我们还需要整理一会儿。如果您不介意，可以稍后再来。</t>
         </is>
       </c>
       <c r="D1859" t="inlineStr">
@@ -43005,7 +45467,7 @@
       </c>
       <c r="C1860" t="inlineStr">
         <is>
-          <t>当然，遵守营业时间也是经营的一部分。既然如此，我便不打扰了。</t>
+          <t>当然，先把店里安排妥当也是经营的一部分。既然如此，我便不打扰了。</t>
         </is>
       </c>
       <c r="D1860" t="inlineStr">
@@ -43209,7 +45671,7 @@
       </c>
       <c r="C1872" t="inlineStr">
         <is>
-          <t>正是如此。所以我们打算在两天后举办一次促销活动。</t>
+          <t>正是如此。所以我们打算在三天后举办一次促销活动。</t>
         </is>
       </c>
       <c r="D1872" t="inlineStr">
@@ -43889,7 +46351,7 @@
       </c>
       <c r="C1912" t="inlineStr">
         <is>
-          <t>距离正式营业已经没有多少时间，我收拾好桌上的账簿，将写了一半的促销告示先放到一旁，准备迎接今天的第一批客人。</t>
+          <t>短暂的整理告一段落，我收拾好桌上的账簿，将写了一半的促销告示先放到一旁，准备继续招呼今天的客人。</t>
         </is>
       </c>
       <c r="D1912" t="inlineStr">
@@ -47091,6 +49553,6254 @@
       <c r="D2100" t="inlineStr">
         <is>
           <t>A-1018.s1-P097; 正文; text staging only, event disabled</t>
+        </is>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="B2101" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p004.text</t>
+        </is>
+      </c>
+      <c r="C2101" t="inlineStr">
+        <is>
+          <t>由于咖啡馆昨天举办了活动，客流量渐渐变大，我和阿黛尔的工作甚至可以用繁忙来形容。这样的热闹延续到了今天，直到中午时分人流量才减少，我们终于可以获得片刻的歇息了。</t>
+        </is>
+      </c>
+      <c r="D2101" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P004; church.1014.s2.arrival; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="B2102" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p006.text</t>
+        </is>
+      </c>
+      <c r="C2102" t="inlineStr">
+        <is>
+          <t>一名中年男人出现，在离我最近的吧台座位坐下</t>
+        </is>
+      </c>
+      <c r="D2102" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P006; church.1014.s2.arrival; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="B2103" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p008.text</t>
+        </is>
+      </c>
+      <c r="C2103" t="inlineStr">
+        <is>
+          <t>「您好，欢迎光临沸点咖啡馆！」</t>
+        </is>
+      </c>
+      <c r="D2103" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P008; church.1014.s2.arrival; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="B2104" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p009.text</t>
+        </is>
+      </c>
+      <c r="C2104" t="inlineStr">
+        <is>
+          <t>「你好。」</t>
+        </is>
+      </c>
+      <c r="D2104" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P009; church.1014.s2.arrival; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="B2105" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p010.text</t>
+        </is>
+      </c>
+      <c r="C2105" t="inlineStr">
+        <is>
+          <t>「先生，请问您想喝点什么呢？店内的咖啡目前广受好评呢。」</t>
+        </is>
+      </c>
+      <c r="D2105" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P010; church.1014.s2.arrival; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="B2106" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p011.text</t>
+        </is>
+      </c>
+      <c r="C2106" t="inlineStr">
+        <is>
+          <t>「是吗，那来一杯经典的无糖黑咖啡。」</t>
+        </is>
+      </c>
+      <c r="D2106" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P011; church.1014.s2.arrival; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="B2107" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p012.text</t>
+        </is>
+      </c>
+      <c r="C2107" t="inlineStr">
+        <is>
+          <t>「好的，请稍等片刻。」</t>
+        </is>
+      </c>
+      <c r="D2107" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P012; church.1014.s2.arrival; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="B2108" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p014.text</t>
+        </is>
+      </c>
+      <c r="C2108" t="inlineStr">
+        <is>
+          <t>「还不错。」</t>
+        </is>
+      </c>
+      <c r="D2108" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P014; church.1014.s2.arrival; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="B2109" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p015.text</t>
+        </is>
+      </c>
+      <c r="C2109" t="inlineStr">
+        <is>
+          <t>「谢谢您的肯定！请慢慢品尝。」</t>
+        </is>
+      </c>
+      <c r="D2109" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P015; church.1014.s2.arrival; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="B2110" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p017.text</t>
+        </is>
+      </c>
+      <c r="C2110" t="inlineStr">
+        <is>
+          <t>暂时没有更多客人了，正好趁闲暇时放松一下吧</t>
+        </is>
+      </c>
+      <c r="D2110" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P017; church.1014.s2.notice_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="B2111" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p018.text</t>
+        </is>
+      </c>
+      <c r="C2111" t="inlineStr">
+        <is>
+          <t>不知道下午客流量怎么样，一旦忙起来就觉得时间过得飞快，不过这也意味着叔叔交给我的咖啡馆逐渐走上正途了。</t>
+        </is>
+      </c>
+      <c r="D2111" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P018; church.1014.s2.notice_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="B2112" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p019.text</t>
+        </is>
+      </c>
+      <c r="C2112" t="inlineStr">
+        <is>
+          <t>说起咖啡馆，没想到背后竟然和一些神秘组织有关系，感觉被牵扯进了很不得了的事件中。</t>
+        </is>
+      </c>
+      <c r="D2112" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P019; church.1014.s2.notice_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="B2113" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p020.text</t>
+        </is>
+      </c>
+      <c r="C2113" t="inlineStr">
+        <is>
+          <t>不知道是不是我的错觉，总觉得这位客人一直在看着我。是对咖啡不满意吗，或者是我今天穿的不对劲？</t>
+        </is>
+      </c>
+      <c r="D2113" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P020; church.1014.s2.notice_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="B2114" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p021.text</t>
+        </is>
+      </c>
+      <c r="C2114" t="inlineStr">
+        <is>
+          <t>他看起来也像是一个工人，今天来的工人怎么这么多，但他应该不会是神秘人那边派来的人吧？好在意，要不问一下吧。</t>
+        </is>
+      </c>
+      <c r="D2114" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P021; church.1014.s2.notice_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="B2115" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p023.text</t>
+        </is>
+      </c>
+      <c r="C2115" t="inlineStr">
+        <is>
+          <t>暂时没有更多客人了，正好趁闲暇时放松一下吧。</t>
+        </is>
+      </c>
+      <c r="D2115" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P023; church.1014.s2.notice_fail; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="B2116" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p024.text</t>
+        </is>
+      </c>
+      <c r="C2116" t="inlineStr">
+        <is>
+          <t>不知道下午客流量怎么样，一旦忙起来就觉得时间过得飞快，不过这也意味着叔叔交给我的咖啡馆逐渐走上正途了。</t>
+        </is>
+      </c>
+      <c r="D2116" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P024; church.1014.s2.notice_fail; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="B2117" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p025.text</t>
+        </is>
+      </c>
+      <c r="C2117" t="inlineStr">
+        <is>
+          <t>说起咖啡馆，没想到其居然和一些说不清的组织有所牵扯，感觉被牵扯进了很不得了的事件中。</t>
+        </is>
+      </c>
+      <c r="D2117" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P025; church.1014.s2.notice_fail; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="B2118" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p026.text</t>
+        </is>
+      </c>
+      <c r="C2118" t="inlineStr">
+        <is>
+          <t>这位客人看起来也像是一个工人，今天的来的工人怎么这么多，但他应该不会是神秘人那边派来的人吧？好在意，要不问一下吧。</t>
+        </is>
+      </c>
+      <c r="D2118" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P026; church.1014.s2.notice_fail; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="B2119" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p027.text</t>
+        </is>
+      </c>
+      <c r="C2119" t="inlineStr">
+        <is>
+          <t>「先生，请问您对咖啡有什么建议吗？咖啡馆重新开业，我们希望能在客人们的建议下进一步提高！如果有想法但是不好意思直接说，也可以通过写信的方式告诉我们，您瞧，我们上午刚收到一封顾客送来的建议信呢。」</t>
+        </is>
+      </c>
+      <c r="D2119" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P027; church.1014.s2.letter_question; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="B2120" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p029.text</t>
+        </is>
+      </c>
+      <c r="C2120" t="inlineStr">
+        <is>
+          <t>我一边出示装着信的信封，一边假装不经意地盯着他</t>
+        </is>
+      </c>
+      <c r="D2120" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P029; church.1014.s2.letter_question; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="B2121" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p030.text</t>
+        </is>
+      </c>
+      <c r="C2121" t="inlineStr">
+        <is>
+          <t>他没有多看信一眼，只是看着我</t>
+        </is>
+      </c>
+      <c r="D2121" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P030; church.1014.s2.letter_question; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="B2122" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p031.a.text</t>
+        </is>
+      </c>
+      <c r="C2122" t="inlineStr">
+        <is>
+          <t>「不，不，没有任何意见。」</t>
+        </is>
+      </c>
+      <c r="D2122" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P031; church.1014.s2.letter_question; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="B2123" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p031.b.text</t>
+        </is>
+      </c>
+      <c r="C2123" t="inlineStr">
+        <is>
+          <t>「店长，我有一个问题想问你。」</t>
+        </is>
+      </c>
+      <c r="D2123" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P031; church.1014.s2.letter_question; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="B2124" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p032.text</t>
+        </is>
+      </c>
+      <c r="C2124" t="inlineStr">
+        <is>
+          <t>「啊，好的，先生，您请问。」</t>
+        </is>
+      </c>
+      <c r="D2124" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P032; church.1014.s2.letter_question; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="B2125" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p033.text</t>
+        </is>
+      </c>
+      <c r="C2125" t="inlineStr">
+        <is>
+          <t>他对信没有任何反应，看来并不是神秘人那边派来的人</t>
+        </is>
+      </c>
+      <c r="D2125" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P033; church.1014.s2.letter_question; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="B2126" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p034.text</t>
+        </is>
+      </c>
+      <c r="C2126" t="inlineStr">
+        <is>
+          <t>或许只是个普通工人吧</t>
+        </is>
+      </c>
+      <c r="D2126" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P034; church.1014.s2.letter_question; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="B2127" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p035.text</t>
+        </is>
+      </c>
+      <c r="C2127" t="inlineStr">
+        <is>
+          <t>「王城中，甚至圣徒街上都并不只有一家咖啡馆，但是它们有些并不向普通平民开放，而我看见各阶层的人民都可以自由进入你们的店中。您是出于怎样的考虑呢？」</t>
+        </is>
+      </c>
+      <c r="D2127" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P035; church.1014.s2.letter_question; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2128">
+      <c r="B2128" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p037.text</t>
+        </is>
+      </c>
+      <c r="C2128" t="inlineStr">
+        <is>
+          <t>「只要能够赚钱就好，我们并不在乎客人的身份。我的叔叔杜瓦尔和前几任店长也是这样做的。将人划分三六九等是政治家的思想，却是和商人无关的。」</t>
+        </is>
+      </c>
+      <c r="D2128" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P037; church.1014.s2.letter_question; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2129">
+      <c r="B2129" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p038.text</t>
+        </is>
+      </c>
+      <c r="C2129" t="inlineStr">
+        <is>
+          <t>「我只是想看见客人喝到我做的咖啡之后露出满意的笑容，这样就已经足够了，别的因素不是我要考虑的。」</t>
+        </is>
+      </c>
+      <c r="D2129" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P038; church.1014.s2.letter_question; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2130">
+      <c r="B2130" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p039.text</t>
+        </is>
+      </c>
+      <c r="C2130" t="inlineStr">
+        <is>
+          <t>「我认为咖啡馆只面向部分人群开放本身就是错误的，其应当是面向普罗大众而存在的，不应以政治地位、经济实力等原因而将部分人拒之门外。我的叔叔杜瓦尔和前几任店长也是这样做的，我延续着他们的精神。」</t>
+        </is>
+      </c>
+      <c r="D2130" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P039; church.1014.s2.letter_question; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2131">
+      <c r="B2131" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p041.text</t>
+        </is>
+      </c>
+      <c r="C2131" t="inlineStr">
+        <is>
+          <t>「好的，我明白了。我之前是一名工人，生活在圣西尔万郊区，但是前段时间不幸在工作中受伤，成为了跛脚。唉，许多工厂都因为这点而排斥我。我近日一直为此感到烦忧，昨日听说圣徒街的沸点咖啡馆重新开业了，味道不错且面向大众开放，我实在感到好奇，所以今日特地前来。」</t>
+        </is>
+      </c>
+      <c r="D2131" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P041; church.1014.s2.relief_question; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2132">
+      <c r="B2132" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p042.text</t>
+        </is>
+      </c>
+      <c r="C2132" t="inlineStr">
+        <is>
+          <t>顺着他的话我不由得认真打量起面前这个男子</t>
+        </is>
+      </c>
+      <c r="D2132" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P042; church.1014.s2.relief_question; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2133">
+      <c r="B2133" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p043.text</t>
+        </is>
+      </c>
+      <c r="C2133" t="inlineStr">
+        <is>
+          <t>眼角周围有淡淡的皱纹，年纪并不小了，身上隐隐传来一阵烟味。或许是最近郁闷时常抽。</t>
+        </is>
+      </c>
+      <c r="D2133" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P043; church.1014.s2.relief_question; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2134">
+      <c r="B2134" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p044.text</t>
+        </is>
+      </c>
+      <c r="C2134" t="inlineStr">
+        <is>
+          <t>但是整体打理得很整齐，眼神也透露出坚毅，看起来是一个对自身和生活有一定追求的人。</t>
+        </is>
+      </c>
+      <c r="D2134" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P044; church.1014.s2.relief_question; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2135">
+      <c r="B2135" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p045.text</t>
+        </is>
+      </c>
+      <c r="C2135" t="inlineStr">
+        <is>
+          <t>「这实在是我们的荣幸，先生。希望这杯咖啡能让您感到些许慰藉。」</t>
+        </is>
+      </c>
+      <c r="D2135" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P045; church.1014.s2.relief_question; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2136">
+      <c r="B2136" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p046.text</t>
+        </is>
+      </c>
+      <c r="C2136" t="inlineStr">
+        <is>
+          <t>「好的。店长，您听闻前几日埃利昂公爵和教会的人在旧城区和圣西尔万郊区救济贫民的事情了吗？」</t>
+        </is>
+      </c>
+      <c r="D2136" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P046; church.1014.s2.relief_question; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2137">
+      <c r="B2137" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p047.text</t>
+        </is>
+      </c>
+      <c r="C2137" t="inlineStr">
+        <is>
+          <t>「有所耳闻。」</t>
+        </is>
+      </c>
+      <c r="D2137" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P047; church.1014.s2.relief_question; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2138">
+      <c r="B2138" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p048.text</t>
+        </is>
+      </c>
+      <c r="C2138" t="inlineStr">
+        <is>
+          <t>「很高兴您有所了解。我那天就在被救济的队伍中，这是我最近感受过的最大的善意了，那粥虽然并不算得上十分美味，但足以饱腹了。虽然当下百姓的生活困难，没想到王庭和教会还是有一些有理想和良心的人为我们这些人而奔走着。」</t>
+        </is>
+      </c>
+      <c r="D2138" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P048; church.1014.s2.relief_question; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2139">
+      <c r="B2139" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p050.text</t>
+        </is>
+      </c>
+      <c r="C2139" t="inlineStr">
+        <is>
+          <t>「很高兴得知这件事，我刚来到此地，没想到上层还有埃利昂公爵这样的人物。」</t>
+        </is>
+      </c>
+      <c r="D2139" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P050; church.1014.s2.relief_question; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2140">
+      <c r="B2140" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p051.text</t>
+        </is>
+      </c>
+      <c r="C2140" t="inlineStr">
+        <is>
+          <t>「很高兴得知这件事，但是我相当怀疑王庭和教会中真的存在这样的人吗？」</t>
+        </is>
+      </c>
+      <c r="D2140" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P051; church.1014.s2.relief_question; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2141">
+      <c r="B2141" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p052.text</t>
+        </is>
+      </c>
+      <c r="C2141" t="inlineStr">
+        <is>
+          <t>「很高兴得知这件事，希望百姓的生活能过得越来越好。」</t>
+        </is>
+      </c>
+      <c r="D2141" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P052; church.1014.s2.relief_question; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2142">
+      <c r="B2142" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p054.text</t>
+        </is>
+      </c>
+      <c r="C2142" t="inlineStr">
+        <is>
+          <t>「正是如此，店长。您不知道昨天的盛况……」</t>
+        </is>
+      </c>
+      <c r="D2142" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P054; church.1014.s2.praise; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2143">
+      <c r="B2143" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p057.text</t>
+        </is>
+      </c>
+      <c r="C2143" t="inlineStr">
+        <is>
+          <t>他突然眯着眼睛打量了我一下</t>
+        </is>
+      </c>
+      <c r="D2143" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P057; church.1014.s2.doubt; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2144">
+      <c r="B2144" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p058.text</t>
+        </is>
+      </c>
+      <c r="C2144" t="inlineStr">
+        <is>
+          <t>「店长，您不相信吗？埃利昂公爵他们施粥是实实在在发生的事。」</t>
+        </is>
+      </c>
+      <c r="D2144" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P058; church.1014.s2.doubt; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2145">
+      <c r="B2145" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p059.text</t>
+        </is>
+      </c>
+      <c r="C2145" t="inlineStr">
+        <is>
+          <t>我感到他的态度冷却了一些</t>
+        </is>
+      </c>
+      <c r="D2145" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P059; church.1014.s2.doubt; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2146">
+      <c r="B2146" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p060.text</t>
+        </is>
+      </c>
+      <c r="C2146" t="inlineStr">
+        <is>
+          <t>「不，先生，我相信这一点。我只是……算了，你当我未曾说过吧。」</t>
+        </is>
+      </c>
+      <c r="D2146" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P060; church.1014.s2.doubt; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2147">
+      <c r="B2147" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p061.text</t>
+        </is>
+      </c>
+      <c r="C2147" t="inlineStr">
+        <is>
+          <t>「好的，您不要紧张，我只是看见您觉得亲切，忍不住多聊了两句。我觉得王庭和教会并非全然糟糕透顶的……」</t>
+        </is>
+      </c>
+      <c r="D2147" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P061; church.1014.s2.doubt; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2148">
+      <c r="B2148" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p064.text</t>
+        </is>
+      </c>
+      <c r="C2148" t="inlineStr">
+        <is>
+          <t>他好像对我的回答并不满意，皱了皱眉</t>
+        </is>
+      </c>
+      <c r="D2148" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P064; church.1014.s2.wish; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2149">
+      <c r="B2149" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p065.text</t>
+        </is>
+      </c>
+      <c r="C2149" t="inlineStr">
+        <is>
+          <t>「好吧……」</t>
+        </is>
+      </c>
+      <c r="D2149" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P065; church.1014.s2.wish; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2150">
+      <c r="B2150" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p067.text</t>
+        </is>
+      </c>
+      <c r="C2150" t="inlineStr">
+        <is>
+          <t>他似乎还想说话，但此时新的客人走近了吧台</t>
+        </is>
+      </c>
+      <c r="D2150" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P067; church.1014.s2.depart; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2151">
+      <c r="B2151" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p068.text</t>
+        </is>
+      </c>
+      <c r="C2151" t="inlineStr">
+        <is>
+          <t>「一不注意，竟然已经这个点了，我还需要去找找有没有我能盛任的工作。感谢您的咖啡，有机会我会再来拜访的。」</t>
+        </is>
+      </c>
+      <c r="D2151" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P068; church.1014.s2.depart; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2152">
+      <c r="B2152" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p069.text</t>
+        </is>
+      </c>
+      <c r="C2152" t="inlineStr">
+        <is>
+          <t>「再见，先生！祝您能早日找到一个满意的工作。」</t>
+        </is>
+      </c>
+      <c r="D2152" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P069; church.1014.s2.depart; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2153">
+      <c r="B2153" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p070.text</t>
+        </is>
+      </c>
+      <c r="C2153" t="inlineStr">
+        <is>
+          <t>他放下咖啡，站起来离开，这时我才发现他的左脚确实行走起来不太便利</t>
+        </is>
+      </c>
+      <c r="D2153" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P070; church.1014.s2.depart; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2154">
+      <c r="B2154" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p071.text</t>
+        </is>
+      </c>
+      <c r="C2154" t="inlineStr">
+        <is>
+          <t>他的身影越来越远，随着咖啡馆的门一开一闭，我便再也看不见他的身影了</t>
+        </is>
+      </c>
+      <c r="D2154" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P071; church.1014.s2.depart; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2155">
+      <c r="B2155" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p073.text</t>
+        </is>
+      </c>
+      <c r="C2155" t="inlineStr">
+        <is>
+          <t>真是不容易</t>
+        </is>
+      </c>
+      <c r="D2155" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P073; church.1014.s2.depart; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2156">
+      <c r="B2156" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p074.text</t>
+        </is>
+      </c>
+      <c r="C2156" t="inlineStr">
+        <is>
+          <t>我在心中叹口气</t>
+        </is>
+      </c>
+      <c r="D2156" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P074; church.1014.s2.depart; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2157">
+      <c r="B2157" t="inlineStr">
+        <is>
+          <t>church.1014.s2.p075.text</t>
+        </is>
+      </c>
+      <c r="C2157" t="inlineStr">
+        <is>
+          <t>然后快速转换思绪，面对客人新的要求，开启了新的工作。</t>
+        </is>
+      </c>
+      <c r="D2157" t="inlineStr">
+        <is>
+          <t>church.1014.s2.P075; church.1014.s2.depart; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2158">
+      <c r="B2158" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p003.text</t>
+        </is>
+      </c>
+      <c r="C2158" t="inlineStr">
+        <is>
+          <t>今天咖啡店的生意也相当不错</t>
+        </is>
+      </c>
+      <c r="D2158" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P003; church.1020.s1.raid; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2159">
+      <c r="B2159" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p004.text</t>
+        </is>
+      </c>
+      <c r="C2159" t="inlineStr">
+        <is>
+          <t>我正在为客人制作咖啡时，突然听见一阵嘈杂的脚步声</t>
+        </is>
+      </c>
+      <c r="D2159" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P004; church.1020.s1.raid; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2160">
+      <c r="B2160" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p006.text</t>
+        </is>
+      </c>
+      <c r="C2160" t="inlineStr">
+        <is>
+          <t>然后是阿黛尔同步响起的惊呼声</t>
+        </is>
+      </c>
+      <c r="D2160" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P006; church.1020.s1.raid; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2161">
+      <c r="B2161" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p007.text</t>
+        </is>
+      </c>
+      <c r="C2161" t="inlineStr">
+        <is>
+          <t>「天呐，教会监察司的人？{playername}店长！{playername}店长！」</t>
+        </is>
+      </c>
+      <c r="D2161" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P007; church.1020.s1.raid; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2162">
+      <c r="B2162" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p008.text</t>
+        </is>
+      </c>
+      <c r="C2162" t="inlineStr">
+        <is>
+          <t>我回过头，看见一群穿着统一制式服装的人</t>
+        </is>
+      </c>
+      <c r="D2162" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P008; church.1020.s1.raid; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2163">
+      <c r="B2163" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p009.text</t>
+        </is>
+      </c>
+      <c r="C2163" t="inlineStr">
+        <is>
+          <t>「教会监察司」，刚才阿黛尔好像这样称呼着他们</t>
+        </is>
+      </c>
+      <c r="D2163" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P009; church.1020.s1.raid; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2164">
+      <c r="B2164" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p010.text</t>
+        </is>
+      </c>
+      <c r="C2164" t="inlineStr">
+        <is>
+          <t>他们站定在咖啡馆中，其中一个看起来像领头的人则缓步站定在我面前</t>
+        </is>
+      </c>
+      <c r="D2164" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P010; church.1020.s1.raid; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2165">
+      <c r="B2165" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p012.text</t>
+        </is>
+      </c>
+      <c r="C2165" t="inlineStr">
+        <is>
+          <t>我面前的客人惊慌失措地在我们之间来回转着，但是不敢有所动静</t>
+        </is>
+      </c>
+      <c r="D2165" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P012; church.1020.s1.raid; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2166">
+      <c r="B2166" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p013.text</t>
+        </is>
+      </c>
+      <c r="C2166" t="inlineStr">
+        <is>
+          <t>「你就是{playername}，沸点咖啡馆的现任店长？」</t>
+        </is>
+      </c>
+      <c r="D2166" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P013; church.1020.s1.raid; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2167">
+      <c r="B2167" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p014.text</t>
+        </is>
+      </c>
+      <c r="C2167" t="inlineStr">
+        <is>
+          <t>「是的。」</t>
+        </is>
+      </c>
+      <c r="D2167" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P014; church.1020.s1.raid; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2168">
+      <c r="B2168" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p015.text</t>
+        </is>
+      </c>
+      <c r="C2168" t="inlineStr">
+        <is>
+          <t>「我们是教会监察司，今日奉命前来圣徒街搜查。我是今日负责带队的监察官，希望你能认真配合调查，不然的话——」</t>
+        </is>
+      </c>
+      <c r="D2168" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P015; church.1020.s1.raid; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2169">
+      <c r="B2169" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p016.text</t>
+        </is>
+      </c>
+      <c r="C2169" t="inlineStr">
+        <is>
+          <t>他未说完，但配合着他凶狠的目光，在场的人都对这未尽的话心知肚明</t>
+        </is>
+      </c>
+      <c r="D2169" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P016; church.1020.s1.raid; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2170">
+      <c r="B2170" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p017.text</t>
+        </is>
+      </c>
+      <c r="C2170" t="inlineStr">
+        <is>
+          <t>我的大脑急速运转着</t>
+        </is>
+      </c>
+      <c r="D2170" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P017; church.1020.s1.raid; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2171">
+      <c r="B2171" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p018.text</t>
+        </is>
+      </c>
+      <c r="C2171" t="inlineStr">
+        <is>
+          <t>教会监察司为什么会来圣徒街搜查？商铺经营不归监察司管吧？哦对了，好像听谁提过前几日街头有人散布修改「王选者」法律的消息……只有这个可能了。不过这和我也没什么大关系，随机应对即可吧。</t>
+        </is>
+      </c>
+      <c r="D2171" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P018; church.1020.s1.raid; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2172">
+      <c r="B2172" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p020.text</t>
+        </is>
+      </c>
+      <c r="C2172" t="inlineStr">
+        <is>
+          <t>「好吧，但是能否请小心对待店中的客人和设备，我们还要继续营业的。」</t>
+        </is>
+      </c>
+      <c r="D2172" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P020; church.1020.s1.raid; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2173">
+      <c r="B2173" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p021.text</t>
+        </is>
+      </c>
+      <c r="C2173" t="inlineStr">
+        <is>
+          <t>「我们咖啡馆正大光明，你们可以随意搜查。但是能否请小心对待店中的客人和设备，我们还要继续营业的。」</t>
+        </is>
+      </c>
+      <c r="D2173" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P021; church.1020.s1.raid; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2174">
+      <c r="B2174" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p022.text</t>
+        </is>
+      </c>
+      <c r="C2174" t="inlineStr">
+        <is>
+          <t>「如果我不同意会怎么样呢？」</t>
+        </is>
+      </c>
+      <c r="D2174" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P022; church.1020.s1.raid; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2175">
+      <c r="B2175" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p024.text</t>
+        </is>
+      </c>
+      <c r="C2175" t="inlineStr">
+        <is>
+          <t>「哼，用不着你来指导工作。」「各人员注意，仔细搜查，不要放过任何一个角落。」</t>
+        </is>
+      </c>
+      <c r="D2175" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P024; church.1020.s1.cooperate; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2176">
+      <c r="B2176" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p027.text</t>
+        </is>
+      </c>
+      <c r="C2176" t="inlineStr">
+        <is>
+          <t>我们隔着吧台看着对方的眼睛对峙，谁也不肯服输，许久他先移开目光并缓慢开口</t>
+        </is>
+      </c>
+      <c r="D2176" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P027; church.1020.s1.defy_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2177">
+      <c r="B2177" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p028.text</t>
+        </is>
+      </c>
+      <c r="C2177" t="inlineStr">
+        <is>
+          <t>「哼，年轻人，我很欣赏你的勇气，但建议你要记得区分勇敢和鲁莽。」「今日是必定要开展检查的。各人员注意，仔细搜查，不要放过任何一个角落。」</t>
+        </is>
+      </c>
+      <c r="D2177" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P028; church.1020.s1.defy_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2178">
+      <c r="B2178" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p030.text</t>
+        </is>
+      </c>
+      <c r="C2178" t="inlineStr">
+        <is>
+          <t>我们隔着吧台看着对方的眼睛对峙，谁也不肯服输，最终我感到他身上的威严压过了我，我率先移开目光</t>
+        </is>
+      </c>
+      <c r="D2178" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P030; church.1020.s1.defy_fail; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2179">
+      <c r="B2179" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p031.text</t>
+        </is>
+      </c>
+      <c r="C2179" t="inlineStr">
+        <is>
+          <t>「年轻人，我想你是刚来到圣诺特，还不太了解情况，我们的搜查不需要你的同意。」「现在碍于你的态度，我可能要采取一些特别措施了，来人。」</t>
+        </is>
+      </c>
+      <c r="D2179" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P031; church.1020.s1.defy_fail; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2180">
+      <c r="B2180" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p032.text</t>
+        </is>
+      </c>
+      <c r="C2180" t="inlineStr">
+        <is>
+          <t>两个穿着制式服装的人从两边走上前来，将我从吧台中推出来，一左一右地扣押着我</t>
+        </is>
+      </c>
+      <c r="D2180" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P032; church.1020.s1.defy_fail; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2181">
+      <c r="B2181" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p033.text</t>
+        </is>
+      </c>
+      <c r="C2181" t="inlineStr">
+        <is>
+          <t>「现在可以配合检查了吧，店长。」「各人员注意，仔细搜查，不要放过任何一个角落。」</t>
+        </is>
+      </c>
+      <c r="D2181" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P033; church.1020.s1.defy_fail; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2182">
+      <c r="B2182" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p035.text</t>
+        </is>
+      </c>
+      <c r="C2182" t="inlineStr">
+        <is>
+          <t>「是。」</t>
+        </is>
+      </c>
+      <c r="D2182" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P035; church.1020.s1.letter_found; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2183">
+      <c r="B2183" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p036.text</t>
+        </is>
+      </c>
+      <c r="C2183" t="inlineStr">
+        <is>
+          <t>他们四下分散开来，我看见他们的身影在大堂中忙碌着，甚至对顾客开展了简短的问询，部分顾客不堪其扰趁乱离开了。</t>
+        </is>
+      </c>
+      <c r="D2183" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P036; church.1020.s1.letter_found; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2184">
+      <c r="B2184" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p037.text</t>
+        </is>
+      </c>
+      <c r="C2184" t="inlineStr">
+        <is>
+          <t>唉，不知道会不会影响以后的生意。</t>
+        </is>
+      </c>
+      <c r="D2184" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P037; church.1020.s1.letter_found; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2185">
+      <c r="B2185" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p038.text</t>
+        </is>
+      </c>
+      <c r="C2185" t="inlineStr">
+        <is>
+          <t>突然想起神秘人给我留下的那封信好像被我顺手放在了吧台的抽屉中，密信他们看不懂应该不要紧……但是我该如何解释呢……</t>
+        </is>
+      </c>
+      <c r="D2185" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P038; church.1020.s1.letter_found; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2186">
+      <c r="B2186" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p039.text</t>
+        </is>
+      </c>
+      <c r="C2186" t="inlineStr">
+        <is>
+          <t>然而怕什么来什么。很快他们便搜查到了吧台区域，在我如鼓擂的心跳声中他们在抽屉中找到了那封信，并递交给了监察官。</t>
+        </is>
+      </c>
+      <c r="D2186" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P039; church.1020.s1.letter_found; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2187">
+      <c r="B2187" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p040.text</t>
+        </is>
+      </c>
+      <c r="C2187" t="inlineStr">
+        <is>
+          <t>监察官打开那封信看了看，然后走到我面前</t>
+        </is>
+      </c>
+      <c r="D2187" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P040; church.1020.s1.letter_found; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2188">
+      <c r="B2188" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p041.text</t>
+        </is>
+      </c>
+      <c r="C2188" t="inlineStr">
+        <is>
+          <t>「解释一下吗，{playername}店长？这封信上写的是什么，告诉我。」</t>
+        </is>
+      </c>
+      <c r="D2188" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P041; church.1020.s1.letter_found; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2189">
+      <c r="B2189" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p044.text</t>
+        </is>
+      </c>
+      <c r="C2189" t="inlineStr">
+        <is>
+          <t>「这是我们内部每日记录进货、出账的账单，为了节省时间而简写为这种形式。」</t>
+        </is>
+      </c>
+      <c r="D2189" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P044; church.1020.s1.letter_found; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2190">
+      <c r="B2190" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p045.text</t>
+        </is>
+      </c>
+      <c r="C2190" t="inlineStr">
+        <is>
+          <t>「这不过我的一封私人信件，监察司奉命搜查商铺，可没有资格逼问一封私人信件写了什么。」</t>
+        </is>
+      </c>
+      <c r="D2190" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P045; church.1020.s1.letter_found; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2191">
+      <c r="B2191" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p046.text</t>
+        </is>
+      </c>
+      <c r="C2191" t="inlineStr">
+        <is>
+          <t>「我想长官你们是来搜查与「王选者」法律相关的吧，这不过一封我的私人信件能有什么关系呢？」</t>
+        </is>
+      </c>
+      <c r="D2191" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P046; church.1020.s1.letter_found; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2192">
+      <c r="B2192" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p047.text</t>
+        </is>
+      </c>
+      <c r="C2192" t="inlineStr">
+        <is>
+          <t>「这不过是一封普通的私人信件，我看不出有什么被怀疑的必要。长官，您不会是早就对我有所怀疑吧？」</t>
+        </is>
+      </c>
+      <c r="D2192" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P047; church.1020.s1.letter_found; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2193">
+      <c r="B2193" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p049.text</t>
+        </is>
+      </c>
+      <c r="C2193" t="inlineStr">
+        <is>
+          <t>「账单？那你详细给我讲讲这个账单的构成。」</t>
+        </is>
+      </c>
+      <c r="D2193" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P049; church.1020.s1.language_intro; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2194">
+      <c r="B2194" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p051.text</t>
+        </is>
+      </c>
+      <c r="C2194" t="inlineStr">
+        <is>
+          <t>我快速回忆了一下信上的数字，然后不疾不徐地开口</t>
+        </is>
+      </c>
+      <c r="D2194" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P051; church.1020.s1.language_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2195">
+      <c r="B2195" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p052.text</t>
+        </is>
+      </c>
+      <c r="C2195" t="inlineStr">
+        <is>
+          <t>「这些数字代表着店里咖啡豆、设备、餐具等物品的购买量、支出金额、每日消耗量、待购买量等数据，我叔叔当店长时就立下了这样的规矩，后面代代传承。」「这本来是我们的商业机密，但是长官你都发问了，我只能悉数奉告了。」</t>
+        </is>
+      </c>
+      <c r="D2195" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P052; church.1020.s1.language_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2196">
+      <c r="B2196" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p053.text</t>
+        </is>
+      </c>
+      <c r="C2196" t="inlineStr">
+        <is>
+          <t>监察官边听着我的讲述边试图理解信上的数字</t>
+        </is>
+      </c>
+      <c r="D2196" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P053; church.1020.s1.language_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2197">
+      <c r="B2197" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p054.text</t>
+        </is>
+      </c>
+      <c r="C2197" t="inlineStr">
+        <is>
+          <t>「哼，听起来倒是有鼻子有眼。」</t>
+        </is>
+      </c>
+      <c r="D2197" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P054; church.1020.s1.language_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2198">
+      <c r="B2198" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p055.text</t>
+        </is>
+      </c>
+      <c r="C2198" t="inlineStr">
+        <is>
+          <t>他低头又看了一遍信纸，眉头紧皱，却没有从中找到能够反驳我的证据，他又盯着我看了片刻，最终将信纸递还给我。</t>
+        </is>
+      </c>
+      <c r="D2198" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P055; church.1020.s1.language_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2199">
+      <c r="B2199" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p056.text</t>
+        </is>
+      </c>
+      <c r="C2199" t="inlineStr">
+        <is>
+          <t>「暂时没有证据证明这封信与我们搜查的东西有关。收好你的东西。」</t>
+        </is>
+      </c>
+      <c r="D2199" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P056; church.1020.s1.language_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2200">
+      <c r="B2200" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p057.text</t>
+        </is>
+      </c>
+      <c r="C2200" t="inlineStr">
+        <is>
+          <t>我接过信纸，尽量平静地点了点头。</t>
+        </is>
+      </c>
+      <c r="D2200" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P057; church.1020.s1.language_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2201">
+      <c r="B2201" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p059.text</t>
+        </is>
+      </c>
+      <c r="C2201" t="inlineStr">
+        <is>
+          <t>我努力组织着语言，试图把信上的内容解释清楚，却发现自己越说越混乱。</t>
+        </is>
+      </c>
+      <c r="D2201" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P059; church.1020.s1.language_fail; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2202">
+      <c r="B2202" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p060.text</t>
+        </is>
+      </c>
+      <c r="C2202" t="inlineStr">
+        <is>
+          <t>「这……这是以前店里留下的账单记录方式，应该是采购……或者别的什么记录，具体内容我也不太清楚。」</t>
+        </is>
+      </c>
+      <c r="D2202" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P060; church.1020.s1.language_fail; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2203">
+      <c r="B2203" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p061.text</t>
+        </is>
+      </c>
+      <c r="C2203" t="inlineStr">
+        <is>
+          <t>监察官的表情逐渐变得严厉</t>
+        </is>
+      </c>
+      <c r="D2203" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P061; church.1020.s1.language_fail; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2204">
+      <c r="B2204" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p062.text</t>
+        </is>
+      </c>
+      <c r="C2204" t="inlineStr">
+        <is>
+          <t>「你自己的店里发现的信，你却连内容都说不清楚？」</t>
+        </is>
+      </c>
+      <c r="D2204" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P062; church.1020.s1.language_fail; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2205">
+      <c r="B2205" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p063.text</t>
+        </is>
+      </c>
+      <c r="C2205" t="inlineStr">
+        <is>
+          <t>我张了张嘴，一时找不到更合适的说辞。</t>
+        </is>
+      </c>
+      <c r="D2205" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P063; church.1020.s1.language_fail; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2206">
+      <c r="B2206" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p064.text</t>
+        </is>
+      </c>
+      <c r="C2206" t="inlineStr">
+        <is>
+          <t>监察官将信纸收了起来，冷冷地看着我。</t>
+        </is>
+      </c>
+      <c r="D2206" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P064; church.1020.s1.language_fail; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2207">
+      <c r="B2207" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p065.text</t>
+        </is>
+      </c>
+      <c r="C2207" t="inlineStr">
+        <is>
+          <t>「你的解释前后矛盾。带走，等候进一步调查。」</t>
+        </is>
+      </c>
+      <c r="D2207" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P065; church.1020.s1.language_fail; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2208">
+      <c r="B2208" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p067.text</t>
+        </is>
+      </c>
+      <c r="C2208" t="inlineStr">
+        <is>
+          <t>「私人信件？我看见的可是写着一串数字的不明信件。」</t>
+        </is>
+      </c>
+      <c r="D2208" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P067; church.1020.s1.courage_intro; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2209">
+      <c r="B2209" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p068.text</t>
+        </is>
+      </c>
+      <c r="C2209" t="inlineStr">
+        <is>
+          <t>我再次对上他探究的眼睛</t>
+        </is>
+      </c>
+      <c r="D2209" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P068; church.1020.s1.courage_intro; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2210">
+      <c r="B2210" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p070.text</t>
+        </is>
+      </c>
+      <c r="C2210" t="inlineStr">
+        <is>
+          <t>我毫不畏惧地直视着他，没有试图争抢那封信，也没有慌张，一字一句地说道</t>
+        </is>
+      </c>
+      <c r="D2210" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P070; church.1020.s1.courage_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2211">
+      <c r="B2211" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p071.text</t>
+        </is>
+      </c>
+      <c r="C2211" t="inlineStr">
+        <is>
+          <t>「您可以搜查，也可以暂时扣下这封信。但在没有证据之前，请不要把无法解读的信件直接说成不法密信。这不过是前任店长给我留下的关于咖啡馆内部账单。」</t>
+        </is>
+      </c>
+      <c r="D2211" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P071; church.1020.s1.courage_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2212">
+      <c r="B2212" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p072.text</t>
+        </is>
+      </c>
+      <c r="C2212" t="inlineStr">
+        <is>
+          <t>咖啡馆内安静了下来，所有人都在看着我们</t>
+        </is>
+      </c>
+      <c r="D2212" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P072; church.1020.s1.courage_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2213">
+      <c r="B2213" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p073.text</t>
+        </is>
+      </c>
+      <c r="C2213" t="inlineStr">
+        <is>
+          <t>我继续说道</t>
+        </is>
+      </c>
+      <c r="D2213" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P073; church.1020.s1.courage_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2214">
+      <c r="B2214" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p074.text</t>
+        </is>
+      </c>
+      <c r="C2214" t="inlineStr">
+        <is>
+          <t>「如果您认为我有问题，可以按照教会的程序调查。我会配合，但不会承认自己没有做过的事。」</t>
+        </is>
+      </c>
+      <c r="D2214" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P074; church.1020.s1.courage_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2215">
+      <c r="B2215" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p075.text</t>
+        </is>
+      </c>
+      <c r="C2215" t="inlineStr">
+        <is>
+          <t>监察官的目光在我脸上停留了许久，像是在判断我究竟是虚张声势，还是确实问心无愧。</t>
+        </is>
+      </c>
+      <c r="D2215" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P075; church.1020.s1.courage_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2216">
+      <c r="B2216" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p076.text</t>
+        </is>
+      </c>
+      <c r="C2216" t="inlineStr">
+        <is>
+          <t>最终他冷哼一声，将信纸拍在桌上。</t>
+        </is>
+      </c>
+      <c r="D2216" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P076; church.1020.s1.courage_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2217">
+      <c r="B2217" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p077.text</t>
+        </is>
+      </c>
+      <c r="C2217" t="inlineStr">
+        <is>
+          <t>「哼，没有证据，我们也不会仅凭一封无从解读的信抓人。收好你的信，但是如果之后我们发现有什么问题，你等着被传唤吧。」</t>
+        </is>
+      </c>
+      <c r="D2217" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P077; church.1020.s1.courage_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2218">
+      <c r="B2218" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p078.text</t>
+        </is>
+      </c>
+      <c r="C2218" t="inlineStr">
+        <is>
+          <t>「我明白。」</t>
+        </is>
+      </c>
+      <c r="D2218" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P078; church.1020.s1.courage_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2219">
+      <c r="B2219" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p080.text</t>
+        </is>
+      </c>
+      <c r="C2219" t="inlineStr">
+        <is>
+          <t>我想要反驳，却被监察官凌厉的目光压得说不出话来。</t>
+        </is>
+      </c>
+      <c r="D2219" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P080; church.1020.s1.courage_fail; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2220">
+      <c r="B2220" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p081.text</t>
+        </is>
+      </c>
+      <c r="C2220" t="inlineStr">
+        <is>
+          <t>「这……这是前任店长给我留下的关于咖啡馆内部账单的信件……但是……我也不知道上面具体是什么意思……」</t>
+        </is>
+      </c>
+      <c r="D2220" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P081; church.1020.s1.courage_fail; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2221">
+      <c r="B2221" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p082.text</t>
+        </is>
+      </c>
+      <c r="C2221" t="inlineStr">
+        <is>
+          <t>「不知道具体意思？那么你怎么知道这是咖啡馆内部账单？」</t>
+        </is>
+      </c>
+      <c r="D2221" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P082; church.1020.s1.courage_fail; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2222">
+      <c r="B2222" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p083.text</t>
+        </is>
+      </c>
+      <c r="C2222" t="inlineStr">
+        <is>
+          <t>我张张嘴又闭上，他充满威严与怀疑的目光刺痛了我，不敢再继续辩解</t>
+        </is>
+      </c>
+      <c r="D2222" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P083; church.1020.s1.courage_fail; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2223">
+      <c r="B2223" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p084.text</t>
+        </is>
+      </c>
+      <c r="C2223" t="inlineStr">
+        <is>
+          <t>监察官看着我的沉默，像是已经得出了自己的判断。</t>
+        </is>
+      </c>
+      <c r="D2223" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P084; church.1020.s1.courage_fail; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2224">
+      <c r="B2224" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p085.text</t>
+        </is>
+      </c>
+      <c r="C2224" t="inlineStr">
+        <is>
+          <t>「那正好，信带走，回去让我们监察司的人好好领会一下你所谓的「私人信件」。至于你，随我们走一趟。」</t>
+        </is>
+      </c>
+      <c r="D2224" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P085; church.1020.s1.courage_fail; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2225">
+      <c r="B2225" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p088.text</t>
+        </is>
+      </c>
+      <c r="C2225" t="inlineStr">
+        <is>
+          <t>「你倒是很清楚我们为何而来。」</t>
+        </is>
+      </c>
+      <c r="D2225" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P088; church.1020.s1.wisdom_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2226">
+      <c r="B2226" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p089.text</t>
+        </is>
+      </c>
+      <c r="C2226" t="inlineStr">
+        <is>
+          <t>我指了指他手中的信纸</t>
+        </is>
+      </c>
+      <c r="D2226" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P089; church.1020.s1.wisdom_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2227">
+      <c r="B2227" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p090.text</t>
+        </is>
+      </c>
+      <c r="C2227" t="inlineStr">
+        <is>
+          <t>「但这只是一封私人信件，是前任店长给我留下的之前店铺的账单，没有提到「王选者」，也没有任何与法律修改相关的内容，只不过是一串普通数字罢了。而且我听闻前几天是在民间宣扬「王选者」，如果对方采取这样隐晦的方式，并不能达到宣传的目的吧。」</t>
+        </is>
+      </c>
+      <c r="D2227" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P090; church.1020.s1.wisdom_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2228">
+      <c r="B2228" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p091.text</t>
+        </is>
+      </c>
+      <c r="C2228" t="inlineStr">
+        <is>
+          <t>监察官听闻多看了我两眼</t>
+        </is>
+      </c>
+      <c r="D2228" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P091; church.1020.s1.wisdom_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2229">
+      <c r="B2229" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p092.text</t>
+        </is>
+      </c>
+      <c r="C2229" t="inlineStr">
+        <is>
+          <t>「你倒是想得挺清楚。不过你说得没错，目前确实没有证据证明这封信与那件事有关。」</t>
+        </is>
+      </c>
+      <c r="D2229" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P092; church.1020.s1.wisdom_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2230">
+      <c r="B2230" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p093.text</t>
+        </is>
+      </c>
+      <c r="C2230" t="inlineStr">
+        <is>
+          <t>他又沉默了片刻，最终选择将信纸递给身旁的监察员，几名监察员低声讨论后也无法确认其中有什么异常。</t>
+        </is>
+      </c>
+      <c r="D2230" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P093; church.1020.s1.wisdom_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2231">
+      <c r="B2231" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p094.text</t>
+        </is>
+      </c>
+      <c r="C2231" t="inlineStr">
+        <is>
+          <t>「信你收好。至于你，继续留在店里接受调查，不得擅自离开圣徒街。」</t>
+        </is>
+      </c>
+      <c r="D2231" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P094; church.1020.s1.wisdom_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2232">
+      <c r="B2232" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p096.text</t>
+        </is>
+      </c>
+      <c r="C2232" t="inlineStr">
+        <is>
+          <t>「你倒是很清楚我们为何而来。」</t>
+        </is>
+      </c>
+      <c r="D2232" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P096; church.1020.s1.wisdom_fail; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2233">
+      <c r="B2233" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p097.text</t>
+        </is>
+      </c>
+      <c r="C2233" t="inlineStr">
+        <is>
+          <t>我试图继续说出一些合理而又道理的理由来摆脱嫌疑，但脑中一片混乱，只能勉强找出几个听起来合理的词。</t>
+        </is>
+      </c>
+      <c r="D2233" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P097; church.1020.s1.wisdom_fail; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2234">
+      <c r="B2234" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p098.text</t>
+        </is>
+      </c>
+      <c r="C2234" t="inlineStr">
+        <is>
+          <t>「这封信……是我与前任店长沟通的私人信件……上面写的东西应该是店铺内部经营状况，可能就是之前他们订购咖啡豆和机器设备的开销……没什么重要的。怎么看都与你们要查的东西无关吧……」</t>
+        </is>
+      </c>
+      <c r="D2234" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P098; church.1020.s1.wisdom_fail; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2235">
+      <c r="B2235" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p099.text</t>
+        </is>
+      </c>
+      <c r="C2235" t="inlineStr">
+        <is>
+          <t>话一出口，我便意识到自己的解释漏洞百出。</t>
+        </is>
+      </c>
+      <c r="D2235" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P099; church.1020.s1.wisdom_fail; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2236">
+      <c r="B2236" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p100.text</t>
+        </is>
+      </c>
+      <c r="C2236" t="inlineStr">
+        <is>
+          <t>「可能？应该？{playername}店长，你连自己要解释什么都不知道。」</t>
+        </is>
+      </c>
+      <c r="D2236" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P100; church.1020.s1.wisdom_fail; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2237">
+      <c r="B2237" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p101.text</t>
+        </is>
+      </c>
+      <c r="C2237" t="inlineStr">
+        <is>
+          <t>我试图继续补充，却只能让事情变得更加糟糕。</t>
+        </is>
+      </c>
+      <c r="D2237" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P101; church.1020.s1.wisdom_fail; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2238">
+      <c r="B2238" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p102.text</t>
+        </is>
+      </c>
+      <c r="C2238" t="inlineStr">
+        <is>
+          <t>「你的说辞无法令人信服。」「先把人带走，信件作为证物收存。」</t>
+        </is>
+      </c>
+      <c r="D2238" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P102; church.1020.s1.wisdom_fail; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2239">
+      <c r="B2239" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p104.text</t>
+        </is>
+      </c>
+      <c r="C2239" t="inlineStr">
+        <is>
+          <t>我注意到监察官虽然拿着信纸，却没有认真揣摩上面的数字含义，反而仔细观察着我的反应</t>
+        </is>
+      </c>
+      <c r="D2239" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P104; church.1020.s1.perception_intro; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2240">
+      <c r="B2240" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p106.text</t>
+        </is>
+      </c>
+      <c r="C2240" t="inlineStr">
+        <is>
+          <t>我看出来了，他并没有读懂信上的内容，他在意的是我是否会因此露出破绽</t>
+        </is>
+      </c>
+      <c r="D2240" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P106; church.1020.s1.perception_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2241">
+      <c r="B2241" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p107.text</t>
+        </is>
+      </c>
+      <c r="C2241" t="inlineStr">
+        <is>
+          <t>我让自己的语气尽量平稳，目光坦荡地对上监察官探究的眼神</t>
+        </is>
+      </c>
+      <c r="D2241" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P107; church.1020.s1.perception_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2242">
+      <c r="B2242" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p108.text</t>
+        </is>
+      </c>
+      <c r="C2242" t="inlineStr">
+        <is>
+          <t>「这不过是前任店长给我留下的店铺内部的账单罢了，这样的单子我这还有很多。不知道长官您要搜查的是什么，但想必是与国家大事相关，我想不会是这种写了一串普通数字的私人信件吧。」</t>
+        </is>
+      </c>
+      <c r="D2242" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P108; church.1020.s1.perception_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2243">
+      <c r="B2243" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p109.text</t>
+        </is>
+      </c>
+      <c r="C2243" t="inlineStr">
+        <is>
+          <t>监察官听了我话又探究地看了信纸两眼</t>
+        </is>
+      </c>
+      <c r="D2243" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P109; church.1020.s1.perception_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2244">
+      <c r="B2244" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p110.text</t>
+        </is>
+      </c>
+      <c r="C2244" t="inlineStr">
+        <is>
+          <t>我趁势说道</t>
+        </is>
+      </c>
+      <c r="D2244" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P110; church.1020.s1.perception_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2245">
+      <c r="B2245" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p111.text</t>
+        </is>
+      </c>
+      <c r="C2245" t="inlineStr">
+        <is>
+          <t>「您可以把它带回去找人辨认。但我相信，无论如何解读，它都只是一张记录店铺经营状况的账单。」</t>
+        </is>
+      </c>
+      <c r="D2245" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P111; church.1020.s1.perception_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2246">
+      <c r="B2246" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p112.text</t>
+        </is>
+      </c>
+      <c r="C2246" t="inlineStr">
+        <is>
+          <t>监察官看向身后的监察员。对方检查了信纸和抽屉，低声说了几句，似乎没有发现新的线索。</t>
+        </is>
+      </c>
+      <c r="D2246" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P112; church.1020.s1.perception_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2247">
+      <c r="B2247" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p113.text</t>
+        </is>
+      </c>
+      <c r="C2247" t="inlineStr">
+        <is>
+          <t>「……暂时按普通信件处理。你继续营业，但近期不要离开圣徒街。」</t>
+        </is>
+      </c>
+      <c r="D2247" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P113; church.1020.s1.perception_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2248">
+      <c r="B2248" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p114.text</t>
+        </is>
+      </c>
+      <c r="C2248" t="inlineStr">
+        <is>
+          <t>「我知道了。」</t>
+        </is>
+      </c>
+      <c r="D2248" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P114; church.1020.s1.perception_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2249">
+      <c r="B2249" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p116.text</t>
+        </is>
+      </c>
+      <c r="C2249" t="inlineStr">
+        <is>
+          <t>我试图观察监察官的脸色以获取更多信息，却没能从他的神情中看出任何端倪。</t>
+        </is>
+      </c>
+      <c r="D2249" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P116; church.1020.s1.perception_fail; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2250">
+      <c r="B2250" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p117.text</t>
+        </is>
+      </c>
+      <c r="C2250" t="inlineStr">
+        <is>
+          <t>「我不知道它是什么……或许是前任店长给我留下的信息吧……前任店长在店里留下了不少东西，我还没有一一检查。」</t>
+        </is>
+      </c>
+      <c r="D2250" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P117; church.1020.s1.perception_fail; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2251">
+      <c r="B2251" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p118.text</t>
+        </is>
+      </c>
+      <c r="C2251" t="inlineStr">
+        <is>
+          <t>「你说自己没有检查过，却在我没有给你出示这封信具体内容的情况下说这是前任店长留下的。显然，你的解释站不住脚。」</t>
+        </is>
+      </c>
+      <c r="D2251" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P118; church.1020.s1.perception_fail; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2252">
+      <c r="B2252" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p119.text</t>
+        </is>
+      </c>
+      <c r="C2252" t="inlineStr">
+        <is>
+          <t>他似笑非笑地看着我</t>
+        </is>
+      </c>
+      <c r="D2252" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P119; church.1020.s1.perception_fail; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2253">
+      <c r="B2253" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p120.text</t>
+        </is>
+      </c>
+      <c r="C2253" t="inlineStr">
+        <is>
+          <t>我这才意识到，自己的话已经被对方抓住了漏洞。</t>
+        </is>
+      </c>
+      <c r="D2253" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P120; church.1020.s1.perception_fail; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2254">
+      <c r="B2254" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p121.text</t>
+        </is>
+      </c>
+      <c r="C2254" t="inlineStr">
+        <is>
+          <t>监察官示意监察员上前，将信纸递交给他，随后监察员将信纸收进一个文件袋中。</t>
+        </is>
+      </c>
+      <c r="D2254" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P121; church.1020.s1.perception_fail; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2255">
+      <c r="B2255" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p122.text</t>
+        </is>
+      </c>
+      <c r="C2255" t="inlineStr">
+        <is>
+          <t>「带走。等你想清楚之后，再向我们解释。」</t>
+        </is>
+      </c>
+      <c r="D2255" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P122; church.1020.s1.perception_fail; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2256">
+      <c r="B2256" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p124.text</t>
+        </is>
+      </c>
+      <c r="C2256" t="inlineStr">
+        <is>
+          <t>很快，教会监察司的人离开了咖啡馆，前往圣徒街其他店铺里搜寻</t>
+        </is>
+      </c>
+      <c r="D2256" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P124; church.1020.s1.cleared; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2257">
+      <c r="B2257" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p125.text</t>
+        </is>
+      </c>
+      <c r="C2257" t="inlineStr">
+        <is>
+          <t>他们离开后，阿黛尔赶紧跑过来关切地询问我</t>
+        </is>
+      </c>
+      <c r="D2257" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P125; church.1020.s1.cleared; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2258">
+      <c r="B2258" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p126.text</t>
+        </is>
+      </c>
+      <c r="C2258" t="inlineStr">
+        <is>
+          <t>「{playername}店长，你刚才真实太厉害了！面对教会监察司的人还能如此镇定地面对！」</t>
+        </is>
+      </c>
+      <c r="D2258" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P126; church.1020.s1.cleared; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2259">
+      <c r="B2259" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p127.text</t>
+        </is>
+      </c>
+      <c r="C2259" t="inlineStr">
+        <is>
+          <t>听完阿黛尔的话我感到一丝无奈，原来刚才的我在她眼里是这样的吗</t>
+        </is>
+      </c>
+      <c r="D2259" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P127; church.1020.s1.cleared; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2260">
+      <c r="B2260" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p128.text</t>
+        </is>
+      </c>
+      <c r="C2260" t="inlineStr">
+        <is>
+          <t>我现在感到一丝后怕，如果刚才没有应对得当，现在的我是会被他们带走审问吗？</t>
+        </is>
+      </c>
+      <c r="D2260" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P128; church.1020.s1.cleared; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2261">
+      <c r="B2261" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p129.text</t>
+        </is>
+      </c>
+      <c r="C2261" t="inlineStr">
+        <is>
+          <t>幸好我事先有想好万一被发现应当如何应对，才逃过这一劫</t>
+        </is>
+      </c>
+      <c r="D2261" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P129; church.1020.s1.cleared; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2262">
+      <c r="B2262" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p130.text</t>
+        </is>
+      </c>
+      <c r="C2262" t="inlineStr">
+        <is>
+          <t>看来以后需要把这些东西隐藏得更加隐蔽才好。不，还是赶紧找个机会把信都给烧掉吧</t>
+        </is>
+      </c>
+      <c r="D2262" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P130; church.1020.s1.cleared; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2263">
+      <c r="B2263" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p131.text</t>
+        </is>
+      </c>
+      <c r="C2263" t="inlineStr">
+        <is>
+          <t>阿黛尔不休的话打断了我的思绪</t>
+        </is>
+      </c>
+      <c r="D2263" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P131; church.1020.s1.cleared; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2264">
+      <c r="B2264" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p132.text</t>
+        </is>
+      </c>
+      <c r="C2264" t="inlineStr">
+        <is>
+          <t>「不过刚才由于监察司的到来，好多顾客都离开了呢……不知道接下来生意会不会受到影响……」</t>
+        </is>
+      </c>
+      <c r="D2264" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P132; church.1020.s1.cleared; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2265">
+      <c r="B2265" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p133.text</t>
+        </is>
+      </c>
+      <c r="C2265" t="inlineStr">
+        <is>
+          <t>这时我才想起刚才被迫停留在我和监察司中间的倒霉顾客</t>
+        </is>
+      </c>
+      <c r="D2265" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P133; church.1020.s1.cleared; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2266">
+      <c r="B2266" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p134.text</t>
+        </is>
+      </c>
+      <c r="C2266" t="inlineStr">
+        <is>
+          <t>目前店里没有发现那位顾客的身影，或许是什么时候趁乱离开了吧</t>
+        </is>
+      </c>
+      <c r="D2266" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P134; church.1020.s1.cleared; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2267">
+      <c r="B2267" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p135.text</t>
+        </is>
+      </c>
+      <c r="C2267" t="inlineStr">
+        <is>
+          <t>店里的设备没有遭到损坏，看来监察司搜查的时候还是有分寸的</t>
+        </is>
+      </c>
+      <c r="D2267" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P135; church.1020.s1.cleared; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2268">
+      <c r="B2268" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p136.text</t>
+        </is>
+      </c>
+      <c r="C2268" t="inlineStr">
+        <is>
+          <t>今天发生了这样的事，未来几天还是低调点吧</t>
+        </is>
+      </c>
+      <c r="D2268" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P136; church.1020.s1.cleared; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2269">
+      <c r="B2269" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p137.text</t>
+        </is>
+      </c>
+      <c r="C2269" t="inlineStr">
+        <is>
+          <t>「希望不会吧。阿黛尔，未来两天我们还是正常营业，但是低调一些。我担心再次引来什么大麻烦。」</t>
+        </is>
+      </c>
+      <c r="D2269" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P137; church.1020.s1.cleared; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2270">
+      <c r="B2270" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p138.text</t>
+        </is>
+      </c>
+      <c r="C2270" t="inlineStr">
+        <is>
+          <t>「我也正有此意呢，店长！」</t>
+        </is>
+      </c>
+      <c r="D2270" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P138; church.1020.s1.cleared; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2271">
+      <c r="B2271" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p139.text</t>
+        </is>
+      </c>
+      <c r="C2271" t="inlineStr">
+        <is>
+          <t>「阿黛尔，振作精神，我们还要准备迎接接下来的客人呢！」</t>
+        </is>
+      </c>
+      <c r="D2271" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P139; church.1020.s1.cleared; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2272">
+      <c r="B2272" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p140.text</t>
+        </is>
+      </c>
+      <c r="C2272" t="inlineStr">
+        <is>
+          <t>「店长，你说得对！那我去门口继续招揽一下客人~」</t>
+        </is>
+      </c>
+      <c r="D2272" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P140; church.1020.s1.cleared; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2273">
+      <c r="B2273" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p141.text</t>
+        </is>
+      </c>
+      <c r="C2273" t="inlineStr">
+        <is>
+          <t>阿黛尔蹦蹦跳跳地离开了</t>
+        </is>
+      </c>
+      <c r="D2273" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P141; church.1020.s1.cleared; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2274">
+      <c r="B2274" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p142.text</t>
+        </is>
+      </c>
+      <c r="C2274" t="inlineStr">
+        <is>
+          <t>我趁机将几封信烧毁，然后若无其事地回到吧台</t>
+        </is>
+      </c>
+      <c r="D2274" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P142; church.1020.s1.cleared; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2275">
+      <c r="B2275" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p144.text</t>
+        </is>
+      </c>
+      <c r="C2275" t="inlineStr">
+        <is>
+          <t>不知道接下来会迎接怎样的挑战和危机呢……</t>
+        </is>
+      </c>
+      <c r="D2275" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P144; church.1020.s1.cleared; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2276">
+      <c r="B2276" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p147.text</t>
+        </is>
+      </c>
+      <c r="C2276" t="inlineStr">
+        <is>
+          <t>我在所有人的注视下被监察司的人带走了，离开咖啡馆前我最后看见的是阿黛尔满是担忧的脸</t>
+        </is>
+      </c>
+      <c r="D2276" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P147; church.1020.s1.detained; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2277">
+      <c r="B2277" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p148.text</t>
+        </is>
+      </c>
+      <c r="C2277" t="inlineStr">
+        <is>
+          <t>他们会如何审问我呢？我要说什么呢？这封信涉及的密文是否会被他们觉察呢？</t>
+        </is>
+      </c>
+      <c r="D2277" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P148; church.1020.s1.detained; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2278">
+      <c r="B2278" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p149.text</t>
+        </is>
+      </c>
+      <c r="C2278" t="inlineStr">
+        <is>
+          <t>带着万千思绪，我被带到了教会看守所中</t>
+        </is>
+      </c>
+      <c r="D2278" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P149; church.1020.s1.detained; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2279">
+      <c r="B2279" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p150.text</t>
+        </is>
+      </c>
+      <c r="C2279" t="inlineStr">
+        <is>
+          <t>啊，从刚毕业的大学生到咖啡馆店长再到在押犯原来只需要一个月吗……</t>
+        </is>
+      </c>
+      <c r="D2279" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P150; church.1020.s1.detained; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2280">
+      <c r="B2280" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p151.text</t>
+        </is>
+      </c>
+      <c r="C2280" t="inlineStr">
+        <is>
+          <t>我被分配进了一个单独的房间，等待监察司的检查结果</t>
+        </is>
+      </c>
+      <c r="D2280" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P151; church.1020.s1.detained; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2281">
+      <c r="B2281" t="inlineStr">
+        <is>
+          <t>church.1020.s1.p152.text</t>
+        </is>
+      </c>
+      <c r="C2281" t="inlineStr">
+        <is>
+          <t>我就此陷入了无尽的等待</t>
+        </is>
+      </c>
+      <c r="D2281" t="inlineStr">
+        <is>
+          <t>church.1020.s1.P152; church.1020.s1.detained; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2282">
+      <c r="B2282" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p006.text</t>
+        </is>
+      </c>
+      <c r="C2282" t="inlineStr">
+        <is>
+          <t>我被带到看守所后，已经见证了第三次日出。</t>
+        </is>
+      </c>
+      <c r="D2282" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P006; church.1023.s1.hearing; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2283">
+      <c r="B2283" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p007.text</t>
+        </is>
+      </c>
+      <c r="C2283" t="inlineStr">
+        <is>
+          <t>在这间狭小的拘押室里，我甚至开始怀念咖啡馆那张吱呀作响的旧椅子。</t>
+        </is>
+      </c>
+      <c r="D2283" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P007; church.1023.s1.hearing; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2284">
+      <c r="B2284" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p008.text</t>
+        </is>
+      </c>
+      <c r="C2284" t="inlineStr">
+        <is>
+          <t>不知道阿黛尔现在怎么样了，咖啡馆有没有正常营业……</t>
+        </is>
+      </c>
+      <c r="D2284" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P008; church.1023.s1.hearing; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2285">
+      <c r="B2285" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p010.text</t>
+        </is>
+      </c>
+      <c r="C2285" t="inlineStr">
+        <is>
+          <t>⌈出来，有人要见你。⌋</t>
+        </is>
+      </c>
+      <c r="D2285" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P010; church.1023.s1.hearing; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2286">
+      <c r="B2286" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p013.text</t>
+        </is>
+      </c>
+      <c r="C2286" t="inlineStr">
+        <is>
+          <t>⌈经过调查，我们没有发现你直接参与非法结社活动的证据。⌋</t>
+        </is>
+      </c>
+      <c r="D2286" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P013; church.1023.s1.hearing; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2287">
+      <c r="B2287" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p014.text</t>
+        </is>
+      </c>
+      <c r="C2287" t="inlineStr">
+        <is>
+          <t>⌈所以我可以离开了？⌋</t>
+        </is>
+      </c>
+      <c r="D2287" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P014; church.1023.s1.hearing; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2288">
+      <c r="B2288" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p015.text</t>
+        </is>
+      </c>
+      <c r="C2288" t="inlineStr">
+        <is>
+          <t>⌈别急。那些密文的来源仍然不明，我们还需要你作出一些保证。⌋</t>
+        </is>
+      </c>
+      <c r="D2288" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P015; church.1023.s1.hearing; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2289">
+      <c r="B2289" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p016.text</t>
+        </is>
+      </c>
+      <c r="C2289" t="inlineStr">
+        <is>
+          <t>⌈如果今后发现任何与乱党有关的情报，你必须向教会报告。⌋</t>
+        </is>
+      </c>
+      <c r="D2289" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P016; church.1023.s1.hearing; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2290">
+      <c r="B2290" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p017.text</t>
+        </is>
+      </c>
+      <c r="C2290" t="inlineStr">
+        <is>
+          <t>⌈……⌋</t>
+        </is>
+      </c>
+      <c r="D2290" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P017; church.1023.s1.hearing; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2291">
+      <c r="B2291" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p018.text</t>
+        </is>
+      </c>
+      <c r="C2291" t="inlineStr">
+        <is>
+          <t>⌈你也可以拒绝。但调查结束前，我们恐怕不能放你走。⌋</t>
+        </is>
+      </c>
+      <c r="D2291" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P018; church.1023.s1.hearing; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2292">
+      <c r="B2292" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p019.text</t>
+        </is>
+      </c>
+      <c r="C2292" t="inlineStr">
+        <is>
+          <t>他看了看桌上的文件，似乎在等待我的回答。</t>
+        </is>
+      </c>
+      <c r="D2292" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P019; church.1023.s1.hearing; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2293">
+      <c r="B2293" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p021.text</t>
+        </is>
+      </c>
+      <c r="C2293" t="inlineStr">
+        <is>
+          <t>⌈既然没有犯罪证据，你们就没有理由继续拘押我。⌋</t>
+        </is>
+      </c>
+      <c r="D2293" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P021; church.1023.s1.hearing; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2294">
+      <c r="B2294" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p022.text</t>
+        </is>
+      </c>
+      <c r="C2294" t="inlineStr">
+        <is>
+          <t>⌈或许我们可以商量一个更方便的解决办法。⌋</t>
+        </is>
+      </c>
+      <c r="D2294" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P022; church.1023.s1.hearing; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2295">
+      <c r="B2295" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p023.text</t>
+        </is>
+      </c>
+      <c r="C2295" t="inlineStr">
+        <is>
+          <t>⌈既然如此，你们就继续调查吧。⌋</t>
+        </is>
+      </c>
+      <c r="D2295" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P023; church.1023.s1.hearing; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2296">
+      <c r="B2296" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p025.text</t>
+        </is>
+      </c>
+      <c r="C2296" t="inlineStr">
+        <is>
+          <t>⌈没有证据就继续拘押一位合法经营的店主，这恐怕也不符合教会的规定吧？⌋</t>
+        </is>
+      </c>
+      <c r="D2296" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P025; church.1023.s1.persuade; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2297">
+      <c r="B2297" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p026.text</t>
+        </is>
+      </c>
+      <c r="C2297" t="inlineStr">
+        <is>
+          <t>⌈你是在质疑监察司的决定？⌋</t>
+        </is>
+      </c>
+      <c r="D2297" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P026; church.1023.s1.persuade; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2298">
+      <c r="B2298" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p027.text</t>
+        </is>
+      </c>
+      <c r="C2298" t="inlineStr">
+        <is>
+          <t>⌈我当然尊重教会的职责，但你刚刚也说了，调查没有发现我参与乱党的证据。⌋</t>
+        </is>
+      </c>
+      <c r="D2298" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P027; church.1023.s1.persuade; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2299">
+      <c r="B2299" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p028.text</t>
+        </is>
+      </c>
+      <c r="C2299" t="inlineStr">
+        <is>
+          <t>⌈况且，沸点咖啡馆在圣徒街经营了那么多年，应该不算一家完全没有人认识的店铺。⌋⌈你们可以向街坊邻居调查，也可以在之后继续观察咖啡馆的经营。但至少现在，没有必要让我继续待在这里。⌋</t>
+        </is>
+      </c>
+      <c r="D2299" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P028; church.1023.s1.persuade; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2300">
+      <c r="B2300" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p029.text</t>
+        </is>
+      </c>
+      <c r="C2300" t="inlineStr">
+        <is>
+          <t>⌈嗯……⌋</t>
+        </is>
+      </c>
+      <c r="D2300" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P029; church.1023.s1.persuade; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2301">
+      <c r="B2301" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p032.text</t>
+        </is>
+      </c>
+      <c r="C2301" t="inlineStr">
+        <is>
+          <t>⌈倒也有些道理。⌋</t>
+        </is>
+      </c>
+      <c r="D2301" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P032; church.1023.s1.persuade_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2302">
+      <c r="B2302" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p033.text</t>
+        </is>
+      </c>
+      <c r="C2302" t="inlineStr">
+        <is>
+          <t>他沉思片刻，在文件上签了字。</t>
+        </is>
+      </c>
+      <c r="D2302" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P033; church.1023.s1.persuade_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2303">
+      <c r="B2303" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p034.text</t>
+        </is>
+      </c>
+      <c r="C2303" t="inlineStr">
+        <is>
+          <t>⌈好吧，你可以走了。但调查还没结束，今后记得配合监察司。⌋</t>
+        </is>
+      </c>
+      <c r="D2303" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P034; church.1023.s1.persuade_pass; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2304">
+      <c r="B2304" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p037.text</t>
+        </is>
+      </c>
+      <c r="C2304" t="inlineStr">
+        <is>
+          <t>⌈是否符合规定，恐怕还轮不到你来判断。带他回去。⌋</t>
+        </is>
+      </c>
+      <c r="D2304" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P037; church.1023.s1.persuade_fail; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2305">
+      <c r="B2305" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p040.text</t>
+        </is>
+      </c>
+      <c r="C2305" t="inlineStr">
+        <is>
+          <t>⌈继续调查既耽误你们的时间，也耽误我的生意。或许有个对双方都方便的办法？⌋</t>
+        </is>
+      </c>
+      <c r="D2305" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P040; church.1023.s1.bribe; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2306">
+      <c r="B2306" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p041.text</t>
+        </is>
+      </c>
+      <c r="C2306" t="inlineStr">
+        <is>
+          <t>我暗示了一下能够支付的金额。</t>
+        </is>
+      </c>
+      <c r="D2306" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P041; church.1023.s1.bribe; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2307">
+      <c r="B2307" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p042.text</t>
+        </is>
+      </c>
+      <c r="C2307" t="inlineStr">
+        <is>
+          <t>监察官抬起头，意味深长地看了我一眼。</t>
+        </is>
+      </c>
+      <c r="D2307" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P042; church.1023.s1.bribe; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2308">
+      <c r="B2308" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p043.text</t>
+        </is>
+      </c>
+      <c r="C2308" t="inlineStr">
+        <is>
+          <t>⌈你是沸点咖啡馆的店长是吧？一会儿我派人跟着你去，把钱打点清楚再说。⌋</t>
+        </is>
+      </c>
+      <c r="D2308" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P043; church.1023.s1.bribe; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2309">
+      <c r="B2309" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p044.text</t>
+        </is>
+      </c>
+      <c r="C2309" t="inlineStr">
+        <is>
+          <t>⌈好的，好的，当然可以。⌋</t>
+        </is>
+      </c>
+      <c r="D2309" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P044; church.1023.s1.bribe; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2310">
+      <c r="B2310" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p045.text</t>
+        </is>
+      </c>
+      <c r="C2310" t="inlineStr">
+        <is>
+          <t>⌈不过我要这个数。⌋</t>
+        </is>
+      </c>
+      <c r="D2310" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P045; church.1023.s1.bribe; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2311">
+      <c r="B2311" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p046.text</t>
+        </is>
+      </c>
+      <c r="C2311" t="inlineStr">
+        <is>
+          <t>⌈抢劫啊？⌋</t>
+        </is>
+      </c>
+      <c r="D2311" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P046; church.1023.s1.bribe; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2312">
+      <c r="B2312" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p047.text</t>
+        </is>
+      </c>
+      <c r="C2312" t="inlineStr">
+        <is>
+          <t>⌈哎，看来你不乐意，那就只好多关几天咯！⌋</t>
+        </is>
+      </c>
+      <c r="D2312" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P047; church.1023.s1.bribe; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2313">
+      <c r="B2313" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p048.text</t>
+        </is>
+      </c>
+      <c r="C2313" t="inlineStr">
+        <is>
+          <t>⌈嘶......看来你是个聪明人。既然没有发现犯罪证据，我们当然没有必要继续浪费时间。⌋</t>
+        </is>
+      </c>
+      <c r="D2313" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P048; church.1023.s1.bribe; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2314">
+      <c r="B2314" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p054.text</t>
+        </is>
+      </c>
+      <c r="C2314" t="inlineStr">
+        <is>
+          <t>看来今天又得在这里过夜了。</t>
+        </is>
+      </c>
+      <c r="D2314" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P054; church.1023.s1.rescue; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2315">
+      <c r="B2315" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p055.text</t>
+        </is>
+      </c>
+      <c r="C2315" t="inlineStr">
+        <is>
+          <t>我靠在墙边，正想着阿黛尔会不会已经把我当成失踪人口，铁门却再次打开了。</t>
+        </is>
+      </c>
+      <c r="D2315" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P055; church.1023.s1.rescue; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2316">
+      <c r="B2316" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p057.text</t>
+        </is>
+      </c>
+      <c r="C2316" t="inlineStr">
+        <is>
+          <t>⌈出来，你可以走了。⌋</t>
+        </is>
+      </c>
+      <c r="D2316" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P057; church.1023.s1.rescue; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2317">
+      <c r="B2317" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p058.text</t>
+        </is>
+      </c>
+      <c r="C2317" t="inlineStr">
+        <is>
+          <t>⌈啊？可是刚刚不是还说……⌋</t>
+        </is>
+      </c>
+      <c r="D2317" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P058; church.1023.s1.rescue; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2318">
+      <c r="B2318" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p059.text</t>
+        </is>
+      </c>
+      <c r="C2318" t="inlineStr">
+        <is>
+          <t>⌈上面送来了新的释放手续。你还想留下来不成？⌋</t>
+        </is>
+      </c>
+      <c r="D2318" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P059; church.1023.s1.rescue; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2319">
+      <c r="B2319" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p060.text</t>
+        </is>
+      </c>
+      <c r="C2319" t="inlineStr">
+        <is>
+          <t>他将一份盖好印章的文件塞进我手中。</t>
+        </is>
+      </c>
+      <c r="D2319" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P060; church.1023.s1.rescue; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2320">
+      <c r="B2320" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p061.text</t>
+        </is>
+      </c>
+      <c r="C2320" t="inlineStr">
+        <is>
+          <t>上面清清楚楚地写着：「证据不足，准予释放。」</t>
+        </is>
+      </c>
+      <c r="D2320" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P061; church.1023.s1.rescue; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2321">
+      <c r="B2321" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p062.text</t>
+        </is>
+      </c>
+      <c r="C2321" t="inlineStr">
+        <is>
+          <t>怎么突然就证据不足了？</t>
+        </is>
+      </c>
+      <c r="D2321" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P062; church.1023.s1.rescue; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2322">
+      <c r="B2322" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p063.text</t>
+        </is>
+      </c>
+      <c r="C2322" t="inlineStr">
+        <is>
+          <t>不过，我当然没有理由拒绝。</t>
+        </is>
+      </c>
+      <c r="D2322" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P063; church.1023.s1.rescue; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2323">
+      <c r="B2323" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p065.text</t>
+        </is>
+      </c>
+      <c r="C2323" t="inlineStr">
+        <is>
+          <t>我看了看那张文件。</t>
+        </is>
+      </c>
+      <c r="D2323" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P065; church.1023.s1.record_notice; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2324">
+      <c r="B2324" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p066.text</t>
+        </is>
+      </c>
+      <c r="C2324" t="inlineStr">
+        <is>
+          <t>上面的印章和其他文书没有什么区别。</t>
+        </is>
+      </c>
+      <c r="D2324" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P066; church.1023.s1.record_notice; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2325">
+      <c r="B2325" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p067.text</t>
+        </is>
+      </c>
+      <c r="C2325" t="inlineStr">
+        <is>
+          <t>不过，在旁边的登记簿上，我的名字似乎被人重新填写过一次。</t>
+        </is>
+      </c>
+      <c r="D2325" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P067; church.1023.s1.record_notice; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2326">
+      <c r="B2326" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p068.text</t>
+        </is>
+      </c>
+      <c r="C2326" t="inlineStr">
+        <is>
+          <t>原本的字迹已经被墨水覆盖，又用另一种笔迹写上了新的处理结果。</t>
+        </is>
+      </c>
+      <c r="D2326" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P068; church.1023.s1.record_notice; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2327">
+      <c r="B2327" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p069.text</t>
+        </is>
+      </c>
+      <c r="C2327" t="inlineStr">
+        <is>
+          <t>而且，记录上标注的释放时间，似乎比我刚刚被带回牢房的时间还要早。</t>
+        </is>
+      </c>
+      <c r="D2327" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P069; church.1023.s1.record_notice; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2328">
+      <c r="B2328" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p070.text</t>
+        </is>
+      </c>
+      <c r="C2328" t="inlineStr">
+        <is>
+          <t>……</t>
+        </is>
+      </c>
+      <c r="D2328" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P070; church.1023.s1.record_notice; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2329">
+      <c r="B2329" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p071.text</t>
+        </is>
+      </c>
+      <c r="C2329" t="inlineStr">
+        <is>
+          <t>有人修改了我的拘押记录？</t>
+        </is>
+      </c>
+      <c r="D2329" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P071; church.1023.s1.record_notice; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2330">
+      <c r="B2330" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p073.text</t>
+        </is>
+      </c>
+      <c r="C2330" t="inlineStr">
+        <is>
+          <t>⌈请问，是谁批准释放我的？⌋</t>
+        </is>
+      </c>
+      <c r="D2330" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P073; church.1023.s1.rescue_depart; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2331">
+      <c r="B2331" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p074.text</t>
+        </is>
+      </c>
+      <c r="C2331" t="inlineStr">
+        <is>
+          <t>⌈登记上写得很清楚，按照规定处理的。⌋</t>
+        </is>
+      </c>
+      <c r="D2331" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P074; church.1023.s1.rescue_depart; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2332">
+      <c r="B2332" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p075.text</t>
+        </is>
+      </c>
+      <c r="C2332" t="inlineStr">
+        <is>
+          <t>⌈我是说，刚刚是谁来办理手续的？⌋</t>
+        </is>
+      </c>
+      <c r="D2332" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P075; church.1023.s1.rescue_depart; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2333">
+      <c r="B2333" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p076.text</t>
+        </is>
+      </c>
+      <c r="C2333" t="inlineStr">
+        <is>
+          <t>⌈我哪知道？今天送过来的文件这么多。⌋</t>
+        </is>
+      </c>
+      <c r="D2333" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P076; church.1023.s1.rescue_depart; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2334">
+      <c r="B2334" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p077.text</t>
+        </is>
+      </c>
+      <c r="C2334" t="inlineStr">
+        <is>
+          <t>⌈话怎么这么多？再问我就和上面说你不服命令，重新把你关进去。⌋</t>
+        </is>
+      </c>
+      <c r="D2334" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P077; church.1023.s1.rescue_depart; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2335">
+      <c r="B2335" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p078.text</t>
+        </is>
+      </c>
+      <c r="C2335" t="inlineStr">
+        <is>
+          <t>⌈……⌋</t>
+        </is>
+      </c>
+      <c r="D2335" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P078; church.1023.s1.rescue_depart; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2336">
+      <c r="B2336" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p079.text</t>
+        </is>
+      </c>
+      <c r="C2336" t="inlineStr">
+        <is>
+          <t>算了。</t>
+        </is>
+      </c>
+      <c r="D2336" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P079; church.1023.s1.rescue_depart; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2337">
+      <c r="B2337" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p080.text</t>
+        </is>
+      </c>
+      <c r="C2337" t="inlineStr">
+        <is>
+          <t>不管究竟是谁帮了我，现在最重要的事情，还是赶紧离开这个地方。</t>
+        </is>
+      </c>
+      <c r="D2337" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P080; church.1023.s1.rescue_depart; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2338">
+      <c r="B2338" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p088.text</t>
+        </is>
+      </c>
+      <c r="C2338" t="inlineStr">
+        <is>
+          <t>⌈我回来了！⌋</t>
+        </is>
+      </c>
+      <c r="D2338" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P088; church.1023.s1.home; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2339">
+      <c r="B2339" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p089.text</t>
+        </is>
+      </c>
+      <c r="C2339" t="inlineStr">
+        <is>
+          <t>⌈……{playername}？⌋</t>
+        </is>
+      </c>
+      <c r="D2339" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P089; church.1023.s1.home; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2340">
+      <c r="B2340" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p090.text</t>
+        </is>
+      </c>
+      <c r="C2340" t="inlineStr">
+        <is>
+          <t>她愣了一下，随即快步走来。</t>
+        </is>
+      </c>
+      <c r="D2340" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P090; church.1023.s1.home; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2341">
+      <c r="B2341" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p091.text</t>
+        </is>
+      </c>
+      <c r="C2341" t="inlineStr">
+        <is>
+          <t>⌈你终于回来了！⌋</t>
+        </is>
+      </c>
+      <c r="D2341" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P091; church.1023.s1.home; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2342">
+      <c r="B2342" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p092.text</t>
+        </is>
+      </c>
+      <c r="C2342" t="inlineStr">
+        <is>
+          <t>⌈他们没有对你怎么样吧？⌋</t>
+        </is>
+      </c>
+      <c r="D2342" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P092; church.1023.s1.home; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2343">
+      <c r="B2343" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p093.text</t>
+        </is>
+      </c>
+      <c r="C2343" t="inlineStr">
+        <is>
+          <t>⌈没有没有，只是被关了几天。⌋</t>
+        </is>
+      </c>
+      <c r="D2343" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P093; church.1023.s1.home; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2344">
+      <c r="B2344" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p094.text</t>
+        </is>
+      </c>
+      <c r="C2344" t="inlineStr">
+        <is>
+          <t>⌈这还叫没什么！我去问了好几次，他们都不肯告诉我什么时候放你回来。⌋</t>
+        </is>
+      </c>
+      <c r="D2344" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P094; church.1023.s1.home; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2345">
+      <c r="B2345" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p095.text</t>
+        </is>
+      </c>
+      <c r="C2345" t="inlineStr">
+        <is>
+          <t>⌈抱歉，让你担心了。⌋</t>
+        </is>
+      </c>
+      <c r="D2345" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P095; church.1023.s1.home; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2346">
+      <c r="B2346" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p096.text</t>
+        </is>
+      </c>
+      <c r="C2346" t="inlineStr">
+        <is>
+          <t>⌈……回来就好。⌋</t>
+        </is>
+      </c>
+      <c r="D2346" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P096; church.1023.s1.home; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2347">
+      <c r="B2347" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p097.text</t>
+        </is>
+      </c>
+      <c r="C2347" t="inlineStr">
+        <is>
+          <t>她替我拉开椅子。</t>
+        </is>
+      </c>
+      <c r="D2347" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P097; church.1023.s1.home; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2348">
+      <c r="B2348" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p098.text</t>
+        </is>
+      </c>
+      <c r="C2348" t="inlineStr">
+        <is>
+          <t>⌈不过，他们怎么突然愿意放人了？⌋</t>
+        </is>
+      </c>
+      <c r="D2348" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P098; church.1023.s1.home; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2349">
+      <c r="B2349" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p101.text</t>
+        </is>
+      </c>
+      <c r="C2349" t="inlineStr">
+        <is>
+          <t>⌈他们本来也没找到犯罪证据，我和监察官讲了讲道理，就把我放了。⌋</t>
+        </is>
+      </c>
+      <c r="D2349" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P101; church.1023.s1.home_persuade; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2350">
+      <c r="B2350" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p102.text</t>
+        </is>
+      </c>
+      <c r="C2350" t="inlineStr">
+        <is>
+          <t>⌈那真是太好了，至少教会的人还愿意讲道理。⌋</t>
+        </is>
+      </c>
+      <c r="D2350" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P102; church.1023.s1.home_persuade; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2351">
+      <c r="B2351" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p103.text</t>
+        </is>
+      </c>
+      <c r="C2351" t="inlineStr">
+        <is>
+          <t>⌈不过，既然他们已经盯上了咖啡馆，以后还是得小心。⌋</t>
+        </is>
+      </c>
+      <c r="D2351" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P103; church.1023.s1.home_persuade; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2352">
+      <c r="B2352" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p105.text</t>
+        </is>
+      </c>
+      <c r="C2352" t="inlineStr">
+        <is>
+          <t>⌈花了点钱，总算让他们同意放人了。⌋</t>
+        </is>
+      </c>
+      <c r="D2352" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P105; church.1023.s1.home_bribe; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2353">
+      <c r="B2353" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p106.text</t>
+        </is>
+      </c>
+      <c r="C2353" t="inlineStr">
+        <is>
+          <t>⌈花钱？你是说……⌋</t>
+        </is>
+      </c>
+      <c r="D2353" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P106; church.1023.s1.home_bribe; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2354">
+      <c r="B2354" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p107.text</t>
+        </is>
+      </c>
+      <c r="C2354" t="inlineStr">
+        <is>
+          <t>⌈嘘！别说出来。⌋</t>
+        </is>
+      </c>
+      <c r="D2354" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P107; church.1023.s1.home_bribe; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2355">
+      <c r="B2355" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p108.text</t>
+        </is>
+      </c>
+      <c r="C2355" t="inlineStr">
+        <is>
+          <t>⌈这些人真是……⌋</t>
+        </is>
+      </c>
+      <c r="D2355" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P108; church.1023.s1.home_bribe; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2356">
+      <c r="B2356" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p109.text</t>
+        </is>
+      </c>
+      <c r="C2356" t="inlineStr">
+        <is>
+          <t>她叹了口气。</t>
+        </is>
+      </c>
+      <c r="D2356" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P109; church.1023.s1.home_bribe; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2357">
+      <c r="B2357" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p110.text</t>
+        </is>
+      </c>
+      <c r="C2357" t="inlineStr">
+        <is>
+          <t>⌈你一会让把钱筹一下送过去。⌋</t>
+        </is>
+      </c>
+      <c r="D2357" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P110; church.1023.s1.home_bribe; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2358">
+      <c r="B2358" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p111.text</t>
+        </is>
+      </c>
+      <c r="C2358" t="inlineStr">
+        <is>
+          <t>⌈我才不做这种事情呢！⌋</t>
+        </is>
+      </c>
+      <c r="D2358" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P111; church.1023.s1.home_bribe; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2359">
+      <c r="B2359" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p112.text</t>
+        </is>
+      </c>
+      <c r="C2359" t="inlineStr">
+        <is>
+          <t>⌈那行，一会儿我去干这脏活累活吧......⌋</t>
+        </is>
+      </c>
+      <c r="D2359" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P112; church.1023.s1.home_bribe; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2360">
+      <c r="B2360" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p114.text</t>
+        </is>
+      </c>
+      <c r="C2360" t="inlineStr">
+        <is>
+          <t>⌈说实话，我也不知道。他们本来还要继续调查，结果突然有人送来文件，说我可以走了。⌋</t>
+        </is>
+      </c>
+      <c r="D2360" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P114; church.1023.s1.home_rescue; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2361">
+      <c r="B2361" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p115.text</t>
+        </is>
+      </c>
+      <c r="C2361" t="inlineStr">
+        <is>
+          <t>⌈突然有人送来文件？⌋</t>
+        </is>
+      </c>
+      <c r="D2361" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P115; church.1023.s1.home_rescue; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2362">
+      <c r="B2362" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p116.text</t>
+        </is>
+      </c>
+      <c r="C2362" t="inlineStr">
+        <is>
+          <t>⌈是啊，连看守都不知道怎么回事。真奇怪。⌋</t>
+        </is>
+      </c>
+      <c r="D2362" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P116; church.1023.s1.home_rescue; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2363">
+      <c r="B2363" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p117.text</t>
+        </is>
+      </c>
+      <c r="C2363" t="inlineStr">
+        <is>
+          <t>阿黛尔似乎想到了什么，沉默了一会儿。</t>
+        </is>
+      </c>
+      <c r="D2363" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P117; church.1023.s1.home_rescue; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2364">
+      <c r="B2364" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p118.text</t>
+        </is>
+      </c>
+      <c r="C2364" t="inlineStr">
+        <is>
+          <t>⌈原来如此......⌋</t>
+        </is>
+      </c>
+      <c r="D2364" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P118; church.1023.s1.home_rescue; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2365">
+      <c r="B2365" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p119.text</t>
+        </is>
+      </c>
+      <c r="C2365" t="inlineStr">
+        <is>
+          <t>⌈你知道些什么？⌋</t>
+        </is>
+      </c>
+      <c r="D2365" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P119; church.1023.s1.home_rescue; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2366">
+      <c r="B2366" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p120.text</t>
+        </is>
+      </c>
+      <c r="C2366" t="inlineStr">
+        <is>
+          <t>⌈啊？没有，我也只是猜测……⌋</t>
+        </is>
+      </c>
+      <c r="D2366" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P120; church.1023.s1.home_rescue; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2367">
+      <c r="B2367" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p121.text</t>
+        </is>
+      </c>
+      <c r="C2367" t="inlineStr">
+        <is>
+          <t>⌈猜测什么？⌋</t>
+        </is>
+      </c>
+      <c r="D2367" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P121; church.1023.s1.home_rescue; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2368">
+      <c r="B2368" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p122.text</t>
+        </is>
+      </c>
+      <c r="C2368" t="inlineStr">
+        <is>
+          <t>⌈以前杜瓦尔先生经营咖啡馆的时候，认识不少人。有些人虽然不方便公开露面，但很重视这家店。⌋</t>
+        </is>
+      </c>
+      <c r="D2368" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P122; church.1023.s1.home_rescue; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2369">
+      <c r="B2369" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p123.text</t>
+        </is>
+      </c>
+      <c r="C2369" t="inlineStr">
+        <is>
+          <t>⌈如果他们知道你被教会带走了，或许不会坐视不管。⌋</t>
+        </is>
+      </c>
+      <c r="D2369" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P123; church.1023.s1.home_rescue; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2370">
+      <c r="B2370" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p124.text</t>
+        </is>
+      </c>
+      <c r="C2370" t="inlineStr">
+        <is>
+          <t>⌈你是说，有人暗中帮了我？⌋</t>
+        </is>
+      </c>
+      <c r="D2370" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P124; church.1023.s1.home_rescue; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2371">
+      <c r="B2371" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p125.text</t>
+        </is>
+      </c>
+      <c r="C2371" t="inlineStr">
+        <is>
+          <t>⌈只是猜测而已，我也不确定。⌋</t>
+        </is>
+      </c>
+      <c r="D2371" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P125; church.1023.s1.home_rescue; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2372">
+      <c r="B2372" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p126.text</t>
+        </is>
+      </c>
+      <c r="C2372" t="inlineStr">
+        <is>
+          <t>她低头整理起桌上的餐具，似乎不打算继续这个话题。</t>
+        </is>
+      </c>
+      <c r="D2372" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P126; church.1023.s1.home_rescue; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2373">
+      <c r="B2373" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p127.text</t>
+        </is>
+      </c>
+      <c r="C2373" t="inlineStr">
+        <is>
+          <t>⌈不过，如果真是他们……看来那些人还没有忘记这里。⌋</t>
+        </is>
+      </c>
+      <c r="D2373" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P127; church.1023.s1.home_rescue; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2374">
+      <c r="B2374" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p128.text</t>
+        </is>
+      </c>
+      <c r="C2374" t="inlineStr">
+        <is>
+          <t>⌈那些人？⌋</t>
+        </is>
+      </c>
+      <c r="D2374" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P128; church.1023.s1.home_rescue; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2375">
+      <c r="B2375" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p129.text</t>
+        </is>
+      </c>
+      <c r="C2375" t="inlineStr">
+        <is>
+          <t>⌈没什么。你才刚回来，先休息吧。⌋</t>
+        </is>
+      </c>
+      <c r="D2375" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P129; church.1023.s1.home_rescue; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2376">
+      <c r="B2376" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p131.text</t>
+        </is>
+      </c>
+      <c r="C2376" t="inlineStr">
+        <is>
+          <t>⌈总之，欢迎回来，店长先生。⌋</t>
+        </is>
+      </c>
+      <c r="D2376" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P131; church.1023.s1.home_end; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2377">
+      <c r="B2377" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p132.text</t>
+        </is>
+      </c>
+      <c r="C2377" t="inlineStr">
+        <is>
+          <t>⌈嗯，我回来了。⌋</t>
+        </is>
+      </c>
+      <c r="D2377" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P132; church.1023.s1.home_end; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2378">
+      <c r="B2378" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p133.text</t>
+        </is>
+      </c>
+      <c r="C2378" t="inlineStr">
+        <is>
+          <t>我靠在椅背上，终于松了口气。</t>
+        </is>
+      </c>
+      <c r="D2378" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P133; church.1023.s1.home_end; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2379">
+      <c r="B2379" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p134.text</t>
+        </is>
+      </c>
+      <c r="C2379" t="inlineStr">
+        <is>
+          <t>咖啡馆似乎什么都没有改变。</t>
+        </is>
+      </c>
+      <c r="D2379" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P134; church.1023.s1.home_end; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2380">
+      <c r="B2380" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p135.text</t>
+        </is>
+      </c>
+      <c r="C2380" t="inlineStr">
+        <is>
+          <t>不过我的心态已经完全不同，</t>
+        </is>
+      </c>
+      <c r="D2380" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P135; church.1023.s1.home_end; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2381">
+      <c r="B2381" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p136.text</t>
+        </is>
+      </c>
+      <c r="C2381" t="inlineStr">
+        <is>
+          <t>在监牢里度过的三天却让我后背发凉。</t>
+        </is>
+      </c>
+      <c r="D2381" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P136; church.1023.s1.home_end; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2382">
+      <c r="B2382" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p137.text</t>
+        </is>
+      </c>
+      <c r="C2382" t="inlineStr">
+        <is>
+          <t>我这次能因信的的事情被抓进去，下一次又会因为什么遭遇不测。</t>
+        </is>
+      </c>
+      <c r="D2382" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P137; church.1023.s1.home_end; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2383">
+      <c r="B2383" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p138.text</t>
+        </is>
+      </c>
+      <c r="C2383" t="inlineStr">
+        <is>
+          <t>三天前，教会监察司的人突然闯进咖啡馆，将我带走。</t>
+        </is>
+      </c>
+      <c r="D2383" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P138; church.1023.s1.home_end; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2384">
+      <c r="B2384" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p139.text</t>
+        </is>
+      </c>
+      <c r="C2384" t="inlineStr">
+        <is>
+          <t>三天后，我终于回到了这里。</t>
+        </is>
+      </c>
+      <c r="D2384" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P139; church.1023.s1.home_end; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2385">
+      <c r="B2385" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p140.text</t>
+        </is>
+      </c>
+      <c r="C2385" t="inlineStr">
+        <is>
+          <t>但那几封密文仍然被扣押在教会手中。</t>
+        </is>
+      </c>
+      <c r="D2385" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P140; church.1023.s1.home_end; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2386">
+      <c r="B2386" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p141.text</t>
+        </is>
+      </c>
+      <c r="C2386" t="inlineStr">
+        <is>
+          <t>而且，在离开看守所之前，他们还专门提醒我：</t>
+        </is>
+      </c>
+      <c r="D2386" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P141; church.1023.s1.home_end; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2387">
+      <c r="B2387" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p142.text</t>
+        </is>
+      </c>
+      <c r="C2387" t="inlineStr">
+        <is>
+          <t>如果发现有关乱党的情报，必须向教会报告。</t>
+        </is>
+      </c>
+      <c r="D2387" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P142; church.1023.s1.home_end; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2388">
+      <c r="B2388" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p143.text</t>
+        </is>
+      </c>
+      <c r="C2388" t="inlineStr">
+        <is>
+          <t>……</t>
+        </is>
+      </c>
+      <c r="D2388" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P143; church.1023.s1.home_end; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2389">
+      <c r="B2389" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p144.text</t>
+        </is>
+      </c>
+      <c r="C2389" t="inlineStr">
+        <is>
+          <t>这算什么意思？</t>
+        </is>
+      </c>
+      <c r="D2389" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P144; church.1023.s1.home_end; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2390">
+      <c r="B2390" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p145.text</t>
+        </is>
+      </c>
+      <c r="C2390" t="inlineStr">
+        <is>
+          <t>今后要是那个神秘人再给我送来几封信，难道我还得主动跑去监察司告诉他们？</t>
+        </is>
+      </c>
+      <c r="D2390" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P145; church.1023.s1.home_end; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2391">
+      <c r="B2391" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p146.text</t>
+        </is>
+      </c>
+      <c r="C2391" t="inlineStr">
+        <is>
+          <t>开什么玩笑。</t>
+        </is>
+      </c>
+      <c r="D2391" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P146; church.1023.s1.home_end; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2392">
+      <c r="B2392" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p147.text</t>
+        </is>
+      </c>
+      <c r="C2392" t="inlineStr">
+        <is>
+          <t>可是，如果不这么做……</t>
+        </is>
+      </c>
+      <c r="D2392" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P147; church.1023.s1.home_end; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2393">
+      <c r="B2393" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p148.text</t>
+        </is>
+      </c>
+      <c r="C2393" t="inlineStr">
+        <is>
+          <t>我抬起头，看向正在厨房里忙碌的阿黛尔。</t>
+        </is>
+      </c>
+      <c r="D2393" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P148; church.1023.s1.home_end; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2394">
+      <c r="B2394" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p149.text</t>
+        </is>
+      </c>
+      <c r="C2394" t="inlineStr">
+        <is>
+          <t>自从来到这家店，怪事就一个接着一个。</t>
+        </is>
+      </c>
+      <c r="D2394" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P149; church.1023.s1.home_end; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2395">
+      <c r="B2395" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p150.text</t>
+        </is>
+      </c>
+      <c r="C2395" t="inlineStr">
+        <is>
+          <t>王都圣诺特的漩涡下面究竟有多少骇人的存在？它们在谋划些什么？为什么我会被卷到这些事情里？我还能保护我和身边的人吗？</t>
+        </is>
+      </c>
+      <c r="D2395" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P150; church.1023.s1.home_end; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2396">
+      <c r="B2396" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p151.text</t>
+        </is>
+      </c>
+      <c r="C2396" t="inlineStr">
+        <is>
+          <t>三日关押积累下来的疲惫与巨大的思考量冲撞着我的思绪，</t>
+        </is>
+      </c>
+      <c r="D2396" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P151; church.1023.s1.home_end; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2397">
+      <c r="B2397" t="inlineStr">
+        <is>
+          <t>church.1023.s1.p152.text</t>
+        </is>
+      </c>
+      <c r="C2397" t="inlineStr">
+        <is>
+          <t>我再也无力去支撑精神，倒在座椅上睡去......</t>
+        </is>
+      </c>
+      <c r="D2397" t="inlineStr">
+        <is>
+          <t>church.1023.s1.P152; church.1023.s1.home_end; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2398">
+      <c r="B2398" t="inlineStr">
+        <is>
+          <t>church.1023.s2.p005.text</t>
+        </is>
+      </c>
+      <c r="C2398" t="inlineStr">
+        <is>
+          <t>距离上次与监察官会面又过了不知多少天</t>
+        </is>
+      </c>
+      <c r="D2398" t="inlineStr">
+        <is>
+          <t>church.1023.s2.P005; church.1023.s2.prison; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2399">
+      <c r="B2399" t="inlineStr">
+        <is>
+          <t>church.1023.s2.p006.text</t>
+        </is>
+      </c>
+      <c r="C2399" t="inlineStr">
+        <is>
+          <t>这段日子里我尝试与外界联系，却都失败了</t>
+        </is>
+      </c>
+      <c r="D2399" t="inlineStr">
+        <is>
+          <t>church.1023.s2.P006; church.1023.s2.prison; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2400">
+      <c r="B2400" t="inlineStr">
+        <is>
+          <t>church.1023.s2.p007.text</t>
+        </is>
+      </c>
+      <c r="C2400" t="inlineStr">
+        <is>
+          <t>我所能接触到的只有这四方墙壁</t>
+        </is>
+      </c>
+      <c r="D2400" t="inlineStr">
+        <is>
+          <t>church.1023.s2.P007; church.1023.s2.prison; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2401">
+      <c r="B2401" t="inlineStr">
+        <is>
+          <t>church.1023.s2.p008.text</t>
+        </is>
+      </c>
+      <c r="C2401" t="inlineStr">
+        <is>
+          <t>不知道今日是何日，不知道咖啡馆怎么样了，不知道阿黛尔怎么样了，不知道我离开之后神秘人是否还在接触咖啡馆……</t>
+        </is>
+      </c>
+      <c r="D2401" t="inlineStr">
+        <is>
+          <t>church.1023.s2.P008; church.1023.s2.prison; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2402">
+      <c r="B2402" t="inlineStr">
+        <is>
+          <t>church.1023.s2.p009.text</t>
+        </is>
+      </c>
+      <c r="C2402" t="inlineStr">
+        <is>
+          <t>不知道……不知道……什么都不知道……</t>
+        </is>
+      </c>
+      <c r="D2402" t="inlineStr">
+        <is>
+          <t>church.1023.s2.P009; church.1023.s2.prison; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2403">
+      <c r="B2403" t="inlineStr">
+        <is>
+          <t>church.1023.s2.p010.text</t>
+        </is>
+      </c>
+      <c r="C2403" t="inlineStr">
+        <is>
+          <t>我的意识在这种日子中渐渐模糊……</t>
+        </is>
+      </c>
+      <c r="D2403" t="inlineStr">
+        <is>
+          <t>church.1023.s2.P010; church.1023.s2.prison; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2404">
+      <c r="B2404" t="inlineStr">
+        <is>
+          <t>church.1023.s2.p013.text</t>
+        </is>
+      </c>
+      <c r="C2404" t="inlineStr">
+        <is>
+          <t>沉寂和单调，是我牢狱生活的全部</t>
+        </is>
+      </c>
+      <c r="D2404" t="inlineStr">
+        <is>
+          <t>church.1023.s2.P013; church.1023.s2.execution; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2405">
+      <c r="B2405" t="inlineStr">
+        <is>
+          <t>church.1023.s2.p014.text</t>
+        </is>
+      </c>
+      <c r="C2405" t="inlineStr">
+        <is>
+          <t>直到某一天我的世界出现了新的声音</t>
+        </is>
+      </c>
+      <c r="D2405" t="inlineStr">
+        <is>
+          <t>church.1023.s2.P014; church.1023.s2.execution; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2406">
+      <c r="B2406" t="inlineStr">
+        <is>
+          <t>church.1023.s2.p016.text</t>
+        </is>
+      </c>
+      <c r="C2406" t="inlineStr">
+        <is>
+          <t>那是几个穿着制服的人，走进了关押我的房间内</t>
+        </is>
+      </c>
+      <c r="D2406" t="inlineStr">
+        <is>
+          <t>church.1023.s2.P016; church.1023.s2.execution; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2407">
+      <c r="B2407" t="inlineStr">
+        <is>
+          <t>church.1023.s2.p017.text</t>
+        </is>
+      </c>
+      <c r="C2407" t="inlineStr">
+        <is>
+          <t>他们对着我说了一串话</t>
+        </is>
+      </c>
+      <c r="D2407" t="inlineStr">
+        <is>
+          <t>church.1023.s2.P017; church.1023.s2.execution; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2408">
+      <c r="B2408" t="inlineStr">
+        <is>
+          <t>church.1023.s2.p018.text</t>
+        </is>
+      </c>
+      <c r="C2408" t="inlineStr">
+        <is>
+          <t>但由于脱离外界太久，意识模糊，我只能隐隐约约辨认出几个词，什么「革命」 「镇压」 「清算」……</t>
+        </is>
+      </c>
+      <c r="D2408" t="inlineStr">
+        <is>
+          <t>church.1023.s2.P018; church.1023.s2.execution; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2409">
+      <c r="B2409" t="inlineStr">
+        <is>
+          <t>church.1023.s2.p019.text</t>
+        </is>
+      </c>
+      <c r="C2409" t="inlineStr">
+        <is>
+          <t>在我还未能理解这些词句的意思时</t>
+        </is>
+      </c>
+      <c r="D2409" t="inlineStr">
+        <is>
+          <t>church.1023.s2.P019; church.1023.s2.execution; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2410">
+      <c r="B2410" t="inlineStr">
+        <is>
+          <t>church.1023.s2.p020.text</t>
+        </is>
+      </c>
+      <c r="C2410" t="inlineStr">
+        <is>
+          <t>我感到我被他们强行从地上拉了起来，被推动着向外走</t>
+        </is>
+      </c>
+      <c r="D2410" t="inlineStr">
+        <is>
+          <t>church.1023.s2.P020; church.1023.s2.execution; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2411">
+      <c r="B2411" t="inlineStr">
+        <is>
+          <t>church.1023.s2.p021.text</t>
+        </is>
+      </c>
+      <c r="C2411" t="inlineStr">
+        <is>
+          <t>方墙以外的世界</t>
+        </is>
+      </c>
+      <c r="D2411" t="inlineStr">
+        <is>
+          <t>church.1023.s2.P021; church.1023.s2.execution; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2412">
+      <c r="B2412" t="inlineStr">
+        <is>
+          <t>church.1023.s2.p022.text</t>
+        </is>
+      </c>
+      <c r="C2412" t="inlineStr">
+        <is>
+          <t>新鲜的空气</t>
+        </is>
+      </c>
+      <c r="D2412" t="inlineStr">
+        <is>
+          <t>church.1023.s2.P022; church.1023.s2.execution; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2413">
+      <c r="B2413" t="inlineStr">
+        <is>
+          <t>church.1023.s2.p023.text</t>
+        </is>
+      </c>
+      <c r="C2413" t="inlineStr">
+        <is>
+          <t>曾经我渴求无数次的东西就这样呈现在我面前</t>
+        </is>
+      </c>
+      <c r="D2413" t="inlineStr">
+        <is>
+          <t>church.1023.s2.P023; church.1023.s2.execution; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2414">
+      <c r="B2414" t="inlineStr">
+        <is>
+          <t>church.1023.s2.p024.text</t>
+        </is>
+      </c>
+      <c r="C2414" t="inlineStr">
+        <is>
+          <t>现下我却无暇顾及</t>
+        </is>
+      </c>
+      <c r="D2414" t="inlineStr">
+        <is>
+          <t>church.1023.s2.P024; church.1023.s2.execution; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2415">
+      <c r="B2415" t="inlineStr">
+        <is>
+          <t>church.1023.s2.p025.text</t>
+        </is>
+      </c>
+      <c r="C2415" t="inlineStr">
+        <is>
+          <t>我不知道我会被他们带往哪里</t>
+        </is>
+      </c>
+      <c r="D2415" t="inlineStr">
+        <is>
+          <t>church.1023.s2.P025; church.1023.s2.execution; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2416">
+      <c r="B2416" t="inlineStr">
+        <is>
+          <t>church.1023.s2.p026.text</t>
+        </is>
+      </c>
+      <c r="C2416" t="inlineStr">
+        <is>
+          <t>就这样走着，走着……</t>
+        </is>
+      </c>
+      <c r="D2416" t="inlineStr">
+        <is>
+          <t>church.1023.s2.P026; church.1023.s2.execution; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2417">
+      <c r="B2417" t="inlineStr">
+        <is>
+          <t>church.1023.s2.p027.text</t>
+        </is>
+      </c>
+      <c r="C2417" t="inlineStr">
+        <is>
+          <t>这里是哪里？</t>
+        </is>
+      </c>
+      <c r="D2417" t="inlineStr">
+        <is>
+          <t>church.1023.s2.P027; church.1023.s2.execution; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2418">
+      <c r="B2418" t="inlineStr">
+        <is>
+          <t>church.1023.s2.p028.text</t>
+        </is>
+      </c>
+      <c r="C2418" t="inlineStr">
+        <is>
+          <t>刑场？</t>
+        </is>
+      </c>
+      <c r="D2418" t="inlineStr">
+        <is>
+          <t>church.1023.s2.P028; church.1023.s2.execution; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2419">
+      <c r="B2419" t="inlineStr">
+        <is>
+          <t>church.1023.s2.p029.text</t>
+        </is>
+      </c>
+      <c r="C2419" t="inlineStr">
+        <is>
+          <t>我要死了吗？</t>
+        </is>
+      </c>
+      <c r="D2419" t="inlineStr">
+        <is>
+          <t>church.1023.s2.P029; church.1023.s2.execution; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2420">
+      <c r="B2420" t="inlineStr">
+        <is>
+          <t>church.1023.s2.p030.text</t>
+        </is>
+      </c>
+      <c r="C2420" t="inlineStr">
+        <is>
+          <t>为什么？</t>
+        </is>
+      </c>
+      <c r="D2420" t="inlineStr">
+        <is>
+          <t>church.1023.s2.P030; church.1023.s2.execution; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2421">
+      <c r="B2421" t="inlineStr">
+        <is>
+          <t>church.1023.s2.p031.text</t>
+        </is>
+      </c>
+      <c r="C2421" t="inlineStr">
+        <is>
+          <t>为什么？为什么？为什么？为什么？为什么？</t>
+        </is>
+      </c>
+      <c r="D2421" t="inlineStr">
+        <is>
+          <t>church.1023.s2.P031; church.1023.s2.execution; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2422">
+      <c r="B2422" t="inlineStr">
+        <is>
+          <t>church.1023.s2.p032.text</t>
+        </is>
+      </c>
+      <c r="C2422" t="inlineStr">
+        <is>
+          <t>带着这样的想法，我迎来了人生的终点。</t>
+        </is>
+      </c>
+      <c r="D2422" t="inlineStr">
+        <is>
+          <t>church.1023.s2.P032; church.1023.s2.execution; Text only, no event/route/result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2423">
+      <c r="A2423" s="3" t="n"/>
+      <c r="B2423" s="3" t="inlineStr">
+        <is>
+          <t>colette.name</t>
+        </is>
+      </c>
+      <c r="C2423" s="3" t="inlineStr">
+        <is>
+          <t>柯莱特·布吕内</t>
+        </is>
+      </c>
+      <c r="D2423" s="3" t="inlineStr">
+        <is>
+          <t>A01 source identity; blocked construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="2424">
+      <c r="A2424" s="3" t="n"/>
+      <c r="B2424" s="3" t="inlineStr">
+        <is>
+          <t>neutral.shopkeeper.name</t>
+        </is>
+      </c>
+      <c r="C2424" s="3" t="inlineStr">
+        <is>
+          <t>店主</t>
+        </is>
+      </c>
+      <c r="D2424" s="3" t="inlineStr">
+        <is>
+          <t>A01 source identity; blocked construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="2425">
+      <c r="A2425" s="3" t="n"/>
+      <c r="B2425" s="3" t="inlineStr">
+        <is>
+          <t>neutral.unknown.name</t>
+        </is>
+      </c>
+      <c r="C2425" s="3" t="inlineStr">
+        <is>
+          <t>？？？</t>
+        </is>
+      </c>
+      <c r="D2425" s="3" t="inlineStr">
+        <is>
+          <t>A01 source identity; blocked construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="2426">
+      <c r="A2426" s="3" t="n"/>
+      <c r="B2426" s="3" t="inlineStr">
+        <is>
+          <t>alienor.name</t>
+        </is>
+      </c>
+      <c r="C2426" s="3" t="inlineStr">
+        <is>
+          <t>阿莉耶诺尔·康多尔</t>
+        </is>
+      </c>
+      <c r="D2426" s="3" t="inlineStr">
+        <is>
+          <t>E source identity/display alias; no narrative addition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2427">
+      <c r="A2427" s="3" t="n"/>
+      <c r="B2427" s="3" t="inlineStr">
+        <is>
+          <t>church.1104.s1.alias.alienor.name</t>
+        </is>
+      </c>
+      <c r="C2427" s="3" t="inlineStr">
+        <is>
+          <t>埃莉诺</t>
+        </is>
+      </c>
+      <c r="D2427" s="3" t="inlineStr">
+        <is>
+          <t>E source identity/display alias; no narrative addition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2428">
+      <c r="A2428" s="3" t="n"/>
+      <c r="B2428" s="3" t="inlineStr">
+        <is>
+          <t>church.1104.s1.alias.landlord.uncertain.name</t>
+        </is>
+      </c>
+      <c r="C2428" s="3" t="inlineStr">
+        <is>
+          <t>房东？</t>
+        </is>
+      </c>
+      <c r="D2428" s="3" t="inlineStr">
+        <is>
+          <t>E source identity/display alias; no narrative addition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2429">
+      <c r="A2429" s="3" t="n"/>
+      <c r="B2429" s="3" t="inlineStr">
+        <is>
+          <t>church.1104.s1.npc.mother.name</t>
+        </is>
+      </c>
+      <c r="C2429" s="3" t="inlineStr">
+        <is>
+          <t>女人</t>
+        </is>
+      </c>
+      <c r="D2429" s="3" t="inlineStr">
+        <is>
+          <t>E source identity/display alias; no narrative addition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2430">
+      <c r="A2430" s="3" t="n"/>
+      <c r="B2430" s="3" t="inlineStr">
+        <is>
+          <t>church.1104.s1.npc.vendor.name</t>
+        </is>
+      </c>
+      <c r="C2430" s="3" t="inlineStr">
+        <is>
+          <t>摊主</t>
+        </is>
+      </c>
+      <c r="D2430" s="3" t="inlineStr">
+        <is>
+          <t>E source identity/display alias; no narrative addition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2431">
+      <c r="A2431" s="3" t="n"/>
+      <c r="B2431" s="3" t="inlineStr">
+        <is>
+          <t>church.1104.s1.npc.civilian_a.name</t>
+        </is>
+      </c>
+      <c r="C2431" s="3" t="inlineStr">
+        <is>
+          <t>平民A</t>
+        </is>
+      </c>
+      <c r="D2431" s="3" t="inlineStr">
+        <is>
+          <t>E source identity/display alias; no narrative addition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2432">
+      <c r="A2432" s="3" t="n"/>
+      <c r="B2432" s="3" t="inlineStr">
+        <is>
+          <t>church.1104.s1.npc.civilian_b.name</t>
+        </is>
+      </c>
+      <c r="C2432" s="3" t="inlineStr">
+        <is>
+          <t>平民B</t>
+        </is>
+      </c>
+      <c r="D2432" s="3" t="inlineStr">
+        <is>
+          <t>E source identity/display alias; no narrative addition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2433">
+      <c r="A2433" s="3" t="n"/>
+      <c r="B2433" s="3" t="inlineStr">
+        <is>
+          <t>church.1104.s1.npc.elder_lady.name</t>
+        </is>
+      </c>
+      <c r="C2433" s="3" t="inlineStr">
+        <is>
+          <t>老妇人</t>
+        </is>
+      </c>
+      <c r="D2433" s="3" t="inlineStr">
+        <is>
+          <t>E source identity/display alias; no narrative addition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2434">
+      <c r="A2434" s="3" t="n"/>
+      <c r="B2434" s="3" t="inlineStr">
+        <is>
+          <t>church.1104.s1.npc.buyer.name</t>
+        </is>
+      </c>
+      <c r="C2434" s="3" t="inlineStr">
+        <is>
+          <t>男子</t>
+        </is>
+      </c>
+      <c r="D2434" s="3" t="inlineStr">
+        <is>
+          <t>E source identity/display alias; no narrative addition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2435">
+      <c r="A2435" s="3" t="n"/>
+      <c r="B2435" s="3" t="inlineStr">
+        <is>
+          <t>church.1104.s1.npc.tenant.name</t>
+        </is>
+      </c>
+      <c r="C2435" s="3" t="inlineStr">
+        <is>
+          <t>男人</t>
+        </is>
+      </c>
+      <c r="D2435" s="3" t="inlineStr">
+        <is>
+          <t>E source identity/display alias; no narrative addition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2436">
+      <c r="A2436" s="3" t="n"/>
+      <c r="B2436" s="3" t="inlineStr">
+        <is>
+          <t>church.1104.s1.npc.landlord.name</t>
+        </is>
+      </c>
+      <c r="C2436" s="3" t="inlineStr">
+        <is>
+          <t>房东</t>
+        </is>
+      </c>
+      <c r="D2436" s="3" t="inlineStr">
+        <is>
+          <t>E source identity/display alias; no narrative addition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2437">
+      <c r="A2437" s="3" t="n"/>
+      <c r="B2437" s="3" t="inlineStr">
+        <is>
+          <t>neutral.reporter.name</t>
+        </is>
+      </c>
+      <c r="C2437" s="3" t="inlineStr">
+        <is>
+          <t>记者</t>
+        </is>
+      </c>
+      <c r="D2437" s="3" t="inlineStr">
+        <is>
+          <t>A05 source identity/display</t>
+        </is>
+      </c>
+    </row>
+    <row r="2438">
+      <c r="A2438" s="3" t="n"/>
+      <c r="B2438" s="3" t="inlineStr">
+        <is>
+          <t>rose.1016.s1.title</t>
+        </is>
+      </c>
+      <c r="C2438" s="3" t="inlineStr">
+        <is>
+          <t>两位访客</t>
+        </is>
+      </c>
+      <c r="D2438" s="3" t="inlineStr">
+        <is>
+          <t>B source fragment, not a formal chapter</t>
+        </is>
+      </c>
+    </row>
+    <row r="2439">
+      <c r="A2439" s="3" t="n"/>
+      <c r="B2439" s="3" t="inlineStr">
+        <is>
+          <t>rose.1016.s1.alias.alienor</t>
+        </is>
+      </c>
+      <c r="C2439" s="3" t="inlineStr">
+        <is>
+          <t>埃莉诺</t>
+        </is>
+      </c>
+      <c r="D2439" s="3" t="inlineStr">
+        <is>
+          <t>B P009/P014 alias; no royal identity disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="2440">
+      <c r="A2440" s="3" t="n"/>
+      <c r="B2440" s="3" t="inlineStr">
+        <is>
+          <t>rose.1012.s1.alias.alienor.name</t>
+        </is>
+      </c>
+      <c r="C2440" s="3" t="inlineStr">
+        <is>
+          <t>埃莉诺</t>
+        </is>
+      </c>
+      <c r="D2440" s="3" t="inlineStr">
+        <is>
+          <t>B1012 explicit display alias; alienor identity reused</t>
+        </is>
+      </c>
+    </row>
+    <row r="2441">
+      <c r="A2441" s="3" t="n"/>
+      <c r="B2441" s="3" t="inlineStr">
+        <is>
+          <t>church.thibaut.name</t>
+        </is>
+      </c>
+      <c r="C2441" s="3" t="inlineStr">
+        <is>
+          <t>客人</t>
+        </is>
+      </c>
+      <c r="D2441" s="3" t="inlineStr">
+        <is>
+          <t>D1014 source guest alias; no hidden identity or portrait substitute</t>
+        </is>
+      </c>
+    </row>
+    <row r="2442">
+      <c r="A2442" s="3" t="n"/>
+      <c r="B2442" s="3" t="inlineStr">
+        <is>
+          <t>church.inspector.name</t>
+        </is>
+      </c>
+      <c r="C2442" s="3" t="inlineStr">
+        <is>
+          <t>监察官</t>
+        </is>
+      </c>
+      <c r="D2442" s="3" t="inlineStr">
+        <is>
+          <t>D1020 source speaker identity/alias; no narrative addition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2443">
+      <c r="A2443" s="3" t="n"/>
+      <c r="B2443" s="3" t="inlineStr">
+        <is>
+          <t>church.inspectors.name</t>
+        </is>
+      </c>
+      <c r="C2443" s="3" t="inlineStr">
+        <is>
+          <t>众监察员</t>
+        </is>
+      </c>
+      <c r="D2443" s="3" t="inlineStr">
+        <is>
+          <t>D1020 source speaker identity/alias; no narrative addition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2444">
+      <c r="A2444" s="3" t="n"/>
+      <c r="B2444" s="3" t="inlineStr">
+        <is>
+          <t>church.1020.s1.inspector.uncertain.name</t>
+        </is>
+      </c>
+      <c r="C2444" s="3" t="inlineStr">
+        <is>
+          <t>疑似领头的人</t>
+        </is>
+      </c>
+      <c r="D2444" s="3" t="inlineStr">
+        <is>
+          <t>D1020 source speaker identity/alias; no narrative addition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2445">
+      <c r="A2445" s="3" t="n"/>
+      <c r="B2445" s="3" t="inlineStr">
+        <is>
+          <t>church.guard.name</t>
+        </is>
+      </c>
+      <c r="C2445" s="3" t="inlineStr">
+        <is>
+          <t>看守</t>
+        </is>
+      </c>
+      <c r="D2445" s="3" t="inlineStr">
+        <is>
+          <t>D generic source speaker; no portrait binding</t>
+        </is>
+      </c>
+    </row>
+    <row r="2446">
+      <c r="A2446" s="3" t="n"/>
+      <c r="B2446" s="3" t="inlineStr">
+        <is>
+          <t>bar.colette.trust_player.name</t>
+        </is>
+      </c>
+      <c r="C2446" s="3" t="inlineStr">
+        <is>
+          <t>柯莱特对玩家的好感</t>
+        </is>
+      </c>
+      <c r="D2446" s="3" t="inlineStr">
+        <is>
+          <t>User-authorized formal relation label</t>
+        </is>
+      </c>
+    </row>
+    <row r="2447">
+      <c r="A2447" s="3" t="n"/>
+      <c r="B2447" s="3" t="inlineStr">
+        <is>
+          <t>bar.adele.trust_player.name</t>
+        </is>
+      </c>
+      <c r="C2447" s="3" t="inlineStr">
+        <is>
+          <t>阿黛尔对玩家的好感</t>
+        </is>
+      </c>
+      <c r="D2447" s="3" t="inlineStr">
+        <is>
+          <t>User-authorized formal relation label</t>
+        </is>
+      </c>
+    </row>
+    <row r="2448">
+      <c r="A2448" s="3" t="n"/>
+      <c r="B2448" s="3" t="inlineStr">
+        <is>
+          <t>bar.antoine.trust_player.name</t>
+        </is>
+      </c>
+      <c r="C2448" s="3" t="inlineStr">
+        <is>
+          <t>安托万对玩家的好感</t>
+        </is>
+      </c>
+      <c r="D2448" s="3" t="inlineStr">
+        <is>
+          <t>User-authorized formal relation label</t>
+        </is>
+      </c>
+    </row>
+    <row r="2449">
+      <c r="A2449" s="3" t="n"/>
+      <c r="B2449" s="3" t="inlineStr">
+        <is>
+          <t>condition.story.rose.1009.s1.completed</t>
+        </is>
+      </c>
+      <c r="C2449" s="3" t="inlineStr">
+        <is>
+          <t>玫瑰线十月九日密见已完成（仅声明，B负责生产）</t>
+        </is>
+      </c>
+      <c r="D2449" s="3" t="inlineStr">
+        <is>
+          <t>User-authorized A01-A04 flag label; B completion is declared only</t>
+        </is>
+      </c>
+    </row>
+    <row r="2450">
+      <c r="A2450" s="3" t="n"/>
+      <c r="B2450" s="3" t="inlineStr">
+        <is>
+          <t>condition.story.neutral.1008.s1.completed</t>
+        </is>
+      </c>
+      <c r="C2450" s="3" t="inlineStr">
+        <is>
+          <t>十月八日市场初遇已完成</t>
+        </is>
+      </c>
+      <c r="D2450" s="3" t="inlineStr">
+        <is>
+          <t>User-authorized A01-A04 flag label; B completion is declared only</t>
+        </is>
+      </c>
+    </row>
+    <row r="2451">
+      <c r="A2451" s="3" t="n"/>
+      <c r="B2451" s="3" t="inlineStr">
+        <is>
+          <t>condition.story.neutral.1010.s1.completed</t>
+        </is>
+      </c>
+      <c r="C2451" s="3" t="inlineStr">
+        <is>
+          <t>十月十日促销筹备已完成</t>
+        </is>
+      </c>
+      <c r="D2451" s="3" t="inlineStr">
+        <is>
+          <t>User-authorized A01-A04 flag label; B completion is declared only</t>
+        </is>
+      </c>
+    </row>
+    <row r="2452">
+      <c r="A2452" s="3" t="n"/>
+      <c r="B2452" s="3" t="inlineStr">
+        <is>
+          <t>condition.story.neutral.1010.s1.frugal_preparation</t>
+        </is>
+      </c>
+      <c r="C2452" s="3" t="inlineStr">
+        <is>
+          <t>本次促销精打细算准备资格（未接账）</t>
+        </is>
+      </c>
+      <c r="D2452" s="3" t="inlineStr">
+        <is>
+          <t>User-authorized A01-A04 flag label; B completion is declared only</t>
+        </is>
+      </c>
+    </row>
+    <row r="2453">
+      <c r="A2453" s="3" t="n"/>
+      <c r="B2453" s="3" t="inlineStr">
+        <is>
+          <t>condition.story.neutral.1010.s2.completed</t>
+        </is>
+      </c>
+      <c r="C2453" s="3" t="inlineStr">
+        <is>
+          <t>十月十日安托万到访已完成</t>
+        </is>
+      </c>
+      <c r="D2453" s="3" t="inlineStr">
+        <is>
+          <t>User-authorized A01-A04 flag label; B completion is declared only</t>
+        </is>
+      </c>
+    </row>
+    <row r="2454">
+      <c r="A2454" s="3" t="n"/>
+      <c r="B2454" s="3" t="inlineStr">
+        <is>
+          <t>condition.story.neutral.1010.s2.antoine_approval</t>
+        </is>
+      </c>
+      <c r="C2454" s="3" t="inlineStr">
+        <is>
+          <t>安托万赏识（控制十月十三日到场）</t>
+        </is>
+      </c>
+      <c r="D2454" s="3" t="inlineStr">
+        <is>
+          <t>User-authorized A01-A04 flag label; B completion is declared only</t>
+        </is>
+      </c>
+    </row>
+    <row r="2455">
+      <c r="A2455" s="3" t="n"/>
+      <c r="B2455" s="3" t="inlineStr">
+        <is>
+          <t>condition.story.neutral.1013.s2.completed</t>
+        </is>
+      </c>
+      <c r="C2455" s="3" t="inlineStr">
+        <is>
+          <t>十月十三日促销已完成</t>
+        </is>
+      </c>
+      <c r="D2455" s="3" t="inlineStr">
+        <is>
+          <t>User-authorized A01-A04 flag label; B completion is declared only</t>
+        </is>
+      </c>
+    </row>
+    <row r="2456">
+      <c r="A2456" s="3" t="n"/>
+      <c r="B2456" s="3" t="inlineStr">
+        <is>
+          <t>condition.story.neutral.1013.s2.orderly_service</t>
+        </is>
+      </c>
+      <c r="C2456" s="3" t="inlineStr">
+        <is>
+          <t>本次促销井然有序资格（未接账）</t>
+        </is>
+      </c>
+      <c r="D2456" s="3" t="inlineStr">
+        <is>
+          <t>User-authorized A01-A04 flag label; B completion is declared only</t>
+        </is>
+      </c>
+    </row>
+    <row r="2457">
+      <c r="A2457" s="3" t="n"/>
+      <c r="B2457" s="3" t="inlineStr">
+        <is>
+          <t>condition.story.neutral.1013.s2.warm_recommendation</t>
+        </is>
+      </c>
+      <c r="C2457" s="3" t="inlineStr">
+        <is>
+          <t>本次促销热情推介资格（未接账）</t>
+        </is>
+      </c>
+      <c r="D2457" s="3" t="inlineStr">
+        <is>
+          <t>User-authorized A01-A04 flag label; B completion is declared only</t>
+        </is>
+      </c>
+    </row>
+    <row r="2458">
+      <c r="A2458" s="3" t="n"/>
+      <c r="B2458" s="3" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.action.name</t>
+        </is>
+      </c>
+      <c r="C2458" s="3" t="inlineStr">
+        <is>
+          <t>大堂区采购</t>
+        </is>
+      </c>
+      <c r="D2458" s="3" t="inlineStr">
+        <is>
+          <t>A01 P008 source-backed map action label; no purchase settlement</t>
+        </is>
+      </c>
+    </row>
+    <row r="2459">
+      <c r="A2459" s="3" t="n"/>
+      <c r="B2459" s="3" t="inlineStr">
+        <is>
+          <t>condition.story.neutral.1018.s1.completed</t>
+        </is>
+      </c>
+      <c r="C2459" s="3" t="inlineStr">
+        <is>
+          <t>记者到访已完成</t>
+        </is>
+      </c>
+      <c r="D2459" s="3" t="inlineStr">
+        <is>
+          <t>A05 reporter state label</t>
+        </is>
+      </c>
+    </row>
+    <row r="2460">
+      <c r="A2460" s="3" t="n"/>
+      <c r="B2460" s="3" t="inlineStr">
+        <is>
+          <t>condition.story.neutral.1018.s1.recommendation_requested</t>
+        </is>
+      </c>
+      <c r="C2460" s="3" t="inlineStr">
+        <is>
+          <t>咖啡馆推荐待刊</t>
+        </is>
+      </c>
+      <c r="D2460" s="3" t="inlineStr">
+        <is>
+          <t>A05 reporter state label</t>
+        </is>
+      </c>
+    </row>
+    <row r="2461">
+      <c r="A2461" s="3" t="n"/>
+      <c r="B2461" s="3" t="inlineStr">
+        <is>
+          <t>condition.story.neutral.1018.s1.advertisement_requested</t>
+        </is>
+      </c>
+      <c r="C2461" s="3" t="inlineStr">
+        <is>
+          <t>咖啡馆广告待刊</t>
+        </is>
+      </c>
+      <c r="D2461" s="3" t="inlineStr">
+        <is>
+          <t>A05 reporter state label</t>
+        </is>
+      </c>
+    </row>
+    <row r="2462">
+      <c r="A2462" s="3" t="n"/>
+      <c r="B2462" s="3" t="inlineStr">
+        <is>
+          <t>condition.story.neutral.1018.s1.printed</t>
+        </is>
+      </c>
+      <c r="C2462" s="3" t="inlineStr">
+        <is>
+          <t>咖啡馆报刊通知已刊出</t>
+        </is>
+      </c>
+      <c r="D2462" s="3" t="inlineStr">
+        <is>
+          <t>A05 reporter state label</t>
+        </is>
+      </c>
+    </row>
+    <row r="2463">
+      <c r="A2463" s="3" t="n"/>
+      <c r="B2463" s="3" t="inlineStr">
+        <is>
+          <t>neutral.1018.s1.notice.title</t>
+        </is>
+      </c>
+      <c r="C2463" s="3" t="inlineStr">
+        <is>
+          <t>《圣诺特之声》</t>
+        </is>
+      </c>
+      <c r="D2463" s="3" t="inlineStr">
+        <is>
+          <t>A05 authorized minimal next-issue Notice; no reward</t>
+        </is>
+      </c>
+    </row>
+    <row r="2464">
+      <c r="A2464" s="3" t="n"/>
+      <c r="B2464" s="3" t="inlineStr">
+        <is>
+          <t>neutral.1018.s1.notice.recommendation.body</t>
+        </is>
+      </c>
+      <c r="C2464" s="3" t="inlineStr">
+        <is>
+          <t>本期侧栏刊登了沸点咖啡馆的推荐文章。</t>
+        </is>
+      </c>
+      <c r="D2464" s="3" t="inlineStr">
+        <is>
+          <t>A05 authorized minimal next-issue Notice; no reward</t>
+        </is>
+      </c>
+    </row>
+    <row r="2465">
+      <c r="A2465" s="3" t="n"/>
+      <c r="B2465" s="3" t="inlineStr">
+        <is>
+          <t>neutral.1018.s1.notice.advertisement.body</t>
+        </is>
+      </c>
+      <c r="C2465" s="3" t="inlineStr">
+        <is>
+          <t>本期商业版刊登了沸点咖啡馆的广告。</t>
+        </is>
+      </c>
+      <c r="D2465" s="3" t="inlineStr">
+        <is>
+          <t>A05 authorized minimal next-issue Notice; no reward</t>
         </is>
       </c>
     </row>

--- a/Assets/ConfigTables/Data/Shared/Text.xlsx
+++ b/Assets/ConfigTables/Data/Shared/Text.xlsx
@@ -13992,7 +13992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2465"/>
+  <dimension ref="A1:D2474"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -55804,6 +55804,159 @@
         </is>
       </c>
     </row>
+    <row r="2466">
+      <c r="B2466" t="inlineStr">
+        <is>
+          <t>action.cafe.enter.name</t>
+        </is>
+      </c>
+      <c r="C2466" t="inlineStr">
+        <is>
+          <t>咖啡馆</t>
+        </is>
+      </c>
+      <c r="D2466" t="inlineStr">
+        <is>
+          <t>配置化免费导航行动</t>
+        </is>
+      </c>
+    </row>
+    <row r="2467">
+      <c r="B2467" t="inlineStr">
+        <is>
+          <t>action.cafe.enter.desc</t>
+        </is>
+      </c>
+      <c r="C2467" t="inlineStr">
+        <is>
+          <t>进入咖啡馆，开始今天的经营。</t>
+        </is>
+      </c>
+      <c r="D2467" t="inlineStr">
+        <is>
+          <t>配置化免费导航行动</t>
+        </is>
+      </c>
+    </row>
+    <row r="2468">
+      <c r="B2468" t="inlineStr">
+        <is>
+          <t>action.cafe.enter.button</t>
+        </is>
+      </c>
+      <c r="C2468" t="inlineStr">
+        <is>
+          <t>进入咖啡馆</t>
+        </is>
+      </c>
+      <c r="D2468" t="inlineStr">
+        <is>
+          <t>配置化免费导航按钮</t>
+        </is>
+      </c>
+    </row>
+    <row r="2469">
+      <c r="B2469" t="inlineStr">
+        <is>
+          <t>test.item.medicine.name</t>
+        </is>
+      </c>
+      <c r="C2469" t="inlineStr">
+        <is>
+          <t>验收用药品</t>
+        </is>
+      </c>
+      <c r="D2469" t="inlineStr">
+        <is>
+          <t>TEST_ONLY：交付隔离夹具物品元数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="2470">
+      <c r="B2470" t="inlineStr">
+        <is>
+          <t>test.item.medicine.desc</t>
+        </is>
+      </c>
+      <c r="C2470" t="inlineStr">
+        <is>
+          <t>仅用于隔离交付验收，不代表正式商品。</t>
+        </is>
+      </c>
+      <c r="D2470" t="inlineStr">
+        <is>
+          <t>TEST_ONLY：交付隔离夹具物品元数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="2471">
+      <c r="B2471" t="inlineStr">
+        <is>
+          <t>test.item.food.name</t>
+        </is>
+      </c>
+      <c r="C2471" t="inlineStr">
+        <is>
+          <t>验收用食品</t>
+        </is>
+      </c>
+      <c r="D2471" t="inlineStr">
+        <is>
+          <t>TEST_ONLY：交付隔离夹具物品元数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="2472">
+      <c r="B2472" t="inlineStr">
+        <is>
+          <t>test.item.food.desc</t>
+        </is>
+      </c>
+      <c r="C2472" t="inlineStr">
+        <is>
+          <t>仅用于隔离交付验收，不代表正式商品。</t>
+        </is>
+      </c>
+      <c r="D2472" t="inlineStr">
+        <is>
+          <t>TEST_ONLY：交付隔离夹具物品元数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="2473">
+      <c r="B2473" t="inlineStr">
+        <is>
+          <t>test.item.delivery_receipt.name</t>
+        </is>
+      </c>
+      <c r="C2473" t="inlineStr">
+        <is>
+          <t>交付验收回执</t>
+        </is>
+      </c>
+      <c r="D2473" t="inlineStr">
+        <is>
+          <t>TEST_ONLY：交付隔离夹具物品元数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="2474">
+      <c r="B2474" t="inlineStr">
+        <is>
+          <t>test.item.delivery_receipt.desc</t>
+        </is>
+      </c>
+      <c r="C2474" t="inlineStr">
+        <is>
+          <t>仅用于隔离交付验收，不代表正式商品。</t>
+        </is>
+      </c>
+      <c r="D2474" t="inlineStr">
+        <is>
+          <t>TEST_ONLY：交付隔离夹具物品元数据</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>

--- a/Assets/ConfigTables/Data/Shared/Text.xlsx
+++ b/Assets/ConfigTables/Data/Shared/Text.xlsx
@@ -1004,12 +1004,6 @@
     <author>D-church source</author>
     <author>C source map</author>
     <author>A-neutral source</author>
-    <author>E-church source routing</author>
-    <author>A-neutral preview</author>
-    <author>B-rose</author>
-    <author>D-church</author>
-    <author>A-neutral-formal</author>
-    <author>A05-neutral-reporter</author>
   </authors>
   <commentList>
     <comment ref="C511" authorId="0" shapeId="0">
@@ -11253,2462 +11247,6 @@
         <t>D:\桌面\文案\中立\MA70.10.18-S1.docx
 A-1018.s1-P097
 我望了一眼记者方才坐过的位置。桌上除了几枚铜币，就只剩下一圈浅淡的杯痕。</t>
-      </text>
-    </comment>
-    <comment ref="C2101" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P004
-由于咖啡馆昨天举办了活动，客流量渐渐变大，我和阿黛尔的工作甚至可以用繁忙来形容。这样的热闹延续到了今天，直到中午时分人流量才减少，我们终于可以获得片刻的歇息了。</t>
-      </text>
-    </comment>
-    <comment ref="C2102" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P006
-一名中年男人出现，在离我最近的吧台座位坐下</t>
-      </text>
-    </comment>
-    <comment ref="C2103" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P008
-{playername}：「您好，欢迎光临沸点咖啡馆！」</t>
-      </text>
-    </comment>
-    <comment ref="C2104" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P009
-客人：（#平静）「你好。」</t>
-      </text>
-    </comment>
-    <comment ref="C2105" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P010
-{playername}：「先生，请问您想喝点什么呢？店内的咖啡目前广受好评呢。」</t>
-      </text>
-    </comment>
-    <comment ref="C2106" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P011
-客人：（#平静）「是吗，那来一杯经典的无糖黑咖啡。」</t>
-      </text>
-    </comment>
-    <comment ref="C2107" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P012
-{playername}：「好的，请稍等片刻。」</t>
-      </text>
-    </comment>
-    <comment ref="C2108" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P014
-客人：（#平静）「还不错。」</t>
-      </text>
-    </comment>
-    <comment ref="C2109" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P015
-{playname}：「谢谢您的肯定！请慢慢品尝。」</t>
-      </text>
-    </comment>
-    <comment ref="C2110" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P017
-暂时没有更多客人了，正好趁闲暇时放松一下吧</t>
-      </text>
-    </comment>
-    <comment ref="C2111" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P018
-不知道下午客流量怎么样，一旦忙起来就觉得时间过得飞快，不过这也意味着叔叔交给我的咖啡馆逐渐走上正途了。</t>
-      </text>
-    </comment>
-    <comment ref="C2112" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P019
-说起咖啡馆，没想到背后竟然和一些神秘组织有关系，感觉被牵扯进了很不得了的事件中。</t>
-      </text>
-    </comment>
-    <comment ref="C2113" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P020
-不知道是不是我的错觉，总觉得这位客人一直在看着我。是对咖啡不满意吗，或者是我今天穿的不对劲？</t>
-      </text>
-    </comment>
-    <comment ref="C2114" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P021
-他看起来也像是一个工人，今天来的工人怎么这么多，但他应该不会是神秘人那边派来的人吧？好在意，要不问一下吧。</t>
-      </text>
-    </comment>
-    <comment ref="C2115" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P023
-暂时没有更多客人了，正好趁闲暇时放松一下吧。</t>
-      </text>
-    </comment>
-    <comment ref="C2116" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P024
-不知道下午客流量怎么样，一旦忙起来就觉得时间过得飞快，不过这也意味着叔叔交给我的咖啡馆逐渐走上正途了。</t>
-      </text>
-    </comment>
-    <comment ref="C2117" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P025
-说起咖啡馆，没想到其居然和一些说不清的组织有所牵扯，感觉被牵扯进了很不得了的事件中。</t>
-      </text>
-    </comment>
-    <comment ref="C2118" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P026
-这位客人看起来也像是一个工人，今天的来的工人怎么这么多，但他应该不会是神秘人那边派来的人吧？好在意，要不问一下吧。</t>
-      </text>
-    </comment>
-    <comment ref="C2119" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P027
-{playername}：「先生，请问您对咖啡有什么建议吗？咖啡馆重新开业，我们希望能在客人们的建议下进一步提高！如果有想法但是不好意思直接说，也可以通过写信的方式告诉我们，您瞧，我们上午刚收到一封顾客送来的建议信呢。」</t>
-      </text>
-    </comment>
-    <comment ref="C2120" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P029
-我一边出示装着信的信封，一边假装不经意地盯着他</t>
-      </text>
-    </comment>
-    <comment ref="C2121" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P030
-他没有多看信一眼，只是看着我</t>
-      </text>
-    </comment>
-    <comment ref="C2122" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P031
-客人：（#平静）「不，不，没有任何意见。」放下咖啡「店长，我有一个问题想问你。」</t>
-      </text>
-    </comment>
-    <comment ref="C2123" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P031
-客人：（#平静）「不，不，没有任何意见。」放下咖啡「店长，我有一个问题想问你。」</t>
-      </text>
-    </comment>
-    <comment ref="C2124" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P032
-{playername}：「啊，好的，先生，您请问。」</t>
-      </text>
-    </comment>
-    <comment ref="C2125" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P033
-他对信没有任何反应，看来并不是神秘人那边派来的人</t>
-      </text>
-    </comment>
-    <comment ref="C2126" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P034
-或许只是个普通工人吧</t>
-      </text>
-    </comment>
-    <comment ref="C2127" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P035
-客人：（#疑惑）「王城中，甚至圣徒街上都并不只有一家咖啡馆，但是它们有些并不向普通平民开放，而我看见各阶层的人民都可以自由进入你们的店中。您是出于怎样的考虑呢？」</t>
-      </text>
-    </comment>
-    <comment ref="C2128" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P037
-①「只要能够赚钱就好，我们并不在乎客人的身份。我的叔叔杜瓦尔和前几任店长也是这样做的。将人划分三六九等是政治家的思想，却是和商人无关的。」[王庭-教会倾向+0]</t>
-      </text>
-    </comment>
-    <comment ref="C2129" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P038
-②「我只是想看见客人喝到我做的咖啡之后露出满意的笑容，这样就已经足够了，别的因素不是我要考虑的。」[王庭-教会倾向+0]</t>
-      </text>
-    </comment>
-    <comment ref="C2130" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P039
-③「我认为咖啡馆只面向部分人群开放本身就是错误的，其应当是面向普罗大众而存在的，不应以政治地位、经济实力等原因而将部分人拒之门外。我的叔叔杜瓦尔和前几任店长也是这样做的，我延续着他们的精神。」[王庭-教会倾向-1]</t>
-      </text>
-    </comment>
-    <comment ref="C2131" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P041
-客人：（#痛苦）「好的，我明白了。我之前是一名工人，生活在圣西尔万郊区，但是前段时间不幸在工作中受伤，成为了跛脚。唉，许多工厂都因为这点而排斥我。我近日一直为此感到烦忧，昨日听说圣徒街的沸点咖啡馆重新开业了，味道不错且面向大众开放，我实在感到好奇，所以今日特地前来。」</t>
-      </text>
-    </comment>
-    <comment ref="C2132" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P042
-顺着他的话我不由得认真打量起面前这个男子</t>
-      </text>
-    </comment>
-    <comment ref="C2133" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P043
-眼角周围有淡淡的皱纹，年纪并不小了，身上隐隐传来一阵烟味。或许是最近郁闷时常抽。</t>
-      </text>
-    </comment>
-    <comment ref="C2134" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P044
-但是整体打理得很整齐，眼神也透露出坚毅，看起来是一个对自身和生活有一定追求的人。</t>
-      </text>
-    </comment>
-    <comment ref="C2135" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P045
-{playername}：「这实在是我们的荣幸，先生。希望这杯咖啡能让您感到些许慰藉。」</t>
-      </text>
-    </comment>
-    <comment ref="C2136" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P046
-客人：（#疑惑）「好的。店长，您听闻前几日埃利昂公爵和教会的人在旧城区和圣西尔万郊区救济贫民的事情了吗？」</t>
-      </text>
-    </comment>
-    <comment ref="C2137" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P047
-{playername}：「有所耳闻。」</t>
-      </text>
-    </comment>
-    <comment ref="C2138" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P048
-客人：（#兴奋）「很高兴您有所了解。我那天就在被救济的队伍中，这是我最近感受过的最大的善意了，那粥虽然并不算得上十分美味，但足以饱腹了。虽然当下百姓的生活困难，没想到王庭和教会还是有一些有理想和良心的人为我们这些人而奔走着。」</t>
-      </text>
-    </comment>
-    <comment ref="C2139" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P050
-①「很高兴得知这件事，我刚来到此地，没想到上层还有埃利昂公爵这样的人物。」</t>
-      </text>
-    </comment>
-    <comment ref="C2140" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P051
-②「很高兴得知这件事，但是我相当怀疑王庭和教会中真的存在这样的人吗？」</t>
-      </text>
-    </comment>
-    <comment ref="C2141" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P052
-③「很高兴得知这件事，希望百姓的生活能过得越来越好。」</t>
-      </text>
-    </comment>
-    <comment ref="C2142" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P054
-客人：（#兴奋）「正是如此，店长。您不知道昨天的盛况……」</t>
-      </text>
-    </comment>
-    <comment ref="C2143" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P057
-他突然眯着眼睛打量了我一下</t>
-      </text>
-    </comment>
-    <comment ref="C2144" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P058
-客人：（#思索）「店长，您不相信吗？埃利昂公爵他们施粥是实实在在发生的事。」</t>
-      </text>
-    </comment>
-    <comment ref="C2145" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P059
-我感到他的态度冷却了一些</t>
-      </text>
-    </comment>
-    <comment ref="C2146" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P060
-{playername}：「不，先生，我相信这一点。我只是……算了，你当我未曾说过吧。」</t>
-      </text>
-    </comment>
-    <comment ref="C2147" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P061
-客人：（#平静）「好的，您不要紧张，我只是看见您觉得亲切，忍不住多聊了两句。我觉得王庭和教会并非全然糟糕透顶的……」</t>
-      </text>
-    </comment>
-    <comment ref="C2148" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P064
-他好像对我的回答并不满意，皱了皱眉</t>
-      </text>
-    </comment>
-    <comment ref="C2149" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P065
-客人：（#平静）「好吧……」</t>
-      </text>
-    </comment>
-    <comment ref="C2150" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P067
-他似乎还想说话，但此时新的客人走近了吧台</t>
-      </text>
-    </comment>
-    <comment ref="C2151" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P068
-客人：（#平静）「一不注意，竟然已经这个点了，我还需要去找找有没有我能盛任的工作。感谢您的咖啡，有机会我会再来拜访的。」</t>
-      </text>
-    </comment>
-    <comment ref="C2152" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P069
-{playername}：「再见，先生！祝您能早日找到一个满意的工作。」</t>
-      </text>
-    </comment>
-    <comment ref="C2153" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P070
-他放下咖啡，站起来离开，这时我才发现他的左脚确实行走起来不太便利</t>
-      </text>
-    </comment>
-    <comment ref="C2154" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P071
-他的身影越来越远，随着咖啡馆的门一开一闭，我便再也看不见他的身影了</t>
-      </text>
-    </comment>
-    <comment ref="C2155" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P073
-真是不容易</t>
-      </text>
-    </comment>
-    <comment ref="C2156" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P074
-我在心中叹口气</t>
-      </text>
-    </comment>
-    <comment ref="C2157" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.14-S2.docx
-church.1014.s2.P075
-然后快速转换思绪，面对客人新的要求，开启了新的工作。</t>
-      </text>
-    </comment>
-    <comment ref="C2158" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P003
-今天咖啡店的生意也相当不错</t>
-      </text>
-    </comment>
-    <comment ref="C2159" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P004
-我正在为客人制作咖啡时，突然听见一阵嘈杂的脚步声</t>
-      </text>
-    </comment>
-    <comment ref="C2160" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P006
-然后是阿黛尔同步响起的惊呼声</t>
-      </text>
-    </comment>
-    <comment ref="C2161" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P007
-阿黛尔·米尼耶：（#迷惑）「天呐，教会监察司的人？{playername}店长！{playername}店长！」</t>
-      </text>
-    </comment>
-    <comment ref="C2162" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P008
-我回过头，看见一群穿着统一制式服装的人</t>
-      </text>
-    </comment>
-    <comment ref="C2163" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P009
-「教会监察司」，刚才阿黛尔好像这样称呼着他们</t>
-      </text>
-    </comment>
-    <comment ref="C2164" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P010
-他们站定在咖啡馆中，其中一个看起来像领头的人则缓步站定在我面前</t>
-      </text>
-    </comment>
-    <comment ref="C2165" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P012
-我面前的客人惊慌失措地在我们之间来回转着，但是不敢有所动静</t>
-      </text>
-    </comment>
-    <comment ref="C2166" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P013
-疑似领头的人：（#迷惑）「你就是{playername}，沸点咖啡馆的现任店长？」</t>
-      </text>
-    </comment>
-    <comment ref="C2167" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P014
-{playername}：「是的。」</t>
-      </text>
-    </comment>
-    <comment ref="C2168" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P015
-疑似领头的人：（#平静）「我们是教会监察司，今日奉命前来圣徒街搜查。我是今日负责带队的监察官，希望你能认真配合调查，不然的话——」</t>
-      </text>
-    </comment>
-    <comment ref="C2169" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P016
-他未说完，但配合着他凶狠的目光，在场的人都对这未尽的话心知肚明</t>
-      </text>
-    </comment>
-    <comment ref="C2170" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P017
-我的大脑急速运转着</t>
-      </text>
-    </comment>
-    <comment ref="C2171" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P018
-教会监察司为什么会来圣徒街搜查？商铺经营不归监察司管吧？哦对了，好像听谁提过前几日街头有人散布修改「王选者」法律的消息……只有这个可能了。不过这和我也没什么大关系，随机应对即可吧。</t>
-      </text>
-    </comment>
-    <comment ref="C2172" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P020
-①「好吧，但是能否请小心对待店中的客人和设备，我们还要继续营业的。」</t>
-      </text>
-    </comment>
-    <comment ref="C2173" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P021
-②「我们咖啡馆正大光明，你们可以随意搜查。但是能否请小心对待店中的客人和设备，我们还要继续营业的。」</t>
-      </text>
-    </comment>
-    <comment ref="C2174" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P022
-③「如果我不同意会怎么样呢？」</t>
-      </text>
-    </comment>
-    <comment ref="C2175" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P024
-监察官：（#不屑）「哼，用不着你来指导工作。」「各人员注意，仔细搜查，不要放过任何一个角落。」</t>
-      </text>
-    </comment>
-    <comment ref="C2176" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P027
-我们隔着吧台看着对方的眼睛对峙，谁也不肯服输，许久他先移开目光并缓慢开口</t>
-      </text>
-    </comment>
-    <comment ref="C2177" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P028
-监察官：（#平静）「哼，年轻人，我很欣赏你的勇气，但建议你要记得区分勇敢和鲁莽。」「今日是必定要开展检查的。各人员注意，仔细搜查，不要放过任何一个角落。」</t>
-      </text>
-    </comment>
-    <comment ref="C2178" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P030
-我们隔着吧台看着对方的眼睛对峙，谁也不肯服输，最终我感到他身上的威严压过了我，我率先移开目光</t>
-      </text>
-    </comment>
-    <comment ref="C2179" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P031
-监察官：（#不屑）「年轻人，我想你是刚来到圣诺特，还不太了解情况，我们的搜查不需要你的同意。」「现在碍于你的态度，我可能要采取一些特别措施了，来人。」</t>
-      </text>
-    </comment>
-    <comment ref="C2180" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P032
-两个穿着制式服装的人从两边走上前来，将我从吧台中推出来，一左一右地扣押着我</t>
-      </text>
-    </comment>
-    <comment ref="C2181" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P033
-监察官：（#平静）「现在可以配合检查了吧，店长。」「各人员注意，仔细搜查，不要放过任何一个角落。」</t>
-      </text>
-    </comment>
-    <comment ref="C2182" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P035
-众监察员：「是。」</t>
-      </text>
-    </comment>
-    <comment ref="C2183" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P036
-他们四下分散开来，我看见他们的身影在大堂中忙碌着，甚至对顾客开展了简短的问询，部分顾客不堪其扰趁乱离开了。</t>
-      </text>
-    </comment>
-    <comment ref="C2184" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P037
-唉，不知道会不会影响以后的生意。</t>
-      </text>
-    </comment>
-    <comment ref="C2185" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P038
-突然想起神秘人给我留下的那封信好像被我顺手放在了吧台的抽屉中，密信他们看不懂应该不要紧……但是我该如何解释呢……</t>
-      </text>
-    </comment>
-    <comment ref="C2186" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P039
-然而怕什么来什么。很快他们便搜查到了吧台区域，在我如鼓擂的心跳声中他们在抽屉中找到了那封信，并递交给了监察官。</t>
-      </text>
-    </comment>
-    <comment ref="C2187" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P040
-监察官打开那封信看了看，然后走到我面前</t>
-      </text>
-    </comment>
-    <comment ref="C2188" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P041
-监察官：（#思索）「解释一下吗，{playername}店长？这封信上写的是什么，告诉我。」</t>
-      </text>
-    </comment>
-    <comment ref="C2189" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P044
-①「这是我们内部每日记录进货、出账的账单，为了节省时间而简写为这种形式。」（语言检定）</t>
-      </text>
-    </comment>
-    <comment ref="C2190" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P045
-②「这不过我的一封私人信件，监察司奉命搜查商铺，可没有资格逼问一封私人信件写了什么。」（勇气检定）</t>
-      </text>
-    </comment>
-    <comment ref="C2191" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P046
-③「我想长官你们是来搜查与「王选者」法律相关的吧，这不过一封我的私人信件能有什么关系呢？」（智慧检定）</t>
-      </text>
-    </comment>
-    <comment ref="C2192" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P047
-④「这不过是一封普通的私人信件，我看不出有什么被怀疑的必要。长官，您不会是早就对我有所怀疑吧？」（知觉检定）</t>
-      </text>
-    </comment>
-    <comment ref="C2193" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P049
-监察官：（#思索）「账单？那你详细给我讲讲这个账单的构成。」</t>
-      </text>
-    </comment>
-    <comment ref="C2194" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P051
-我快速回忆了一下信上的数字，然后不疾不徐地开口</t>
-      </text>
-    </comment>
-    <comment ref="C2195" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P052
-{playername}：「这些数字代表着店里咖啡豆、设备、餐具等物品的购买量、支出金额、每日消耗量、待购买量等数据，我叔叔当店长时就立下了这样的规矩，后面代代传承。」「这本来是我们的商业机密，但是长官你都发问了，我只能悉数奉告了。」</t>
-      </text>
-    </comment>
-    <comment ref="C2196" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P053
-监察官边听着我的讲述边试图理解信上的数字</t>
-      </text>
-    </comment>
-    <comment ref="C2197" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P054
-监察官：（#思索）「哼，听起来倒是有鼻子有眼。」</t>
-      </text>
-    </comment>
-    <comment ref="C2198" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P055
-他低头又看了一遍信纸，眉头紧皱，却没有从中找到能够反驳我的证据，他又盯着我看了片刻，最终将信纸递还给我。</t>
-      </text>
-    </comment>
-    <comment ref="C2199" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P056
-监察官：（#平静）「暂时没有证据证明这封信与我们搜查的东西有关。收好你的东西。」</t>
-      </text>
-    </comment>
-    <comment ref="C2200" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P057
-我接过信纸，尽量平静地点了点头。</t>
-      </text>
-    </comment>
-    <comment ref="C2201" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P059
-我努力组织着语言，试图把信上的内容解释清楚，却发现自己越说越混乱。</t>
-      </text>
-    </comment>
-    <comment ref="C2202" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P060
-{playername}：「这……这是以前店里留下的账单记录方式，应该是采购……或者别的什么记录，具体内容我也不太清楚。」</t>
-      </text>
-    </comment>
-    <comment ref="C2203" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P061
-监察官的表情逐渐变得严厉</t>
-      </text>
-    </comment>
-    <comment ref="C2204" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P062
-监察官：（#思索）「你自己的店里发现的信，你却连内容都说不清楚？」</t>
-      </text>
-    </comment>
-    <comment ref="C2205" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P063
-我张了张嘴，一时找不到更合适的说辞。</t>
-      </text>
-    </comment>
-    <comment ref="C2206" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P064
-监察官将信纸收了起来，冷冷地看着我。</t>
-      </text>
-    </comment>
-    <comment ref="C2207" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P065
-监察官：）#平静「你的解释前后矛盾。带走，等候进一步调查。」</t>
-      </text>
-    </comment>
-    <comment ref="C2208" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P067
-监察官：（#思索）「私人信件？我看见的可是写着一串数字的不明信件。」</t>
-      </text>
-    </comment>
-    <comment ref="C2209" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P068
-我再次对上他探究的眼睛</t>
-      </text>
-    </comment>
-    <comment ref="C2210" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P070
-我毫不畏惧地直视着他，没有试图争抢那封信，也没有慌张，一字一句地说道</t>
-      </text>
-    </comment>
-    <comment ref="C2211" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P071
-{playername}；「您可以搜查，也可以暂时扣下这封信。但在没有证据之前，请不要把无法解读的信件直接说成不法密信。这不过是前任店长给我留下的关于咖啡馆内部账单。」</t>
-      </text>
-    </comment>
-    <comment ref="C2212" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P072
-咖啡馆内安静了下来，所有人都在看着我们</t>
-      </text>
-    </comment>
-    <comment ref="C2213" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P073
-我继续说道</t>
-      </text>
-    </comment>
-    <comment ref="C2214" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P074
-{playername}：「如果您认为我有问题，可以按照教会的程序调查。我会配合，但不会承认自己没有做过的事。」</t>
-      </text>
-    </comment>
-    <comment ref="C2215" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P075
-监察官的目光在我脸上停留了许久，像是在判断我究竟是虚张声势，还是确实问心无愧。</t>
-      </text>
-    </comment>
-    <comment ref="C2216" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P076
-最终他冷哼一声，将信纸拍在桌上。</t>
-      </text>
-    </comment>
-    <comment ref="C2217" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P077
-监察官：（#平静）「哼，没有证据，我们也不会仅凭一封无从解读的信抓人。收好你的信，但是如果之后我们发现有什么问题，你等着被传唤吧。」</t>
-      </text>
-    </comment>
-    <comment ref="C2218" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P078
-{playername}：「我明白。」</t>
-      </text>
-    </comment>
-    <comment ref="C2219" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P080
-我想要反驳，却被监察官凌厉的目光压得说不出话来。</t>
-      </text>
-    </comment>
-    <comment ref="C2220" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P081
-{playername}：「这……这是前任店长给我留下的关于咖啡馆内部账单的信件……但是……我也不知道上面具体是什么意思……」</t>
-      </text>
-    </comment>
-    <comment ref="C2221" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P082
-监察官：（#思索）「不知道具体意思？那么你怎么知道这是咖啡馆内部账单？」</t>
-      </text>
-    </comment>
-    <comment ref="C2222" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P083
-我张张嘴又闭上，他充满威严与怀疑的目光刺痛了我，不敢再继续辩解</t>
-      </text>
-    </comment>
-    <comment ref="C2223" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P084
-监察官看着我的沉默，像是已经得出了自己的判断。</t>
-      </text>
-    </comment>
-    <comment ref="C2224" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P085
-监察官：（#平静）「那正好，信带走，回去让我们监察司的人好好领会一下你所谓的「私人信件」。至于你，随我们走一趟。」</t>
-      </text>
-    </comment>
-    <comment ref="C2225" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P088
-监察官：（#思索）「你倒是很清楚我们为何而来。」</t>
-      </text>
-    </comment>
-    <comment ref="C2226" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P089
-我指了指他手中的信纸</t>
-      </text>
-    </comment>
-    <comment ref="C2227" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P090
-{playername}：「但这只是一封私人信件，是前任店长给我留下的之前店铺的账单，没有提到「王选者」，也没有任何与法律修改相关的内容，只不过是一串普通数字罢了。而且我听闻前几天是在民间宣扬「王选者」，如果对方采取这样隐晦的方式，并不能达到宣传的目的吧。」</t>
-      </text>
-    </comment>
-    <comment ref="C2228" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P091
-监察官听闻多看了我两眼</t>
-      </text>
-    </comment>
-    <comment ref="C2229" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P092
-监察官：（#思索）「你倒是想得挺清楚。不过你说得没错，目前确实没有证据证明这封信与那件事有关。」</t>
-      </text>
-    </comment>
-    <comment ref="C2230" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P093
-他又沉默了片刻，最终选择将信纸递给身旁的监察员，几名监察员低声讨论后也无法确认其中有什么异常。</t>
-      </text>
-    </comment>
-    <comment ref="C2231" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P094
-监察官：（#平静）「信你收好。至于你，继续留在店里接受调查，不得擅自离开圣徒街。」</t>
-      </text>
-    </comment>
-    <comment ref="C2232" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P096
-监察官：（#思索）「你倒是很清楚我们为何而来。」</t>
-      </text>
-    </comment>
-    <comment ref="C2233" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P097
-我试图继续说出一些合理而又道理的理由来摆脱嫌疑，但脑中一片混乱，只能勉强找出几个听起来合理的词。</t>
-      </text>
-    </comment>
-    <comment ref="C2234" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P098
-{playername}：「这封信……是我与前任店长沟通的私人信件……上面写的东西应该是店铺内部经营状况，可能就是之前他们订购咖啡豆和机器设备的开销……没什么重要的。怎么看都与你们要查的东西无关吧……」</t>
-      </text>
-    </comment>
-    <comment ref="C2235" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P099
-话一出口，我便意识到自己的解释漏洞百出。</t>
-      </text>
-    </comment>
-    <comment ref="C2236" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P100
-监察官：（#思索）「可能？应该？{playername}店长，你连自己要解释什么都不知道。」</t>
-      </text>
-    </comment>
-    <comment ref="C2237" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P101
-我试图继续补充，却只能让事情变得更加糟糕。</t>
-      </text>
-    </comment>
-    <comment ref="C2238" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P102
-监察官：（#平静）「你的说辞无法令人信服。」「先把人带走，信件作为证物收存。」</t>
-      </text>
-    </comment>
-    <comment ref="C2239" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P104
-我注意到监察官虽然拿着信纸，却没有认真揣摩上面的数字含义，反而仔细观察着我的反应</t>
-      </text>
-    </comment>
-    <comment ref="C2240" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P106
-我看出来了，他并没有读懂信上的内容，他在意的是我是否会因此露出破绽</t>
-      </text>
-    </comment>
-    <comment ref="C2241" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P107
-我让自己的语气尽量平稳，目光坦荡地对上监察官探究的眼神</t>
-      </text>
-    </comment>
-    <comment ref="C2242" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P108
-{playernanem}：「这不过是前任店长给我留下的店铺内部的账单罢了，这样的单子我这还有很多。不知道长官您要搜查的是什么，但想必是与国家大事相关，我想不会是这种写了一串普通数字的私人信件吧。」</t>
-      </text>
-    </comment>
-    <comment ref="C2243" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P109
-监察官听了我话又探究地看了信纸两眼</t>
-      </text>
-    </comment>
-    <comment ref="C2244" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P110
-我趁势说道</t>
-      </text>
-    </comment>
-    <comment ref="C2245" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P111
-{playername}：「您可以把它带回去找人辨认。但我相信，无论如何解读，它都只是一张记录店铺经营状况的账单。」</t>
-      </text>
-    </comment>
-    <comment ref="C2246" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P112
-监察官看向身后的监察员。对方检查了信纸和抽屉，低声说了几句，似乎没有发现新的线索。</t>
-      </text>
-    </comment>
-    <comment ref="C2247" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P113
-监察官：（#平静）「……暂时按普通信件处理。你继续营业，但近期不要离开圣徒街。」</t>
-      </text>
-    </comment>
-    <comment ref="C2248" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P114
-{playernmae}：「我知道了。」</t>
-      </text>
-    </comment>
-    <comment ref="C2249" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P116
-我试图观察监察官的脸色以获取更多信息，却没能从他的神情中看出任何端倪。</t>
-      </text>
-    </comment>
-    <comment ref="C2250" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P117
-{playername}：「我不知道它是什么……或许是前任店长给我留下的信息吧……前任店长在店里留下了不少东西，我还没有一一检查。」</t>
-      </text>
-    </comment>
-    <comment ref="C2251" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P118
-监察官：（#平静）「你说自己没有检查过，却在我没有给你出示这封信具体内容的情况下说这是前任店长留下的。显然，你的解释站不住脚。」</t>
-      </text>
-    </comment>
-    <comment ref="C2252" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P119
-他似笑非笑地看着我</t>
-      </text>
-    </comment>
-    <comment ref="C2253" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P120
-我这才意识到，自己的话已经被对方抓住了漏洞。</t>
-      </text>
-    </comment>
-    <comment ref="C2254" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P121
-监察官示意监察员上前，将信纸递交给他，随后监察员将信纸收进一个文件袋中。</t>
-      </text>
-    </comment>
-    <comment ref="C2255" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P122
-监察官：（#平静）「带走。等你想清楚之后，再向我们解释。」</t>
-      </text>
-    </comment>
-    <comment ref="C2256" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P124
-很快，教会监察司的人离开了咖啡馆，前往圣徒街其他店铺里搜寻</t>
-      </text>
-    </comment>
-    <comment ref="C2257" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P125
-他们离开后，阿黛尔赶紧跑过来关切地询问我</t>
-      </text>
-    </comment>
-    <comment ref="C2258" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P126
-阿黛尔·米尼耶：（#激动）「{playername}店长，你刚才真实太厉害了！面对教会监察司的人还能如此镇定地面对！」</t>
-      </text>
-    </comment>
-    <comment ref="C2259" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P127
-听完阿黛尔的话我感到一丝无奈，原来刚才的我在她眼里是这样的吗</t>
-      </text>
-    </comment>
-    <comment ref="C2260" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P128
-我现在感到一丝后怕，如果刚才没有应对得当，现在的我是会被他们带走审问吗？</t>
-      </text>
-    </comment>
-    <comment ref="C2261" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P129
-幸好我事先有想好万一被发现应当如何应对，才逃过这一劫</t>
-      </text>
-    </comment>
-    <comment ref="C2262" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P130
-看来以后需要把这些东西隐藏得更加隐蔽才好。不，还是赶紧找个机会把信都给烧掉吧</t>
-      </text>
-    </comment>
-    <comment ref="C2263" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P131
-阿黛尔不休的话打断了我的思绪</t>
-      </text>
-    </comment>
-    <comment ref="C2264" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P132
-阿黛尔·米尼耶：（#悲伤）「不过刚才由于监察司的到来，好多顾客都离开了呢……不知道接下来生意会不会受到影响……」</t>
-      </text>
-    </comment>
-    <comment ref="C2265" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P133
-这时我才想起刚才被迫停留在我和监察司中间的倒霉顾客</t>
-      </text>
-    </comment>
-    <comment ref="C2266" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P134
-目前店里没有发现那位顾客的身影，或许是什么时候趁乱离开了吧</t>
-      </text>
-    </comment>
-    <comment ref="C2267" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P135
-店里的设备没有遭到损坏，看来监察司搜查的时候还是有分寸的</t>
-      </text>
-    </comment>
-    <comment ref="C2268" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P136
-今天发生了这样的事，未来几天还是低调点吧</t>
-      </text>
-    </comment>
-    <comment ref="C2269" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P137
-{playername}：「希望不会吧。阿黛尔，未来两天我们还是正常营业，但是低调一些。我担心再次引来什么大麻烦。」</t>
-      </text>
-    </comment>
-    <comment ref="C2270" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P138
-阿黛尔·米尼耶：（#开心）「我也正有此意呢，店长！」</t>
-      </text>
-    </comment>
-    <comment ref="C2271" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P139
-{playername}：「阿黛尔，振作精神，我们还要准备迎接接下来的客人呢！」</t>
-      </text>
-    </comment>
-    <comment ref="C2272" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P140
-阿黛尔·米尼耶：（#开心）「店长，你说得对！那我去门口继续招揽一下客人~」</t>
-      </text>
-    </comment>
-    <comment ref="C2273" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P141
-阿黛尔蹦蹦跳跳地离开了</t>
-      </text>
-    </comment>
-    <comment ref="C2274" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P142
-我趁机将几封信烧毁，然后若无其事地回到吧台</t>
-      </text>
-    </comment>
-    <comment ref="C2275" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P144
-不知道接下来会迎接怎样的挑战和危机呢……</t>
-      </text>
-    </comment>
-    <comment ref="C2276" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P147
-我在所有人的注视下被监察司的人带走了，离开咖啡馆前我最后看见的是阿黛尔满是担忧的脸</t>
-      </text>
-    </comment>
-    <comment ref="C2277" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P148
-他们会如何审问我呢？我要说什么呢？这封信涉及的密文是否会被他们觉察呢？</t>
-      </text>
-    </comment>
-    <comment ref="C2278" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P149
-带着万千思绪，我被带到了教会看守所中</t>
-      </text>
-    </comment>
-    <comment ref="C2279" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P150
-啊，从刚毕业的大学生到咖啡馆店长再到在押犯原来只需要一个月吗……</t>
-      </text>
-    </comment>
-    <comment ref="C2280" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P151
-我被分配进了一个单独的房间，等待监察司的检查结果</t>
-      </text>
-    </comment>
-    <comment ref="C2281" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.20-S1.docx
-church.1020.s1.P152
-我就此陷入了无尽的等待</t>
-      </text>
-    </comment>
-    <comment ref="C2282" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P006
-我被带到看守所后，已经见证了第三次日出。</t>
-      </text>
-    </comment>
-    <comment ref="C2283" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P007
-在这间狭小的拘押室里，我甚至开始怀念咖啡馆那张吱呀作响的旧椅子。</t>
-      </text>
-    </comment>
-    <comment ref="C2284" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P008
-不知道阿黛尔现在怎么样了，咖啡馆有没有正常营业……</t>
-      </text>
-    </comment>
-    <comment ref="C2285" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P010
-看守：⌈出来，有人要见你。⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2286" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P013
-监察官：⌈经过调查，我们没有发现你直接参与非法结社活动的证据。⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2287" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P014
-{playername}：⌈所以我可以离开了？⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2288" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P015
-监察官：⌈别急。那些密文的来源仍然不明，我们还需要你作出一些保证。⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2289" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P016
-监察官：⌈如果今后发现任何与乱党有关的情报，你必须向教会报告。⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2290" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P017
-{playername}：⌈……⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2291" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P018
-监察官：⌈你也可以拒绝。但调查结束前，我们恐怕不能放你走。⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2292" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P019
-他看了看桌上的文件，似乎在等待我的回答。</t>
-      </text>
-    </comment>
-    <comment ref="C2293" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P021
-①⌈既然没有犯罪证据，你们就没有理由继续拘押我。⌋（语言检定）</t>
-      </text>
-    </comment>
-    <comment ref="C2294" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P022
-②⌈或许我们可以商量一个更方便的解决办法。⌋（资金条件）</t>
-      </text>
-    </comment>
-    <comment ref="C2295" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P023
-③⌈既然如此，你们就继续调查吧。⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2296" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P025
-{playername}：⌈没有证据就继续拘押一位合法经营的店主，这恐怕也不符合教会的规定吧？⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2297" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P026
-监察官：⌈你是在质疑监察司的决定？⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2298" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P027
-{playername}：⌈我当然尊重教会的职责，但你刚刚也说了，调查没有发现我参与乱党的证据。⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2299" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P028
-{playername}：⌈况且，沸点咖啡馆在圣徒街经营了那么多年，应该不算一家完全没有人认识的店铺。⌋⌈你们可以向街坊邻居调查，也可以在之后继续观察咖啡馆的经营。但至少现在，没有必要让我继续待在这里。⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2300" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P029
-监察官：⌈嗯……⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2301" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P032
-监察官：⌈倒也有些道理。⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2302" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P033
-他沉思片刻，在文件上签了字。</t>
-      </text>
-    </comment>
-    <comment ref="C2303" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P034
-监察官：⌈好吧，你可以走了。但调查还没结束，今后记得配合监察司。⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2304" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P037
-监察官：⌈是否符合规定，恐怕还轮不到你来判断。带他回去。⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2305" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P040
-{playername}：⌈继续调查既耽误你们的时间，也耽误我的生意。或许有个对双方都方便的办法？⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2306" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P041
-我暗示了一下能够支付的金额。</t>
-      </text>
-    </comment>
-    <comment ref="C2307" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P042
-监察官抬起头，意味深长地看了我一眼。</t>
-      </text>
-    </comment>
-    <comment ref="C2308" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P043
-监察官：⌈你是沸点咖啡馆的店长是吧？一会儿我派人跟着你去，把钱打点清楚再说。⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2309" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P044
-{playername}：⌈好的，好的，当然可以。⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2310" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P045
-监察官：⌈不过我要这个数。⌋（数值待定）</t>
-      </text>
-    </comment>
-    <comment ref="C2311" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P046
-{playername}：⌈抢劫啊？⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2312" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P047
-监察官：⌈哎，看来你不乐意，那就只好多关几天咯！⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2313" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P048
-监察官：⌈嘶......看来你是个聪明人。既然没有发现犯罪证据，我们当然没有必要继续浪费时间。⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2314" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P054
-看来今天又得在这里过夜了。</t>
-      </text>
-    </comment>
-    <comment ref="C2315" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P055
-我靠在墙边，正想着阿黛尔会不会已经把我当成失踪人口，铁门却再次打开了。</t>
-      </text>
-    </comment>
-    <comment ref="C2316" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P057
-看守：⌈出来，你可以走了。⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2317" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P058
-{playername}：⌈啊？可是刚刚不是还说……⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2318" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P059
-看守：⌈上面送来了新的释放手续。你还想留下来不成？⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2319" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P060
-他将一份盖好印章的文件塞进我手中。</t>
-      </text>
-    </comment>
-    <comment ref="C2320" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P061
-上面清清楚楚地写着：「证据不足，准予释放。」</t>
-      </text>
-    </comment>
-    <comment ref="C2321" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P062
-怎么突然就证据不足了？</t>
-      </text>
-    </comment>
-    <comment ref="C2322" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P063
-不过，我当然没有理由拒绝。</t>
-      </text>
-    </comment>
-    <comment ref="C2323" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P065
-我看了看那张文件。</t>
-      </text>
-    </comment>
-    <comment ref="C2324" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P066
-上面的印章和其他文书没有什么区别。</t>
-      </text>
-    </comment>
-    <comment ref="C2325" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P067
-不过，在旁边的登记簿上，我的名字似乎被人重新填写过一次。</t>
-      </text>
-    </comment>
-    <comment ref="C2326" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P068
-原本的字迹已经被墨水覆盖，又用另一种笔迹写上了新的处理结果。</t>
-      </text>
-    </comment>
-    <comment ref="C2327" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P069
-而且，记录上标注的释放时间，似乎比我刚刚被带回牢房的时间还要早。</t>
-      </text>
-    </comment>
-    <comment ref="C2328" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P070
-……</t>
-      </text>
-    </comment>
-    <comment ref="C2329" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P071
-有人修改了我的拘押记录？</t>
-      </text>
-    </comment>
-    <comment ref="C2330" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P073
-{playername}：⌈请问，是谁批准释放我的？⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2331" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P074
-看守：⌈登记上写得很清楚，按照规定处理的。⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2332" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P075
-{playername}：⌈我是说，刚刚是谁来办理手续的？⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2333" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P076
-看守：⌈我哪知道？今天送过来的文件这么多。⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2334" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P077
-看守：⌈话怎么这么多？再问我就和上面说你不服命令，重新把你关进去。⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2335" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P078
-{playername}：⌈……⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2336" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P079
-算了。</t>
-      </text>
-    </comment>
-    <comment ref="C2337" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P080
-不管究竟是谁帮了我，现在最重要的事情，还是赶紧离开这个地方。</t>
-      </text>
-    </comment>
-    <comment ref="C2338" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P088
-{playername}：⌈我回来了！⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2339" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P089
-阿黛尔：（#迷惑）⌈……{playername}？⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2340" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P090
-她愣了一下，随即快步走来。</t>
-      </text>
-    </comment>
-    <comment ref="C2341" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P091
-阿黛尔：（#兴奋）⌈你终于回来了！⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2342" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P092
-阿黛尔：（#焦虑）⌈他们没有对你怎么样吧？⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2343" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P093
-{playername}：⌈没有没有，只是被关了几天。⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2344" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P094
-阿黛尔：（#焦虑）⌈这还叫没什么！我去问了好几次，他们都不肯告诉我什么时候放你回来。⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2345" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P095
-{playername}：⌈抱歉，让你担心了。⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2346" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P096
-阿黛尔：（#平静）⌈……回来就好。⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2347" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P097
-她替我拉开椅子。</t>
-      </text>
-    </comment>
-    <comment ref="C2348" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P098
-阿黛尔：（#思索）⌈不过，他们怎么突然愿意放人了？⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2349" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P101
-{playername}：⌈他们本来也没找到犯罪证据，我和监察官讲了讲道理，就把我放了。⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2350" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P102
-阿黛尔：（#开心）⌈那真是太好了，至少教会的人还愿意讲道理。⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2351" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P103
-阿黛尔：（#思索）⌈不过，既然他们已经盯上了咖啡馆，以后还是得小心。⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2352" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P105
-{playername}：⌈花了点钱，总算让他们同意放人了。⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2353" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P106
-阿黛尔：（#迷惑）⌈花钱？你是说……⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2354" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P107
-{playername}：⌈嘘！别说出来。⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2355" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P108
-阿黛尔：（#焦虑）⌈这些人真是……⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2356" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P109
-她叹了口气。</t>
-      </text>
-    </comment>
-    <comment ref="C2357" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P110
-{playername}：⌈你一会让把钱筹一下送过去。⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2358" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P111
-阿黛尔：（#生气）⌈我才不做这种事情呢！⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2359" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P112
-{playername}：⌈那行，一会儿我去干这脏活累活吧......⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2360" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P114
-{playername}：⌈说实话，我也不知道。他们本来还要继续调查，结果突然有人送来文件，说我可以走了。⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2361" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P115
-阿黛尔：（#迷惑）⌈突然有人送来文件？⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2362" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P116
-{playername}：⌈是啊，连看守都不知道怎么回事。真奇怪。⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2363" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P117
-阿黛尔似乎想到了什么，沉默了一会儿。</t>
-      </text>
-    </comment>
-    <comment ref="C2364" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P118
-阿黛尔：（#思索）⌈原来如此......⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2365" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P119
-{playername}：⌈你知道些什么？⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2366" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P120
-阿黛尔：（#焦虑）⌈啊？没有，我也只是猜测……⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2367" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P121
-{playername}：⌈猜测什么？⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2368" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P122
-阿黛尔：（#思索）⌈以前杜瓦尔先生经营咖啡馆的时候，认识不少人。有些人虽然不方便公开露面，但很重视这家店。⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2369" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P123
-阿黛尔：（#思索）⌈如果他们知道你被教会带走了，或许不会坐视不管。⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2370" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P124
-{playername}：⌈你是说，有人暗中帮了我？⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2371" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P125
-阿黛尔：（#平静）⌈只是猜测而已，我也不确定。⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2372" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P126
-她低头整理起桌上的餐具，似乎不打算继续这个话题。</t>
-      </text>
-    </comment>
-    <comment ref="C2373" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P127
-阿黛尔：（#思索）⌈不过，如果真是他们……看来那些人还没有忘记这里。⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2374" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P128
-{playername}：⌈那些人？⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2375" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P129
-阿黛尔：（#尴尬）⌈没什么。你才刚回来，先休息吧。⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2376" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P131
-阿黛尔：（#开心）⌈总之，欢迎回来，店长先生。⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2377" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P132
-{playername}：⌈嗯，我回来了。⌋</t>
-      </text>
-    </comment>
-    <comment ref="C2378" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P133
-我靠在椅背上，终于松了口气。</t>
-      </text>
-    </comment>
-    <comment ref="C2379" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P134
-咖啡馆似乎什么都没有改变。</t>
-      </text>
-    </comment>
-    <comment ref="C2380" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P135
-不过我的心态已经完全不同，</t>
-      </text>
-    </comment>
-    <comment ref="C2381" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P136
-在监牢里度过的三天却让我后背发凉。</t>
-      </text>
-    </comment>
-    <comment ref="C2382" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P137
-我这次能因信的的事情被抓进去，下一次又会因为什么遭遇不测。</t>
-      </text>
-    </comment>
-    <comment ref="C2383" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P138
-三天前，教会监察司的人突然闯进咖啡馆，将我带走。</t>
-      </text>
-    </comment>
-    <comment ref="C2384" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P139
-三天后，我终于回到了这里。</t>
-      </text>
-    </comment>
-    <comment ref="C2385" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P140
-但那几封密文仍然被扣押在教会手中。</t>
-      </text>
-    </comment>
-    <comment ref="C2386" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P141
-而且，在离开看守所之前，他们还专门提醒我：</t>
-      </text>
-    </comment>
-    <comment ref="C2387" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P142
-如果发现有关乱党的情报，必须向教会报告。</t>
-      </text>
-    </comment>
-    <comment ref="C2388" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P143
-……</t>
-      </text>
-    </comment>
-    <comment ref="C2389" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P144
-这算什么意思？</t>
-      </text>
-    </comment>
-    <comment ref="C2390" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P145
-今后要是那个神秘人再给我送来几封信，难道我还得主动跑去监察司告诉他们？</t>
-      </text>
-    </comment>
-    <comment ref="C2391" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P146
-开什么玩笑。</t>
-      </text>
-    </comment>
-    <comment ref="C2392" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P147
-可是，如果不这么做……</t>
-      </text>
-    </comment>
-    <comment ref="C2393" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P148
-我抬起头，看向正在厨房里忙碌的阿黛尔。</t>
-      </text>
-    </comment>
-    <comment ref="C2394" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P149
-自从来到这家店，怪事就一个接着一个。</t>
-      </text>
-    </comment>
-    <comment ref="C2395" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P150
-王都圣诺特的漩涡下面究竟有多少骇人的存在？它们在谋划些什么？为什么我会被卷到这些事情里？我还能保护我和身边的人吗？</t>
-      </text>
-    </comment>
-    <comment ref="C2396" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P151
-三日关押积累下来的疲惫与巨大的思考量冲撞着我的思绪，</t>
-      </text>
-    </comment>
-    <comment ref="C2397" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S1.docx
-church.1023.s1.P152
-我再也无力去支撑精神，倒在座椅上睡去......</t>
-      </text>
-    </comment>
-    <comment ref="C2398" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
-church.1023.s2.P005
-距离上次与监察官会面又过了不知多少天</t>
-      </text>
-    </comment>
-    <comment ref="C2399" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
-church.1023.s2.P006
-这段日子里我尝试与外界联系，却都失败了</t>
-      </text>
-    </comment>
-    <comment ref="C2400" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
-church.1023.s2.P007
-我所能接触到的只有这四方墙壁</t>
-      </text>
-    </comment>
-    <comment ref="C2401" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
-church.1023.s2.P008
-不知道今日是何日，不知道咖啡馆怎么样了，不知道阿黛尔怎么样了，不知道我离开之后神秘人是否还在接触咖啡馆……</t>
-      </text>
-    </comment>
-    <comment ref="C2402" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
-church.1023.s2.P009
-不知道……不知道……什么都不知道……</t>
-      </text>
-    </comment>
-    <comment ref="C2403" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
-church.1023.s2.P010
-我的意识在这种日子中渐渐模糊……</t>
-      </text>
-    </comment>
-    <comment ref="C2404" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
-church.1023.s2.P013
-沉寂和单调，是我牢狱生活的全部</t>
-      </text>
-    </comment>
-    <comment ref="C2405" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
-church.1023.s2.P014
-直到某一天我的世界出现了新的声音</t>
-      </text>
-    </comment>
-    <comment ref="C2406" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
-church.1023.s2.P016
-那是几个穿着制服的人，走进了关押我的房间内</t>
-      </text>
-    </comment>
-    <comment ref="C2407" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
-church.1023.s2.P017
-他们对着我说了一串话</t>
-      </text>
-    </comment>
-    <comment ref="C2408" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
-church.1023.s2.P018
-但由于脱离外界太久，意识模糊，我只能隐隐约约辨认出几个词，什么「革命」 「镇压」 「清算」……</t>
-      </text>
-    </comment>
-    <comment ref="C2409" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
-church.1023.s2.P019
-在我还未能理解这些词句的意思时</t>
-      </text>
-    </comment>
-    <comment ref="C2410" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
-church.1023.s2.P020
-我感到我被他们强行从地上拉了起来，被推动着向外走</t>
-      </text>
-    </comment>
-    <comment ref="C2411" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
-church.1023.s2.P021
-方墙以外的世界</t>
-      </text>
-    </comment>
-    <comment ref="C2412" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
-church.1023.s2.P022
-新鲜的空气</t>
-      </text>
-    </comment>
-    <comment ref="C2413" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
-church.1023.s2.P023
-曾经我渴求无数次的东西就这样呈现在我面前</t>
-      </text>
-    </comment>
-    <comment ref="C2414" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
-church.1023.s2.P024
-现下我却无暇顾及</t>
-      </text>
-    </comment>
-    <comment ref="C2415" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
-church.1023.s2.P025
-我不知道我会被他们带往哪里</t>
-      </text>
-    </comment>
-    <comment ref="C2416" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
-church.1023.s2.P026
-就这样走着，走着……</t>
-      </text>
-    </comment>
-    <comment ref="C2417" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
-church.1023.s2.P027
-这里是哪里？</t>
-      </text>
-    </comment>
-    <comment ref="C2418" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
-church.1023.s2.P028
-刑场？</t>
-      </text>
-    </comment>
-    <comment ref="C2419" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
-church.1023.s2.P029
-我要死了吗？</t>
-      </text>
-    </comment>
-    <comment ref="C2420" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
-church.1023.s2.P030
-为什么？</t>
-      </text>
-    </comment>
-    <comment ref="C2421" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
-church.1023.s2.P031
-为什么？为什么？为什么？为什么？为什么？</t>
-      </text>
-    </comment>
-    <comment ref="C2422" authorId="3" shapeId="0">
-      <text>
-        <t>D:\桌面\文案\王庭教会\MA70.10.23-S2.docx
-church.1023.s2.P032
-带着这样的想法，我迎来了人生的终点。</t>
-      </text>
-    </comment>
-    <comment ref="B2426" authorId="6" shapeId="0">
-      <text>
-        <t>{
-  "scope": "E blocked configuration preparation"
-}</t>
-      </text>
-    </comment>
-    <comment ref="B2427" authorId="6" shapeId="0">
-      <text>
-        <t>{
-  "scope": "E blocked configuration preparation"
-}</t>
-      </text>
-    </comment>
-    <comment ref="B2428" authorId="6" shapeId="0">
-      <text>
-        <t>{
-  "scope": "E blocked configuration preparation"
-}</t>
-      </text>
-    </comment>
-    <comment ref="B2429" authorId="6" shapeId="0">
-      <text>
-        <t>{
-  "scope": "E blocked configuration preparation"
-}</t>
-      </text>
-    </comment>
-    <comment ref="B2430" authorId="6" shapeId="0">
-      <text>
-        <t>{
-  "scope": "E blocked configuration preparation"
-}</t>
-      </text>
-    </comment>
-    <comment ref="B2431" authorId="6" shapeId="0">
-      <text>
-        <t>{
-  "scope": "E blocked configuration preparation"
-}</t>
-      </text>
-    </comment>
-    <comment ref="B2432" authorId="6" shapeId="0">
-      <text>
-        <t>{
-  "scope": "E blocked configuration preparation"
-}</t>
-      </text>
-    </comment>
-    <comment ref="B2433" authorId="6" shapeId="0">
-      <text>
-        <t>{
-  "scope": "E blocked configuration preparation"
-}</t>
-      </text>
-    </comment>
-    <comment ref="B2434" authorId="6" shapeId="0">
-      <text>
-        <t>{
-  "scope": "E blocked configuration preparation"
-}</t>
-      </text>
-    </comment>
-    <comment ref="B2435" authorId="6" shapeId="0">
-      <text>
-        <t>{
-  "scope": "E blocked configuration preparation"
-}</t>
-      </text>
-    </comment>
-    <comment ref="B2436" authorId="6" shapeId="0">
-      <text>
-        <t>{
-  "scope": "E blocked configuration preparation"
-}</t>
-      </text>
-    </comment>
-    <comment ref="B2437" authorId="7" shapeId="0">
-      <text>
-        <t>{"batch": "A05", "source_map_line": "1447b2784eca6638ccf67a572ba8863d0abd3b6db0e02bb6015bac2457ca108a"}</t>
-      </text>
-    </comment>
-    <comment ref="B2438" authorId="8" shapeId="0">
-      <text>
-        <t>B1016 source mapped; stops at P015; no completion or brewing</t>
-      </text>
-    </comment>
-    <comment ref="B2439" authorId="8" shapeId="0">
-      <text>
-        <t>B1016 source mapped; stops at P015; no completion or brewing</t>
-      </text>
-    </comment>
-    <comment ref="B2440" authorId="8" shapeId="0">
-      <text>
-        <t>B1012 source-map; result-free blocked construction</t>
-      </text>
-    </comment>
-    <comment ref="B2445" authorId="9" shapeId="0">
-      <text>
-        <t>D1023 blocked source preparation; source numbering preserved; no outcomes.</t>
-      </text>
-    </comment>
-    <comment ref="B2446" authorId="10" shapeId="0">
-      <text>
-        <t>{"batch": "A01-A04-formal", "authorization": "User A01-A04 formal source-table decision", "owner": null}</t>
-      </text>
-    </comment>
-    <comment ref="B2447" authorId="10" shapeId="0">
-      <text>
-        <t>{"batch": "A01-A04-formal", "authorization": "User A01-A04 formal source-table decision", "owner": null}</t>
-      </text>
-    </comment>
-    <comment ref="B2448" authorId="10" shapeId="0">
-      <text>
-        <t>{"batch": "A01-A04-formal", "authorization": "User A01-A04 formal source-table decision", "owner": null}</t>
-      </text>
-    </comment>
-    <comment ref="B2449" authorId="10" shapeId="0">
-      <text>
-        <t>{"batch": "A01-A04-formal", "authorization": "User A01-A04 formal source-table decision", "owner": null}</t>
-      </text>
-    </comment>
-    <comment ref="B2450" authorId="10" shapeId="0">
-      <text>
-        <t>{"batch": "A01-A04-formal", "authorization": "User A01-A04 formal source-table decision", "owner": null}</t>
-      </text>
-    </comment>
-    <comment ref="B2451" authorId="10" shapeId="0">
-      <text>
-        <t>{"batch": "A01-A04-formal", "authorization": "User A01-A04 formal source-table decision", "owner": null}</t>
-      </text>
-    </comment>
-    <comment ref="B2452" authorId="10" shapeId="0">
-      <text>
-        <t>{"batch": "A01-A04-formal", "authorization": "User A01-A04 formal source-table decision", "owner": null}</t>
-      </text>
-    </comment>
-    <comment ref="B2453" authorId="10" shapeId="0">
-      <text>
-        <t>{"batch": "A01-A04-formal", "authorization": "User A01-A04 formal source-table decision", "owner": null}</t>
-      </text>
-    </comment>
-    <comment ref="B2454" authorId="10" shapeId="0">
-      <text>
-        <t>{"batch": "A01-A04-formal", "authorization": "User A01-A04 formal source-table decision", "owner": null}</t>
-      </text>
-    </comment>
-    <comment ref="B2455" authorId="10" shapeId="0">
-      <text>
-        <t>{"batch": "A01-A04-formal", "authorization": "User A01-A04 formal source-table decision", "owner": null}</t>
-      </text>
-    </comment>
-    <comment ref="B2456" authorId="10" shapeId="0">
-      <text>
-        <t>{"batch": "A01-A04-formal", "authorization": "User A01-A04 formal source-table decision", "owner": null}</t>
-      </text>
-    </comment>
-    <comment ref="B2457" authorId="10" shapeId="0">
-      <text>
-        <t>{"batch": "A01-A04-formal", "authorization": "User A01-A04 formal source-table decision", "owner": null}</t>
-      </text>
-    </comment>
-    <comment ref="B2458" authorId="10" shapeId="0">
-      <text>
-        <t>{"batch": "A01-A04-formal", "authorization": "User A01-A04 formal source-table decision", "owner": null}</t>
-      </text>
-    </comment>
-    <comment ref="B2459" authorId="11" shapeId="0">
-      <text>
-        <t>{"batch": "A05-reporter", "authorization": "Parent-authorized A05 formal source tables"}</t>
-      </text>
-    </comment>
-    <comment ref="B2460" authorId="11" shapeId="0">
-      <text>
-        <t>{"batch": "A05-reporter", "authorization": "Parent-authorized A05 formal source tables"}</t>
-      </text>
-    </comment>
-    <comment ref="B2461" authorId="11" shapeId="0">
-      <text>
-        <t>{"batch": "A05-reporter", "authorization": "Parent-authorized A05 formal source tables"}</t>
-      </text>
-    </comment>
-    <comment ref="B2462" authorId="11" shapeId="0">
-      <text>
-        <t>{"batch": "A05-reporter", "authorization": "Parent-authorized A05 formal source tables"}</t>
-      </text>
-    </comment>
-    <comment ref="B2463" authorId="11" shapeId="0">
-      <text>
-        <t>{"batch": "A05-reporter", "authorization": "Parent-authorized A05 formal source tables"}</t>
-      </text>
-    </comment>
-    <comment ref="B2464" authorId="11" shapeId="0">
-      <text>
-        <t>{"batch": "A05-reporter", "authorization": "Parent-authorized A05 formal source tables"}</t>
-      </text>
-    </comment>
-    <comment ref="B2465" authorId="11" shapeId="0">
-      <text>
-        <t>{"batch": "A05-reporter", "authorization": "Parent-authorized A05 formal source tables"}</t>
       </text>
     </comment>
   </commentList>
@@ -13992,7 +11530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2474"/>
+  <dimension ref="A1:D2100"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -44957,7 +42495,7 @@
       </c>
       <c r="C1830" t="inlineStr">
         <is>
-          <t>那就定在三天后，怎么样？</t>
+          <t>那就定在两天后，怎么样？</t>
         </is>
       </c>
       <c r="D1830" t="inlineStr">
@@ -44974,7 +42512,7 @@
       </c>
       <c r="C1831" t="inlineStr">
         <is>
-          <t>三天后……好！时间应该足够了！</t>
+          <t>两天后……好！时间应该足够了！</t>
         </is>
       </c>
       <c r="D1831" t="inlineStr">
@@ -44991,7 +42529,7 @@
       </c>
       <c r="C1832" t="inlineStr">
         <is>
-          <t>那就先按这个安排准备，今天营业结束后，我们再一起核对一下细节。</t>
+          <t>那今天营业结束后，我们就一起商量一下具体的安排。</t>
         </is>
       </c>
       <c r="D1832" t="inlineStr">
@@ -45127,7 +42665,7 @@
       </c>
       <c r="C1840" t="inlineStr">
         <is>
-          <t>早间的第一拨客人散去后，咖啡馆迎来了一段短暂的整理时间。</t>
+          <t>清晨的咖啡馆还没有正式营业。</t>
         </is>
       </c>
       <c r="D1840" t="inlineStr">
@@ -45144,7 +42682,7 @@
       </c>
       <c r="C1841" t="inlineStr">
         <is>
-          <t>为了准备即将到来的促销活动，我趁客流稍缓整理了一下店里。桌椅已经摆放妥当，柜台上堆着几张写了一半的告示，旁边则是昨晚整理好的账簿。</t>
+          <t>为了准备即将到来的促销活动，我比往常早起了一些。桌椅已经摆放妥当，柜台上堆着几张写了一半的告示，旁边则是昨晚整理好的账簿。</t>
         </is>
       </c>
       <c r="D1841" t="inlineStr">
@@ -45178,7 +42716,7 @@
       </c>
       <c r="C1843" t="inlineStr">
         <is>
-          <t>早上好。请问现在方便接待吗？</t>
+          <t>早安。请问这里已经开始营业了吗？</t>
         </is>
       </c>
       <c r="D1843" t="inlineStr">
@@ -45229,7 +42767,7 @@
       </c>
       <c r="C1846" t="inlineStr">
         <is>
-          <t>看来我来得不太凑巧。不过，既然门没有锁上，想必也不至于打扰太久。</t>
+          <t>看来我来得稍早了一些。不过，既然门没有锁上，想必也不至于打扰太久。</t>
         </is>
       </c>
       <c r="D1846" t="inlineStr">
@@ -45246,7 +42784,7 @@
       </c>
       <c r="C1847" t="inlineStr">
         <is>
-          <t>您好，先生。我们正在整理店里。</t>
+          <t>您好，先生。我们确实还没正式营业。</t>
         </is>
       </c>
       <c r="D1847" t="inlineStr">
@@ -45382,7 +42920,7 @@
       </c>
       <c r="C1855" t="inlineStr">
         <is>
-          <t>您是第一次来这里吗？我们正在整理，不过咖啡已经准备好了。若是不介意，不妨进来坐坐。</t>
+          <t>您是第一次来这里吗？虽然还没正式营业，不过咖啡已经准备好了。若是不介意，不妨进来坐坐。</t>
         </is>
       </c>
       <c r="D1855" t="inlineStr">
@@ -45399,7 +42937,7 @@
       </c>
       <c r="C1856" t="inlineStr">
         <is>
-          <t>如此说来，我倒没有拒绝的理由了。能在早间遇到一位热情的店主，总是件令人愉快的事。</t>
+          <t>如此说来，我倒没有拒绝的理由了。能在清晨遇到一位热情的店主，总是件令人愉快的事。</t>
         </is>
       </c>
       <c r="D1856" t="inlineStr">
@@ -45416,7 +42954,7 @@
       </c>
       <c r="C1857" t="inlineStr">
         <is>
-          <t>您要是愿意的话，也可以先坐一会儿。我们很快就能整理好。</t>
+          <t>您要是愿意的话，也可以先坐一会儿。我们很快就能营业了。</t>
         </is>
       </c>
       <c r="D1857" t="inlineStr">
@@ -45450,7 +42988,7 @@
       </c>
       <c r="C1859" t="inlineStr">
         <is>
-          <t>抱歉，先生，我们还需要整理一会儿。如果您不介意，可以稍后再来。</t>
+          <t>抱歉，先生，我们还需要准备一会儿。如果您不介意，可以等正式营业之后再来。</t>
         </is>
       </c>
       <c r="D1859" t="inlineStr">
@@ -45467,7 +43005,7 @@
       </c>
       <c r="C1860" t="inlineStr">
         <is>
-          <t>当然，先把店里安排妥当也是经营的一部分。既然如此，我便不打扰了。</t>
+          <t>当然，遵守营业时间也是经营的一部分。既然如此，我便不打扰了。</t>
         </is>
       </c>
       <c r="D1860" t="inlineStr">
@@ -45671,7 +43209,7 @@
       </c>
       <c r="C1872" t="inlineStr">
         <is>
-          <t>正是如此。所以我们打算在三天后举办一次促销活动。</t>
+          <t>正是如此。所以我们打算在两天后举办一次促销活动。</t>
         </is>
       </c>
       <c r="D1872" t="inlineStr">
@@ -46351,7 +43889,7 @@
       </c>
       <c r="C1912" t="inlineStr">
         <is>
-          <t>短暂的整理告一段落，我收拾好桌上的账簿，将写了一半的促销告示先放到一旁，准备继续招呼今天的客人。</t>
+          <t>距离正式营业已经没有多少时间，我收拾好桌上的账簿，将写了一半的促销告示先放到一旁，准备迎接今天的第一批客人。</t>
         </is>
       </c>
       <c r="D1912" t="inlineStr">
@@ -49553,6407 +47091,6 @@
       <c r="D2100" t="inlineStr">
         <is>
           <t>A-1018.s1-P097; 正文; text staging only, event disabled</t>
-        </is>
-      </c>
-    </row>
-    <row r="2101">
-      <c r="B2101" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p004.text</t>
-        </is>
-      </c>
-      <c r="C2101" t="inlineStr">
-        <is>
-          <t>由于咖啡馆昨天举办了活动，客流量渐渐变大，我和阿黛尔的工作甚至可以用繁忙来形容。这样的热闹延续到了今天，直到中午时分人流量才减少，我们终于可以获得片刻的歇息了。</t>
-        </is>
-      </c>
-      <c r="D2101" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P004; church.1014.s2.arrival; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2102">
-      <c r="B2102" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p006.text</t>
-        </is>
-      </c>
-      <c r="C2102" t="inlineStr">
-        <is>
-          <t>一名中年男人出现，在离我最近的吧台座位坐下</t>
-        </is>
-      </c>
-      <c r="D2102" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P006; church.1014.s2.arrival; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2103">
-      <c r="B2103" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p008.text</t>
-        </is>
-      </c>
-      <c r="C2103" t="inlineStr">
-        <is>
-          <t>「您好，欢迎光临沸点咖啡馆！」</t>
-        </is>
-      </c>
-      <c r="D2103" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P008; church.1014.s2.arrival; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2104">
-      <c r="B2104" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p009.text</t>
-        </is>
-      </c>
-      <c r="C2104" t="inlineStr">
-        <is>
-          <t>「你好。」</t>
-        </is>
-      </c>
-      <c r="D2104" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P009; church.1014.s2.arrival; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2105">
-      <c r="B2105" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p010.text</t>
-        </is>
-      </c>
-      <c r="C2105" t="inlineStr">
-        <is>
-          <t>「先生，请问您想喝点什么呢？店内的咖啡目前广受好评呢。」</t>
-        </is>
-      </c>
-      <c r="D2105" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P010; church.1014.s2.arrival; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2106">
-      <c r="B2106" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p011.text</t>
-        </is>
-      </c>
-      <c r="C2106" t="inlineStr">
-        <is>
-          <t>「是吗，那来一杯经典的无糖黑咖啡。」</t>
-        </is>
-      </c>
-      <c r="D2106" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P011; church.1014.s2.arrival; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2107">
-      <c r="B2107" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p012.text</t>
-        </is>
-      </c>
-      <c r="C2107" t="inlineStr">
-        <is>
-          <t>「好的，请稍等片刻。」</t>
-        </is>
-      </c>
-      <c r="D2107" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P012; church.1014.s2.arrival; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2108">
-      <c r="B2108" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p014.text</t>
-        </is>
-      </c>
-      <c r="C2108" t="inlineStr">
-        <is>
-          <t>「还不错。」</t>
-        </is>
-      </c>
-      <c r="D2108" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P014; church.1014.s2.arrival; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2109">
-      <c r="B2109" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p015.text</t>
-        </is>
-      </c>
-      <c r="C2109" t="inlineStr">
-        <is>
-          <t>「谢谢您的肯定！请慢慢品尝。」</t>
-        </is>
-      </c>
-      <c r="D2109" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P015; church.1014.s2.arrival; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2110">
-      <c r="B2110" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p017.text</t>
-        </is>
-      </c>
-      <c r="C2110" t="inlineStr">
-        <is>
-          <t>暂时没有更多客人了，正好趁闲暇时放松一下吧</t>
-        </is>
-      </c>
-      <c r="D2110" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P017; church.1014.s2.notice_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2111">
-      <c r="B2111" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p018.text</t>
-        </is>
-      </c>
-      <c r="C2111" t="inlineStr">
-        <is>
-          <t>不知道下午客流量怎么样，一旦忙起来就觉得时间过得飞快，不过这也意味着叔叔交给我的咖啡馆逐渐走上正途了。</t>
-        </is>
-      </c>
-      <c r="D2111" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P018; church.1014.s2.notice_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2112">
-      <c r="B2112" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p019.text</t>
-        </is>
-      </c>
-      <c r="C2112" t="inlineStr">
-        <is>
-          <t>说起咖啡馆，没想到背后竟然和一些神秘组织有关系，感觉被牵扯进了很不得了的事件中。</t>
-        </is>
-      </c>
-      <c r="D2112" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P019; church.1014.s2.notice_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2113">
-      <c r="B2113" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p020.text</t>
-        </is>
-      </c>
-      <c r="C2113" t="inlineStr">
-        <is>
-          <t>不知道是不是我的错觉，总觉得这位客人一直在看着我。是对咖啡不满意吗，或者是我今天穿的不对劲？</t>
-        </is>
-      </c>
-      <c r="D2113" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P020; church.1014.s2.notice_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2114">
-      <c r="B2114" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p021.text</t>
-        </is>
-      </c>
-      <c r="C2114" t="inlineStr">
-        <is>
-          <t>他看起来也像是一个工人，今天来的工人怎么这么多，但他应该不会是神秘人那边派来的人吧？好在意，要不问一下吧。</t>
-        </is>
-      </c>
-      <c r="D2114" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P021; church.1014.s2.notice_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2115">
-      <c r="B2115" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p023.text</t>
-        </is>
-      </c>
-      <c r="C2115" t="inlineStr">
-        <is>
-          <t>暂时没有更多客人了，正好趁闲暇时放松一下吧。</t>
-        </is>
-      </c>
-      <c r="D2115" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P023; church.1014.s2.notice_fail; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2116">
-      <c r="B2116" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p024.text</t>
-        </is>
-      </c>
-      <c r="C2116" t="inlineStr">
-        <is>
-          <t>不知道下午客流量怎么样，一旦忙起来就觉得时间过得飞快，不过这也意味着叔叔交给我的咖啡馆逐渐走上正途了。</t>
-        </is>
-      </c>
-      <c r="D2116" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P024; church.1014.s2.notice_fail; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2117">
-      <c r="B2117" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p025.text</t>
-        </is>
-      </c>
-      <c r="C2117" t="inlineStr">
-        <is>
-          <t>说起咖啡馆，没想到其居然和一些说不清的组织有所牵扯，感觉被牵扯进了很不得了的事件中。</t>
-        </is>
-      </c>
-      <c r="D2117" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P025; church.1014.s2.notice_fail; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2118">
-      <c r="B2118" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p026.text</t>
-        </is>
-      </c>
-      <c r="C2118" t="inlineStr">
-        <is>
-          <t>这位客人看起来也像是一个工人，今天的来的工人怎么这么多，但他应该不会是神秘人那边派来的人吧？好在意，要不问一下吧。</t>
-        </is>
-      </c>
-      <c r="D2118" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P026; church.1014.s2.notice_fail; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2119">
-      <c r="B2119" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p027.text</t>
-        </is>
-      </c>
-      <c r="C2119" t="inlineStr">
-        <is>
-          <t>「先生，请问您对咖啡有什么建议吗？咖啡馆重新开业，我们希望能在客人们的建议下进一步提高！如果有想法但是不好意思直接说，也可以通过写信的方式告诉我们，您瞧，我们上午刚收到一封顾客送来的建议信呢。」</t>
-        </is>
-      </c>
-      <c r="D2119" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P027; church.1014.s2.letter_question; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2120">
-      <c r="B2120" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p029.text</t>
-        </is>
-      </c>
-      <c r="C2120" t="inlineStr">
-        <is>
-          <t>我一边出示装着信的信封，一边假装不经意地盯着他</t>
-        </is>
-      </c>
-      <c r="D2120" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P029; church.1014.s2.letter_question; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2121">
-      <c r="B2121" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p030.text</t>
-        </is>
-      </c>
-      <c r="C2121" t="inlineStr">
-        <is>
-          <t>他没有多看信一眼，只是看着我</t>
-        </is>
-      </c>
-      <c r="D2121" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P030; church.1014.s2.letter_question; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2122">
-      <c r="B2122" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p031.a.text</t>
-        </is>
-      </c>
-      <c r="C2122" t="inlineStr">
-        <is>
-          <t>「不，不，没有任何意见。」</t>
-        </is>
-      </c>
-      <c r="D2122" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P031; church.1014.s2.letter_question; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2123">
-      <c r="B2123" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p031.b.text</t>
-        </is>
-      </c>
-      <c r="C2123" t="inlineStr">
-        <is>
-          <t>「店长，我有一个问题想问你。」</t>
-        </is>
-      </c>
-      <c r="D2123" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P031; church.1014.s2.letter_question; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2124">
-      <c r="B2124" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p032.text</t>
-        </is>
-      </c>
-      <c r="C2124" t="inlineStr">
-        <is>
-          <t>「啊，好的，先生，您请问。」</t>
-        </is>
-      </c>
-      <c r="D2124" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P032; church.1014.s2.letter_question; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2125">
-      <c r="B2125" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p033.text</t>
-        </is>
-      </c>
-      <c r="C2125" t="inlineStr">
-        <is>
-          <t>他对信没有任何反应，看来并不是神秘人那边派来的人</t>
-        </is>
-      </c>
-      <c r="D2125" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P033; church.1014.s2.letter_question; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2126">
-      <c r="B2126" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p034.text</t>
-        </is>
-      </c>
-      <c r="C2126" t="inlineStr">
-        <is>
-          <t>或许只是个普通工人吧</t>
-        </is>
-      </c>
-      <c r="D2126" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P034; church.1014.s2.letter_question; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2127">
-      <c r="B2127" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p035.text</t>
-        </is>
-      </c>
-      <c r="C2127" t="inlineStr">
-        <is>
-          <t>「王城中，甚至圣徒街上都并不只有一家咖啡馆，但是它们有些并不向普通平民开放，而我看见各阶层的人民都可以自由进入你们的店中。您是出于怎样的考虑呢？」</t>
-        </is>
-      </c>
-      <c r="D2127" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P035; church.1014.s2.letter_question; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2128">
-      <c r="B2128" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p037.text</t>
-        </is>
-      </c>
-      <c r="C2128" t="inlineStr">
-        <is>
-          <t>「只要能够赚钱就好，我们并不在乎客人的身份。我的叔叔杜瓦尔和前几任店长也是这样做的。将人划分三六九等是政治家的思想，却是和商人无关的。」</t>
-        </is>
-      </c>
-      <c r="D2128" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P037; church.1014.s2.letter_question; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2129">
-      <c r="B2129" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p038.text</t>
-        </is>
-      </c>
-      <c r="C2129" t="inlineStr">
-        <is>
-          <t>「我只是想看见客人喝到我做的咖啡之后露出满意的笑容，这样就已经足够了，别的因素不是我要考虑的。」</t>
-        </is>
-      </c>
-      <c r="D2129" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P038; church.1014.s2.letter_question; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2130">
-      <c r="B2130" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p039.text</t>
-        </is>
-      </c>
-      <c r="C2130" t="inlineStr">
-        <is>
-          <t>「我认为咖啡馆只面向部分人群开放本身就是错误的，其应当是面向普罗大众而存在的，不应以政治地位、经济实力等原因而将部分人拒之门外。我的叔叔杜瓦尔和前几任店长也是这样做的，我延续着他们的精神。」</t>
-        </is>
-      </c>
-      <c r="D2130" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P039; church.1014.s2.letter_question; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2131">
-      <c r="B2131" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p041.text</t>
-        </is>
-      </c>
-      <c r="C2131" t="inlineStr">
-        <is>
-          <t>「好的，我明白了。我之前是一名工人，生活在圣西尔万郊区，但是前段时间不幸在工作中受伤，成为了跛脚。唉，许多工厂都因为这点而排斥我。我近日一直为此感到烦忧，昨日听说圣徒街的沸点咖啡馆重新开业了，味道不错且面向大众开放，我实在感到好奇，所以今日特地前来。」</t>
-        </is>
-      </c>
-      <c r="D2131" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P041; church.1014.s2.relief_question; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2132">
-      <c r="B2132" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p042.text</t>
-        </is>
-      </c>
-      <c r="C2132" t="inlineStr">
-        <is>
-          <t>顺着他的话我不由得认真打量起面前这个男子</t>
-        </is>
-      </c>
-      <c r="D2132" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P042; church.1014.s2.relief_question; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2133">
-      <c r="B2133" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p043.text</t>
-        </is>
-      </c>
-      <c r="C2133" t="inlineStr">
-        <is>
-          <t>眼角周围有淡淡的皱纹，年纪并不小了，身上隐隐传来一阵烟味。或许是最近郁闷时常抽。</t>
-        </is>
-      </c>
-      <c r="D2133" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P043; church.1014.s2.relief_question; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2134">
-      <c r="B2134" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p044.text</t>
-        </is>
-      </c>
-      <c r="C2134" t="inlineStr">
-        <is>
-          <t>但是整体打理得很整齐，眼神也透露出坚毅，看起来是一个对自身和生活有一定追求的人。</t>
-        </is>
-      </c>
-      <c r="D2134" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P044; church.1014.s2.relief_question; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2135">
-      <c r="B2135" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p045.text</t>
-        </is>
-      </c>
-      <c r="C2135" t="inlineStr">
-        <is>
-          <t>「这实在是我们的荣幸，先生。希望这杯咖啡能让您感到些许慰藉。」</t>
-        </is>
-      </c>
-      <c r="D2135" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P045; church.1014.s2.relief_question; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2136">
-      <c r="B2136" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p046.text</t>
-        </is>
-      </c>
-      <c r="C2136" t="inlineStr">
-        <is>
-          <t>「好的。店长，您听闻前几日埃利昂公爵和教会的人在旧城区和圣西尔万郊区救济贫民的事情了吗？」</t>
-        </is>
-      </c>
-      <c r="D2136" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P046; church.1014.s2.relief_question; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2137">
-      <c r="B2137" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p047.text</t>
-        </is>
-      </c>
-      <c r="C2137" t="inlineStr">
-        <is>
-          <t>「有所耳闻。」</t>
-        </is>
-      </c>
-      <c r="D2137" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P047; church.1014.s2.relief_question; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2138">
-      <c r="B2138" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p048.text</t>
-        </is>
-      </c>
-      <c r="C2138" t="inlineStr">
-        <is>
-          <t>「很高兴您有所了解。我那天就在被救济的队伍中，这是我最近感受过的最大的善意了，那粥虽然并不算得上十分美味，但足以饱腹了。虽然当下百姓的生活困难，没想到王庭和教会还是有一些有理想和良心的人为我们这些人而奔走着。」</t>
-        </is>
-      </c>
-      <c r="D2138" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P048; church.1014.s2.relief_question; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2139">
-      <c r="B2139" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p050.text</t>
-        </is>
-      </c>
-      <c r="C2139" t="inlineStr">
-        <is>
-          <t>「很高兴得知这件事，我刚来到此地，没想到上层还有埃利昂公爵这样的人物。」</t>
-        </is>
-      </c>
-      <c r="D2139" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P050; church.1014.s2.relief_question; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2140">
-      <c r="B2140" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p051.text</t>
-        </is>
-      </c>
-      <c r="C2140" t="inlineStr">
-        <is>
-          <t>「很高兴得知这件事，但是我相当怀疑王庭和教会中真的存在这样的人吗？」</t>
-        </is>
-      </c>
-      <c r="D2140" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P051; church.1014.s2.relief_question; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2141">
-      <c r="B2141" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p052.text</t>
-        </is>
-      </c>
-      <c r="C2141" t="inlineStr">
-        <is>
-          <t>「很高兴得知这件事，希望百姓的生活能过得越来越好。」</t>
-        </is>
-      </c>
-      <c r="D2141" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P052; church.1014.s2.relief_question; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2142">
-      <c r="B2142" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p054.text</t>
-        </is>
-      </c>
-      <c r="C2142" t="inlineStr">
-        <is>
-          <t>「正是如此，店长。您不知道昨天的盛况……」</t>
-        </is>
-      </c>
-      <c r="D2142" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P054; church.1014.s2.praise; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2143">
-      <c r="B2143" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p057.text</t>
-        </is>
-      </c>
-      <c r="C2143" t="inlineStr">
-        <is>
-          <t>他突然眯着眼睛打量了我一下</t>
-        </is>
-      </c>
-      <c r="D2143" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P057; church.1014.s2.doubt; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2144">
-      <c r="B2144" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p058.text</t>
-        </is>
-      </c>
-      <c r="C2144" t="inlineStr">
-        <is>
-          <t>「店长，您不相信吗？埃利昂公爵他们施粥是实实在在发生的事。」</t>
-        </is>
-      </c>
-      <c r="D2144" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P058; church.1014.s2.doubt; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2145">
-      <c r="B2145" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p059.text</t>
-        </is>
-      </c>
-      <c r="C2145" t="inlineStr">
-        <is>
-          <t>我感到他的态度冷却了一些</t>
-        </is>
-      </c>
-      <c r="D2145" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P059; church.1014.s2.doubt; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2146">
-      <c r="B2146" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p060.text</t>
-        </is>
-      </c>
-      <c r="C2146" t="inlineStr">
-        <is>
-          <t>「不，先生，我相信这一点。我只是……算了，你当我未曾说过吧。」</t>
-        </is>
-      </c>
-      <c r="D2146" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P060; church.1014.s2.doubt; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2147">
-      <c r="B2147" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p061.text</t>
-        </is>
-      </c>
-      <c r="C2147" t="inlineStr">
-        <is>
-          <t>「好的，您不要紧张，我只是看见您觉得亲切，忍不住多聊了两句。我觉得王庭和教会并非全然糟糕透顶的……」</t>
-        </is>
-      </c>
-      <c r="D2147" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P061; church.1014.s2.doubt; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2148">
-      <c r="B2148" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p064.text</t>
-        </is>
-      </c>
-      <c r="C2148" t="inlineStr">
-        <is>
-          <t>他好像对我的回答并不满意，皱了皱眉</t>
-        </is>
-      </c>
-      <c r="D2148" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P064; church.1014.s2.wish; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2149">
-      <c r="B2149" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p065.text</t>
-        </is>
-      </c>
-      <c r="C2149" t="inlineStr">
-        <is>
-          <t>「好吧……」</t>
-        </is>
-      </c>
-      <c r="D2149" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P065; church.1014.s2.wish; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2150">
-      <c r="B2150" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p067.text</t>
-        </is>
-      </c>
-      <c r="C2150" t="inlineStr">
-        <is>
-          <t>他似乎还想说话，但此时新的客人走近了吧台</t>
-        </is>
-      </c>
-      <c r="D2150" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P067; church.1014.s2.depart; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2151">
-      <c r="B2151" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p068.text</t>
-        </is>
-      </c>
-      <c r="C2151" t="inlineStr">
-        <is>
-          <t>「一不注意，竟然已经这个点了，我还需要去找找有没有我能盛任的工作。感谢您的咖啡，有机会我会再来拜访的。」</t>
-        </is>
-      </c>
-      <c r="D2151" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P068; church.1014.s2.depart; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2152">
-      <c r="B2152" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p069.text</t>
-        </is>
-      </c>
-      <c r="C2152" t="inlineStr">
-        <is>
-          <t>「再见，先生！祝您能早日找到一个满意的工作。」</t>
-        </is>
-      </c>
-      <c r="D2152" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P069; church.1014.s2.depart; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2153">
-      <c r="B2153" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p070.text</t>
-        </is>
-      </c>
-      <c r="C2153" t="inlineStr">
-        <is>
-          <t>他放下咖啡，站起来离开，这时我才发现他的左脚确实行走起来不太便利</t>
-        </is>
-      </c>
-      <c r="D2153" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P070; church.1014.s2.depart; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2154">
-      <c r="B2154" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p071.text</t>
-        </is>
-      </c>
-      <c r="C2154" t="inlineStr">
-        <is>
-          <t>他的身影越来越远，随着咖啡馆的门一开一闭，我便再也看不见他的身影了</t>
-        </is>
-      </c>
-      <c r="D2154" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P071; church.1014.s2.depart; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2155">
-      <c r="B2155" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p073.text</t>
-        </is>
-      </c>
-      <c r="C2155" t="inlineStr">
-        <is>
-          <t>真是不容易</t>
-        </is>
-      </c>
-      <c r="D2155" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P073; church.1014.s2.depart; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2156">
-      <c r="B2156" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p074.text</t>
-        </is>
-      </c>
-      <c r="C2156" t="inlineStr">
-        <is>
-          <t>我在心中叹口气</t>
-        </is>
-      </c>
-      <c r="D2156" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P074; church.1014.s2.depart; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2157">
-      <c r="B2157" t="inlineStr">
-        <is>
-          <t>church.1014.s2.p075.text</t>
-        </is>
-      </c>
-      <c r="C2157" t="inlineStr">
-        <is>
-          <t>然后快速转换思绪，面对客人新的要求，开启了新的工作。</t>
-        </is>
-      </c>
-      <c r="D2157" t="inlineStr">
-        <is>
-          <t>church.1014.s2.P075; church.1014.s2.depart; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2158">
-      <c r="B2158" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p003.text</t>
-        </is>
-      </c>
-      <c r="C2158" t="inlineStr">
-        <is>
-          <t>今天咖啡店的生意也相当不错</t>
-        </is>
-      </c>
-      <c r="D2158" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P003; church.1020.s1.raid; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2159">
-      <c r="B2159" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p004.text</t>
-        </is>
-      </c>
-      <c r="C2159" t="inlineStr">
-        <is>
-          <t>我正在为客人制作咖啡时，突然听见一阵嘈杂的脚步声</t>
-        </is>
-      </c>
-      <c r="D2159" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P004; church.1020.s1.raid; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2160">
-      <c r="B2160" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p006.text</t>
-        </is>
-      </c>
-      <c r="C2160" t="inlineStr">
-        <is>
-          <t>然后是阿黛尔同步响起的惊呼声</t>
-        </is>
-      </c>
-      <c r="D2160" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P006; church.1020.s1.raid; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2161">
-      <c r="B2161" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p007.text</t>
-        </is>
-      </c>
-      <c r="C2161" t="inlineStr">
-        <is>
-          <t>「天呐，教会监察司的人？{playername}店长！{playername}店长！」</t>
-        </is>
-      </c>
-      <c r="D2161" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P007; church.1020.s1.raid; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2162">
-      <c r="B2162" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p008.text</t>
-        </is>
-      </c>
-      <c r="C2162" t="inlineStr">
-        <is>
-          <t>我回过头，看见一群穿着统一制式服装的人</t>
-        </is>
-      </c>
-      <c r="D2162" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P008; church.1020.s1.raid; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2163">
-      <c r="B2163" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p009.text</t>
-        </is>
-      </c>
-      <c r="C2163" t="inlineStr">
-        <is>
-          <t>「教会监察司」，刚才阿黛尔好像这样称呼着他们</t>
-        </is>
-      </c>
-      <c r="D2163" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P009; church.1020.s1.raid; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2164">
-      <c r="B2164" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p010.text</t>
-        </is>
-      </c>
-      <c r="C2164" t="inlineStr">
-        <is>
-          <t>他们站定在咖啡馆中，其中一个看起来像领头的人则缓步站定在我面前</t>
-        </is>
-      </c>
-      <c r="D2164" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P010; church.1020.s1.raid; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2165">
-      <c r="B2165" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p012.text</t>
-        </is>
-      </c>
-      <c r="C2165" t="inlineStr">
-        <is>
-          <t>我面前的客人惊慌失措地在我们之间来回转着，但是不敢有所动静</t>
-        </is>
-      </c>
-      <c r="D2165" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P012; church.1020.s1.raid; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2166">
-      <c r="B2166" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p013.text</t>
-        </is>
-      </c>
-      <c r="C2166" t="inlineStr">
-        <is>
-          <t>「你就是{playername}，沸点咖啡馆的现任店长？」</t>
-        </is>
-      </c>
-      <c r="D2166" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P013; church.1020.s1.raid; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2167">
-      <c r="B2167" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p014.text</t>
-        </is>
-      </c>
-      <c r="C2167" t="inlineStr">
-        <is>
-          <t>「是的。」</t>
-        </is>
-      </c>
-      <c r="D2167" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P014; church.1020.s1.raid; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2168">
-      <c r="B2168" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p015.text</t>
-        </is>
-      </c>
-      <c r="C2168" t="inlineStr">
-        <is>
-          <t>「我们是教会监察司，今日奉命前来圣徒街搜查。我是今日负责带队的监察官，希望你能认真配合调查，不然的话——」</t>
-        </is>
-      </c>
-      <c r="D2168" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P015; church.1020.s1.raid; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2169">
-      <c r="B2169" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p016.text</t>
-        </is>
-      </c>
-      <c r="C2169" t="inlineStr">
-        <is>
-          <t>他未说完，但配合着他凶狠的目光，在场的人都对这未尽的话心知肚明</t>
-        </is>
-      </c>
-      <c r="D2169" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P016; church.1020.s1.raid; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2170">
-      <c r="B2170" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p017.text</t>
-        </is>
-      </c>
-      <c r="C2170" t="inlineStr">
-        <is>
-          <t>我的大脑急速运转着</t>
-        </is>
-      </c>
-      <c r="D2170" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P017; church.1020.s1.raid; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2171">
-      <c r="B2171" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p018.text</t>
-        </is>
-      </c>
-      <c r="C2171" t="inlineStr">
-        <is>
-          <t>教会监察司为什么会来圣徒街搜查？商铺经营不归监察司管吧？哦对了，好像听谁提过前几日街头有人散布修改「王选者」法律的消息……只有这个可能了。不过这和我也没什么大关系，随机应对即可吧。</t>
-        </is>
-      </c>
-      <c r="D2171" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P018; church.1020.s1.raid; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2172">
-      <c r="B2172" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p020.text</t>
-        </is>
-      </c>
-      <c r="C2172" t="inlineStr">
-        <is>
-          <t>「好吧，但是能否请小心对待店中的客人和设备，我们还要继续营业的。」</t>
-        </is>
-      </c>
-      <c r="D2172" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P020; church.1020.s1.raid; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2173">
-      <c r="B2173" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p021.text</t>
-        </is>
-      </c>
-      <c r="C2173" t="inlineStr">
-        <is>
-          <t>「我们咖啡馆正大光明，你们可以随意搜查。但是能否请小心对待店中的客人和设备，我们还要继续营业的。」</t>
-        </is>
-      </c>
-      <c r="D2173" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P021; church.1020.s1.raid; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2174">
-      <c r="B2174" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p022.text</t>
-        </is>
-      </c>
-      <c r="C2174" t="inlineStr">
-        <is>
-          <t>「如果我不同意会怎么样呢？」</t>
-        </is>
-      </c>
-      <c r="D2174" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P022; church.1020.s1.raid; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2175">
-      <c r="B2175" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p024.text</t>
-        </is>
-      </c>
-      <c r="C2175" t="inlineStr">
-        <is>
-          <t>「哼，用不着你来指导工作。」「各人员注意，仔细搜查，不要放过任何一个角落。」</t>
-        </is>
-      </c>
-      <c r="D2175" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P024; church.1020.s1.cooperate; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2176">
-      <c r="B2176" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p027.text</t>
-        </is>
-      </c>
-      <c r="C2176" t="inlineStr">
-        <is>
-          <t>我们隔着吧台看着对方的眼睛对峙，谁也不肯服输，许久他先移开目光并缓慢开口</t>
-        </is>
-      </c>
-      <c r="D2176" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P027; church.1020.s1.defy_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2177">
-      <c r="B2177" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p028.text</t>
-        </is>
-      </c>
-      <c r="C2177" t="inlineStr">
-        <is>
-          <t>「哼，年轻人，我很欣赏你的勇气，但建议你要记得区分勇敢和鲁莽。」「今日是必定要开展检查的。各人员注意，仔细搜查，不要放过任何一个角落。」</t>
-        </is>
-      </c>
-      <c r="D2177" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P028; church.1020.s1.defy_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2178">
-      <c r="B2178" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p030.text</t>
-        </is>
-      </c>
-      <c r="C2178" t="inlineStr">
-        <is>
-          <t>我们隔着吧台看着对方的眼睛对峙，谁也不肯服输，最终我感到他身上的威严压过了我，我率先移开目光</t>
-        </is>
-      </c>
-      <c r="D2178" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P030; church.1020.s1.defy_fail; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2179">
-      <c r="B2179" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p031.text</t>
-        </is>
-      </c>
-      <c r="C2179" t="inlineStr">
-        <is>
-          <t>「年轻人，我想你是刚来到圣诺特，还不太了解情况，我们的搜查不需要你的同意。」「现在碍于你的态度，我可能要采取一些特别措施了，来人。」</t>
-        </is>
-      </c>
-      <c r="D2179" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P031; church.1020.s1.defy_fail; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2180">
-      <c r="B2180" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p032.text</t>
-        </is>
-      </c>
-      <c r="C2180" t="inlineStr">
-        <is>
-          <t>两个穿着制式服装的人从两边走上前来，将我从吧台中推出来，一左一右地扣押着我</t>
-        </is>
-      </c>
-      <c r="D2180" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P032; church.1020.s1.defy_fail; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2181">
-      <c r="B2181" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p033.text</t>
-        </is>
-      </c>
-      <c r="C2181" t="inlineStr">
-        <is>
-          <t>「现在可以配合检查了吧，店长。」「各人员注意，仔细搜查，不要放过任何一个角落。」</t>
-        </is>
-      </c>
-      <c r="D2181" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P033; church.1020.s1.defy_fail; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2182">
-      <c r="B2182" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p035.text</t>
-        </is>
-      </c>
-      <c r="C2182" t="inlineStr">
-        <is>
-          <t>「是。」</t>
-        </is>
-      </c>
-      <c r="D2182" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P035; church.1020.s1.letter_found; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2183">
-      <c r="B2183" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p036.text</t>
-        </is>
-      </c>
-      <c r="C2183" t="inlineStr">
-        <is>
-          <t>他们四下分散开来，我看见他们的身影在大堂中忙碌着，甚至对顾客开展了简短的问询，部分顾客不堪其扰趁乱离开了。</t>
-        </is>
-      </c>
-      <c r="D2183" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P036; church.1020.s1.letter_found; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2184">
-      <c r="B2184" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p037.text</t>
-        </is>
-      </c>
-      <c r="C2184" t="inlineStr">
-        <is>
-          <t>唉，不知道会不会影响以后的生意。</t>
-        </is>
-      </c>
-      <c r="D2184" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P037; church.1020.s1.letter_found; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2185">
-      <c r="B2185" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p038.text</t>
-        </is>
-      </c>
-      <c r="C2185" t="inlineStr">
-        <is>
-          <t>突然想起神秘人给我留下的那封信好像被我顺手放在了吧台的抽屉中，密信他们看不懂应该不要紧……但是我该如何解释呢……</t>
-        </is>
-      </c>
-      <c r="D2185" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P038; church.1020.s1.letter_found; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2186">
-      <c r="B2186" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p039.text</t>
-        </is>
-      </c>
-      <c r="C2186" t="inlineStr">
-        <is>
-          <t>然而怕什么来什么。很快他们便搜查到了吧台区域，在我如鼓擂的心跳声中他们在抽屉中找到了那封信，并递交给了监察官。</t>
-        </is>
-      </c>
-      <c r="D2186" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P039; church.1020.s1.letter_found; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2187">
-      <c r="B2187" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p040.text</t>
-        </is>
-      </c>
-      <c r="C2187" t="inlineStr">
-        <is>
-          <t>监察官打开那封信看了看，然后走到我面前</t>
-        </is>
-      </c>
-      <c r="D2187" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P040; church.1020.s1.letter_found; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2188">
-      <c r="B2188" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p041.text</t>
-        </is>
-      </c>
-      <c r="C2188" t="inlineStr">
-        <is>
-          <t>「解释一下吗，{playername}店长？这封信上写的是什么，告诉我。」</t>
-        </is>
-      </c>
-      <c r="D2188" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P041; church.1020.s1.letter_found; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2189">
-      <c r="B2189" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p044.text</t>
-        </is>
-      </c>
-      <c r="C2189" t="inlineStr">
-        <is>
-          <t>「这是我们内部每日记录进货、出账的账单，为了节省时间而简写为这种形式。」</t>
-        </is>
-      </c>
-      <c r="D2189" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P044; church.1020.s1.letter_found; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2190">
-      <c r="B2190" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p045.text</t>
-        </is>
-      </c>
-      <c r="C2190" t="inlineStr">
-        <is>
-          <t>「这不过我的一封私人信件，监察司奉命搜查商铺，可没有资格逼问一封私人信件写了什么。」</t>
-        </is>
-      </c>
-      <c r="D2190" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P045; church.1020.s1.letter_found; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2191">
-      <c r="B2191" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p046.text</t>
-        </is>
-      </c>
-      <c r="C2191" t="inlineStr">
-        <is>
-          <t>「我想长官你们是来搜查与「王选者」法律相关的吧，这不过一封我的私人信件能有什么关系呢？」</t>
-        </is>
-      </c>
-      <c r="D2191" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P046; church.1020.s1.letter_found; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2192">
-      <c r="B2192" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p047.text</t>
-        </is>
-      </c>
-      <c r="C2192" t="inlineStr">
-        <is>
-          <t>「这不过是一封普通的私人信件，我看不出有什么被怀疑的必要。长官，您不会是早就对我有所怀疑吧？」</t>
-        </is>
-      </c>
-      <c r="D2192" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P047; church.1020.s1.letter_found; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2193">
-      <c r="B2193" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p049.text</t>
-        </is>
-      </c>
-      <c r="C2193" t="inlineStr">
-        <is>
-          <t>「账单？那你详细给我讲讲这个账单的构成。」</t>
-        </is>
-      </c>
-      <c r="D2193" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P049; church.1020.s1.language_intro; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2194">
-      <c r="B2194" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p051.text</t>
-        </is>
-      </c>
-      <c r="C2194" t="inlineStr">
-        <is>
-          <t>我快速回忆了一下信上的数字，然后不疾不徐地开口</t>
-        </is>
-      </c>
-      <c r="D2194" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P051; church.1020.s1.language_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2195">
-      <c r="B2195" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p052.text</t>
-        </is>
-      </c>
-      <c r="C2195" t="inlineStr">
-        <is>
-          <t>「这些数字代表着店里咖啡豆、设备、餐具等物品的购买量、支出金额、每日消耗量、待购买量等数据，我叔叔当店长时就立下了这样的规矩，后面代代传承。」「这本来是我们的商业机密，但是长官你都发问了，我只能悉数奉告了。」</t>
-        </is>
-      </c>
-      <c r="D2195" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P052; church.1020.s1.language_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2196">
-      <c r="B2196" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p053.text</t>
-        </is>
-      </c>
-      <c r="C2196" t="inlineStr">
-        <is>
-          <t>监察官边听着我的讲述边试图理解信上的数字</t>
-        </is>
-      </c>
-      <c r="D2196" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P053; church.1020.s1.language_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2197">
-      <c r="B2197" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p054.text</t>
-        </is>
-      </c>
-      <c r="C2197" t="inlineStr">
-        <is>
-          <t>「哼，听起来倒是有鼻子有眼。」</t>
-        </is>
-      </c>
-      <c r="D2197" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P054; church.1020.s1.language_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2198">
-      <c r="B2198" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p055.text</t>
-        </is>
-      </c>
-      <c r="C2198" t="inlineStr">
-        <is>
-          <t>他低头又看了一遍信纸，眉头紧皱，却没有从中找到能够反驳我的证据，他又盯着我看了片刻，最终将信纸递还给我。</t>
-        </is>
-      </c>
-      <c r="D2198" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P055; church.1020.s1.language_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2199">
-      <c r="B2199" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p056.text</t>
-        </is>
-      </c>
-      <c r="C2199" t="inlineStr">
-        <is>
-          <t>「暂时没有证据证明这封信与我们搜查的东西有关。收好你的东西。」</t>
-        </is>
-      </c>
-      <c r="D2199" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P056; church.1020.s1.language_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2200">
-      <c r="B2200" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p057.text</t>
-        </is>
-      </c>
-      <c r="C2200" t="inlineStr">
-        <is>
-          <t>我接过信纸，尽量平静地点了点头。</t>
-        </is>
-      </c>
-      <c r="D2200" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P057; church.1020.s1.language_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2201">
-      <c r="B2201" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p059.text</t>
-        </is>
-      </c>
-      <c r="C2201" t="inlineStr">
-        <is>
-          <t>我努力组织着语言，试图把信上的内容解释清楚，却发现自己越说越混乱。</t>
-        </is>
-      </c>
-      <c r="D2201" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P059; church.1020.s1.language_fail; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2202">
-      <c r="B2202" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p060.text</t>
-        </is>
-      </c>
-      <c r="C2202" t="inlineStr">
-        <is>
-          <t>「这……这是以前店里留下的账单记录方式，应该是采购……或者别的什么记录，具体内容我也不太清楚。」</t>
-        </is>
-      </c>
-      <c r="D2202" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P060; church.1020.s1.language_fail; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2203">
-      <c r="B2203" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p061.text</t>
-        </is>
-      </c>
-      <c r="C2203" t="inlineStr">
-        <is>
-          <t>监察官的表情逐渐变得严厉</t>
-        </is>
-      </c>
-      <c r="D2203" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P061; church.1020.s1.language_fail; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2204">
-      <c r="B2204" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p062.text</t>
-        </is>
-      </c>
-      <c r="C2204" t="inlineStr">
-        <is>
-          <t>「你自己的店里发现的信，你却连内容都说不清楚？」</t>
-        </is>
-      </c>
-      <c r="D2204" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P062; church.1020.s1.language_fail; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2205">
-      <c r="B2205" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p063.text</t>
-        </is>
-      </c>
-      <c r="C2205" t="inlineStr">
-        <is>
-          <t>我张了张嘴，一时找不到更合适的说辞。</t>
-        </is>
-      </c>
-      <c r="D2205" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P063; church.1020.s1.language_fail; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2206">
-      <c r="B2206" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p064.text</t>
-        </is>
-      </c>
-      <c r="C2206" t="inlineStr">
-        <is>
-          <t>监察官将信纸收了起来，冷冷地看着我。</t>
-        </is>
-      </c>
-      <c r="D2206" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P064; church.1020.s1.language_fail; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2207">
-      <c r="B2207" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p065.text</t>
-        </is>
-      </c>
-      <c r="C2207" t="inlineStr">
-        <is>
-          <t>「你的解释前后矛盾。带走，等候进一步调查。」</t>
-        </is>
-      </c>
-      <c r="D2207" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P065; church.1020.s1.language_fail; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2208">
-      <c r="B2208" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p067.text</t>
-        </is>
-      </c>
-      <c r="C2208" t="inlineStr">
-        <is>
-          <t>「私人信件？我看见的可是写着一串数字的不明信件。」</t>
-        </is>
-      </c>
-      <c r="D2208" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P067; church.1020.s1.courage_intro; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2209">
-      <c r="B2209" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p068.text</t>
-        </is>
-      </c>
-      <c r="C2209" t="inlineStr">
-        <is>
-          <t>我再次对上他探究的眼睛</t>
-        </is>
-      </c>
-      <c r="D2209" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P068; church.1020.s1.courage_intro; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2210">
-      <c r="B2210" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p070.text</t>
-        </is>
-      </c>
-      <c r="C2210" t="inlineStr">
-        <is>
-          <t>我毫不畏惧地直视着他，没有试图争抢那封信，也没有慌张，一字一句地说道</t>
-        </is>
-      </c>
-      <c r="D2210" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P070; church.1020.s1.courage_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2211">
-      <c r="B2211" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p071.text</t>
-        </is>
-      </c>
-      <c r="C2211" t="inlineStr">
-        <is>
-          <t>「您可以搜查，也可以暂时扣下这封信。但在没有证据之前，请不要把无法解读的信件直接说成不法密信。这不过是前任店长给我留下的关于咖啡馆内部账单。」</t>
-        </is>
-      </c>
-      <c r="D2211" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P071; church.1020.s1.courage_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2212">
-      <c r="B2212" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p072.text</t>
-        </is>
-      </c>
-      <c r="C2212" t="inlineStr">
-        <is>
-          <t>咖啡馆内安静了下来，所有人都在看着我们</t>
-        </is>
-      </c>
-      <c r="D2212" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P072; church.1020.s1.courage_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2213">
-      <c r="B2213" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p073.text</t>
-        </is>
-      </c>
-      <c r="C2213" t="inlineStr">
-        <is>
-          <t>我继续说道</t>
-        </is>
-      </c>
-      <c r="D2213" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P073; church.1020.s1.courage_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2214">
-      <c r="B2214" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p074.text</t>
-        </is>
-      </c>
-      <c r="C2214" t="inlineStr">
-        <is>
-          <t>「如果您认为我有问题，可以按照教会的程序调查。我会配合，但不会承认自己没有做过的事。」</t>
-        </is>
-      </c>
-      <c r="D2214" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P074; church.1020.s1.courage_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2215">
-      <c r="B2215" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p075.text</t>
-        </is>
-      </c>
-      <c r="C2215" t="inlineStr">
-        <is>
-          <t>监察官的目光在我脸上停留了许久，像是在判断我究竟是虚张声势，还是确实问心无愧。</t>
-        </is>
-      </c>
-      <c r="D2215" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P075; church.1020.s1.courage_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2216">
-      <c r="B2216" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p076.text</t>
-        </is>
-      </c>
-      <c r="C2216" t="inlineStr">
-        <is>
-          <t>最终他冷哼一声，将信纸拍在桌上。</t>
-        </is>
-      </c>
-      <c r="D2216" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P076; church.1020.s1.courage_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2217">
-      <c r="B2217" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p077.text</t>
-        </is>
-      </c>
-      <c r="C2217" t="inlineStr">
-        <is>
-          <t>「哼，没有证据，我们也不会仅凭一封无从解读的信抓人。收好你的信，但是如果之后我们发现有什么问题，你等着被传唤吧。」</t>
-        </is>
-      </c>
-      <c r="D2217" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P077; church.1020.s1.courage_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2218">
-      <c r="B2218" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p078.text</t>
-        </is>
-      </c>
-      <c r="C2218" t="inlineStr">
-        <is>
-          <t>「我明白。」</t>
-        </is>
-      </c>
-      <c r="D2218" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P078; church.1020.s1.courage_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2219">
-      <c r="B2219" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p080.text</t>
-        </is>
-      </c>
-      <c r="C2219" t="inlineStr">
-        <is>
-          <t>我想要反驳，却被监察官凌厉的目光压得说不出话来。</t>
-        </is>
-      </c>
-      <c r="D2219" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P080; church.1020.s1.courage_fail; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2220">
-      <c r="B2220" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p081.text</t>
-        </is>
-      </c>
-      <c r="C2220" t="inlineStr">
-        <is>
-          <t>「这……这是前任店长给我留下的关于咖啡馆内部账单的信件……但是……我也不知道上面具体是什么意思……」</t>
-        </is>
-      </c>
-      <c r="D2220" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P081; church.1020.s1.courage_fail; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2221">
-      <c r="B2221" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p082.text</t>
-        </is>
-      </c>
-      <c r="C2221" t="inlineStr">
-        <is>
-          <t>「不知道具体意思？那么你怎么知道这是咖啡馆内部账单？」</t>
-        </is>
-      </c>
-      <c r="D2221" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P082; church.1020.s1.courage_fail; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2222">
-      <c r="B2222" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p083.text</t>
-        </is>
-      </c>
-      <c r="C2222" t="inlineStr">
-        <is>
-          <t>我张张嘴又闭上，他充满威严与怀疑的目光刺痛了我，不敢再继续辩解</t>
-        </is>
-      </c>
-      <c r="D2222" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P083; church.1020.s1.courage_fail; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2223">
-      <c r="B2223" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p084.text</t>
-        </is>
-      </c>
-      <c r="C2223" t="inlineStr">
-        <is>
-          <t>监察官看着我的沉默，像是已经得出了自己的判断。</t>
-        </is>
-      </c>
-      <c r="D2223" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P084; church.1020.s1.courage_fail; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2224">
-      <c r="B2224" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p085.text</t>
-        </is>
-      </c>
-      <c r="C2224" t="inlineStr">
-        <is>
-          <t>「那正好，信带走，回去让我们监察司的人好好领会一下你所谓的「私人信件」。至于你，随我们走一趟。」</t>
-        </is>
-      </c>
-      <c r="D2224" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P085; church.1020.s1.courage_fail; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2225">
-      <c r="B2225" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p088.text</t>
-        </is>
-      </c>
-      <c r="C2225" t="inlineStr">
-        <is>
-          <t>「你倒是很清楚我们为何而来。」</t>
-        </is>
-      </c>
-      <c r="D2225" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P088; church.1020.s1.wisdom_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2226">
-      <c r="B2226" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p089.text</t>
-        </is>
-      </c>
-      <c r="C2226" t="inlineStr">
-        <is>
-          <t>我指了指他手中的信纸</t>
-        </is>
-      </c>
-      <c r="D2226" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P089; church.1020.s1.wisdom_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2227">
-      <c r="B2227" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p090.text</t>
-        </is>
-      </c>
-      <c r="C2227" t="inlineStr">
-        <is>
-          <t>「但这只是一封私人信件，是前任店长给我留下的之前店铺的账单，没有提到「王选者」，也没有任何与法律修改相关的内容，只不过是一串普通数字罢了。而且我听闻前几天是在民间宣扬「王选者」，如果对方采取这样隐晦的方式，并不能达到宣传的目的吧。」</t>
-        </is>
-      </c>
-      <c r="D2227" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P090; church.1020.s1.wisdom_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2228">
-      <c r="B2228" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p091.text</t>
-        </is>
-      </c>
-      <c r="C2228" t="inlineStr">
-        <is>
-          <t>监察官听闻多看了我两眼</t>
-        </is>
-      </c>
-      <c r="D2228" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P091; church.1020.s1.wisdom_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2229">
-      <c r="B2229" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p092.text</t>
-        </is>
-      </c>
-      <c r="C2229" t="inlineStr">
-        <is>
-          <t>「你倒是想得挺清楚。不过你说得没错，目前确实没有证据证明这封信与那件事有关。」</t>
-        </is>
-      </c>
-      <c r="D2229" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P092; church.1020.s1.wisdom_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2230">
-      <c r="B2230" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p093.text</t>
-        </is>
-      </c>
-      <c r="C2230" t="inlineStr">
-        <is>
-          <t>他又沉默了片刻，最终选择将信纸递给身旁的监察员，几名监察员低声讨论后也无法确认其中有什么异常。</t>
-        </is>
-      </c>
-      <c r="D2230" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P093; church.1020.s1.wisdom_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2231">
-      <c r="B2231" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p094.text</t>
-        </is>
-      </c>
-      <c r="C2231" t="inlineStr">
-        <is>
-          <t>「信你收好。至于你，继续留在店里接受调查，不得擅自离开圣徒街。」</t>
-        </is>
-      </c>
-      <c r="D2231" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P094; church.1020.s1.wisdom_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2232">
-      <c r="B2232" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p096.text</t>
-        </is>
-      </c>
-      <c r="C2232" t="inlineStr">
-        <is>
-          <t>「你倒是很清楚我们为何而来。」</t>
-        </is>
-      </c>
-      <c r="D2232" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P096; church.1020.s1.wisdom_fail; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2233">
-      <c r="B2233" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p097.text</t>
-        </is>
-      </c>
-      <c r="C2233" t="inlineStr">
-        <is>
-          <t>我试图继续说出一些合理而又道理的理由来摆脱嫌疑，但脑中一片混乱，只能勉强找出几个听起来合理的词。</t>
-        </is>
-      </c>
-      <c r="D2233" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P097; church.1020.s1.wisdom_fail; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2234">
-      <c r="B2234" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p098.text</t>
-        </is>
-      </c>
-      <c r="C2234" t="inlineStr">
-        <is>
-          <t>「这封信……是我与前任店长沟通的私人信件……上面写的东西应该是店铺内部经营状况，可能就是之前他们订购咖啡豆和机器设备的开销……没什么重要的。怎么看都与你们要查的东西无关吧……」</t>
-        </is>
-      </c>
-      <c r="D2234" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P098; church.1020.s1.wisdom_fail; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2235">
-      <c r="B2235" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p099.text</t>
-        </is>
-      </c>
-      <c r="C2235" t="inlineStr">
-        <is>
-          <t>话一出口，我便意识到自己的解释漏洞百出。</t>
-        </is>
-      </c>
-      <c r="D2235" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P099; church.1020.s1.wisdom_fail; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2236">
-      <c r="B2236" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p100.text</t>
-        </is>
-      </c>
-      <c r="C2236" t="inlineStr">
-        <is>
-          <t>「可能？应该？{playername}店长，你连自己要解释什么都不知道。」</t>
-        </is>
-      </c>
-      <c r="D2236" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P100; church.1020.s1.wisdom_fail; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2237">
-      <c r="B2237" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p101.text</t>
-        </is>
-      </c>
-      <c r="C2237" t="inlineStr">
-        <is>
-          <t>我试图继续补充，却只能让事情变得更加糟糕。</t>
-        </is>
-      </c>
-      <c r="D2237" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P101; church.1020.s1.wisdom_fail; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2238">
-      <c r="B2238" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p102.text</t>
-        </is>
-      </c>
-      <c r="C2238" t="inlineStr">
-        <is>
-          <t>「你的说辞无法令人信服。」「先把人带走，信件作为证物收存。」</t>
-        </is>
-      </c>
-      <c r="D2238" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P102; church.1020.s1.wisdom_fail; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2239">
-      <c r="B2239" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p104.text</t>
-        </is>
-      </c>
-      <c r="C2239" t="inlineStr">
-        <is>
-          <t>我注意到监察官虽然拿着信纸，却没有认真揣摩上面的数字含义，反而仔细观察着我的反应</t>
-        </is>
-      </c>
-      <c r="D2239" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P104; church.1020.s1.perception_intro; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2240">
-      <c r="B2240" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p106.text</t>
-        </is>
-      </c>
-      <c r="C2240" t="inlineStr">
-        <is>
-          <t>我看出来了，他并没有读懂信上的内容，他在意的是我是否会因此露出破绽</t>
-        </is>
-      </c>
-      <c r="D2240" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P106; church.1020.s1.perception_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2241">
-      <c r="B2241" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p107.text</t>
-        </is>
-      </c>
-      <c r="C2241" t="inlineStr">
-        <is>
-          <t>我让自己的语气尽量平稳，目光坦荡地对上监察官探究的眼神</t>
-        </is>
-      </c>
-      <c r="D2241" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P107; church.1020.s1.perception_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2242">
-      <c r="B2242" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p108.text</t>
-        </is>
-      </c>
-      <c r="C2242" t="inlineStr">
-        <is>
-          <t>「这不过是前任店长给我留下的店铺内部的账单罢了，这样的单子我这还有很多。不知道长官您要搜查的是什么，但想必是与国家大事相关，我想不会是这种写了一串普通数字的私人信件吧。」</t>
-        </is>
-      </c>
-      <c r="D2242" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P108; church.1020.s1.perception_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2243">
-      <c r="B2243" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p109.text</t>
-        </is>
-      </c>
-      <c r="C2243" t="inlineStr">
-        <is>
-          <t>监察官听了我话又探究地看了信纸两眼</t>
-        </is>
-      </c>
-      <c r="D2243" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P109; church.1020.s1.perception_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2244">
-      <c r="B2244" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p110.text</t>
-        </is>
-      </c>
-      <c r="C2244" t="inlineStr">
-        <is>
-          <t>我趁势说道</t>
-        </is>
-      </c>
-      <c r="D2244" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P110; church.1020.s1.perception_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2245">
-      <c r="B2245" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p111.text</t>
-        </is>
-      </c>
-      <c r="C2245" t="inlineStr">
-        <is>
-          <t>「您可以把它带回去找人辨认。但我相信，无论如何解读，它都只是一张记录店铺经营状况的账单。」</t>
-        </is>
-      </c>
-      <c r="D2245" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P111; church.1020.s1.perception_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2246">
-      <c r="B2246" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p112.text</t>
-        </is>
-      </c>
-      <c r="C2246" t="inlineStr">
-        <is>
-          <t>监察官看向身后的监察员。对方检查了信纸和抽屉，低声说了几句，似乎没有发现新的线索。</t>
-        </is>
-      </c>
-      <c r="D2246" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P112; church.1020.s1.perception_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2247">
-      <c r="B2247" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p113.text</t>
-        </is>
-      </c>
-      <c r="C2247" t="inlineStr">
-        <is>
-          <t>「……暂时按普通信件处理。你继续营业，但近期不要离开圣徒街。」</t>
-        </is>
-      </c>
-      <c r="D2247" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P113; church.1020.s1.perception_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2248">
-      <c r="B2248" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p114.text</t>
-        </is>
-      </c>
-      <c r="C2248" t="inlineStr">
-        <is>
-          <t>「我知道了。」</t>
-        </is>
-      </c>
-      <c r="D2248" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P114; church.1020.s1.perception_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2249">
-      <c r="B2249" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p116.text</t>
-        </is>
-      </c>
-      <c r="C2249" t="inlineStr">
-        <is>
-          <t>我试图观察监察官的脸色以获取更多信息，却没能从他的神情中看出任何端倪。</t>
-        </is>
-      </c>
-      <c r="D2249" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P116; church.1020.s1.perception_fail; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2250">
-      <c r="B2250" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p117.text</t>
-        </is>
-      </c>
-      <c r="C2250" t="inlineStr">
-        <is>
-          <t>「我不知道它是什么……或许是前任店长给我留下的信息吧……前任店长在店里留下了不少东西，我还没有一一检查。」</t>
-        </is>
-      </c>
-      <c r="D2250" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P117; church.1020.s1.perception_fail; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2251">
-      <c r="B2251" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p118.text</t>
-        </is>
-      </c>
-      <c r="C2251" t="inlineStr">
-        <is>
-          <t>「你说自己没有检查过，却在我没有给你出示这封信具体内容的情况下说这是前任店长留下的。显然，你的解释站不住脚。」</t>
-        </is>
-      </c>
-      <c r="D2251" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P118; church.1020.s1.perception_fail; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2252">
-      <c r="B2252" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p119.text</t>
-        </is>
-      </c>
-      <c r="C2252" t="inlineStr">
-        <is>
-          <t>他似笑非笑地看着我</t>
-        </is>
-      </c>
-      <c r="D2252" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P119; church.1020.s1.perception_fail; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2253">
-      <c r="B2253" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p120.text</t>
-        </is>
-      </c>
-      <c r="C2253" t="inlineStr">
-        <is>
-          <t>我这才意识到，自己的话已经被对方抓住了漏洞。</t>
-        </is>
-      </c>
-      <c r="D2253" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P120; church.1020.s1.perception_fail; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2254">
-      <c r="B2254" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p121.text</t>
-        </is>
-      </c>
-      <c r="C2254" t="inlineStr">
-        <is>
-          <t>监察官示意监察员上前，将信纸递交给他，随后监察员将信纸收进一个文件袋中。</t>
-        </is>
-      </c>
-      <c r="D2254" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P121; church.1020.s1.perception_fail; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2255">
-      <c r="B2255" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p122.text</t>
-        </is>
-      </c>
-      <c r="C2255" t="inlineStr">
-        <is>
-          <t>「带走。等你想清楚之后，再向我们解释。」</t>
-        </is>
-      </c>
-      <c r="D2255" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P122; church.1020.s1.perception_fail; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2256">
-      <c r="B2256" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p124.text</t>
-        </is>
-      </c>
-      <c r="C2256" t="inlineStr">
-        <is>
-          <t>很快，教会监察司的人离开了咖啡馆，前往圣徒街其他店铺里搜寻</t>
-        </is>
-      </c>
-      <c r="D2256" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P124; church.1020.s1.cleared; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2257">
-      <c r="B2257" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p125.text</t>
-        </is>
-      </c>
-      <c r="C2257" t="inlineStr">
-        <is>
-          <t>他们离开后，阿黛尔赶紧跑过来关切地询问我</t>
-        </is>
-      </c>
-      <c r="D2257" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P125; church.1020.s1.cleared; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2258">
-      <c r="B2258" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p126.text</t>
-        </is>
-      </c>
-      <c r="C2258" t="inlineStr">
-        <is>
-          <t>「{playername}店长，你刚才真实太厉害了！面对教会监察司的人还能如此镇定地面对！」</t>
-        </is>
-      </c>
-      <c r="D2258" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P126; church.1020.s1.cleared; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2259">
-      <c r="B2259" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p127.text</t>
-        </is>
-      </c>
-      <c r="C2259" t="inlineStr">
-        <is>
-          <t>听完阿黛尔的话我感到一丝无奈，原来刚才的我在她眼里是这样的吗</t>
-        </is>
-      </c>
-      <c r="D2259" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P127; church.1020.s1.cleared; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2260">
-      <c r="B2260" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p128.text</t>
-        </is>
-      </c>
-      <c r="C2260" t="inlineStr">
-        <is>
-          <t>我现在感到一丝后怕，如果刚才没有应对得当，现在的我是会被他们带走审问吗？</t>
-        </is>
-      </c>
-      <c r="D2260" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P128; church.1020.s1.cleared; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2261">
-      <c r="B2261" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p129.text</t>
-        </is>
-      </c>
-      <c r="C2261" t="inlineStr">
-        <is>
-          <t>幸好我事先有想好万一被发现应当如何应对，才逃过这一劫</t>
-        </is>
-      </c>
-      <c r="D2261" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P129; church.1020.s1.cleared; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2262">
-      <c r="B2262" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p130.text</t>
-        </is>
-      </c>
-      <c r="C2262" t="inlineStr">
-        <is>
-          <t>看来以后需要把这些东西隐藏得更加隐蔽才好。不，还是赶紧找个机会把信都给烧掉吧</t>
-        </is>
-      </c>
-      <c r="D2262" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P130; church.1020.s1.cleared; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2263">
-      <c r="B2263" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p131.text</t>
-        </is>
-      </c>
-      <c r="C2263" t="inlineStr">
-        <is>
-          <t>阿黛尔不休的话打断了我的思绪</t>
-        </is>
-      </c>
-      <c r="D2263" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P131; church.1020.s1.cleared; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2264">
-      <c r="B2264" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p132.text</t>
-        </is>
-      </c>
-      <c r="C2264" t="inlineStr">
-        <is>
-          <t>「不过刚才由于监察司的到来，好多顾客都离开了呢……不知道接下来生意会不会受到影响……」</t>
-        </is>
-      </c>
-      <c r="D2264" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P132; church.1020.s1.cleared; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2265">
-      <c r="B2265" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p133.text</t>
-        </is>
-      </c>
-      <c r="C2265" t="inlineStr">
-        <is>
-          <t>这时我才想起刚才被迫停留在我和监察司中间的倒霉顾客</t>
-        </is>
-      </c>
-      <c r="D2265" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P133; church.1020.s1.cleared; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2266">
-      <c r="B2266" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p134.text</t>
-        </is>
-      </c>
-      <c r="C2266" t="inlineStr">
-        <is>
-          <t>目前店里没有发现那位顾客的身影，或许是什么时候趁乱离开了吧</t>
-        </is>
-      </c>
-      <c r="D2266" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P134; church.1020.s1.cleared; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2267">
-      <c r="B2267" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p135.text</t>
-        </is>
-      </c>
-      <c r="C2267" t="inlineStr">
-        <is>
-          <t>店里的设备没有遭到损坏，看来监察司搜查的时候还是有分寸的</t>
-        </is>
-      </c>
-      <c r="D2267" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P135; church.1020.s1.cleared; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2268">
-      <c r="B2268" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p136.text</t>
-        </is>
-      </c>
-      <c r="C2268" t="inlineStr">
-        <is>
-          <t>今天发生了这样的事，未来几天还是低调点吧</t>
-        </is>
-      </c>
-      <c r="D2268" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P136; church.1020.s1.cleared; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2269">
-      <c r="B2269" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p137.text</t>
-        </is>
-      </c>
-      <c r="C2269" t="inlineStr">
-        <is>
-          <t>「希望不会吧。阿黛尔，未来两天我们还是正常营业，但是低调一些。我担心再次引来什么大麻烦。」</t>
-        </is>
-      </c>
-      <c r="D2269" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P137; church.1020.s1.cleared; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2270">
-      <c r="B2270" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p138.text</t>
-        </is>
-      </c>
-      <c r="C2270" t="inlineStr">
-        <is>
-          <t>「我也正有此意呢，店长！」</t>
-        </is>
-      </c>
-      <c r="D2270" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P138; church.1020.s1.cleared; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2271">
-      <c r="B2271" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p139.text</t>
-        </is>
-      </c>
-      <c r="C2271" t="inlineStr">
-        <is>
-          <t>「阿黛尔，振作精神，我们还要准备迎接接下来的客人呢！」</t>
-        </is>
-      </c>
-      <c r="D2271" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P139; church.1020.s1.cleared; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2272">
-      <c r="B2272" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p140.text</t>
-        </is>
-      </c>
-      <c r="C2272" t="inlineStr">
-        <is>
-          <t>「店长，你说得对！那我去门口继续招揽一下客人~」</t>
-        </is>
-      </c>
-      <c r="D2272" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P140; church.1020.s1.cleared; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2273">
-      <c r="B2273" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p141.text</t>
-        </is>
-      </c>
-      <c r="C2273" t="inlineStr">
-        <is>
-          <t>阿黛尔蹦蹦跳跳地离开了</t>
-        </is>
-      </c>
-      <c r="D2273" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P141; church.1020.s1.cleared; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2274">
-      <c r="B2274" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p142.text</t>
-        </is>
-      </c>
-      <c r="C2274" t="inlineStr">
-        <is>
-          <t>我趁机将几封信烧毁，然后若无其事地回到吧台</t>
-        </is>
-      </c>
-      <c r="D2274" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P142; church.1020.s1.cleared; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2275">
-      <c r="B2275" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p144.text</t>
-        </is>
-      </c>
-      <c r="C2275" t="inlineStr">
-        <is>
-          <t>不知道接下来会迎接怎样的挑战和危机呢……</t>
-        </is>
-      </c>
-      <c r="D2275" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P144; church.1020.s1.cleared; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2276">
-      <c r="B2276" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p147.text</t>
-        </is>
-      </c>
-      <c r="C2276" t="inlineStr">
-        <is>
-          <t>我在所有人的注视下被监察司的人带走了，离开咖啡馆前我最后看见的是阿黛尔满是担忧的脸</t>
-        </is>
-      </c>
-      <c r="D2276" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P147; church.1020.s1.detained; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2277">
-      <c r="B2277" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p148.text</t>
-        </is>
-      </c>
-      <c r="C2277" t="inlineStr">
-        <is>
-          <t>他们会如何审问我呢？我要说什么呢？这封信涉及的密文是否会被他们觉察呢？</t>
-        </is>
-      </c>
-      <c r="D2277" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P148; church.1020.s1.detained; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2278">
-      <c r="B2278" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p149.text</t>
-        </is>
-      </c>
-      <c r="C2278" t="inlineStr">
-        <is>
-          <t>带着万千思绪，我被带到了教会看守所中</t>
-        </is>
-      </c>
-      <c r="D2278" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P149; church.1020.s1.detained; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2279">
-      <c r="B2279" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p150.text</t>
-        </is>
-      </c>
-      <c r="C2279" t="inlineStr">
-        <is>
-          <t>啊，从刚毕业的大学生到咖啡馆店长再到在押犯原来只需要一个月吗……</t>
-        </is>
-      </c>
-      <c r="D2279" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P150; church.1020.s1.detained; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2280">
-      <c r="B2280" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p151.text</t>
-        </is>
-      </c>
-      <c r="C2280" t="inlineStr">
-        <is>
-          <t>我被分配进了一个单独的房间，等待监察司的检查结果</t>
-        </is>
-      </c>
-      <c r="D2280" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P151; church.1020.s1.detained; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2281">
-      <c r="B2281" t="inlineStr">
-        <is>
-          <t>church.1020.s1.p152.text</t>
-        </is>
-      </c>
-      <c r="C2281" t="inlineStr">
-        <is>
-          <t>我就此陷入了无尽的等待</t>
-        </is>
-      </c>
-      <c r="D2281" t="inlineStr">
-        <is>
-          <t>church.1020.s1.P152; church.1020.s1.detained; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2282">
-      <c r="B2282" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p006.text</t>
-        </is>
-      </c>
-      <c r="C2282" t="inlineStr">
-        <is>
-          <t>我被带到看守所后，已经见证了第三次日出。</t>
-        </is>
-      </c>
-      <c r="D2282" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P006; church.1023.s1.hearing; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2283">
-      <c r="B2283" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p007.text</t>
-        </is>
-      </c>
-      <c r="C2283" t="inlineStr">
-        <is>
-          <t>在这间狭小的拘押室里，我甚至开始怀念咖啡馆那张吱呀作响的旧椅子。</t>
-        </is>
-      </c>
-      <c r="D2283" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P007; church.1023.s1.hearing; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2284">
-      <c r="B2284" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p008.text</t>
-        </is>
-      </c>
-      <c r="C2284" t="inlineStr">
-        <is>
-          <t>不知道阿黛尔现在怎么样了，咖啡馆有没有正常营业……</t>
-        </is>
-      </c>
-      <c r="D2284" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P008; church.1023.s1.hearing; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2285">
-      <c r="B2285" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p010.text</t>
-        </is>
-      </c>
-      <c r="C2285" t="inlineStr">
-        <is>
-          <t>⌈出来，有人要见你。⌋</t>
-        </is>
-      </c>
-      <c r="D2285" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P010; church.1023.s1.hearing; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2286">
-      <c r="B2286" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p013.text</t>
-        </is>
-      </c>
-      <c r="C2286" t="inlineStr">
-        <is>
-          <t>⌈经过调查，我们没有发现你直接参与非法结社活动的证据。⌋</t>
-        </is>
-      </c>
-      <c r="D2286" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P013; church.1023.s1.hearing; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2287">
-      <c r="B2287" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p014.text</t>
-        </is>
-      </c>
-      <c r="C2287" t="inlineStr">
-        <is>
-          <t>⌈所以我可以离开了？⌋</t>
-        </is>
-      </c>
-      <c r="D2287" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P014; church.1023.s1.hearing; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2288">
-      <c r="B2288" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p015.text</t>
-        </is>
-      </c>
-      <c r="C2288" t="inlineStr">
-        <is>
-          <t>⌈别急。那些密文的来源仍然不明，我们还需要你作出一些保证。⌋</t>
-        </is>
-      </c>
-      <c r="D2288" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P015; church.1023.s1.hearing; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2289">
-      <c r="B2289" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p016.text</t>
-        </is>
-      </c>
-      <c r="C2289" t="inlineStr">
-        <is>
-          <t>⌈如果今后发现任何与乱党有关的情报，你必须向教会报告。⌋</t>
-        </is>
-      </c>
-      <c r="D2289" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P016; church.1023.s1.hearing; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2290">
-      <c r="B2290" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p017.text</t>
-        </is>
-      </c>
-      <c r="C2290" t="inlineStr">
-        <is>
-          <t>⌈……⌋</t>
-        </is>
-      </c>
-      <c r="D2290" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P017; church.1023.s1.hearing; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2291">
-      <c r="B2291" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p018.text</t>
-        </is>
-      </c>
-      <c r="C2291" t="inlineStr">
-        <is>
-          <t>⌈你也可以拒绝。但调查结束前，我们恐怕不能放你走。⌋</t>
-        </is>
-      </c>
-      <c r="D2291" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P018; church.1023.s1.hearing; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2292">
-      <c r="B2292" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p019.text</t>
-        </is>
-      </c>
-      <c r="C2292" t="inlineStr">
-        <is>
-          <t>他看了看桌上的文件，似乎在等待我的回答。</t>
-        </is>
-      </c>
-      <c r="D2292" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P019; church.1023.s1.hearing; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2293">
-      <c r="B2293" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p021.text</t>
-        </is>
-      </c>
-      <c r="C2293" t="inlineStr">
-        <is>
-          <t>⌈既然没有犯罪证据，你们就没有理由继续拘押我。⌋</t>
-        </is>
-      </c>
-      <c r="D2293" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P021; church.1023.s1.hearing; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2294">
-      <c r="B2294" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p022.text</t>
-        </is>
-      </c>
-      <c r="C2294" t="inlineStr">
-        <is>
-          <t>⌈或许我们可以商量一个更方便的解决办法。⌋</t>
-        </is>
-      </c>
-      <c r="D2294" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P022; church.1023.s1.hearing; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2295">
-      <c r="B2295" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p023.text</t>
-        </is>
-      </c>
-      <c r="C2295" t="inlineStr">
-        <is>
-          <t>⌈既然如此，你们就继续调查吧。⌋</t>
-        </is>
-      </c>
-      <c r="D2295" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P023; church.1023.s1.hearing; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2296">
-      <c r="B2296" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p025.text</t>
-        </is>
-      </c>
-      <c r="C2296" t="inlineStr">
-        <is>
-          <t>⌈没有证据就继续拘押一位合法经营的店主，这恐怕也不符合教会的规定吧？⌋</t>
-        </is>
-      </c>
-      <c r="D2296" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P025; church.1023.s1.persuade; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2297">
-      <c r="B2297" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p026.text</t>
-        </is>
-      </c>
-      <c r="C2297" t="inlineStr">
-        <is>
-          <t>⌈你是在质疑监察司的决定？⌋</t>
-        </is>
-      </c>
-      <c r="D2297" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P026; church.1023.s1.persuade; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2298">
-      <c r="B2298" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p027.text</t>
-        </is>
-      </c>
-      <c r="C2298" t="inlineStr">
-        <is>
-          <t>⌈我当然尊重教会的职责，但你刚刚也说了，调查没有发现我参与乱党的证据。⌋</t>
-        </is>
-      </c>
-      <c r="D2298" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P027; church.1023.s1.persuade; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2299">
-      <c r="B2299" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p028.text</t>
-        </is>
-      </c>
-      <c r="C2299" t="inlineStr">
-        <is>
-          <t>⌈况且，沸点咖啡馆在圣徒街经营了那么多年，应该不算一家完全没有人认识的店铺。⌋⌈你们可以向街坊邻居调查，也可以在之后继续观察咖啡馆的经营。但至少现在，没有必要让我继续待在这里。⌋</t>
-        </is>
-      </c>
-      <c r="D2299" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P028; church.1023.s1.persuade; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2300">
-      <c r="B2300" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p029.text</t>
-        </is>
-      </c>
-      <c r="C2300" t="inlineStr">
-        <is>
-          <t>⌈嗯……⌋</t>
-        </is>
-      </c>
-      <c r="D2300" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P029; church.1023.s1.persuade; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2301">
-      <c r="B2301" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p032.text</t>
-        </is>
-      </c>
-      <c r="C2301" t="inlineStr">
-        <is>
-          <t>⌈倒也有些道理。⌋</t>
-        </is>
-      </c>
-      <c r="D2301" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P032; church.1023.s1.persuade_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2302">
-      <c r="B2302" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p033.text</t>
-        </is>
-      </c>
-      <c r="C2302" t="inlineStr">
-        <is>
-          <t>他沉思片刻，在文件上签了字。</t>
-        </is>
-      </c>
-      <c r="D2302" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P033; church.1023.s1.persuade_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2303">
-      <c r="B2303" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p034.text</t>
-        </is>
-      </c>
-      <c r="C2303" t="inlineStr">
-        <is>
-          <t>⌈好吧，你可以走了。但调查还没结束，今后记得配合监察司。⌋</t>
-        </is>
-      </c>
-      <c r="D2303" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P034; church.1023.s1.persuade_pass; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2304">
-      <c r="B2304" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p037.text</t>
-        </is>
-      </c>
-      <c r="C2304" t="inlineStr">
-        <is>
-          <t>⌈是否符合规定，恐怕还轮不到你来判断。带他回去。⌋</t>
-        </is>
-      </c>
-      <c r="D2304" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P037; church.1023.s1.persuade_fail; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2305">
-      <c r="B2305" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p040.text</t>
-        </is>
-      </c>
-      <c r="C2305" t="inlineStr">
-        <is>
-          <t>⌈继续调查既耽误你们的时间，也耽误我的生意。或许有个对双方都方便的办法？⌋</t>
-        </is>
-      </c>
-      <c r="D2305" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P040; church.1023.s1.bribe; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2306">
-      <c r="B2306" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p041.text</t>
-        </is>
-      </c>
-      <c r="C2306" t="inlineStr">
-        <is>
-          <t>我暗示了一下能够支付的金额。</t>
-        </is>
-      </c>
-      <c r="D2306" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P041; church.1023.s1.bribe; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2307">
-      <c r="B2307" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p042.text</t>
-        </is>
-      </c>
-      <c r="C2307" t="inlineStr">
-        <is>
-          <t>监察官抬起头，意味深长地看了我一眼。</t>
-        </is>
-      </c>
-      <c r="D2307" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P042; church.1023.s1.bribe; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2308">
-      <c r="B2308" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p043.text</t>
-        </is>
-      </c>
-      <c r="C2308" t="inlineStr">
-        <is>
-          <t>⌈你是沸点咖啡馆的店长是吧？一会儿我派人跟着你去，把钱打点清楚再说。⌋</t>
-        </is>
-      </c>
-      <c r="D2308" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P043; church.1023.s1.bribe; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2309">
-      <c r="B2309" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p044.text</t>
-        </is>
-      </c>
-      <c r="C2309" t="inlineStr">
-        <is>
-          <t>⌈好的，好的，当然可以。⌋</t>
-        </is>
-      </c>
-      <c r="D2309" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P044; church.1023.s1.bribe; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2310">
-      <c r="B2310" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p045.text</t>
-        </is>
-      </c>
-      <c r="C2310" t="inlineStr">
-        <is>
-          <t>⌈不过我要这个数。⌋</t>
-        </is>
-      </c>
-      <c r="D2310" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P045; church.1023.s1.bribe; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2311">
-      <c r="B2311" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p046.text</t>
-        </is>
-      </c>
-      <c r="C2311" t="inlineStr">
-        <is>
-          <t>⌈抢劫啊？⌋</t>
-        </is>
-      </c>
-      <c r="D2311" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P046; church.1023.s1.bribe; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2312">
-      <c r="B2312" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p047.text</t>
-        </is>
-      </c>
-      <c r="C2312" t="inlineStr">
-        <is>
-          <t>⌈哎，看来你不乐意，那就只好多关几天咯！⌋</t>
-        </is>
-      </c>
-      <c r="D2312" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P047; church.1023.s1.bribe; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2313">
-      <c r="B2313" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p048.text</t>
-        </is>
-      </c>
-      <c r="C2313" t="inlineStr">
-        <is>
-          <t>⌈嘶......看来你是个聪明人。既然没有发现犯罪证据，我们当然没有必要继续浪费时间。⌋</t>
-        </is>
-      </c>
-      <c r="D2313" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P048; church.1023.s1.bribe; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2314">
-      <c r="B2314" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p054.text</t>
-        </is>
-      </c>
-      <c r="C2314" t="inlineStr">
-        <is>
-          <t>看来今天又得在这里过夜了。</t>
-        </is>
-      </c>
-      <c r="D2314" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P054; church.1023.s1.rescue; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2315">
-      <c r="B2315" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p055.text</t>
-        </is>
-      </c>
-      <c r="C2315" t="inlineStr">
-        <is>
-          <t>我靠在墙边，正想着阿黛尔会不会已经把我当成失踪人口，铁门却再次打开了。</t>
-        </is>
-      </c>
-      <c r="D2315" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P055; church.1023.s1.rescue; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2316">
-      <c r="B2316" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p057.text</t>
-        </is>
-      </c>
-      <c r="C2316" t="inlineStr">
-        <is>
-          <t>⌈出来，你可以走了。⌋</t>
-        </is>
-      </c>
-      <c r="D2316" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P057; church.1023.s1.rescue; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2317">
-      <c r="B2317" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p058.text</t>
-        </is>
-      </c>
-      <c r="C2317" t="inlineStr">
-        <is>
-          <t>⌈啊？可是刚刚不是还说……⌋</t>
-        </is>
-      </c>
-      <c r="D2317" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P058; church.1023.s1.rescue; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2318">
-      <c r="B2318" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p059.text</t>
-        </is>
-      </c>
-      <c r="C2318" t="inlineStr">
-        <is>
-          <t>⌈上面送来了新的释放手续。你还想留下来不成？⌋</t>
-        </is>
-      </c>
-      <c r="D2318" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P059; church.1023.s1.rescue; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2319">
-      <c r="B2319" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p060.text</t>
-        </is>
-      </c>
-      <c r="C2319" t="inlineStr">
-        <is>
-          <t>他将一份盖好印章的文件塞进我手中。</t>
-        </is>
-      </c>
-      <c r="D2319" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P060; church.1023.s1.rescue; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2320">
-      <c r="B2320" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p061.text</t>
-        </is>
-      </c>
-      <c r="C2320" t="inlineStr">
-        <is>
-          <t>上面清清楚楚地写着：「证据不足，准予释放。」</t>
-        </is>
-      </c>
-      <c r="D2320" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P061; church.1023.s1.rescue; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2321">
-      <c r="B2321" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p062.text</t>
-        </is>
-      </c>
-      <c r="C2321" t="inlineStr">
-        <is>
-          <t>怎么突然就证据不足了？</t>
-        </is>
-      </c>
-      <c r="D2321" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P062; church.1023.s1.rescue; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2322">
-      <c r="B2322" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p063.text</t>
-        </is>
-      </c>
-      <c r="C2322" t="inlineStr">
-        <is>
-          <t>不过，我当然没有理由拒绝。</t>
-        </is>
-      </c>
-      <c r="D2322" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P063; church.1023.s1.rescue; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2323">
-      <c r="B2323" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p065.text</t>
-        </is>
-      </c>
-      <c r="C2323" t="inlineStr">
-        <is>
-          <t>我看了看那张文件。</t>
-        </is>
-      </c>
-      <c r="D2323" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P065; church.1023.s1.record_notice; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2324">
-      <c r="B2324" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p066.text</t>
-        </is>
-      </c>
-      <c r="C2324" t="inlineStr">
-        <is>
-          <t>上面的印章和其他文书没有什么区别。</t>
-        </is>
-      </c>
-      <c r="D2324" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P066; church.1023.s1.record_notice; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2325">
-      <c r="B2325" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p067.text</t>
-        </is>
-      </c>
-      <c r="C2325" t="inlineStr">
-        <is>
-          <t>不过，在旁边的登记簿上，我的名字似乎被人重新填写过一次。</t>
-        </is>
-      </c>
-      <c r="D2325" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P067; church.1023.s1.record_notice; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2326">
-      <c r="B2326" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p068.text</t>
-        </is>
-      </c>
-      <c r="C2326" t="inlineStr">
-        <is>
-          <t>原本的字迹已经被墨水覆盖，又用另一种笔迹写上了新的处理结果。</t>
-        </is>
-      </c>
-      <c r="D2326" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P068; church.1023.s1.record_notice; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2327">
-      <c r="B2327" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p069.text</t>
-        </is>
-      </c>
-      <c r="C2327" t="inlineStr">
-        <is>
-          <t>而且，记录上标注的释放时间，似乎比我刚刚被带回牢房的时间还要早。</t>
-        </is>
-      </c>
-      <c r="D2327" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P069; church.1023.s1.record_notice; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2328">
-      <c r="B2328" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p070.text</t>
-        </is>
-      </c>
-      <c r="C2328" t="inlineStr">
-        <is>
-          <t>……</t>
-        </is>
-      </c>
-      <c r="D2328" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P070; church.1023.s1.record_notice; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2329">
-      <c r="B2329" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p071.text</t>
-        </is>
-      </c>
-      <c r="C2329" t="inlineStr">
-        <is>
-          <t>有人修改了我的拘押记录？</t>
-        </is>
-      </c>
-      <c r="D2329" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P071; church.1023.s1.record_notice; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2330">
-      <c r="B2330" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p073.text</t>
-        </is>
-      </c>
-      <c r="C2330" t="inlineStr">
-        <is>
-          <t>⌈请问，是谁批准释放我的？⌋</t>
-        </is>
-      </c>
-      <c r="D2330" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P073; church.1023.s1.rescue_depart; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2331">
-      <c r="B2331" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p074.text</t>
-        </is>
-      </c>
-      <c r="C2331" t="inlineStr">
-        <is>
-          <t>⌈登记上写得很清楚，按照规定处理的。⌋</t>
-        </is>
-      </c>
-      <c r="D2331" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P074; church.1023.s1.rescue_depart; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2332">
-      <c r="B2332" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p075.text</t>
-        </is>
-      </c>
-      <c r="C2332" t="inlineStr">
-        <is>
-          <t>⌈我是说，刚刚是谁来办理手续的？⌋</t>
-        </is>
-      </c>
-      <c r="D2332" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P075; church.1023.s1.rescue_depart; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2333">
-      <c r="B2333" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p076.text</t>
-        </is>
-      </c>
-      <c r="C2333" t="inlineStr">
-        <is>
-          <t>⌈我哪知道？今天送过来的文件这么多。⌋</t>
-        </is>
-      </c>
-      <c r="D2333" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P076; church.1023.s1.rescue_depart; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2334">
-      <c r="B2334" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p077.text</t>
-        </is>
-      </c>
-      <c r="C2334" t="inlineStr">
-        <is>
-          <t>⌈话怎么这么多？再问我就和上面说你不服命令，重新把你关进去。⌋</t>
-        </is>
-      </c>
-      <c r="D2334" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P077; church.1023.s1.rescue_depart; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2335">
-      <c r="B2335" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p078.text</t>
-        </is>
-      </c>
-      <c r="C2335" t="inlineStr">
-        <is>
-          <t>⌈……⌋</t>
-        </is>
-      </c>
-      <c r="D2335" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P078; church.1023.s1.rescue_depart; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2336">
-      <c r="B2336" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p079.text</t>
-        </is>
-      </c>
-      <c r="C2336" t="inlineStr">
-        <is>
-          <t>算了。</t>
-        </is>
-      </c>
-      <c r="D2336" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P079; church.1023.s1.rescue_depart; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2337">
-      <c r="B2337" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p080.text</t>
-        </is>
-      </c>
-      <c r="C2337" t="inlineStr">
-        <is>
-          <t>不管究竟是谁帮了我，现在最重要的事情，还是赶紧离开这个地方。</t>
-        </is>
-      </c>
-      <c r="D2337" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P080; church.1023.s1.rescue_depart; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2338">
-      <c r="B2338" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p088.text</t>
-        </is>
-      </c>
-      <c r="C2338" t="inlineStr">
-        <is>
-          <t>⌈我回来了！⌋</t>
-        </is>
-      </c>
-      <c r="D2338" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P088; church.1023.s1.home; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2339">
-      <c r="B2339" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p089.text</t>
-        </is>
-      </c>
-      <c r="C2339" t="inlineStr">
-        <is>
-          <t>⌈……{playername}？⌋</t>
-        </is>
-      </c>
-      <c r="D2339" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P089; church.1023.s1.home; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2340">
-      <c r="B2340" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p090.text</t>
-        </is>
-      </c>
-      <c r="C2340" t="inlineStr">
-        <is>
-          <t>她愣了一下，随即快步走来。</t>
-        </is>
-      </c>
-      <c r="D2340" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P090; church.1023.s1.home; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2341">
-      <c r="B2341" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p091.text</t>
-        </is>
-      </c>
-      <c r="C2341" t="inlineStr">
-        <is>
-          <t>⌈你终于回来了！⌋</t>
-        </is>
-      </c>
-      <c r="D2341" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P091; church.1023.s1.home; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2342">
-      <c r="B2342" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p092.text</t>
-        </is>
-      </c>
-      <c r="C2342" t="inlineStr">
-        <is>
-          <t>⌈他们没有对你怎么样吧？⌋</t>
-        </is>
-      </c>
-      <c r="D2342" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P092; church.1023.s1.home; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2343">
-      <c r="B2343" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p093.text</t>
-        </is>
-      </c>
-      <c r="C2343" t="inlineStr">
-        <is>
-          <t>⌈没有没有，只是被关了几天。⌋</t>
-        </is>
-      </c>
-      <c r="D2343" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P093; church.1023.s1.home; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2344">
-      <c r="B2344" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p094.text</t>
-        </is>
-      </c>
-      <c r="C2344" t="inlineStr">
-        <is>
-          <t>⌈这还叫没什么！我去问了好几次，他们都不肯告诉我什么时候放你回来。⌋</t>
-        </is>
-      </c>
-      <c r="D2344" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P094; church.1023.s1.home; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2345">
-      <c r="B2345" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p095.text</t>
-        </is>
-      </c>
-      <c r="C2345" t="inlineStr">
-        <is>
-          <t>⌈抱歉，让你担心了。⌋</t>
-        </is>
-      </c>
-      <c r="D2345" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P095; church.1023.s1.home; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2346">
-      <c r="B2346" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p096.text</t>
-        </is>
-      </c>
-      <c r="C2346" t="inlineStr">
-        <is>
-          <t>⌈……回来就好。⌋</t>
-        </is>
-      </c>
-      <c r="D2346" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P096; church.1023.s1.home; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2347">
-      <c r="B2347" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p097.text</t>
-        </is>
-      </c>
-      <c r="C2347" t="inlineStr">
-        <is>
-          <t>她替我拉开椅子。</t>
-        </is>
-      </c>
-      <c r="D2347" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P097; church.1023.s1.home; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2348">
-      <c r="B2348" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p098.text</t>
-        </is>
-      </c>
-      <c r="C2348" t="inlineStr">
-        <is>
-          <t>⌈不过，他们怎么突然愿意放人了？⌋</t>
-        </is>
-      </c>
-      <c r="D2348" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P098; church.1023.s1.home; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2349">
-      <c r="B2349" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p101.text</t>
-        </is>
-      </c>
-      <c r="C2349" t="inlineStr">
-        <is>
-          <t>⌈他们本来也没找到犯罪证据，我和监察官讲了讲道理，就把我放了。⌋</t>
-        </is>
-      </c>
-      <c r="D2349" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P101; church.1023.s1.home_persuade; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2350">
-      <c r="B2350" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p102.text</t>
-        </is>
-      </c>
-      <c r="C2350" t="inlineStr">
-        <is>
-          <t>⌈那真是太好了，至少教会的人还愿意讲道理。⌋</t>
-        </is>
-      </c>
-      <c r="D2350" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P102; church.1023.s1.home_persuade; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2351">
-      <c r="B2351" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p103.text</t>
-        </is>
-      </c>
-      <c r="C2351" t="inlineStr">
-        <is>
-          <t>⌈不过，既然他们已经盯上了咖啡馆，以后还是得小心。⌋</t>
-        </is>
-      </c>
-      <c r="D2351" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P103; church.1023.s1.home_persuade; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2352">
-      <c r="B2352" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p105.text</t>
-        </is>
-      </c>
-      <c r="C2352" t="inlineStr">
-        <is>
-          <t>⌈花了点钱，总算让他们同意放人了。⌋</t>
-        </is>
-      </c>
-      <c r="D2352" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P105; church.1023.s1.home_bribe; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2353">
-      <c r="B2353" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p106.text</t>
-        </is>
-      </c>
-      <c r="C2353" t="inlineStr">
-        <is>
-          <t>⌈花钱？你是说……⌋</t>
-        </is>
-      </c>
-      <c r="D2353" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P106; church.1023.s1.home_bribe; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2354">
-      <c r="B2354" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p107.text</t>
-        </is>
-      </c>
-      <c r="C2354" t="inlineStr">
-        <is>
-          <t>⌈嘘！别说出来。⌋</t>
-        </is>
-      </c>
-      <c r="D2354" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P107; church.1023.s1.home_bribe; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2355">
-      <c r="B2355" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p108.text</t>
-        </is>
-      </c>
-      <c r="C2355" t="inlineStr">
-        <is>
-          <t>⌈这些人真是……⌋</t>
-        </is>
-      </c>
-      <c r="D2355" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P108; church.1023.s1.home_bribe; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2356">
-      <c r="B2356" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p109.text</t>
-        </is>
-      </c>
-      <c r="C2356" t="inlineStr">
-        <is>
-          <t>她叹了口气。</t>
-        </is>
-      </c>
-      <c r="D2356" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P109; church.1023.s1.home_bribe; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2357">
-      <c r="B2357" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p110.text</t>
-        </is>
-      </c>
-      <c r="C2357" t="inlineStr">
-        <is>
-          <t>⌈你一会让把钱筹一下送过去。⌋</t>
-        </is>
-      </c>
-      <c r="D2357" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P110; church.1023.s1.home_bribe; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2358">
-      <c r="B2358" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p111.text</t>
-        </is>
-      </c>
-      <c r="C2358" t="inlineStr">
-        <is>
-          <t>⌈我才不做这种事情呢！⌋</t>
-        </is>
-      </c>
-      <c r="D2358" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P111; church.1023.s1.home_bribe; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2359">
-      <c r="B2359" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p112.text</t>
-        </is>
-      </c>
-      <c r="C2359" t="inlineStr">
-        <is>
-          <t>⌈那行，一会儿我去干这脏活累活吧......⌋</t>
-        </is>
-      </c>
-      <c r="D2359" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P112; church.1023.s1.home_bribe; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2360">
-      <c r="B2360" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p114.text</t>
-        </is>
-      </c>
-      <c r="C2360" t="inlineStr">
-        <is>
-          <t>⌈说实话，我也不知道。他们本来还要继续调查，结果突然有人送来文件，说我可以走了。⌋</t>
-        </is>
-      </c>
-      <c r="D2360" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P114; church.1023.s1.home_rescue; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2361">
-      <c r="B2361" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p115.text</t>
-        </is>
-      </c>
-      <c r="C2361" t="inlineStr">
-        <is>
-          <t>⌈突然有人送来文件？⌋</t>
-        </is>
-      </c>
-      <c r="D2361" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P115; church.1023.s1.home_rescue; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2362">
-      <c r="B2362" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p116.text</t>
-        </is>
-      </c>
-      <c r="C2362" t="inlineStr">
-        <is>
-          <t>⌈是啊，连看守都不知道怎么回事。真奇怪。⌋</t>
-        </is>
-      </c>
-      <c r="D2362" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P116; church.1023.s1.home_rescue; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2363">
-      <c r="B2363" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p117.text</t>
-        </is>
-      </c>
-      <c r="C2363" t="inlineStr">
-        <is>
-          <t>阿黛尔似乎想到了什么，沉默了一会儿。</t>
-        </is>
-      </c>
-      <c r="D2363" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P117; church.1023.s1.home_rescue; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2364">
-      <c r="B2364" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p118.text</t>
-        </is>
-      </c>
-      <c r="C2364" t="inlineStr">
-        <is>
-          <t>⌈原来如此......⌋</t>
-        </is>
-      </c>
-      <c r="D2364" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P118; church.1023.s1.home_rescue; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2365">
-      <c r="B2365" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p119.text</t>
-        </is>
-      </c>
-      <c r="C2365" t="inlineStr">
-        <is>
-          <t>⌈你知道些什么？⌋</t>
-        </is>
-      </c>
-      <c r="D2365" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P119; church.1023.s1.home_rescue; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2366">
-      <c r="B2366" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p120.text</t>
-        </is>
-      </c>
-      <c r="C2366" t="inlineStr">
-        <is>
-          <t>⌈啊？没有，我也只是猜测……⌋</t>
-        </is>
-      </c>
-      <c r="D2366" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P120; church.1023.s1.home_rescue; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2367">
-      <c r="B2367" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p121.text</t>
-        </is>
-      </c>
-      <c r="C2367" t="inlineStr">
-        <is>
-          <t>⌈猜测什么？⌋</t>
-        </is>
-      </c>
-      <c r="D2367" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P121; church.1023.s1.home_rescue; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2368">
-      <c r="B2368" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p122.text</t>
-        </is>
-      </c>
-      <c r="C2368" t="inlineStr">
-        <is>
-          <t>⌈以前杜瓦尔先生经营咖啡馆的时候，认识不少人。有些人虽然不方便公开露面，但很重视这家店。⌋</t>
-        </is>
-      </c>
-      <c r="D2368" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P122; church.1023.s1.home_rescue; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2369">
-      <c r="B2369" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p123.text</t>
-        </is>
-      </c>
-      <c r="C2369" t="inlineStr">
-        <is>
-          <t>⌈如果他们知道你被教会带走了，或许不会坐视不管。⌋</t>
-        </is>
-      </c>
-      <c r="D2369" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P123; church.1023.s1.home_rescue; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2370">
-      <c r="B2370" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p124.text</t>
-        </is>
-      </c>
-      <c r="C2370" t="inlineStr">
-        <is>
-          <t>⌈你是说，有人暗中帮了我？⌋</t>
-        </is>
-      </c>
-      <c r="D2370" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P124; church.1023.s1.home_rescue; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2371">
-      <c r="B2371" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p125.text</t>
-        </is>
-      </c>
-      <c r="C2371" t="inlineStr">
-        <is>
-          <t>⌈只是猜测而已，我也不确定。⌋</t>
-        </is>
-      </c>
-      <c r="D2371" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P125; church.1023.s1.home_rescue; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2372">
-      <c r="B2372" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p126.text</t>
-        </is>
-      </c>
-      <c r="C2372" t="inlineStr">
-        <is>
-          <t>她低头整理起桌上的餐具，似乎不打算继续这个话题。</t>
-        </is>
-      </c>
-      <c r="D2372" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P126; church.1023.s1.home_rescue; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2373">
-      <c r="B2373" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p127.text</t>
-        </is>
-      </c>
-      <c r="C2373" t="inlineStr">
-        <is>
-          <t>⌈不过，如果真是他们……看来那些人还没有忘记这里。⌋</t>
-        </is>
-      </c>
-      <c r="D2373" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P127; church.1023.s1.home_rescue; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2374">
-      <c r="B2374" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p128.text</t>
-        </is>
-      </c>
-      <c r="C2374" t="inlineStr">
-        <is>
-          <t>⌈那些人？⌋</t>
-        </is>
-      </c>
-      <c r="D2374" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P128; church.1023.s1.home_rescue; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2375">
-      <c r="B2375" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p129.text</t>
-        </is>
-      </c>
-      <c r="C2375" t="inlineStr">
-        <is>
-          <t>⌈没什么。你才刚回来，先休息吧。⌋</t>
-        </is>
-      </c>
-      <c r="D2375" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P129; church.1023.s1.home_rescue; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2376">
-      <c r="B2376" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p131.text</t>
-        </is>
-      </c>
-      <c r="C2376" t="inlineStr">
-        <is>
-          <t>⌈总之，欢迎回来，店长先生。⌋</t>
-        </is>
-      </c>
-      <c r="D2376" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P131; church.1023.s1.home_end; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2377">
-      <c r="B2377" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p132.text</t>
-        </is>
-      </c>
-      <c r="C2377" t="inlineStr">
-        <is>
-          <t>⌈嗯，我回来了。⌋</t>
-        </is>
-      </c>
-      <c r="D2377" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P132; church.1023.s1.home_end; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2378">
-      <c r="B2378" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p133.text</t>
-        </is>
-      </c>
-      <c r="C2378" t="inlineStr">
-        <is>
-          <t>我靠在椅背上，终于松了口气。</t>
-        </is>
-      </c>
-      <c r="D2378" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P133; church.1023.s1.home_end; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2379">
-      <c r="B2379" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p134.text</t>
-        </is>
-      </c>
-      <c r="C2379" t="inlineStr">
-        <is>
-          <t>咖啡馆似乎什么都没有改变。</t>
-        </is>
-      </c>
-      <c r="D2379" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P134; church.1023.s1.home_end; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2380">
-      <c r="B2380" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p135.text</t>
-        </is>
-      </c>
-      <c r="C2380" t="inlineStr">
-        <is>
-          <t>不过我的心态已经完全不同，</t>
-        </is>
-      </c>
-      <c r="D2380" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P135; church.1023.s1.home_end; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2381">
-      <c r="B2381" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p136.text</t>
-        </is>
-      </c>
-      <c r="C2381" t="inlineStr">
-        <is>
-          <t>在监牢里度过的三天却让我后背发凉。</t>
-        </is>
-      </c>
-      <c r="D2381" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P136; church.1023.s1.home_end; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2382">
-      <c r="B2382" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p137.text</t>
-        </is>
-      </c>
-      <c r="C2382" t="inlineStr">
-        <is>
-          <t>我这次能因信的的事情被抓进去，下一次又会因为什么遭遇不测。</t>
-        </is>
-      </c>
-      <c r="D2382" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P137; church.1023.s1.home_end; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2383">
-      <c r="B2383" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p138.text</t>
-        </is>
-      </c>
-      <c r="C2383" t="inlineStr">
-        <is>
-          <t>三天前，教会监察司的人突然闯进咖啡馆，将我带走。</t>
-        </is>
-      </c>
-      <c r="D2383" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P138; church.1023.s1.home_end; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2384">
-      <c r="B2384" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p139.text</t>
-        </is>
-      </c>
-      <c r="C2384" t="inlineStr">
-        <is>
-          <t>三天后，我终于回到了这里。</t>
-        </is>
-      </c>
-      <c r="D2384" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P139; church.1023.s1.home_end; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2385">
-      <c r="B2385" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p140.text</t>
-        </is>
-      </c>
-      <c r="C2385" t="inlineStr">
-        <is>
-          <t>但那几封密文仍然被扣押在教会手中。</t>
-        </is>
-      </c>
-      <c r="D2385" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P140; church.1023.s1.home_end; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2386">
-      <c r="B2386" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p141.text</t>
-        </is>
-      </c>
-      <c r="C2386" t="inlineStr">
-        <is>
-          <t>而且，在离开看守所之前，他们还专门提醒我：</t>
-        </is>
-      </c>
-      <c r="D2386" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P141; church.1023.s1.home_end; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2387">
-      <c r="B2387" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p142.text</t>
-        </is>
-      </c>
-      <c r="C2387" t="inlineStr">
-        <is>
-          <t>如果发现有关乱党的情报，必须向教会报告。</t>
-        </is>
-      </c>
-      <c r="D2387" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P142; church.1023.s1.home_end; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2388">
-      <c r="B2388" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p143.text</t>
-        </is>
-      </c>
-      <c r="C2388" t="inlineStr">
-        <is>
-          <t>……</t>
-        </is>
-      </c>
-      <c r="D2388" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P143; church.1023.s1.home_end; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2389">
-      <c r="B2389" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p144.text</t>
-        </is>
-      </c>
-      <c r="C2389" t="inlineStr">
-        <is>
-          <t>这算什么意思？</t>
-        </is>
-      </c>
-      <c r="D2389" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P144; church.1023.s1.home_end; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2390">
-      <c r="B2390" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p145.text</t>
-        </is>
-      </c>
-      <c r="C2390" t="inlineStr">
-        <is>
-          <t>今后要是那个神秘人再给我送来几封信，难道我还得主动跑去监察司告诉他们？</t>
-        </is>
-      </c>
-      <c r="D2390" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P145; church.1023.s1.home_end; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2391">
-      <c r="B2391" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p146.text</t>
-        </is>
-      </c>
-      <c r="C2391" t="inlineStr">
-        <is>
-          <t>开什么玩笑。</t>
-        </is>
-      </c>
-      <c r="D2391" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P146; church.1023.s1.home_end; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2392">
-      <c r="B2392" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p147.text</t>
-        </is>
-      </c>
-      <c r="C2392" t="inlineStr">
-        <is>
-          <t>可是，如果不这么做……</t>
-        </is>
-      </c>
-      <c r="D2392" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P147; church.1023.s1.home_end; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2393">
-      <c r="B2393" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p148.text</t>
-        </is>
-      </c>
-      <c r="C2393" t="inlineStr">
-        <is>
-          <t>我抬起头，看向正在厨房里忙碌的阿黛尔。</t>
-        </is>
-      </c>
-      <c r="D2393" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P148; church.1023.s1.home_end; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2394">
-      <c r="B2394" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p149.text</t>
-        </is>
-      </c>
-      <c r="C2394" t="inlineStr">
-        <is>
-          <t>自从来到这家店，怪事就一个接着一个。</t>
-        </is>
-      </c>
-      <c r="D2394" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P149; church.1023.s1.home_end; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2395">
-      <c r="B2395" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p150.text</t>
-        </is>
-      </c>
-      <c r="C2395" t="inlineStr">
-        <is>
-          <t>王都圣诺特的漩涡下面究竟有多少骇人的存在？它们在谋划些什么？为什么我会被卷到这些事情里？我还能保护我和身边的人吗？</t>
-        </is>
-      </c>
-      <c r="D2395" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P150; church.1023.s1.home_end; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2396">
-      <c r="B2396" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p151.text</t>
-        </is>
-      </c>
-      <c r="C2396" t="inlineStr">
-        <is>
-          <t>三日关押积累下来的疲惫与巨大的思考量冲撞着我的思绪，</t>
-        </is>
-      </c>
-      <c r="D2396" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P151; church.1023.s1.home_end; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2397">
-      <c r="B2397" t="inlineStr">
-        <is>
-          <t>church.1023.s1.p152.text</t>
-        </is>
-      </c>
-      <c r="C2397" t="inlineStr">
-        <is>
-          <t>我再也无力去支撑精神，倒在座椅上睡去......</t>
-        </is>
-      </c>
-      <c r="D2397" t="inlineStr">
-        <is>
-          <t>church.1023.s1.P152; church.1023.s1.home_end; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2398">
-      <c r="B2398" t="inlineStr">
-        <is>
-          <t>church.1023.s2.p005.text</t>
-        </is>
-      </c>
-      <c r="C2398" t="inlineStr">
-        <is>
-          <t>距离上次与监察官会面又过了不知多少天</t>
-        </is>
-      </c>
-      <c r="D2398" t="inlineStr">
-        <is>
-          <t>church.1023.s2.P005; church.1023.s2.prison; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2399">
-      <c r="B2399" t="inlineStr">
-        <is>
-          <t>church.1023.s2.p006.text</t>
-        </is>
-      </c>
-      <c r="C2399" t="inlineStr">
-        <is>
-          <t>这段日子里我尝试与外界联系，却都失败了</t>
-        </is>
-      </c>
-      <c r="D2399" t="inlineStr">
-        <is>
-          <t>church.1023.s2.P006; church.1023.s2.prison; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2400">
-      <c r="B2400" t="inlineStr">
-        <is>
-          <t>church.1023.s2.p007.text</t>
-        </is>
-      </c>
-      <c r="C2400" t="inlineStr">
-        <is>
-          <t>我所能接触到的只有这四方墙壁</t>
-        </is>
-      </c>
-      <c r="D2400" t="inlineStr">
-        <is>
-          <t>church.1023.s2.P007; church.1023.s2.prison; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2401">
-      <c r="B2401" t="inlineStr">
-        <is>
-          <t>church.1023.s2.p008.text</t>
-        </is>
-      </c>
-      <c r="C2401" t="inlineStr">
-        <is>
-          <t>不知道今日是何日，不知道咖啡馆怎么样了，不知道阿黛尔怎么样了，不知道我离开之后神秘人是否还在接触咖啡馆……</t>
-        </is>
-      </c>
-      <c r="D2401" t="inlineStr">
-        <is>
-          <t>church.1023.s2.P008; church.1023.s2.prison; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2402">
-      <c r="B2402" t="inlineStr">
-        <is>
-          <t>church.1023.s2.p009.text</t>
-        </is>
-      </c>
-      <c r="C2402" t="inlineStr">
-        <is>
-          <t>不知道……不知道……什么都不知道……</t>
-        </is>
-      </c>
-      <c r="D2402" t="inlineStr">
-        <is>
-          <t>church.1023.s2.P009; church.1023.s2.prison; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2403">
-      <c r="B2403" t="inlineStr">
-        <is>
-          <t>church.1023.s2.p010.text</t>
-        </is>
-      </c>
-      <c r="C2403" t="inlineStr">
-        <is>
-          <t>我的意识在这种日子中渐渐模糊……</t>
-        </is>
-      </c>
-      <c r="D2403" t="inlineStr">
-        <is>
-          <t>church.1023.s2.P010; church.1023.s2.prison; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2404">
-      <c r="B2404" t="inlineStr">
-        <is>
-          <t>church.1023.s2.p013.text</t>
-        </is>
-      </c>
-      <c r="C2404" t="inlineStr">
-        <is>
-          <t>沉寂和单调，是我牢狱生活的全部</t>
-        </is>
-      </c>
-      <c r="D2404" t="inlineStr">
-        <is>
-          <t>church.1023.s2.P013; church.1023.s2.execution; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2405">
-      <c r="B2405" t="inlineStr">
-        <is>
-          <t>church.1023.s2.p014.text</t>
-        </is>
-      </c>
-      <c r="C2405" t="inlineStr">
-        <is>
-          <t>直到某一天我的世界出现了新的声音</t>
-        </is>
-      </c>
-      <c r="D2405" t="inlineStr">
-        <is>
-          <t>church.1023.s2.P014; church.1023.s2.execution; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2406">
-      <c r="B2406" t="inlineStr">
-        <is>
-          <t>church.1023.s2.p016.text</t>
-        </is>
-      </c>
-      <c r="C2406" t="inlineStr">
-        <is>
-          <t>那是几个穿着制服的人，走进了关押我的房间内</t>
-        </is>
-      </c>
-      <c r="D2406" t="inlineStr">
-        <is>
-          <t>church.1023.s2.P016; church.1023.s2.execution; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2407">
-      <c r="B2407" t="inlineStr">
-        <is>
-          <t>church.1023.s2.p017.text</t>
-        </is>
-      </c>
-      <c r="C2407" t="inlineStr">
-        <is>
-          <t>他们对着我说了一串话</t>
-        </is>
-      </c>
-      <c r="D2407" t="inlineStr">
-        <is>
-          <t>church.1023.s2.P017; church.1023.s2.execution; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2408">
-      <c r="B2408" t="inlineStr">
-        <is>
-          <t>church.1023.s2.p018.text</t>
-        </is>
-      </c>
-      <c r="C2408" t="inlineStr">
-        <is>
-          <t>但由于脱离外界太久，意识模糊，我只能隐隐约约辨认出几个词，什么「革命」 「镇压」 「清算」……</t>
-        </is>
-      </c>
-      <c r="D2408" t="inlineStr">
-        <is>
-          <t>church.1023.s2.P018; church.1023.s2.execution; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2409">
-      <c r="B2409" t="inlineStr">
-        <is>
-          <t>church.1023.s2.p019.text</t>
-        </is>
-      </c>
-      <c r="C2409" t="inlineStr">
-        <is>
-          <t>在我还未能理解这些词句的意思时</t>
-        </is>
-      </c>
-      <c r="D2409" t="inlineStr">
-        <is>
-          <t>church.1023.s2.P019; church.1023.s2.execution; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2410">
-      <c r="B2410" t="inlineStr">
-        <is>
-          <t>church.1023.s2.p020.text</t>
-        </is>
-      </c>
-      <c r="C2410" t="inlineStr">
-        <is>
-          <t>我感到我被他们强行从地上拉了起来，被推动着向外走</t>
-        </is>
-      </c>
-      <c r="D2410" t="inlineStr">
-        <is>
-          <t>church.1023.s2.P020; church.1023.s2.execution; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2411">
-      <c r="B2411" t="inlineStr">
-        <is>
-          <t>church.1023.s2.p021.text</t>
-        </is>
-      </c>
-      <c r="C2411" t="inlineStr">
-        <is>
-          <t>方墙以外的世界</t>
-        </is>
-      </c>
-      <c r="D2411" t="inlineStr">
-        <is>
-          <t>church.1023.s2.P021; church.1023.s2.execution; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2412">
-      <c r="B2412" t="inlineStr">
-        <is>
-          <t>church.1023.s2.p022.text</t>
-        </is>
-      </c>
-      <c r="C2412" t="inlineStr">
-        <is>
-          <t>新鲜的空气</t>
-        </is>
-      </c>
-      <c r="D2412" t="inlineStr">
-        <is>
-          <t>church.1023.s2.P022; church.1023.s2.execution; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2413">
-      <c r="B2413" t="inlineStr">
-        <is>
-          <t>church.1023.s2.p023.text</t>
-        </is>
-      </c>
-      <c r="C2413" t="inlineStr">
-        <is>
-          <t>曾经我渴求无数次的东西就这样呈现在我面前</t>
-        </is>
-      </c>
-      <c r="D2413" t="inlineStr">
-        <is>
-          <t>church.1023.s2.P023; church.1023.s2.execution; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2414">
-      <c r="B2414" t="inlineStr">
-        <is>
-          <t>church.1023.s2.p024.text</t>
-        </is>
-      </c>
-      <c r="C2414" t="inlineStr">
-        <is>
-          <t>现下我却无暇顾及</t>
-        </is>
-      </c>
-      <c r="D2414" t="inlineStr">
-        <is>
-          <t>church.1023.s2.P024; church.1023.s2.execution; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2415">
-      <c r="B2415" t="inlineStr">
-        <is>
-          <t>church.1023.s2.p025.text</t>
-        </is>
-      </c>
-      <c r="C2415" t="inlineStr">
-        <is>
-          <t>我不知道我会被他们带往哪里</t>
-        </is>
-      </c>
-      <c r="D2415" t="inlineStr">
-        <is>
-          <t>church.1023.s2.P025; church.1023.s2.execution; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2416">
-      <c r="B2416" t="inlineStr">
-        <is>
-          <t>church.1023.s2.p026.text</t>
-        </is>
-      </c>
-      <c r="C2416" t="inlineStr">
-        <is>
-          <t>就这样走着，走着……</t>
-        </is>
-      </c>
-      <c r="D2416" t="inlineStr">
-        <is>
-          <t>church.1023.s2.P026; church.1023.s2.execution; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2417">
-      <c r="B2417" t="inlineStr">
-        <is>
-          <t>church.1023.s2.p027.text</t>
-        </is>
-      </c>
-      <c r="C2417" t="inlineStr">
-        <is>
-          <t>这里是哪里？</t>
-        </is>
-      </c>
-      <c r="D2417" t="inlineStr">
-        <is>
-          <t>church.1023.s2.P027; church.1023.s2.execution; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2418">
-      <c r="B2418" t="inlineStr">
-        <is>
-          <t>church.1023.s2.p028.text</t>
-        </is>
-      </c>
-      <c r="C2418" t="inlineStr">
-        <is>
-          <t>刑场？</t>
-        </is>
-      </c>
-      <c r="D2418" t="inlineStr">
-        <is>
-          <t>church.1023.s2.P028; church.1023.s2.execution; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2419">
-      <c r="B2419" t="inlineStr">
-        <is>
-          <t>church.1023.s2.p029.text</t>
-        </is>
-      </c>
-      <c r="C2419" t="inlineStr">
-        <is>
-          <t>我要死了吗？</t>
-        </is>
-      </c>
-      <c r="D2419" t="inlineStr">
-        <is>
-          <t>church.1023.s2.P029; church.1023.s2.execution; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2420">
-      <c r="B2420" t="inlineStr">
-        <is>
-          <t>church.1023.s2.p030.text</t>
-        </is>
-      </c>
-      <c r="C2420" t="inlineStr">
-        <is>
-          <t>为什么？</t>
-        </is>
-      </c>
-      <c r="D2420" t="inlineStr">
-        <is>
-          <t>church.1023.s2.P030; church.1023.s2.execution; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2421">
-      <c r="B2421" t="inlineStr">
-        <is>
-          <t>church.1023.s2.p031.text</t>
-        </is>
-      </c>
-      <c r="C2421" t="inlineStr">
-        <is>
-          <t>为什么？为什么？为什么？为什么？为什么？</t>
-        </is>
-      </c>
-      <c r="D2421" t="inlineStr">
-        <is>
-          <t>church.1023.s2.P031; church.1023.s2.execution; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2422">
-      <c r="B2422" t="inlineStr">
-        <is>
-          <t>church.1023.s2.p032.text</t>
-        </is>
-      </c>
-      <c r="C2422" t="inlineStr">
-        <is>
-          <t>带着这样的想法，我迎来了人生的终点。</t>
-        </is>
-      </c>
-      <c r="D2422" t="inlineStr">
-        <is>
-          <t>church.1023.s2.P032; church.1023.s2.execution; Text only, no event/route/result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2423">
-      <c r="A2423" s="3" t="n"/>
-      <c r="B2423" s="3" t="inlineStr">
-        <is>
-          <t>colette.name</t>
-        </is>
-      </c>
-      <c r="C2423" s="3" t="inlineStr">
-        <is>
-          <t>柯莱特·布吕内</t>
-        </is>
-      </c>
-      <c r="D2423" s="3" t="inlineStr">
-        <is>
-          <t>A01 source identity; blocked construction</t>
-        </is>
-      </c>
-    </row>
-    <row r="2424">
-      <c r="A2424" s="3" t="n"/>
-      <c r="B2424" s="3" t="inlineStr">
-        <is>
-          <t>neutral.shopkeeper.name</t>
-        </is>
-      </c>
-      <c r="C2424" s="3" t="inlineStr">
-        <is>
-          <t>店主</t>
-        </is>
-      </c>
-      <c r="D2424" s="3" t="inlineStr">
-        <is>
-          <t>A01 source identity; blocked construction</t>
-        </is>
-      </c>
-    </row>
-    <row r="2425">
-      <c r="A2425" s="3" t="n"/>
-      <c r="B2425" s="3" t="inlineStr">
-        <is>
-          <t>neutral.unknown.name</t>
-        </is>
-      </c>
-      <c r="C2425" s="3" t="inlineStr">
-        <is>
-          <t>？？？</t>
-        </is>
-      </c>
-      <c r="D2425" s="3" t="inlineStr">
-        <is>
-          <t>A01 source identity; blocked construction</t>
-        </is>
-      </c>
-    </row>
-    <row r="2426">
-      <c r="A2426" s="3" t="n"/>
-      <c r="B2426" s="3" t="inlineStr">
-        <is>
-          <t>alienor.name</t>
-        </is>
-      </c>
-      <c r="C2426" s="3" t="inlineStr">
-        <is>
-          <t>阿莉耶诺尔·康多尔</t>
-        </is>
-      </c>
-      <c r="D2426" s="3" t="inlineStr">
-        <is>
-          <t>E source identity/display alias; no narrative addition</t>
-        </is>
-      </c>
-    </row>
-    <row r="2427">
-      <c r="A2427" s="3" t="n"/>
-      <c r="B2427" s="3" t="inlineStr">
-        <is>
-          <t>church.1104.s1.alias.alienor.name</t>
-        </is>
-      </c>
-      <c r="C2427" s="3" t="inlineStr">
-        <is>
-          <t>埃莉诺</t>
-        </is>
-      </c>
-      <c r="D2427" s="3" t="inlineStr">
-        <is>
-          <t>E source identity/display alias; no narrative addition</t>
-        </is>
-      </c>
-    </row>
-    <row r="2428">
-      <c r="A2428" s="3" t="n"/>
-      <c r="B2428" s="3" t="inlineStr">
-        <is>
-          <t>church.1104.s1.alias.landlord.uncertain.name</t>
-        </is>
-      </c>
-      <c r="C2428" s="3" t="inlineStr">
-        <is>
-          <t>房东？</t>
-        </is>
-      </c>
-      <c r="D2428" s="3" t="inlineStr">
-        <is>
-          <t>E source identity/display alias; no narrative addition</t>
-        </is>
-      </c>
-    </row>
-    <row r="2429">
-      <c r="A2429" s="3" t="n"/>
-      <c r="B2429" s="3" t="inlineStr">
-        <is>
-          <t>church.1104.s1.npc.mother.name</t>
-        </is>
-      </c>
-      <c r="C2429" s="3" t="inlineStr">
-        <is>
-          <t>女人</t>
-        </is>
-      </c>
-      <c r="D2429" s="3" t="inlineStr">
-        <is>
-          <t>E source identity/display alias; no narrative addition</t>
-        </is>
-      </c>
-    </row>
-    <row r="2430">
-      <c r="A2430" s="3" t="n"/>
-      <c r="B2430" s="3" t="inlineStr">
-        <is>
-          <t>church.1104.s1.npc.vendor.name</t>
-        </is>
-      </c>
-      <c r="C2430" s="3" t="inlineStr">
-        <is>
-          <t>摊主</t>
-        </is>
-      </c>
-      <c r="D2430" s="3" t="inlineStr">
-        <is>
-          <t>E source identity/display alias; no narrative addition</t>
-        </is>
-      </c>
-    </row>
-    <row r="2431">
-      <c r="A2431" s="3" t="n"/>
-      <c r="B2431" s="3" t="inlineStr">
-        <is>
-          <t>church.1104.s1.npc.civilian_a.name</t>
-        </is>
-      </c>
-      <c r="C2431" s="3" t="inlineStr">
-        <is>
-          <t>平民A</t>
-        </is>
-      </c>
-      <c r="D2431" s="3" t="inlineStr">
-        <is>
-          <t>E source identity/display alias; no narrative addition</t>
-        </is>
-      </c>
-    </row>
-    <row r="2432">
-      <c r="A2432" s="3" t="n"/>
-      <c r="B2432" s="3" t="inlineStr">
-        <is>
-          <t>church.1104.s1.npc.civilian_b.name</t>
-        </is>
-      </c>
-      <c r="C2432" s="3" t="inlineStr">
-        <is>
-          <t>平民B</t>
-        </is>
-      </c>
-      <c r="D2432" s="3" t="inlineStr">
-        <is>
-          <t>E source identity/display alias; no narrative addition</t>
-        </is>
-      </c>
-    </row>
-    <row r="2433">
-      <c r="A2433" s="3" t="n"/>
-      <c r="B2433" s="3" t="inlineStr">
-        <is>
-          <t>church.1104.s1.npc.elder_lady.name</t>
-        </is>
-      </c>
-      <c r="C2433" s="3" t="inlineStr">
-        <is>
-          <t>老妇人</t>
-        </is>
-      </c>
-      <c r="D2433" s="3" t="inlineStr">
-        <is>
-          <t>E source identity/display alias; no narrative addition</t>
-        </is>
-      </c>
-    </row>
-    <row r="2434">
-      <c r="A2434" s="3" t="n"/>
-      <c r="B2434" s="3" t="inlineStr">
-        <is>
-          <t>church.1104.s1.npc.buyer.name</t>
-        </is>
-      </c>
-      <c r="C2434" s="3" t="inlineStr">
-        <is>
-          <t>男子</t>
-        </is>
-      </c>
-      <c r="D2434" s="3" t="inlineStr">
-        <is>
-          <t>E source identity/display alias; no narrative addition</t>
-        </is>
-      </c>
-    </row>
-    <row r="2435">
-      <c r="A2435" s="3" t="n"/>
-      <c r="B2435" s="3" t="inlineStr">
-        <is>
-          <t>church.1104.s1.npc.tenant.name</t>
-        </is>
-      </c>
-      <c r="C2435" s="3" t="inlineStr">
-        <is>
-          <t>男人</t>
-        </is>
-      </c>
-      <c r="D2435" s="3" t="inlineStr">
-        <is>
-          <t>E source identity/display alias; no narrative addition</t>
-        </is>
-      </c>
-    </row>
-    <row r="2436">
-      <c r="A2436" s="3" t="n"/>
-      <c r="B2436" s="3" t="inlineStr">
-        <is>
-          <t>church.1104.s1.npc.landlord.name</t>
-        </is>
-      </c>
-      <c r="C2436" s="3" t="inlineStr">
-        <is>
-          <t>房东</t>
-        </is>
-      </c>
-      <c r="D2436" s="3" t="inlineStr">
-        <is>
-          <t>E source identity/display alias; no narrative addition</t>
-        </is>
-      </c>
-    </row>
-    <row r="2437">
-      <c r="A2437" s="3" t="n"/>
-      <c r="B2437" s="3" t="inlineStr">
-        <is>
-          <t>neutral.reporter.name</t>
-        </is>
-      </c>
-      <c r="C2437" s="3" t="inlineStr">
-        <is>
-          <t>记者</t>
-        </is>
-      </c>
-      <c r="D2437" s="3" t="inlineStr">
-        <is>
-          <t>A05 source identity/display</t>
-        </is>
-      </c>
-    </row>
-    <row r="2438">
-      <c r="A2438" s="3" t="n"/>
-      <c r="B2438" s="3" t="inlineStr">
-        <is>
-          <t>rose.1016.s1.title</t>
-        </is>
-      </c>
-      <c r="C2438" s="3" t="inlineStr">
-        <is>
-          <t>两位访客</t>
-        </is>
-      </c>
-      <c r="D2438" s="3" t="inlineStr">
-        <is>
-          <t>B source fragment, not a formal chapter</t>
-        </is>
-      </c>
-    </row>
-    <row r="2439">
-      <c r="A2439" s="3" t="n"/>
-      <c r="B2439" s="3" t="inlineStr">
-        <is>
-          <t>rose.1016.s1.alias.alienor</t>
-        </is>
-      </c>
-      <c r="C2439" s="3" t="inlineStr">
-        <is>
-          <t>埃莉诺</t>
-        </is>
-      </c>
-      <c r="D2439" s="3" t="inlineStr">
-        <is>
-          <t>B P009/P014 alias; no royal identity disclosure</t>
-        </is>
-      </c>
-    </row>
-    <row r="2440">
-      <c r="A2440" s="3" t="n"/>
-      <c r="B2440" s="3" t="inlineStr">
-        <is>
-          <t>rose.1012.s1.alias.alienor.name</t>
-        </is>
-      </c>
-      <c r="C2440" s="3" t="inlineStr">
-        <is>
-          <t>埃莉诺</t>
-        </is>
-      </c>
-      <c r="D2440" s="3" t="inlineStr">
-        <is>
-          <t>B1012 explicit display alias; alienor identity reused</t>
-        </is>
-      </c>
-    </row>
-    <row r="2441">
-      <c r="A2441" s="3" t="n"/>
-      <c r="B2441" s="3" t="inlineStr">
-        <is>
-          <t>church.thibaut.name</t>
-        </is>
-      </c>
-      <c r="C2441" s="3" t="inlineStr">
-        <is>
-          <t>客人</t>
-        </is>
-      </c>
-      <c r="D2441" s="3" t="inlineStr">
-        <is>
-          <t>D1014 source guest alias; no hidden identity or portrait substitute</t>
-        </is>
-      </c>
-    </row>
-    <row r="2442">
-      <c r="A2442" s="3" t="n"/>
-      <c r="B2442" s="3" t="inlineStr">
-        <is>
-          <t>church.inspector.name</t>
-        </is>
-      </c>
-      <c r="C2442" s="3" t="inlineStr">
-        <is>
-          <t>监察官</t>
-        </is>
-      </c>
-      <c r="D2442" s="3" t="inlineStr">
-        <is>
-          <t>D1020 source speaker identity/alias; no narrative addition</t>
-        </is>
-      </c>
-    </row>
-    <row r="2443">
-      <c r="A2443" s="3" t="n"/>
-      <c r="B2443" s="3" t="inlineStr">
-        <is>
-          <t>church.inspectors.name</t>
-        </is>
-      </c>
-      <c r="C2443" s="3" t="inlineStr">
-        <is>
-          <t>众监察员</t>
-        </is>
-      </c>
-      <c r="D2443" s="3" t="inlineStr">
-        <is>
-          <t>D1020 source speaker identity/alias; no narrative addition</t>
-        </is>
-      </c>
-    </row>
-    <row r="2444">
-      <c r="A2444" s="3" t="n"/>
-      <c r="B2444" s="3" t="inlineStr">
-        <is>
-          <t>church.1020.s1.inspector.uncertain.name</t>
-        </is>
-      </c>
-      <c r="C2444" s="3" t="inlineStr">
-        <is>
-          <t>疑似领头的人</t>
-        </is>
-      </c>
-      <c r="D2444" s="3" t="inlineStr">
-        <is>
-          <t>D1020 source speaker identity/alias; no narrative addition</t>
-        </is>
-      </c>
-    </row>
-    <row r="2445">
-      <c r="A2445" s="3" t="n"/>
-      <c r="B2445" s="3" t="inlineStr">
-        <is>
-          <t>church.guard.name</t>
-        </is>
-      </c>
-      <c r="C2445" s="3" t="inlineStr">
-        <is>
-          <t>看守</t>
-        </is>
-      </c>
-      <c r="D2445" s="3" t="inlineStr">
-        <is>
-          <t>D generic source speaker; no portrait binding</t>
-        </is>
-      </c>
-    </row>
-    <row r="2446">
-      <c r="A2446" s="3" t="n"/>
-      <c r="B2446" s="3" t="inlineStr">
-        <is>
-          <t>bar.colette.trust_player.name</t>
-        </is>
-      </c>
-      <c r="C2446" s="3" t="inlineStr">
-        <is>
-          <t>柯莱特对玩家的好感</t>
-        </is>
-      </c>
-      <c r="D2446" s="3" t="inlineStr">
-        <is>
-          <t>User-authorized formal relation label</t>
-        </is>
-      </c>
-    </row>
-    <row r="2447">
-      <c r="A2447" s="3" t="n"/>
-      <c r="B2447" s="3" t="inlineStr">
-        <is>
-          <t>bar.adele.trust_player.name</t>
-        </is>
-      </c>
-      <c r="C2447" s="3" t="inlineStr">
-        <is>
-          <t>阿黛尔对玩家的好感</t>
-        </is>
-      </c>
-      <c r="D2447" s="3" t="inlineStr">
-        <is>
-          <t>User-authorized formal relation label</t>
-        </is>
-      </c>
-    </row>
-    <row r="2448">
-      <c r="A2448" s="3" t="n"/>
-      <c r="B2448" s="3" t="inlineStr">
-        <is>
-          <t>bar.antoine.trust_player.name</t>
-        </is>
-      </c>
-      <c r="C2448" s="3" t="inlineStr">
-        <is>
-          <t>安托万对玩家的好感</t>
-        </is>
-      </c>
-      <c r="D2448" s="3" t="inlineStr">
-        <is>
-          <t>User-authorized formal relation label</t>
-        </is>
-      </c>
-    </row>
-    <row r="2449">
-      <c r="A2449" s="3" t="n"/>
-      <c r="B2449" s="3" t="inlineStr">
-        <is>
-          <t>condition.story.rose.1009.s1.completed</t>
-        </is>
-      </c>
-      <c r="C2449" s="3" t="inlineStr">
-        <is>
-          <t>玫瑰线十月九日密见已完成（仅声明，B负责生产）</t>
-        </is>
-      </c>
-      <c r="D2449" s="3" t="inlineStr">
-        <is>
-          <t>User-authorized A01-A04 flag label; B completion is declared only</t>
-        </is>
-      </c>
-    </row>
-    <row r="2450">
-      <c r="A2450" s="3" t="n"/>
-      <c r="B2450" s="3" t="inlineStr">
-        <is>
-          <t>condition.story.neutral.1008.s1.completed</t>
-        </is>
-      </c>
-      <c r="C2450" s="3" t="inlineStr">
-        <is>
-          <t>十月八日市场初遇已完成</t>
-        </is>
-      </c>
-      <c r="D2450" s="3" t="inlineStr">
-        <is>
-          <t>User-authorized A01-A04 flag label; B completion is declared only</t>
-        </is>
-      </c>
-    </row>
-    <row r="2451">
-      <c r="A2451" s="3" t="n"/>
-      <c r="B2451" s="3" t="inlineStr">
-        <is>
-          <t>condition.story.neutral.1010.s1.completed</t>
-        </is>
-      </c>
-      <c r="C2451" s="3" t="inlineStr">
-        <is>
-          <t>十月十日促销筹备已完成</t>
-        </is>
-      </c>
-      <c r="D2451" s="3" t="inlineStr">
-        <is>
-          <t>User-authorized A01-A04 flag label; B completion is declared only</t>
-        </is>
-      </c>
-    </row>
-    <row r="2452">
-      <c r="A2452" s="3" t="n"/>
-      <c r="B2452" s="3" t="inlineStr">
-        <is>
-          <t>condition.story.neutral.1010.s1.frugal_preparation</t>
-        </is>
-      </c>
-      <c r="C2452" s="3" t="inlineStr">
-        <is>
-          <t>本次促销精打细算准备资格（未接账）</t>
-        </is>
-      </c>
-      <c r="D2452" s="3" t="inlineStr">
-        <is>
-          <t>User-authorized A01-A04 flag label; B completion is declared only</t>
-        </is>
-      </c>
-    </row>
-    <row r="2453">
-      <c r="A2453" s="3" t="n"/>
-      <c r="B2453" s="3" t="inlineStr">
-        <is>
-          <t>condition.story.neutral.1010.s2.completed</t>
-        </is>
-      </c>
-      <c r="C2453" s="3" t="inlineStr">
-        <is>
-          <t>十月十日安托万到访已完成</t>
-        </is>
-      </c>
-      <c r="D2453" s="3" t="inlineStr">
-        <is>
-          <t>User-authorized A01-A04 flag label; B completion is declared only</t>
-        </is>
-      </c>
-    </row>
-    <row r="2454">
-      <c r="A2454" s="3" t="n"/>
-      <c r="B2454" s="3" t="inlineStr">
-        <is>
-          <t>condition.story.neutral.1010.s2.antoine_approval</t>
-        </is>
-      </c>
-      <c r="C2454" s="3" t="inlineStr">
-        <is>
-          <t>安托万赏识（控制十月十三日到场）</t>
-        </is>
-      </c>
-      <c r="D2454" s="3" t="inlineStr">
-        <is>
-          <t>User-authorized A01-A04 flag label; B completion is declared only</t>
-        </is>
-      </c>
-    </row>
-    <row r="2455">
-      <c r="A2455" s="3" t="n"/>
-      <c r="B2455" s="3" t="inlineStr">
-        <is>
-          <t>condition.story.neutral.1013.s2.completed</t>
-        </is>
-      </c>
-      <c r="C2455" s="3" t="inlineStr">
-        <is>
-          <t>十月十三日促销已完成</t>
-        </is>
-      </c>
-      <c r="D2455" s="3" t="inlineStr">
-        <is>
-          <t>User-authorized A01-A04 flag label; B completion is declared only</t>
-        </is>
-      </c>
-    </row>
-    <row r="2456">
-      <c r="A2456" s="3" t="n"/>
-      <c r="B2456" s="3" t="inlineStr">
-        <is>
-          <t>condition.story.neutral.1013.s2.orderly_service</t>
-        </is>
-      </c>
-      <c r="C2456" s="3" t="inlineStr">
-        <is>
-          <t>本次促销井然有序资格（未接账）</t>
-        </is>
-      </c>
-      <c r="D2456" s="3" t="inlineStr">
-        <is>
-          <t>User-authorized A01-A04 flag label; B completion is declared only</t>
-        </is>
-      </c>
-    </row>
-    <row r="2457">
-      <c r="A2457" s="3" t="n"/>
-      <c r="B2457" s="3" t="inlineStr">
-        <is>
-          <t>condition.story.neutral.1013.s2.warm_recommendation</t>
-        </is>
-      </c>
-      <c r="C2457" s="3" t="inlineStr">
-        <is>
-          <t>本次促销热情推介资格（未接账）</t>
-        </is>
-      </c>
-      <c r="D2457" s="3" t="inlineStr">
-        <is>
-          <t>User-authorized A01-A04 flag label; B completion is declared only</t>
-        </is>
-      </c>
-    </row>
-    <row r="2458">
-      <c r="A2458" s="3" t="n"/>
-      <c r="B2458" s="3" t="inlineStr">
-        <is>
-          <t>neutral.1008.s1.action.name</t>
-        </is>
-      </c>
-      <c r="C2458" s="3" t="inlineStr">
-        <is>
-          <t>大堂区采购</t>
-        </is>
-      </c>
-      <c r="D2458" s="3" t="inlineStr">
-        <is>
-          <t>A01 P008 source-backed map action label; no purchase settlement</t>
-        </is>
-      </c>
-    </row>
-    <row r="2459">
-      <c r="A2459" s="3" t="n"/>
-      <c r="B2459" s="3" t="inlineStr">
-        <is>
-          <t>condition.story.neutral.1018.s1.completed</t>
-        </is>
-      </c>
-      <c r="C2459" s="3" t="inlineStr">
-        <is>
-          <t>记者到访已完成</t>
-        </is>
-      </c>
-      <c r="D2459" s="3" t="inlineStr">
-        <is>
-          <t>A05 reporter state label</t>
-        </is>
-      </c>
-    </row>
-    <row r="2460">
-      <c r="A2460" s="3" t="n"/>
-      <c r="B2460" s="3" t="inlineStr">
-        <is>
-          <t>condition.story.neutral.1018.s1.recommendation_requested</t>
-        </is>
-      </c>
-      <c r="C2460" s="3" t="inlineStr">
-        <is>
-          <t>咖啡馆推荐待刊</t>
-        </is>
-      </c>
-      <c r="D2460" s="3" t="inlineStr">
-        <is>
-          <t>A05 reporter state label</t>
-        </is>
-      </c>
-    </row>
-    <row r="2461">
-      <c r="A2461" s="3" t="n"/>
-      <c r="B2461" s="3" t="inlineStr">
-        <is>
-          <t>condition.story.neutral.1018.s1.advertisement_requested</t>
-        </is>
-      </c>
-      <c r="C2461" s="3" t="inlineStr">
-        <is>
-          <t>咖啡馆广告待刊</t>
-        </is>
-      </c>
-      <c r="D2461" s="3" t="inlineStr">
-        <is>
-          <t>A05 reporter state label</t>
-        </is>
-      </c>
-    </row>
-    <row r="2462">
-      <c r="A2462" s="3" t="n"/>
-      <c r="B2462" s="3" t="inlineStr">
-        <is>
-          <t>condition.story.neutral.1018.s1.printed</t>
-        </is>
-      </c>
-      <c r="C2462" s="3" t="inlineStr">
-        <is>
-          <t>咖啡馆报刊通知已刊出</t>
-        </is>
-      </c>
-      <c r="D2462" s="3" t="inlineStr">
-        <is>
-          <t>A05 reporter state label</t>
-        </is>
-      </c>
-    </row>
-    <row r="2463">
-      <c r="A2463" s="3" t="n"/>
-      <c r="B2463" s="3" t="inlineStr">
-        <is>
-          <t>neutral.1018.s1.notice.title</t>
-        </is>
-      </c>
-      <c r="C2463" s="3" t="inlineStr">
-        <is>
-          <t>《圣诺特之声》</t>
-        </is>
-      </c>
-      <c r="D2463" s="3" t="inlineStr">
-        <is>
-          <t>A05 authorized minimal next-issue Notice; no reward</t>
-        </is>
-      </c>
-    </row>
-    <row r="2464">
-      <c r="A2464" s="3" t="n"/>
-      <c r="B2464" s="3" t="inlineStr">
-        <is>
-          <t>neutral.1018.s1.notice.recommendation.body</t>
-        </is>
-      </c>
-      <c r="C2464" s="3" t="inlineStr">
-        <is>
-          <t>本期侧栏刊登了沸点咖啡馆的推荐文章。</t>
-        </is>
-      </c>
-      <c r="D2464" s="3" t="inlineStr">
-        <is>
-          <t>A05 authorized minimal next-issue Notice; no reward</t>
-        </is>
-      </c>
-    </row>
-    <row r="2465">
-      <c r="A2465" s="3" t="n"/>
-      <c r="B2465" s="3" t="inlineStr">
-        <is>
-          <t>neutral.1018.s1.notice.advertisement.body</t>
-        </is>
-      </c>
-      <c r="C2465" s="3" t="inlineStr">
-        <is>
-          <t>本期商业版刊登了沸点咖啡馆的广告。</t>
-        </is>
-      </c>
-      <c r="D2465" s="3" t="inlineStr">
-        <is>
-          <t>A05 authorized minimal next-issue Notice; no reward</t>
-        </is>
-      </c>
-    </row>
-    <row r="2466">
-      <c r="B2466" t="inlineStr">
-        <is>
-          <t>action.cafe.enter.name</t>
-        </is>
-      </c>
-      <c r="C2466" t="inlineStr">
-        <is>
-          <t>咖啡馆</t>
-        </is>
-      </c>
-      <c r="D2466" t="inlineStr">
-        <is>
-          <t>配置化免费导航行动</t>
-        </is>
-      </c>
-    </row>
-    <row r="2467">
-      <c r="B2467" t="inlineStr">
-        <is>
-          <t>action.cafe.enter.desc</t>
-        </is>
-      </c>
-      <c r="C2467" t="inlineStr">
-        <is>
-          <t>进入咖啡馆，开始今天的经营。</t>
-        </is>
-      </c>
-      <c r="D2467" t="inlineStr">
-        <is>
-          <t>配置化免费导航行动</t>
-        </is>
-      </c>
-    </row>
-    <row r="2468">
-      <c r="B2468" t="inlineStr">
-        <is>
-          <t>action.cafe.enter.button</t>
-        </is>
-      </c>
-      <c r="C2468" t="inlineStr">
-        <is>
-          <t>进入咖啡馆</t>
-        </is>
-      </c>
-      <c r="D2468" t="inlineStr">
-        <is>
-          <t>配置化免费导航按钮</t>
-        </is>
-      </c>
-    </row>
-    <row r="2469">
-      <c r="B2469" t="inlineStr">
-        <is>
-          <t>test.item.medicine.name</t>
-        </is>
-      </c>
-      <c r="C2469" t="inlineStr">
-        <is>
-          <t>验收用药品</t>
-        </is>
-      </c>
-      <c r="D2469" t="inlineStr">
-        <is>
-          <t>TEST_ONLY：交付隔离夹具物品元数据</t>
-        </is>
-      </c>
-    </row>
-    <row r="2470">
-      <c r="B2470" t="inlineStr">
-        <is>
-          <t>test.item.medicine.desc</t>
-        </is>
-      </c>
-      <c r="C2470" t="inlineStr">
-        <is>
-          <t>仅用于隔离交付验收，不代表正式商品。</t>
-        </is>
-      </c>
-      <c r="D2470" t="inlineStr">
-        <is>
-          <t>TEST_ONLY：交付隔离夹具物品元数据</t>
-        </is>
-      </c>
-    </row>
-    <row r="2471">
-      <c r="B2471" t="inlineStr">
-        <is>
-          <t>test.item.food.name</t>
-        </is>
-      </c>
-      <c r="C2471" t="inlineStr">
-        <is>
-          <t>验收用食品</t>
-        </is>
-      </c>
-      <c r="D2471" t="inlineStr">
-        <is>
-          <t>TEST_ONLY：交付隔离夹具物品元数据</t>
-        </is>
-      </c>
-    </row>
-    <row r="2472">
-      <c r="B2472" t="inlineStr">
-        <is>
-          <t>test.item.food.desc</t>
-        </is>
-      </c>
-      <c r="C2472" t="inlineStr">
-        <is>
-          <t>仅用于隔离交付验收，不代表正式商品。</t>
-        </is>
-      </c>
-      <c r="D2472" t="inlineStr">
-        <is>
-          <t>TEST_ONLY：交付隔离夹具物品元数据</t>
-        </is>
-      </c>
-    </row>
-    <row r="2473">
-      <c r="B2473" t="inlineStr">
-        <is>
-          <t>test.item.delivery_receipt.name</t>
-        </is>
-      </c>
-      <c r="C2473" t="inlineStr">
-        <is>
-          <t>交付验收回执</t>
-        </is>
-      </c>
-      <c r="D2473" t="inlineStr">
-        <is>
-          <t>TEST_ONLY：交付隔离夹具物品元数据</t>
-        </is>
-      </c>
-    </row>
-    <row r="2474">
-      <c r="B2474" t="inlineStr">
-        <is>
-          <t>test.item.delivery_receipt.desc</t>
-        </is>
-      </c>
-      <c r="C2474" t="inlineStr">
-        <is>
-          <t>仅用于隔离交付验收，不代表正式商品。</t>
-        </is>
-      </c>
-      <c r="D2474" t="inlineStr">
-        <is>
-          <t>TEST_ONLY：交付隔离夹具物品元数据</t>
         </is>
       </c>
     </row>

--- a/Assets/ConfigTables/Data/Shared/Text.xlsx
+++ b/Assets/ConfigTables/Data/Shared/Text.xlsx
@@ -11530,7 +11530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2100"/>
+  <dimension ref="A1:D2111"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -40664,7 +40664,7 @@
       </c>
       <c r="D1722" t="inlineStr">
         <is>
-          <t>A-1008-P004; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -40681,7 +40681,7 @@
       </c>
       <c r="D1723" t="inlineStr">
         <is>
-          <t>A-1008-P005; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -40698,7 +40698,7 @@
       </c>
       <c r="D1724" t="inlineStr">
         <is>
-          <t>A-1008-P006; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -40715,7 +40715,7 @@
       </c>
       <c r="D1725" t="inlineStr">
         <is>
-          <t>A-1008-P008; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -40732,7 +40732,7 @@
       </c>
       <c r="D1726" t="inlineStr">
         <is>
-          <t>A-1008-P009; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -40749,7 +40749,7 @@
       </c>
       <c r="D1727" t="inlineStr">
         <is>
-          <t>A-1008-P010; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -40766,7 +40766,7 @@
       </c>
       <c r="D1728" t="inlineStr">
         <is>
-          <t>A-1008-P011; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -40783,7 +40783,7 @@
       </c>
       <c r="D1729" t="inlineStr">
         <is>
-          <t>A-1008-P014; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -40800,7 +40800,7 @@
       </c>
       <c r="D1730" t="inlineStr">
         <is>
-          <t>A-1008-P015; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -40817,7 +40817,7 @@
       </c>
       <c r="D1731" t="inlineStr">
         <is>
-          <t>A-1008-P016; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -40834,7 +40834,7 @@
       </c>
       <c r="D1732" t="inlineStr">
         <is>
-          <t>A-1008-P017; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -40851,7 +40851,7 @@
       </c>
       <c r="D1733" t="inlineStr">
         <is>
-          <t>A-1008-P018; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -40868,7 +40868,7 @@
       </c>
       <c r="D1734" t="inlineStr">
         <is>
-          <t>A-1008-P020; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -40885,7 +40885,7 @@
       </c>
       <c r="D1735" t="inlineStr">
         <is>
-          <t>A-1008-P021; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -40902,7 +40902,7 @@
       </c>
       <c r="D1736" t="inlineStr">
         <is>
-          <t>A-1008-P023; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -40919,7 +40919,7 @@
       </c>
       <c r="D1737" t="inlineStr">
         <is>
-          <t>A-1008-P024; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -40936,7 +40936,7 @@
       </c>
       <c r="D1738" t="inlineStr">
         <is>
-          <t>A-1008-P025; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -40953,7 +40953,7 @@
       </c>
       <c r="D1739" t="inlineStr">
         <is>
-          <t>A-1008-P026; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -40970,7 +40970,7 @@
       </c>
       <c r="D1740" t="inlineStr">
         <is>
-          <t>A-1008-P027; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -40987,7 +40987,7 @@
       </c>
       <c r="D1741" t="inlineStr">
         <is>
-          <t>A-1008-P028; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41004,7 +41004,7 @@
       </c>
       <c r="D1742" t="inlineStr">
         <is>
-          <t>A-1008-P029; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41021,7 +41021,7 @@
       </c>
       <c r="D1743" t="inlineStr">
         <is>
-          <t>A-1008-P030; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41038,7 +41038,7 @@
       </c>
       <c r="D1744" t="inlineStr">
         <is>
-          <t>A-1008-P031; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41055,7 +41055,7 @@
       </c>
       <c r="D1745" t="inlineStr">
         <is>
-          <t>A-1008-P032; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41072,7 +41072,7 @@
       </c>
       <c r="D1746" t="inlineStr">
         <is>
-          <t>A-1008-P034; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41089,7 +41089,7 @@
       </c>
       <c r="D1747" t="inlineStr">
         <is>
-          <t>A-1008-P036; 选项; text staging only, event disabled</t>
+          <t>A01 formal content; choice; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41106,7 +41106,7 @@
       </c>
       <c r="D1748" t="inlineStr">
         <is>
-          <t>A-1008-P037; 选项; text staging only, event disabled</t>
+          <t>A01 formal content; choice; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41123,7 +41123,7 @@
       </c>
       <c r="D1749" t="inlineStr">
         <is>
-          <t>A-1008-P038; 选项; text staging only, event disabled</t>
+          <t>A01 formal content; choice; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41140,7 +41140,7 @@
       </c>
       <c r="D1750" t="inlineStr">
         <is>
-          <t>A-1008-P040; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41157,7 +41157,7 @@
       </c>
       <c r="D1751" t="inlineStr">
         <is>
-          <t>A-1008-P041; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41174,7 +41174,7 @@
       </c>
       <c r="D1752" t="inlineStr">
         <is>
-          <t>A-1008-P042; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41191,7 +41191,7 @@
       </c>
       <c r="D1753" t="inlineStr">
         <is>
-          <t>A-1008-P044; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41208,7 +41208,7 @@
       </c>
       <c r="D1754" t="inlineStr">
         <is>
-          <t>A-1008-P048; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41225,7 +41225,7 @@
       </c>
       <c r="D1755" t="inlineStr">
         <is>
-          <t>A-1008-P049; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41242,7 +41242,7 @@
       </c>
       <c r="D1756" t="inlineStr">
         <is>
-          <t>A-1008-P053; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41259,7 +41259,7 @@
       </c>
       <c r="D1757" t="inlineStr">
         <is>
-          <t>A-1008-P054; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41276,7 +41276,7 @@
       </c>
       <c r="D1758" t="inlineStr">
         <is>
-          <t>A-1008-P056; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41293,7 +41293,7 @@
       </c>
       <c r="D1759" t="inlineStr">
         <is>
-          <t>A-1008-P057; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41310,7 +41310,7 @@
       </c>
       <c r="D1760" t="inlineStr">
         <is>
-          <t>A-1008-P058; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41327,7 +41327,7 @@
       </c>
       <c r="D1761" t="inlineStr">
         <is>
-          <t>A-1008-P059; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41344,7 +41344,7 @@
       </c>
       <c r="D1762" t="inlineStr">
         <is>
-          <t>A-1008-P060; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41361,7 +41361,7 @@
       </c>
       <c r="D1763" t="inlineStr">
         <is>
-          <t>A-1008-P061; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41378,7 +41378,7 @@
       </c>
       <c r="D1764" t="inlineStr">
         <is>
-          <t>A-1008-P062; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41395,7 +41395,7 @@
       </c>
       <c r="D1765" t="inlineStr">
         <is>
-          <t>A-1008-P063; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41412,7 +41412,7 @@
       </c>
       <c r="D1766" t="inlineStr">
         <is>
-          <t>A-1008-P064; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41429,7 +41429,7 @@
       </c>
       <c r="D1767" t="inlineStr">
         <is>
-          <t>A-1008-P065; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41446,7 +41446,7 @@
       </c>
       <c r="D1768" t="inlineStr">
         <is>
-          <t>A-1008-P066; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41463,7 +41463,7 @@
       </c>
       <c r="D1769" t="inlineStr">
         <is>
-          <t>A-1008-P067; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41480,7 +41480,7 @@
       </c>
       <c r="D1770" t="inlineStr">
         <is>
-          <t>A-1008-P068; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41497,7 +41497,7 @@
       </c>
       <c r="D1771" t="inlineStr">
         <is>
-          <t>A-1008-P069; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41514,7 +41514,7 @@
       </c>
       <c r="D1772" t="inlineStr">
         <is>
-          <t>A-1008-P070; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41531,7 +41531,7 @@
       </c>
       <c r="D1773" t="inlineStr">
         <is>
-          <t>A-1008-P071; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41548,7 +41548,7 @@
       </c>
       <c r="D1774" t="inlineStr">
         <is>
-          <t>A-1008-P072; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41565,7 +41565,7 @@
       </c>
       <c r="D1775" t="inlineStr">
         <is>
-          <t>A-1008-P073; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41582,7 +41582,7 @@
       </c>
       <c r="D1776" t="inlineStr">
         <is>
-          <t>A-1008-P074; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41599,7 +41599,7 @@
       </c>
       <c r="D1777" t="inlineStr">
         <is>
-          <t>A-1008-P075; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41616,7 +41616,7 @@
       </c>
       <c r="D1778" t="inlineStr">
         <is>
-          <t>A-1008-P076; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41633,7 +41633,7 @@
       </c>
       <c r="D1779" t="inlineStr">
         <is>
-          <t>A-1008-P077; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41650,7 +41650,7 @@
       </c>
       <c r="D1780" t="inlineStr">
         <is>
-          <t>A-1008-P078; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41667,7 +41667,7 @@
       </c>
       <c r="D1781" t="inlineStr">
         <is>
-          <t>A-1008-P080; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41684,7 +41684,7 @@
       </c>
       <c r="D1782" t="inlineStr">
         <is>
-          <t>A-1008-P083; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41701,7 +41701,7 @@
       </c>
       <c r="D1783" t="inlineStr">
         <is>
-          <t>A-1008-P084; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -41718,7 +41718,7 @@
       </c>
       <c r="D1784" t="inlineStr">
         <is>
-          <t>A-1008-P085; 正文; text staging only, event disabled</t>
+          <t>A01 formal content; dialogue; source-map A01</t>
         </is>
       </c>
     </row>
@@ -47091,6 +47091,193 @@
       <c r="D2100" t="inlineStr">
         <is>
           <t>A-1018.s1-P097; 正文; text staging only, event disabled</t>
+        </is>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="B2101" t="inlineStr">
+        <is>
+          <t>neutral.1008.s1.title</t>
+        </is>
+      </c>
+      <c r="C2101" t="inlineStr">
+        <is>
+          <t>10月8日：大堂区采购与柯莱特初遇</t>
+        </is>
+      </c>
+      <c r="D2101" t="inlineStr">
+        <is>
+          <t>A01 event title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="B2102" t="inlineStr">
+        <is>
+          <t>action.neutral.1008.s1.name</t>
+        </is>
+      </c>
+      <c r="C2102" t="inlineStr">
+        <is>
+          <t>大堂区采购</t>
+        </is>
+      </c>
+      <c r="D2102" t="inlineStr">
+        <is>
+          <t>A01 MapAction name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="B2103" t="inlineStr">
+        <is>
+          <t>action.neutral.1008.s1.desc</t>
+        </is>
+      </c>
+      <c r="C2103" t="inlineStr">
+        <is>
+          <t>前往大堂区采购咖啡馆所需的日常用品。</t>
+        </is>
+      </c>
+      <c r="D2103" t="inlineStr">
+        <is>
+          <t>A01 MapAction description; no AP or purchase result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="B2104" t="inlineStr">
+        <is>
+          <t>condition.story.neutral.1008.s1.completed</t>
+        </is>
+      </c>
+      <c r="C2104" t="inlineStr">
+        <is>
+          <t>10月8日中立剧情已完成</t>
+        </is>
+      </c>
+      <c r="D2104" t="inlineStr">
+        <is>
+          <t>A01 completion fact display name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="B2105" t="inlineStr">
+        <is>
+          <t>character.market.shopkeeper.name</t>
+        </is>
+      </c>
+      <c r="C2105" t="inlineStr">
+        <is>
+          <t>店主</t>
+        </is>
+      </c>
+      <c r="D2105" t="inlineStr">
+        <is>
+          <t>A01 shopkeeper display name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="B2106" t="inlineStr">
+        <is>
+          <t>character.market.shopkeeper.desc</t>
+        </is>
+      </c>
+      <c r="C2106" t="inlineStr">
+        <is>
+          <t>大堂区杂货铺店主。</t>
+        </is>
+      </c>
+      <c r="D2106" t="inlineStr">
+        <is>
+          <t>A01 shopkeeper object description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="B2107" t="inlineStr">
+        <is>
+          <t>character.neutral.1008.unknown.name</t>
+        </is>
+      </c>
+      <c r="C2107" t="inlineStr">
+        <is>
+          <t>？？？</t>
+        </is>
+      </c>
+      <c r="D2107" t="inlineStr">
+        <is>
+          <t>A01 anonymous speaker before Colette reveal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="B2108" t="inlineStr">
+        <is>
+          <t>character.neutral.1008.unknown.desc</t>
+        </is>
+      </c>
+      <c r="C2108" t="inlineStr">
+        <is>
+          <t>尚未确认身份的说话人。</t>
+        </is>
+      </c>
+      <c r="D2108" t="inlineStr">
+        <is>
+          <t>A01 anonymous speaker object description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="B2109" t="inlineStr">
+        <is>
+          <t>action.rose.1009.s1.name</t>
+        </is>
+      </c>
+      <c r="C2109" t="inlineStr">
+        <is>
+          <t>赴布塔克俱乐部之约</t>
+        </is>
+      </c>
+      <c r="D2109" t="inlineStr">
+        <is>
+          <t>B-1009 地图行动名称；圣徒街入口</t>
+        </is>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="B2110" t="inlineStr">
+        <is>
+          <t>action.rose.1009.s1.desc</t>
+        </is>
+      </c>
+      <c r="C2110" t="inlineStr">
+        <is>
+          <t>按照密信前往布塔克俱乐部赴约。有人在那里等你，也许咖啡馆遭遇的麻烦终于能找到答案。</t>
+        </is>
+      </c>
+      <c r="D2110" t="inlineStr">
+        <is>
+          <t>B-1009 地图行动描述；成品文案</t>
+        </is>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="B2111" t="inlineStr">
+        <is>
+          <t>condition.story.rose.1009.s1.completed</t>
+        </is>
+      </c>
+      <c r="C2111" t="inlineStr">
+        <is>
+          <t>布塔克俱乐部赴约已完成</t>
+        </is>
+      </c>
+      <c r="D2111" t="inlineStr">
+        <is>
+          <t>B-1009 一次性剧情完成标记</t>
         </is>
       </c>
     </row>

--- a/Assets/ConfigTables/Data/Shared/Text.xlsx
+++ b/Assets/ConfigTables/Data/Shared/Text.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="30720" windowHeight="13380" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Text" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Text" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -14907,12 +14907,12 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>顾客B</t>
+          <t>顾客</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>文案-新手教程.docx；原文保留</t>
+          <t>玩家教程修订；原稿保留在 cafe.tutorial.source.*；按键细节由工作台指引负责</t>
         </is>
       </c>
     </row>
@@ -15060,12 +15060,12 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>customer_arrives</t>
+          <t>第一位客人</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>文案-新手教程.docx；原文保留</t>
+          <t>玩家教程修订；原稿保留在 cafe.tutorial.source.*；按键细节由工作台指引负责</t>
         </is>
       </c>
     </row>
@@ -15077,12 +15077,12 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>进来的是一个衣着普通的老太太，记不住脸</t>
+          <t>进来的是一位衣着普通的男人，看起来是附近的居民。</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>原稿段落 15</t>
+          <t>玩家教程修订；原稿保留在 cafe.tutorial.source.*；按键细节由工作台指引负责</t>
         </is>
       </c>
     </row>
@@ -15162,12 +15162,12 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>她看了我一眼，我回以微笑。</t>
+          <t>他看了我一眼，我回以微笑。</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>原稿段落 20</t>
+          <t>玩家教程修订；原稿保留在 cafe.tutorial.source.*；按键细节由工作台指引负责</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>perception_success</t>
+          <t>熟悉的老客人</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>文案-新手教程.docx；原文保留</t>
+          <t>玩家教程修订；原稿保留在 cafe.tutorial.source.*；按键细节由工作台指引负责</t>
         </is>
       </c>
     </row>
@@ -15281,12 +15281,12 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>阿黛尔，你和这位太太说说这两天你做了什么</t>
+          <t>阿黛尔，你和这位先生说说这两天你做了什么。</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>原稿段落 26</t>
+          <t>玩家教程修订；原稿保留在 cafe.tutorial.source.*；按键细节由工作台指引负责</t>
         </is>
       </c>
     </row>
@@ -15349,12 +15349,12 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>perception_failure</t>
+          <t>难以捉摸的客人</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>文案-新手教程.docx；原文保留</t>
+          <t>玩家教程修订；原稿保留在 cafe.tutorial.source.*；按键细节由工作台指引负责</t>
         </is>
       </c>
     </row>
@@ -15366,12 +15366,12 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>不知怎么，总感觉她身上的气息突然变了</t>
+          <t>不知怎么，总感觉他身上的气息突然变了。</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>原稿段落 31</t>
+          <t>玩家教程修订；原稿保留在 cafe.tutorial.source.*；按键细节由工作台指引负责</t>
         </is>
       </c>
     </row>
@@ -15383,12 +15383,12 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>我没心思琢磨古怪的老太太爱琢磨些什么</t>
+          <t>我没心思琢磨这位客人在想些什么。</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>原稿段落 32</t>
+          <t>玩家教程修订；原稿保留在 cafe.tutorial.source.*；按键细节由工作台指引负责</t>
         </is>
       </c>
     </row>
@@ -15400,12 +15400,12 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>还好她把视线收了回去</t>
+          <t>还好他把视线收了回去。</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>原稿段落 33</t>
+          <t>玩家教程修订；原稿保留在 cafe.tutorial.source.*；按键细节由工作台指引负责</t>
         </is>
       </c>
     </row>
@@ -15417,12 +15417,12 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>order_confirmed</t>
+          <t>确认订单</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>文案-新手教程.docx；原文保留</t>
+          <t>玩家教程修订；原稿保留在 cafe.tutorial.source.*；按键细节由工作台指引负责</t>
         </is>
       </c>
     </row>
@@ -15434,12 +15434,12 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>可能是看出老太太想点餐，阿黛尔塞去一张自己无聊手绘的餐单</t>
+          <t>看出这位先生想点餐，阿黛尔递给他一张亲手绘制的餐单。</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>原稿段落 35</t>
+          <t>玩家教程修订；原稿保留在 cafe.tutorial.source.*；按键细节由工作台指引负责</t>
         </is>
       </c>
     </row>
@@ -15451,12 +15451,12 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>小杯装黑咖啡 ，无糖，就这样</t>
+          <t>大杯黑咖啡，不加糖，就这样。</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>原稿段落 36</t>
+          <t>玩家教程修订；原稿保留在 cafe.tutorial.source.*；按键细节由工作台指引负责</t>
         </is>
       </c>
     </row>
@@ -15468,12 +15468,12 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>B太太——新沸点咖啡的第一位客人</t>
+          <t>这位先生是重新开张的沸点咖啡馆的第一位客人。</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>原稿段落 37</t>
+          <t>玩家教程修订；原稿保留在 cafe.tutorial.source.*；按键细节由工作台指引负责</t>
         </is>
       </c>
     </row>
@@ -15502,12 +15502,12 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>workstation_open</t>
+          <t>前往工作台</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>文案-新手教程.docx；原文保留</t>
+          <t>玩家教程修订；原稿保留在 cafe.tutorial.source.*；按键细节由工作台指引负责</t>
         </is>
       </c>
     </row>
@@ -15519,12 +15519,12 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>[演出说明：背景：大堂-吧台；UI正式开放，点击吧台的桌面可立刻转换至操作台视角，]</t>
+          <t>接下来去工作台制作客人的咖啡。点击大堂中的箭头标志，进入工作台。</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>原稿段落 40</t>
+          <t>玩家教程修订；原稿保留在 cafe.tutorial.source.*；按键细节由工作台指引负责</t>
         </is>
       </c>
     </row>
@@ -15536,12 +15536,12 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>make_coffee_base</t>
+          <t>制作黑咖啡</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>文案-新手教程.docx；原文保留</t>
+          <t>玩家教程修订；原稿保留在 cafe.tutorial.source.*；按键细节由工作台指引负责</t>
         </is>
       </c>
     </row>
@@ -15553,12 +15553,12 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>哎呀呀，还没正式营业，就有了一笔生意进账。但是店长，你都不说话。看着有点紧张？哦，因为是第一次！我会全程提醒你的！首先，要确认客户订单上的需求！</t>
+          <t>别紧张，店长，我会陪着你的。客人要的是大杯无糖黑咖啡，我们就从磨豆开始吧。</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>原稿段落 45</t>
+          <t>玩家教程修订；原稿保留在 cafe.tutorial.source.*；按键细节由工作台指引负责</t>
         </is>
       </c>
     </row>
@@ -15570,12 +15570,12 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>顾客姓名：B顾客要求：无糖黑咖，其他随便配料表:咖啡原液（咖啡粉+开水）根据浓度/甜度要求，加入适量清水/方糖顾客姓名：B顾客要求：无糖黑咖，其他随便配料表:咖啡原液（咖啡粉+开水）根据浓度/甜度要求，加入适量清水/方糖</t>
+          <t>制作目标：研磨咖啡豆，用热水煮成黑咖啡，再装入杯中。不需要加糖。</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>原稿段落 46</t>
+          <t>玩家教程修订；原稿保留在 cafe.tutorial.source.*；按键细节由工作台指引负责</t>
         </is>
       </c>
     </row>
@@ -15587,12 +15587,12 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>按照要求，首先我们要配置咖啡原液；然后将其注杯——</t>
+          <t>工作台会一步步提示你。先学会取放原料，再试着启动设备。</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>原稿段落 51</t>
+          <t>玩家教程修订；原稿保留在 cafe.tutorial.source.*；按键细节由工作台指引负责</t>
         </is>
       </c>
     </row>
@@ -15604,12 +15604,12 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>pour_into_cup</t>
+          <t>装杯</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>文案-新手教程.docx；原文保留</t>
+          <t>玩家教程修订；原稿保留在 cafe.tutorial.source.*；按键细节由工作台指引负责</t>
         </is>
       </c>
     </row>
@@ -15621,12 +15621,12 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>按照要求，首先我们要配置咖啡原液；然后将其注杯——</t>
+          <t>咖啡做好了。准备一个空杯，把壶里的咖啡倒进去，就可以出餐啦。</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>原稿段落 51</t>
+          <t>玩家教程修订；原稿保留在 cafe.tutorial.source.*；按键细节由工作台指引负责</t>
         </is>
       </c>
     </row>
@@ -15638,12 +15638,12 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>adjust_strength</t>
+          <t>认识浓度</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>文案-新手教程.docx；原文保留</t>
+          <t>玩家教程修订；原稿保留在 cafe.tutorial.source.*；按键细节由工作台指引负责</t>
         </is>
       </c>
     </row>
@@ -15655,12 +15655,12 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>其后，查看浓度与甜度要求，判断是否添入清水与方糖；今天顾客似乎只要求了无糖；</t>
+          <t>加清水会让咖啡变淡。这次先按当前配方完成黑咖啡，不必额外调浓度。</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>原稿段落 52</t>
+          <t>玩家教程修订；原稿保留在 cafe.tutorial.source.*；按键细节由工作台指引负责</t>
         </is>
       </c>
     </row>
@@ -15672,12 +15672,12 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>adjust_sweetness</t>
+          <t>确认甜度</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>文案-新手教程.docx；原文保留</t>
+          <t>玩家教程修订；原稿保留在 cafe.tutorial.source.*；按键细节由工作台指引负责</t>
         </is>
       </c>
     </row>
@@ -15689,12 +15689,12 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>其后，查看浓度与甜度要求，判断是否添入清水与方糖；今天顾客似乎只要求了无糖；</t>
+          <t>客人要无糖黑咖啡，这次不需要加糖。</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>原稿段落 52</t>
+          <t>玩家教程修订；原稿保留在 cafe.tutorial.source.*；按键细节由工作台指引负责</t>
         </is>
       </c>
     </row>
@@ -15995,12 +15995,12 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>serve_customer</t>
+          <t>交付咖啡</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>文案-新手教程.docx；原文保留</t>
+          <t>玩家教程修订；原稿保留在 cafe.tutorial.source.*；按键细节由工作台指引负责</t>
         </is>
       </c>
     </row>
@@ -16284,12 +16284,12 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>ending</t>
+          <t>新的开始</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>文案-新手教程.docx；原文保留</t>
+          <t>玩家教程修订；原稿保留在 cafe.tutorial.source.*；按键细节由工作台指引负责</t>
         </is>
       </c>
     </row>

--- a/Assets/ConfigTables/Data/Shared/Text.xlsx
+++ b/Assets/ConfigTables/Data/Shared/Text.xlsx
@@ -15519,7 +15519,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>接下来去工作台制作客人的咖啡。点击大堂中的箭头标志，进入工作台。</t>
+          <t>接下来去工作台制作客人的咖啡。点击大厅右侧吧台处的箭头或吧台，进入工作台。</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
